--- a/Consolidado Incidentes y Medidas Correctivas (Formato Interno).xlsx
+++ b/Consolidado Incidentes y Medidas Correctivas (Formato Interno).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30611"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30613"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Entrega de turno 09.04.2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F54D139D-0FC3-47F5-B8C7-F67934ED07DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9F8D4187-88E1-4B9B-8F2C-07618ACD9B07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Hoja2!$C$5:$C$57</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$2:$COT$290</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$2:$COT$292</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Hoja1!$A$1:$N$284</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -138,7 +138,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1468" uniqueCount="649">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1491" uniqueCount="660">
   <si>
     <t xml:space="preserve">INCIDENTES CONTRATO </t>
   </si>
@@ -1863,6 +1863,9 @@
 </t>
   </si>
   <si>
+    <t xml:space="preserve">CERRADO </t>
+  </si>
+  <si>
     <t>Conductor debe realizar curso:                                                                                     Inducción al reglamento de tránsito en mina.                                                                         Manejo a la defensiva de Mutual.</t>
   </si>
   <si>
@@ -1888,9 +1891,6 @@
   </si>
   <si>
     <t>Taller a capataces realizado por área de  HGP, donde se aborde el paso a paso previo al uso de plataforma de andamios.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CERRADO </t>
   </si>
   <si>
     <t>Medida de carácter administrativo</t>
@@ -2319,10 +2319,35 @@
     <t>Minibús empresa SKIC en maniobra de retroceso, impacta a baja energía minibús de la misma empresa que se encontraba estacionado, ambos se encontraban sin pasajeros en su interior, resultando sin lesionados.​</t>
   </si>
   <si>
+    <t>Establecer horarios de Colación para Conductores buses 
+r. Generar Nota Interna y difundir a Conductores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Departamento de Servicio (Jose Gonzalez)
+</t>
+  </si>
+  <si>
     <t>ESGUINCE GRADO 1</t>
   </si>
   <si>
     <t xml:space="preserve">Trabajador refiere que al pisar un desnivel, siente  una molestia menor en el pie derecho. Al no considerarlo importante en ese momento, omitió reportar el hecho a su línea de supervisión de manera oportuna. Sin embargo, debido a la persistencia del malestar durante la jornada de hoy, procede a informar la situación. </t>
+  </si>
+  <si>
+    <t>Taller Reforzamiento ART sobre La importancia de la planificación y Elaboración ART
+*Personal Montaje Electrico ambos turnos /Contratados sal 30/09/2026</t>
+  </si>
+  <si>
+    <t>Gerente Construcción /Superintendente
+ Electrico</t>
+  </si>
+  <si>
+    <t>pendiente ingreso Turno B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reforzamiento Identificacion de riesgos en actividades rutinarias en desplazamiento. A través de Charla del Administrador deContrato </t>
+  </si>
+  <si>
+    <t>Pendiente Ingreso Turno B</t>
   </si>
   <si>
     <t>GOLPE EN CANASTILLO DE EQUIPO MANIPULADOR</t>
@@ -2333,7 +2358,17 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">PENDIENTE REVISIÓN DE ICAM POR JAIME GALLEGOS </t>
+    <t xml:space="preserve">Realizar reforzamiento Operadores antes de Iniciar maniobras en espacios restringidos . Deben Realizar una identificación  y evaluación previas del area.
+*Operadores ambos turnos
+</t>
+  </si>
+  <si>
+    <t>Mauricio Gonzalez /HernanCortes
+Jefe Base Deysu</t>
+  </si>
+  <si>
+    <t>Quiebre Rutina "Percepcion del Riesgo" 
+*Operadores de Turno 10x10 B</t>
   </si>
   <si>
     <t>REEMPLAZO DE NEUMÁTICO EN LUGAR NO HABILITADO.</t>
@@ -2342,7 +2377,16 @@
     <t>Se detectan trabajadores realizando cambio de neumático de retroexcavadora de forma insegura.</t>
   </si>
   <si>
-    <t>PENDIENTE ICAM</t>
+    <t>Check List de habilitación de area(360°)
+*Re instrucción a todos el personal mecanico mantención sobre el correcto uso Check List 360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observación de Conducta , trabajo Mantención Mecanica.
+*Registro en ZIGTH, mes ctubre </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Re-instrucción a todo el personal mecanico sobre ARTenfocadoen entorno , no solo en la tarea.
+*Registro de Asistencia </t>
   </si>
   <si>
     <t>INCIDENTES RELACIONADOS A CINTAS DE CONFINAMIENTO</t>
@@ -2982,7 +3026,7 @@
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="366">
+  <cellXfs count="370">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3521,9 +3565,6 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3542,17 +3583,68 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3569,13 +3661,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3594,24 +3680,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3735,12 +3803,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3869,14 +3931,8 @@
     <xf numFmtId="14" fontId="31" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -4474,7 +4530,7 @@
 <file path=xl/namedSheetViews/namedSheetView1.xml><?xml version="1.0" encoding="utf-8"?>
 <namedSheetViews xmlns="http://schemas.microsoft.com/office/spreadsheetml/2019/namedsheetviews" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <namedSheetView name="Vista 1" id="{CE0CDC46-C5E0-48C3-BF10-36800D88BDCE}">
-    <nsvFilter filterId="{00000000-0001-0000-0000-000000000000}" ref="A2:COT291" tableId="0"/>
+    <nsvFilter filterId="{00000000-0001-0000-0000-000000000000}" ref="A2:COT296" tableId="0"/>
   </namedSheetView>
 </namedSheetViews>
 </file>
@@ -4742,7 +4798,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:COT292"/>
+  <dimension ref="A1:COT298"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="2" max="3" width="18" customWidth="1"/>
@@ -4759,19 +4815,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="29.25" customHeight="1">
-      <c r="A1" s="283" t="s">
+      <c r="A1" s="289" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="284"/>
-      <c r="C1" s="284"/>
-      <c r="D1" s="284"/>
-      <c r="E1" s="284"/>
-      <c r="F1" s="284"/>
-      <c r="G1" s="284"/>
-      <c r="H1" s="284"/>
-      <c r="I1" s="284"/>
-      <c r="J1" s="284"/>
-      <c r="K1" s="285"/>
+      <c r="B1" s="290"/>
+      <c r="C1" s="290"/>
+      <c r="D1" s="290"/>
+      <c r="E1" s="290"/>
+      <c r="F1" s="290"/>
+      <c r="G1" s="290"/>
+      <c r="H1" s="290"/>
+      <c r="I1" s="290"/>
+      <c r="J1" s="290"/>
+      <c r="K1" s="291"/>
     </row>
     <row r="2" spans="1:13" ht="25.5" customHeight="1">
       <c r="A2" s="51" t="s">
@@ -4815,22 +4871,22 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="30" customHeight="1">
-      <c r="A3" s="288">
+      <c r="A3" s="294">
         <v>1</v>
       </c>
-      <c r="B3" s="208">
+      <c r="B3" s="222">
         <v>45709</v>
       </c>
-      <c r="C3" s="208" t="s">
+      <c r="C3" s="222" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="226" t="s">
+      <c r="D3" s="234" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="226" t="s">
+      <c r="E3" s="234" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="227" t="s">
+      <c r="F3" s="235" t="s">
         <v>17</v>
       </c>
       <c r="G3" s="13" t="s">
@@ -4845,20 +4901,20 @@
       <c r="J3" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="K3" s="207" t="s">
+      <c r="K3" s="221" t="s">
         <v>21</v>
       </c>
-      <c r="L3" s="213" t="s">
+      <c r="L3" s="202" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="39.950000000000003" customHeight="1">
-      <c r="A4" s="288"/>
-      <c r="B4" s="207"/>
-      <c r="C4" s="208"/>
-      <c r="D4" s="226"/>
-      <c r="E4" s="226"/>
-      <c r="F4" s="227"/>
+      <c r="A4" s="294"/>
+      <c r="B4" s="221"/>
+      <c r="C4" s="222"/>
+      <c r="D4" s="234"/>
+      <c r="E4" s="234"/>
+      <c r="F4" s="235"/>
       <c r="G4" s="13" t="s">
         <v>23</v>
       </c>
@@ -4871,16 +4927,16 @@
       <c r="J4" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="K4" s="207"/>
-      <c r="L4" s="207"/>
+      <c r="K4" s="221"/>
+      <c r="L4" s="221"/>
     </row>
     <row r="5" spans="1:13" ht="39.950000000000003" customHeight="1">
-      <c r="A5" s="288"/>
-      <c r="B5" s="207"/>
-      <c r="C5" s="208"/>
-      <c r="D5" s="226"/>
-      <c r="E5" s="226"/>
-      <c r="F5" s="227"/>
+      <c r="A5" s="294"/>
+      <c r="B5" s="221"/>
+      <c r="C5" s="222"/>
+      <c r="D5" s="234"/>
+      <c r="E5" s="234"/>
+      <c r="F5" s="235"/>
       <c r="G5" s="13" t="s">
         <v>24</v>
       </c>
@@ -4893,16 +4949,16 @@
       <c r="J5" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="K5" s="207"/>
-      <c r="L5" s="207"/>
+      <c r="K5" s="221"/>
+      <c r="L5" s="221"/>
     </row>
     <row r="6" spans="1:13" ht="38.25" customHeight="1">
-      <c r="A6" s="288"/>
-      <c r="B6" s="207"/>
-      <c r="C6" s="208"/>
-      <c r="D6" s="226"/>
-      <c r="E6" s="226"/>
-      <c r="F6" s="227"/>
+      <c r="A6" s="294"/>
+      <c r="B6" s="221"/>
+      <c r="C6" s="222"/>
+      <c r="D6" s="234"/>
+      <c r="E6" s="234"/>
+      <c r="F6" s="235"/>
       <c r="G6" s="14" t="s">
         <v>25</v>
       </c>
@@ -4915,72 +4971,72 @@
       <c r="J6" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="K6" s="207"/>
-      <c r="L6" s="207"/>
+      <c r="K6" s="221"/>
+      <c r="L6" s="221"/>
     </row>
     <row r="7" spans="1:13" ht="69.75" customHeight="1">
-      <c r="A7" s="288">
+      <c r="A7" s="294">
         <v>2</v>
       </c>
-      <c r="B7" s="280">
+      <c r="B7" s="286">
         <v>45731</v>
       </c>
-      <c r="C7" s="207" t="s">
+      <c r="C7" s="221" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="206" t="s">
+      <c r="D7" s="220" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="206" t="s">
+      <c r="E7" s="220" t="s">
         <v>27</v>
       </c>
-      <c r="F7" s="227" t="s">
+      <c r="F7" s="235" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="281" t="s">
+      <c r="G7" s="287" t="s">
         <v>29</v>
       </c>
-      <c r="H7" s="279" t="s">
+      <c r="H7" s="285" t="s">
         <v>30</v>
       </c>
-      <c r="I7" s="263" t="s">
+      <c r="I7" s="269" t="s">
         <v>31</v>
       </c>
-      <c r="J7" s="292"/>
-      <c r="K7" s="286"/>
-      <c r="L7" s="207"/>
+      <c r="J7" s="298"/>
+      <c r="K7" s="292"/>
+      <c r="L7" s="221"/>
     </row>
     <row r="8" spans="1:13" ht="39.950000000000003" customHeight="1">
-      <c r="A8" s="288"/>
-      <c r="B8" s="290"/>
-      <c r="C8" s="207"/>
-      <c r="D8" s="206"/>
-      <c r="E8" s="206"/>
-      <c r="F8" s="227"/>
-      <c r="G8" s="281"/>
-      <c r="H8" s="279"/>
-      <c r="I8" s="280"/>
-      <c r="J8" s="292"/>
-      <c r="K8" s="286"/>
-      <c r="L8" s="207"/>
+      <c r="A8" s="294"/>
+      <c r="B8" s="296"/>
+      <c r="C8" s="221"/>
+      <c r="D8" s="220"/>
+      <c r="E8" s="220"/>
+      <c r="F8" s="235"/>
+      <c r="G8" s="287"/>
+      <c r="H8" s="285"/>
+      <c r="I8" s="286"/>
+      <c r="J8" s="298"/>
+      <c r="K8" s="292"/>
+      <c r="L8" s="221"/>
     </row>
     <row r="9" spans="1:13" ht="115.5" customHeight="1">
-      <c r="A9" s="288">
+      <c r="A9" s="294">
         <v>3</v>
       </c>
-      <c r="B9" s="208">
+      <c r="B9" s="222">
         <v>45739</v>
       </c>
-      <c r="C9" s="208" t="s">
+      <c r="C9" s="222" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="226" t="s">
+      <c r="D9" s="234" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="226" t="s">
+      <c r="E9" s="234" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="227" t="s">
+      <c r="F9" s="235" t="s">
         <v>34</v>
       </c>
       <c r="G9" s="13" t="s">
@@ -4995,20 +5051,20 @@
       <c r="J9" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="K9" s="207" t="s">
+      <c r="K9" s="221" t="s">
         <v>21</v>
       </c>
-      <c r="L9" s="207" t="s">
+      <c r="L9" s="221" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="63.6" customHeight="1">
-      <c r="A10" s="288"/>
-      <c r="B10" s="207"/>
-      <c r="C10" s="208"/>
-      <c r="D10" s="226"/>
-      <c r="E10" s="226"/>
-      <c r="F10" s="227"/>
+      <c r="A10" s="294"/>
+      <c r="B10" s="221"/>
+      <c r="C10" s="222"/>
+      <c r="D10" s="234"/>
+      <c r="E10" s="234"/>
+      <c r="F10" s="235"/>
       <c r="G10" s="13" t="s">
         <v>36</v>
       </c>
@@ -5021,26 +5077,26 @@
       <c r="J10" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="K10" s="207"/>
-      <c r="L10" s="207"/>
+      <c r="K10" s="221"/>
+      <c r="L10" s="221"/>
     </row>
     <row r="11" spans="1:13" ht="81" customHeight="1">
-      <c r="A11" s="288">
+      <c r="A11" s="294">
         <v>4</v>
       </c>
-      <c r="B11" s="208">
+      <c r="B11" s="222">
         <v>45744</v>
       </c>
-      <c r="C11" s="208" t="s">
+      <c r="C11" s="222" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="226" t="s">
+      <c r="D11" s="234" t="s">
         <v>38</v>
       </c>
-      <c r="E11" s="226" t="s">
+      <c r="E11" s="234" t="s">
         <v>27</v>
       </c>
-      <c r="F11" s="227" t="s">
+      <c r="F11" s="235" t="s">
         <v>39</v>
       </c>
       <c r="G11" s="14" t="s">
@@ -5055,20 +5111,20 @@
       <c r="J11" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="K11" s="207" t="s">
+      <c r="K11" s="221" t="s">
         <v>42</v>
       </c>
-      <c r="L11" s="212" t="s">
+      <c r="L11" s="200" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="54.6" customHeight="1">
-      <c r="A12" s="288"/>
-      <c r="B12" s="207"/>
-      <c r="C12" s="208"/>
-      <c r="D12" s="226"/>
-      <c r="E12" s="226"/>
-      <c r="F12" s="227"/>
+      <c r="A12" s="294"/>
+      <c r="B12" s="221"/>
+      <c r="C12" s="222"/>
+      <c r="D12" s="234"/>
+      <c r="E12" s="234"/>
+      <c r="F12" s="235"/>
       <c r="G12" s="14" t="s">
         <v>43</v>
       </c>
@@ -5081,16 +5137,16 @@
       <c r="J12" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="K12" s="207"/>
-      <c r="L12" s="259"/>
+      <c r="K12" s="221"/>
+      <c r="L12" s="201"/>
     </row>
     <row r="13" spans="1:13" ht="54.6" customHeight="1">
-      <c r="A13" s="288"/>
-      <c r="B13" s="207"/>
-      <c r="C13" s="208"/>
-      <c r="D13" s="226"/>
-      <c r="E13" s="226"/>
-      <c r="F13" s="227"/>
+      <c r="A13" s="294"/>
+      <c r="B13" s="221"/>
+      <c r="C13" s="222"/>
+      <c r="D13" s="234"/>
+      <c r="E13" s="234"/>
+      <c r="F13" s="235"/>
       <c r="G13" s="14" t="s">
         <v>45</v>
       </c>
@@ -5103,26 +5159,26 @@
       <c r="J13" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="K13" s="207"/>
-      <c r="L13" s="213"/>
+      <c r="K13" s="221"/>
+      <c r="L13" s="202"/>
     </row>
     <row r="14" spans="1:13" ht="40.5" customHeight="1">
-      <c r="A14" s="291">
+      <c r="A14" s="297">
         <v>5</v>
       </c>
-      <c r="B14" s="208">
+      <c r="B14" s="222">
         <v>45746</v>
       </c>
-      <c r="C14" s="208" t="s">
+      <c r="C14" s="222" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="269" t="s">
+      <c r="D14" s="275" t="s">
         <v>46</v>
       </c>
-      <c r="E14" s="269" t="s">
+      <c r="E14" s="275" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="227" t="s">
+      <c r="F14" s="235" t="s">
         <v>48</v>
       </c>
       <c r="G14" s="13" t="s">
@@ -5137,20 +5193,20 @@
       <c r="J14" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="K14" s="207" t="s">
+      <c r="K14" s="221" t="s">
         <v>22</v>
       </c>
-      <c r="L14" s="212" t="s">
+      <c r="L14" s="200" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="48" customHeight="1">
-      <c r="A15" s="291"/>
-      <c r="B15" s="207"/>
-      <c r="C15" s="208"/>
-      <c r="D15" s="269"/>
-      <c r="E15" s="269"/>
-      <c r="F15" s="227"/>
+      <c r="A15" s="297"/>
+      <c r="B15" s="221"/>
+      <c r="C15" s="222"/>
+      <c r="D15" s="275"/>
+      <c r="E15" s="275"/>
+      <c r="F15" s="235"/>
       <c r="G15" s="13" t="s">
         <v>51</v>
       </c>
@@ -5163,16 +5219,16 @@
       <c r="J15" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="K15" s="207"/>
-      <c r="L15" s="259"/>
+      <c r="K15" s="221"/>
+      <c r="L15" s="201"/>
     </row>
     <row r="16" spans="1:13" ht="48" customHeight="1">
-      <c r="A16" s="291"/>
-      <c r="B16" s="207"/>
-      <c r="C16" s="208"/>
-      <c r="D16" s="269"/>
-      <c r="E16" s="269"/>
-      <c r="F16" s="227"/>
+      <c r="A16" s="297"/>
+      <c r="B16" s="221"/>
+      <c r="C16" s="222"/>
+      <c r="D16" s="275"/>
+      <c r="E16" s="275"/>
+      <c r="F16" s="235"/>
       <c r="G16" s="13" t="s">
         <v>53</v>
       </c>
@@ -5185,16 +5241,16 @@
       <c r="J16" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="K16" s="207"/>
-      <c r="L16" s="259"/>
+      <c r="K16" s="221"/>
+      <c r="L16" s="201"/>
     </row>
     <row r="17" spans="1:12" ht="48" customHeight="1">
-      <c r="A17" s="291"/>
-      <c r="B17" s="207"/>
-      <c r="C17" s="208"/>
-      <c r="D17" s="269"/>
-      <c r="E17" s="269"/>
-      <c r="F17" s="227"/>
+      <c r="A17" s="297"/>
+      <c r="B17" s="221"/>
+      <c r="C17" s="222"/>
+      <c r="D17" s="275"/>
+      <c r="E17" s="275"/>
+      <c r="F17" s="235"/>
       <c r="G17" s="13" t="s">
         <v>54</v>
       </c>
@@ -5207,142 +5263,142 @@
       <c r="J17" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="K17" s="207"/>
-      <c r="L17" s="213"/>
+      <c r="K17" s="221"/>
+      <c r="L17" s="202"/>
     </row>
     <row r="18" spans="1:12" ht="70.5" customHeight="1">
-      <c r="A18" s="288">
+      <c r="A18" s="294">
         <v>6</v>
       </c>
-      <c r="B18" s="280">
+      <c r="B18" s="286">
         <v>45756</v>
       </c>
-      <c r="C18" s="208" t="s">
+      <c r="C18" s="222" t="s">
         <v>32</v>
       </c>
-      <c r="D18" s="226" t="s">
+      <c r="D18" s="234" t="s">
         <v>56</v>
       </c>
-      <c r="E18" s="226" t="s">
+      <c r="E18" s="234" t="s">
         <v>27</v>
       </c>
-      <c r="F18" s="227" t="s">
+      <c r="F18" s="235" t="s">
         <v>57</v>
       </c>
-      <c r="G18" s="281" t="s">
+      <c r="G18" s="287" t="s">
         <v>29</v>
       </c>
-      <c r="H18" s="279" t="s">
+      <c r="H18" s="285" t="s">
         <v>30</v>
       </c>
-      <c r="I18" s="263" t="s">
+      <c r="I18" s="269" t="s">
         <v>31</v>
       </c>
-      <c r="J18" s="292"/>
-      <c r="K18" s="286"/>
-      <c r="L18" s="257"/>
+      <c r="J18" s="298"/>
+      <c r="K18" s="292"/>
+      <c r="L18" s="265"/>
     </row>
     <row r="19" spans="1:12" ht="33.6" customHeight="1">
-      <c r="A19" s="288"/>
-      <c r="B19" s="290"/>
-      <c r="C19" s="208"/>
-      <c r="D19" s="226"/>
-      <c r="E19" s="226"/>
-      <c r="F19" s="227"/>
-      <c r="G19" s="281"/>
-      <c r="H19" s="279"/>
-      <c r="I19" s="282"/>
-      <c r="J19" s="292"/>
-      <c r="K19" s="286"/>
-      <c r="L19" s="257"/>
+      <c r="A19" s="294"/>
+      <c r="B19" s="296"/>
+      <c r="C19" s="222"/>
+      <c r="D19" s="234"/>
+      <c r="E19" s="234"/>
+      <c r="F19" s="235"/>
+      <c r="G19" s="287"/>
+      <c r="H19" s="285"/>
+      <c r="I19" s="288"/>
+      <c r="J19" s="298"/>
+      <c r="K19" s="292"/>
+      <c r="L19" s="265"/>
     </row>
     <row r="20" spans="1:12" ht="33.6" customHeight="1">
-      <c r="A20" s="288"/>
-      <c r="B20" s="290"/>
-      <c r="C20" s="208"/>
-      <c r="D20" s="226"/>
-      <c r="E20" s="226"/>
-      <c r="F20" s="227"/>
-      <c r="G20" s="281"/>
-      <c r="H20" s="279"/>
-      <c r="I20" s="282"/>
-      <c r="J20" s="292"/>
-      <c r="K20" s="286"/>
-      <c r="L20" s="257"/>
+      <c r="A20" s="294"/>
+      <c r="B20" s="296"/>
+      <c r="C20" s="222"/>
+      <c r="D20" s="234"/>
+      <c r="E20" s="234"/>
+      <c r="F20" s="235"/>
+      <c r="G20" s="287"/>
+      <c r="H20" s="285"/>
+      <c r="I20" s="288"/>
+      <c r="J20" s="298"/>
+      <c r="K20" s="292"/>
+      <c r="L20" s="265"/>
     </row>
     <row r="21" spans="1:12" ht="33.6" customHeight="1">
-      <c r="A21" s="288"/>
-      <c r="B21" s="290"/>
-      <c r="C21" s="208"/>
-      <c r="D21" s="226"/>
-      <c r="E21" s="226"/>
-      <c r="F21" s="227"/>
-      <c r="G21" s="281"/>
-      <c r="H21" s="279"/>
-      <c r="I21" s="282"/>
-      <c r="J21" s="292"/>
-      <c r="K21" s="286"/>
-      <c r="L21" s="257"/>
+      <c r="A21" s="294"/>
+      <c r="B21" s="296"/>
+      <c r="C21" s="222"/>
+      <c r="D21" s="234"/>
+      <c r="E21" s="234"/>
+      <c r="F21" s="235"/>
+      <c r="G21" s="287"/>
+      <c r="H21" s="285"/>
+      <c r="I21" s="288"/>
+      <c r="J21" s="298"/>
+      <c r="K21" s="292"/>
+      <c r="L21" s="265"/>
     </row>
     <row r="22" spans="1:12" ht="33.6" customHeight="1">
-      <c r="A22" s="288"/>
-      <c r="B22" s="290"/>
-      <c r="C22" s="208"/>
-      <c r="D22" s="226"/>
-      <c r="E22" s="226"/>
-      <c r="F22" s="227"/>
-      <c r="G22" s="281"/>
-      <c r="H22" s="279"/>
-      <c r="I22" s="282"/>
-      <c r="J22" s="292"/>
-      <c r="K22" s="286"/>
-      <c r="L22" s="257"/>
+      <c r="A22" s="294"/>
+      <c r="B22" s="296"/>
+      <c r="C22" s="222"/>
+      <c r="D22" s="234"/>
+      <c r="E22" s="234"/>
+      <c r="F22" s="235"/>
+      <c r="G22" s="287"/>
+      <c r="H22" s="285"/>
+      <c r="I22" s="288"/>
+      <c r="J22" s="298"/>
+      <c r="K22" s="292"/>
+      <c r="L22" s="265"/>
     </row>
     <row r="23" spans="1:12" ht="33.6" customHeight="1">
-      <c r="A23" s="288"/>
-      <c r="B23" s="290"/>
-      <c r="C23" s="208"/>
-      <c r="D23" s="226"/>
-      <c r="E23" s="226"/>
-      <c r="F23" s="227"/>
-      <c r="G23" s="281"/>
-      <c r="H23" s="279"/>
-      <c r="I23" s="282"/>
-      <c r="J23" s="292"/>
-      <c r="K23" s="286"/>
-      <c r="L23" s="257"/>
+      <c r="A23" s="294"/>
+      <c r="B23" s="296"/>
+      <c r="C23" s="222"/>
+      <c r="D23" s="234"/>
+      <c r="E23" s="234"/>
+      <c r="F23" s="235"/>
+      <c r="G23" s="287"/>
+      <c r="H23" s="285"/>
+      <c r="I23" s="288"/>
+      <c r="J23" s="298"/>
+      <c r="K23" s="292"/>
+      <c r="L23" s="265"/>
     </row>
     <row r="24" spans="1:12" ht="33.6" customHeight="1">
-      <c r="A24" s="288"/>
-      <c r="B24" s="290"/>
-      <c r="C24" s="208"/>
-      <c r="D24" s="226"/>
-      <c r="E24" s="226"/>
-      <c r="F24" s="227"/>
-      <c r="G24" s="281"/>
-      <c r="H24" s="279"/>
-      <c r="I24" s="282"/>
-      <c r="J24" s="292"/>
-      <c r="K24" s="286"/>
-      <c r="L24" s="257"/>
+      <c r="A24" s="294"/>
+      <c r="B24" s="296"/>
+      <c r="C24" s="222"/>
+      <c r="D24" s="234"/>
+      <c r="E24" s="234"/>
+      <c r="F24" s="235"/>
+      <c r="G24" s="287"/>
+      <c r="H24" s="285"/>
+      <c r="I24" s="288"/>
+      <c r="J24" s="298"/>
+      <c r="K24" s="292"/>
+      <c r="L24" s="265"/>
     </row>
     <row r="25" spans="1:12" ht="97.5" customHeight="1">
-      <c r="A25" s="272">
+      <c r="A25" s="278">
         <v>7</v>
       </c>
-      <c r="B25" s="289">
+      <c r="B25" s="295">
         <v>45757</v>
       </c>
-      <c r="C25" s="289" t="s">
+      <c r="C25" s="295" t="s">
         <v>32</v>
       </c>
-      <c r="D25" s="225" t="s">
+      <c r="D25" s="233" t="s">
         <v>58</v>
       </c>
-      <c r="E25" s="225" t="s">
+      <c r="E25" s="233" t="s">
         <v>27</v>
       </c>
-      <c r="F25" s="246" t="s">
+      <c r="F25" s="254" t="s">
         <v>59</v>
       </c>
       <c r="G25" s="22" t="s">
@@ -5357,20 +5413,20 @@
       <c r="J25" s="74" t="s">
         <v>20</v>
       </c>
-      <c r="K25" s="287" t="s">
+      <c r="K25" s="293" t="s">
         <v>42</v>
       </c>
-      <c r="L25" s="207" t="s">
+      <c r="L25" s="221" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="68.099999999999994" customHeight="1">
-      <c r="A26" s="272"/>
-      <c r="B26" s="262"/>
-      <c r="C26" s="289"/>
-      <c r="D26" s="225"/>
-      <c r="E26" s="225"/>
-      <c r="F26" s="246"/>
+      <c r="A26" s="278"/>
+      <c r="B26" s="268"/>
+      <c r="C26" s="295"/>
+      <c r="D26" s="233"/>
+      <c r="E26" s="233"/>
+      <c r="F26" s="254"/>
       <c r="G26" s="14" t="s">
         <v>62</v>
       </c>
@@ -5383,26 +5439,26 @@
       <c r="J26" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="K26" s="287"/>
-      <c r="L26" s="207"/>
+      <c r="K26" s="293"/>
+      <c r="L26" s="221"/>
     </row>
     <row r="27" spans="1:12" ht="88.5" customHeight="1">
-      <c r="A27" s="288">
+      <c r="A27" s="294">
         <v>8</v>
       </c>
-      <c r="B27" s="208">
+      <c r="B27" s="222">
         <v>45760</v>
       </c>
-      <c r="C27" s="208" t="s">
+      <c r="C27" s="222" t="s">
         <v>32</v>
       </c>
-      <c r="D27" s="226" t="s">
+      <c r="D27" s="234" t="s">
         <v>63</v>
       </c>
-      <c r="E27" s="226" t="s">
+      <c r="E27" s="234" t="s">
         <v>27</v>
       </c>
-      <c r="F27" s="227" t="s">
+      <c r="F27" s="235" t="s">
         <v>64</v>
       </c>
       <c r="G27" s="14" t="s">
@@ -5417,20 +5473,20 @@
       <c r="J27" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="K27" s="206" t="s">
+      <c r="K27" s="220" t="s">
         <v>42</v>
       </c>
-      <c r="L27" s="207" t="s">
+      <c r="L27" s="221" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="88.5" customHeight="1">
-      <c r="A28" s="288"/>
-      <c r="B28" s="207"/>
-      <c r="C28" s="208"/>
-      <c r="D28" s="226"/>
-      <c r="E28" s="226"/>
-      <c r="F28" s="227"/>
+      <c r="A28" s="294"/>
+      <c r="B28" s="221"/>
+      <c r="C28" s="222"/>
+      <c r="D28" s="234"/>
+      <c r="E28" s="234"/>
+      <c r="F28" s="235"/>
       <c r="G28" s="14" t="s">
         <v>62</v>
       </c>
@@ -5443,26 +5499,26 @@
       <c r="J28" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="K28" s="206"/>
-      <c r="L28" s="207"/>
+      <c r="K28" s="220"/>
+      <c r="L28" s="221"/>
     </row>
     <row r="29" spans="1:12" ht="72" customHeight="1">
-      <c r="A29" s="288">
+      <c r="A29" s="294">
         <v>9</v>
       </c>
-      <c r="B29" s="208">
+      <c r="B29" s="222">
         <v>45764</v>
       </c>
-      <c r="C29" s="208" t="s">
+      <c r="C29" s="222" t="s">
         <v>14</v>
       </c>
-      <c r="D29" s="226" t="s">
+      <c r="D29" s="234" t="s">
         <v>66</v>
       </c>
-      <c r="E29" s="226" t="s">
+      <c r="E29" s="234" t="s">
         <v>27</v>
       </c>
-      <c r="F29" s="227" t="s">
+      <c r="F29" s="235" t="s">
         <v>67</v>
       </c>
       <c r="G29" s="14" t="s">
@@ -5477,20 +5533,20 @@
       <c r="J29" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="K29" s="206" t="s">
+      <c r="K29" s="220" t="s">
         <v>22</v>
       </c>
-      <c r="L29" s="207" t="s">
+      <c r="L29" s="221" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="72" customHeight="1">
-      <c r="A30" s="288"/>
-      <c r="B30" s="208"/>
-      <c r="C30" s="208"/>
-      <c r="D30" s="226"/>
-      <c r="E30" s="226"/>
-      <c r="F30" s="227"/>
+      <c r="A30" s="294"/>
+      <c r="B30" s="222"/>
+      <c r="C30" s="222"/>
+      <c r="D30" s="234"/>
+      <c r="E30" s="234"/>
+      <c r="F30" s="235"/>
       <c r="G30" s="14" t="s">
         <v>70</v>
       </c>
@@ -5503,16 +5559,16 @@
       <c r="J30" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="K30" s="206"/>
-      <c r="L30" s="207"/>
+      <c r="K30" s="220"/>
+      <c r="L30" s="221"/>
     </row>
     <row r="31" spans="1:12" ht="72" customHeight="1">
-      <c r="A31" s="288"/>
-      <c r="B31" s="208"/>
-      <c r="C31" s="208"/>
-      <c r="D31" s="226"/>
-      <c r="E31" s="226"/>
-      <c r="F31" s="227"/>
+      <c r="A31" s="294"/>
+      <c r="B31" s="222"/>
+      <c r="C31" s="222"/>
+      <c r="D31" s="234"/>
+      <c r="E31" s="234"/>
+      <c r="F31" s="235"/>
       <c r="G31" s="14" t="s">
         <v>72</v>
       </c>
@@ -5525,26 +5581,26 @@
       <c r="J31" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="K31" s="206"/>
-      <c r="L31" s="207"/>
+      <c r="K31" s="220"/>
+      <c r="L31" s="221"/>
     </row>
     <row r="32" spans="1:12" ht="81" customHeight="1">
-      <c r="A32" s="288">
+      <c r="A32" s="294">
         <v>10</v>
       </c>
-      <c r="B32" s="208">
+      <c r="B32" s="222">
         <v>45771</v>
       </c>
-      <c r="C32" s="208" t="s">
+      <c r="C32" s="222" t="s">
         <v>14</v>
       </c>
-      <c r="D32" s="226" t="s">
+      <c r="D32" s="234" t="s">
         <v>73</v>
       </c>
-      <c r="E32" s="226" t="s">
+      <c r="E32" s="234" t="s">
         <v>27</v>
       </c>
-      <c r="F32" s="227" t="s">
+      <c r="F32" s="235" t="s">
         <v>74</v>
       </c>
       <c r="G32" s="14" t="s">
@@ -5559,20 +5615,20 @@
       <c r="J32" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="K32" s="206" t="s">
+      <c r="K32" s="220" t="s">
         <v>22</v>
       </c>
-      <c r="L32" s="207" t="s">
+      <c r="L32" s="221" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="33" spans="1:12" ht="57.6" customHeight="1">
-      <c r="A33" s="288"/>
-      <c r="B33" s="208"/>
-      <c r="C33" s="208"/>
-      <c r="D33" s="226"/>
-      <c r="E33" s="226"/>
-      <c r="F33" s="227"/>
+      <c r="A33" s="294"/>
+      <c r="B33" s="222"/>
+      <c r="C33" s="222"/>
+      <c r="D33" s="234"/>
+      <c r="E33" s="234"/>
+      <c r="F33" s="235"/>
       <c r="G33" s="14" t="s">
         <v>76</v>
       </c>
@@ -5585,26 +5641,26 @@
       <c r="J33" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="K33" s="206"/>
-      <c r="L33" s="207"/>
+      <c r="K33" s="220"/>
+      <c r="L33" s="221"/>
     </row>
     <row r="34" spans="1:12" ht="56.45" customHeight="1">
-      <c r="A34" s="288">
+      <c r="A34" s="294">
         <v>11</v>
       </c>
-      <c r="B34" s="208">
+      <c r="B34" s="222">
         <v>45773</v>
       </c>
-      <c r="C34" s="208" t="s">
+      <c r="C34" s="222" t="s">
         <v>32</v>
       </c>
-      <c r="D34" s="226" t="s">
+      <c r="D34" s="234" t="s">
         <v>77</v>
       </c>
-      <c r="E34" s="226" t="s">
+      <c r="E34" s="234" t="s">
         <v>78</v>
       </c>
-      <c r="F34" s="227" t="s">
+      <c r="F34" s="235" t="s">
         <v>79</v>
       </c>
       <c r="G34" s="14" t="s">
@@ -5619,20 +5675,20 @@
       <c r="J34" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="K34" s="256" t="s">
+      <c r="K34" s="264" t="s">
         <v>42</v>
       </c>
-      <c r="L34" s="207" t="s">
+      <c r="L34" s="221" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:12" ht="56.45" customHeight="1">
-      <c r="A35" s="288"/>
-      <c r="B35" s="208"/>
-      <c r="C35" s="208"/>
-      <c r="D35" s="226"/>
-      <c r="E35" s="226"/>
-      <c r="F35" s="227"/>
+      <c r="A35" s="294"/>
+      <c r="B35" s="222"/>
+      <c r="C35" s="222"/>
+      <c r="D35" s="234"/>
+      <c r="E35" s="234"/>
+      <c r="F35" s="235"/>
       <c r="G35" s="14" t="s">
         <v>81</v>
       </c>
@@ -5645,16 +5701,16 @@
       <c r="J35" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="K35" s="256"/>
-      <c r="L35" s="207"/>
+      <c r="K35" s="264"/>
+      <c r="L35" s="221"/>
     </row>
     <row r="36" spans="1:12" ht="56.45" customHeight="1">
-      <c r="A36" s="288"/>
-      <c r="B36" s="208"/>
-      <c r="C36" s="208"/>
-      <c r="D36" s="226"/>
-      <c r="E36" s="226"/>
-      <c r="F36" s="227"/>
+      <c r="A36" s="294"/>
+      <c r="B36" s="222"/>
+      <c r="C36" s="222"/>
+      <c r="D36" s="234"/>
+      <c r="E36" s="234"/>
+      <c r="F36" s="235"/>
       <c r="G36" s="14" t="s">
         <v>82</v>
       </c>
@@ -5667,26 +5723,26 @@
       <c r="J36" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="K36" s="256"/>
-      <c r="L36" s="207"/>
+      <c r="K36" s="264"/>
+      <c r="L36" s="221"/>
     </row>
     <row r="37" spans="1:12" ht="58.5" customHeight="1">
-      <c r="A37" s="288">
+      <c r="A37" s="294">
         <v>12</v>
       </c>
-      <c r="B37" s="208">
+      <c r="B37" s="222">
         <v>45776</v>
       </c>
-      <c r="C37" s="208" t="s">
+      <c r="C37" s="222" t="s">
         <v>32</v>
       </c>
-      <c r="D37" s="206" t="s">
+      <c r="D37" s="220" t="s">
         <v>83</v>
       </c>
-      <c r="E37" s="206" t="s">
+      <c r="E37" s="220" t="s">
         <v>78</v>
       </c>
-      <c r="F37" s="227" t="s">
+      <c r="F37" s="235" t="s">
         <v>84</v>
       </c>
       <c r="G37" s="14" t="s">
@@ -5701,7 +5757,7 @@
       <c r="J37" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="K37" s="262" t="s">
+      <c r="K37" s="268" t="s">
         <v>22</v>
       </c>
       <c r="L37" s="24" t="s">
@@ -5709,12 +5765,12 @@
       </c>
     </row>
     <row r="38" spans="1:12" ht="58.5" customHeight="1">
-      <c r="A38" s="288"/>
-      <c r="B38" s="207"/>
-      <c r="C38" s="208"/>
-      <c r="D38" s="206"/>
-      <c r="E38" s="206"/>
-      <c r="F38" s="227"/>
+      <c r="A38" s="294"/>
+      <c r="B38" s="221"/>
+      <c r="C38" s="222"/>
+      <c r="D38" s="220"/>
+      <c r="E38" s="220"/>
+      <c r="F38" s="235"/>
       <c r="G38" s="14" t="s">
         <v>62</v>
       </c>
@@ -5727,18 +5783,18 @@
       <c r="J38" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K38" s="262"/>
+      <c r="K38" s="268"/>
       <c r="L38" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="58.5" customHeight="1">
-      <c r="A39" s="288"/>
-      <c r="B39" s="207"/>
-      <c r="C39" s="208"/>
-      <c r="D39" s="206"/>
-      <c r="E39" s="206"/>
-      <c r="F39" s="227"/>
+      <c r="A39" s="294"/>
+      <c r="B39" s="221"/>
+      <c r="C39" s="222"/>
+      <c r="D39" s="220"/>
+      <c r="E39" s="220"/>
+      <c r="F39" s="235"/>
       <c r="G39" s="14" t="s">
         <v>90</v>
       </c>
@@ -5751,176 +5807,176 @@
       <c r="J39" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K39" s="262"/>
+      <c r="K39" s="268"/>
       <c r="L39" s="12"/>
     </row>
     <row r="40" spans="1:12" ht="97.5" customHeight="1">
-      <c r="A40" s="288">
+      <c r="A40" s="294">
         <v>13</v>
       </c>
-      <c r="B40" s="208">
+      <c r="B40" s="222">
         <v>45781</v>
       </c>
-      <c r="C40" s="208" t="s">
+      <c r="C40" s="222" t="s">
         <v>14</v>
       </c>
-      <c r="D40" s="226" t="s">
+      <c r="D40" s="234" t="s">
         <v>92</v>
       </c>
-      <c r="E40" s="226" t="s">
+      <c r="E40" s="234" t="s">
         <v>27</v>
       </c>
-      <c r="F40" s="227" t="s">
+      <c r="F40" s="235" t="s">
         <v>93</v>
       </c>
-      <c r="G40" s="281" t="s">
+      <c r="G40" s="287" t="s">
         <v>29</v>
       </c>
-      <c r="H40" s="295" t="s">
+      <c r="H40" s="301" t="s">
         <v>30</v>
       </c>
-      <c r="I40" s="263" t="s">
+      <c r="I40" s="269" t="s">
         <v>31</v>
       </c>
-      <c r="J40" s="276"/>
-      <c r="K40" s="271"/>
-      <c r="L40" s="257"/>
+      <c r="J40" s="282"/>
+      <c r="K40" s="277"/>
+      <c r="L40" s="265"/>
     </row>
     <row r="41" spans="1:12" ht="33.6" customHeight="1">
-      <c r="A41" s="288"/>
-      <c r="B41" s="290"/>
-      <c r="C41" s="208"/>
-      <c r="D41" s="226"/>
-      <c r="E41" s="226"/>
-      <c r="F41" s="227"/>
-      <c r="G41" s="281"/>
-      <c r="H41" s="295"/>
-      <c r="I41" s="282"/>
-      <c r="J41" s="276"/>
-      <c r="K41" s="271"/>
-      <c r="L41" s="257"/>
+      <c r="A41" s="294"/>
+      <c r="B41" s="296"/>
+      <c r="C41" s="222"/>
+      <c r="D41" s="234"/>
+      <c r="E41" s="234"/>
+      <c r="F41" s="235"/>
+      <c r="G41" s="287"/>
+      <c r="H41" s="301"/>
+      <c r="I41" s="288"/>
+      <c r="J41" s="282"/>
+      <c r="K41" s="277"/>
+      <c r="L41" s="265"/>
     </row>
     <row r="42" spans="1:12" ht="33.6" customHeight="1">
-      <c r="A42" s="288"/>
-      <c r="B42" s="290"/>
-      <c r="C42" s="208"/>
-      <c r="D42" s="226"/>
-      <c r="E42" s="226"/>
-      <c r="F42" s="227"/>
-      <c r="G42" s="281"/>
-      <c r="H42" s="295"/>
-      <c r="I42" s="282"/>
-      <c r="J42" s="276"/>
-      <c r="K42" s="271"/>
-      <c r="L42" s="257"/>
+      <c r="A42" s="294"/>
+      <c r="B42" s="296"/>
+      <c r="C42" s="222"/>
+      <c r="D42" s="234"/>
+      <c r="E42" s="234"/>
+      <c r="F42" s="235"/>
+      <c r="G42" s="287"/>
+      <c r="H42" s="301"/>
+      <c r="I42" s="288"/>
+      <c r="J42" s="282"/>
+      <c r="K42" s="277"/>
+      <c r="L42" s="265"/>
     </row>
     <row r="43" spans="1:12" ht="33.6" customHeight="1">
-      <c r="A43" s="288"/>
-      <c r="B43" s="290"/>
-      <c r="C43" s="208"/>
-      <c r="D43" s="226"/>
-      <c r="E43" s="226"/>
-      <c r="F43" s="227"/>
-      <c r="G43" s="281"/>
-      <c r="H43" s="295"/>
-      <c r="I43" s="282"/>
-      <c r="J43" s="276"/>
-      <c r="K43" s="271"/>
-      <c r="L43" s="257"/>
+      <c r="A43" s="294"/>
+      <c r="B43" s="296"/>
+      <c r="C43" s="222"/>
+      <c r="D43" s="234"/>
+      <c r="E43" s="234"/>
+      <c r="F43" s="235"/>
+      <c r="G43" s="287"/>
+      <c r="H43" s="301"/>
+      <c r="I43" s="288"/>
+      <c r="J43" s="282"/>
+      <c r="K43" s="277"/>
+      <c r="L43" s="265"/>
     </row>
     <row r="44" spans="1:12" ht="33.6" customHeight="1">
-      <c r="A44" s="288">
+      <c r="A44" s="294">
         <v>14</v>
       </c>
-      <c r="B44" s="280">
+      <c r="B44" s="286">
         <v>45786</v>
       </c>
-      <c r="C44" s="207" t="s">
+      <c r="C44" s="221" t="s">
         <v>14</v>
       </c>
-      <c r="D44" s="206" t="s">
+      <c r="D44" s="220" t="s">
         <v>94</v>
       </c>
-      <c r="E44" s="206" t="s">
+      <c r="E44" s="220" t="s">
         <v>95</v>
       </c>
-      <c r="F44" s="227" t="s">
+      <c r="F44" s="235" t="s">
         <v>96</v>
       </c>
-      <c r="G44" s="277" t="s">
+      <c r="G44" s="283" t="s">
         <v>97</v>
       </c>
-      <c r="H44" s="279" t="s">
+      <c r="H44" s="285" t="s">
         <v>30</v>
       </c>
-      <c r="I44" s="275" t="s">
+      <c r="I44" s="281" t="s">
         <v>30</v>
       </c>
-      <c r="J44" s="276" t="s">
+      <c r="J44" s="282" t="s">
         <v>20</v>
       </c>
-      <c r="K44" s="271"/>
-      <c r="L44" s="257"/>
+      <c r="K44" s="277"/>
+      <c r="L44" s="265"/>
     </row>
     <row r="45" spans="1:12" ht="33.6" customHeight="1">
-      <c r="A45" s="288"/>
-      <c r="B45" s="290"/>
-      <c r="C45" s="207"/>
-      <c r="D45" s="206"/>
-      <c r="E45" s="206"/>
-      <c r="F45" s="227"/>
-      <c r="G45" s="277"/>
-      <c r="H45" s="279"/>
-      <c r="I45" s="275"/>
-      <c r="J45" s="276"/>
-      <c r="K45" s="271"/>
-      <c r="L45" s="257"/>
+      <c r="A45" s="294"/>
+      <c r="B45" s="296"/>
+      <c r="C45" s="221"/>
+      <c r="D45" s="220"/>
+      <c r="E45" s="220"/>
+      <c r="F45" s="235"/>
+      <c r="G45" s="283"/>
+      <c r="H45" s="285"/>
+      <c r="I45" s="281"/>
+      <c r="J45" s="282"/>
+      <c r="K45" s="277"/>
+      <c r="L45" s="265"/>
     </row>
     <row r="46" spans="1:12" ht="33.6" customHeight="1">
-      <c r="A46" s="288"/>
-      <c r="B46" s="290"/>
-      <c r="C46" s="207"/>
-      <c r="D46" s="206"/>
-      <c r="E46" s="206"/>
-      <c r="F46" s="227"/>
-      <c r="G46" s="277"/>
-      <c r="H46" s="279"/>
-      <c r="I46" s="275"/>
-      <c r="J46" s="276"/>
-      <c r="K46" s="271"/>
-      <c r="L46" s="257"/>
+      <c r="A46" s="294"/>
+      <c r="B46" s="296"/>
+      <c r="C46" s="221"/>
+      <c r="D46" s="220"/>
+      <c r="E46" s="220"/>
+      <c r="F46" s="235"/>
+      <c r="G46" s="283"/>
+      <c r="H46" s="285"/>
+      <c r="I46" s="281"/>
+      <c r="J46" s="282"/>
+      <c r="K46" s="277"/>
+      <c r="L46" s="265"/>
     </row>
     <row r="47" spans="1:12" ht="33.6" customHeight="1">
-      <c r="A47" s="288"/>
-      <c r="B47" s="290"/>
-      <c r="C47" s="207"/>
-      <c r="D47" s="206"/>
-      <c r="E47" s="206"/>
-      <c r="F47" s="227"/>
-      <c r="G47" s="277"/>
-      <c r="H47" s="279"/>
-      <c r="I47" s="275"/>
-      <c r="J47" s="276"/>
-      <c r="K47" s="271"/>
-      <c r="L47" s="257"/>
+      <c r="A47" s="294"/>
+      <c r="B47" s="296"/>
+      <c r="C47" s="221"/>
+      <c r="D47" s="220"/>
+      <c r="E47" s="220"/>
+      <c r="F47" s="235"/>
+      <c r="G47" s="283"/>
+      <c r="H47" s="285"/>
+      <c r="I47" s="281"/>
+      <c r="J47" s="282"/>
+      <c r="K47" s="277"/>
+      <c r="L47" s="265"/>
     </row>
     <row r="48" spans="1:12" ht="46.5" customHeight="1">
-      <c r="A48" s="291">
+      <c r="A48" s="297">
         <v>15</v>
       </c>
-      <c r="B48" s="293">
+      <c r="B48" s="299">
         <v>45787</v>
       </c>
-      <c r="C48" s="293" t="s">
+      <c r="C48" s="299" t="s">
         <v>14</v>
       </c>
-      <c r="D48" s="269" t="s">
+      <c r="D48" s="275" t="s">
         <v>98</v>
       </c>
-      <c r="E48" s="269" t="s">
+      <c r="E48" s="275" t="s">
         <v>47</v>
       </c>
-      <c r="F48" s="227" t="s">
+      <c r="F48" s="235" t="s">
         <v>99</v>
       </c>
       <c r="G48" s="14" t="s">
@@ -5935,20 +5991,20 @@
       <c r="J48" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K48" s="256" t="s">
+      <c r="K48" s="264" t="s">
         <v>22</v>
       </c>
-      <c r="L48" s="207" t="s">
+      <c r="L48" s="221" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="49" spans="1:13" ht="46.5" customHeight="1">
-      <c r="A49" s="291"/>
-      <c r="B49" s="218"/>
-      <c r="C49" s="293"/>
-      <c r="D49" s="269"/>
-      <c r="E49" s="269"/>
-      <c r="F49" s="227"/>
+      <c r="A49" s="297"/>
+      <c r="B49" s="226"/>
+      <c r="C49" s="299"/>
+      <c r="D49" s="275"/>
+      <c r="E49" s="275"/>
+      <c r="F49" s="235"/>
       <c r="G49" s="14" t="s">
         <v>102</v>
       </c>
@@ -5961,16 +6017,16 @@
       <c r="J49" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K49" s="256"/>
-      <c r="L49" s="207"/>
+      <c r="K49" s="264"/>
+      <c r="L49" s="221"/>
     </row>
     <row r="50" spans="1:13" ht="46.5" customHeight="1">
-      <c r="A50" s="291"/>
-      <c r="B50" s="218"/>
-      <c r="C50" s="293"/>
-      <c r="D50" s="269"/>
-      <c r="E50" s="269"/>
-      <c r="F50" s="227"/>
+      <c r="A50" s="297"/>
+      <c r="B50" s="226"/>
+      <c r="C50" s="299"/>
+      <c r="D50" s="275"/>
+      <c r="E50" s="275"/>
+      <c r="F50" s="235"/>
       <c r="G50" s="14" t="s">
         <v>104</v>
       </c>
@@ -5983,16 +6039,16 @@
       <c r="J50" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K50" s="256"/>
-      <c r="L50" s="207"/>
+      <c r="K50" s="264"/>
+      <c r="L50" s="221"/>
     </row>
     <row r="51" spans="1:13" ht="46.5" customHeight="1">
-      <c r="A51" s="291"/>
-      <c r="B51" s="218"/>
-      <c r="C51" s="293"/>
-      <c r="D51" s="269"/>
-      <c r="E51" s="269"/>
-      <c r="F51" s="227"/>
+      <c r="A51" s="297"/>
+      <c r="B51" s="226"/>
+      <c r="C51" s="299"/>
+      <c r="D51" s="275"/>
+      <c r="E51" s="275"/>
+      <c r="F51" s="235"/>
       <c r="G51" s="14" t="s">
         <v>105</v>
       </c>
@@ -6005,16 +6061,16 @@
       <c r="J51" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K51" s="256"/>
-      <c r="L51" s="207"/>
+      <c r="K51" s="264"/>
+      <c r="L51" s="221"/>
     </row>
     <row r="52" spans="1:13" ht="46.5" customHeight="1">
-      <c r="A52" s="291"/>
-      <c r="B52" s="218"/>
-      <c r="C52" s="293"/>
-      <c r="D52" s="269"/>
-      <c r="E52" s="269"/>
-      <c r="F52" s="227"/>
+      <c r="A52" s="297"/>
+      <c r="B52" s="226"/>
+      <c r="C52" s="299"/>
+      <c r="D52" s="275"/>
+      <c r="E52" s="275"/>
+      <c r="F52" s="235"/>
       <c r="G52" s="14" t="s">
         <v>107</v>
       </c>
@@ -6027,26 +6083,26 @@
       <c r="J52" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K52" s="256"/>
-      <c r="L52" s="207"/>
+      <c r="K52" s="264"/>
+      <c r="L52" s="221"/>
     </row>
     <row r="53" spans="1:13" ht="78" customHeight="1">
-      <c r="A53" s="291">
+      <c r="A53" s="297">
         <v>16</v>
       </c>
-      <c r="B53" s="269">
+      <c r="B53" s="275">
         <v>45800</v>
       </c>
-      <c r="C53" s="269" t="s">
+      <c r="C53" s="275" t="s">
         <v>32</v>
       </c>
-      <c r="D53" s="269" t="s">
+      <c r="D53" s="275" t="s">
         <v>108</v>
       </c>
-      <c r="E53" s="269" t="s">
+      <c r="E53" s="275" t="s">
         <v>47</v>
       </c>
-      <c r="F53" s="227" t="s">
+      <c r="F53" s="235" t="s">
         <v>109</v>
       </c>
       <c r="G53" s="26" t="s">
@@ -6061,20 +6117,20 @@
       <c r="J53" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K53" s="256" t="s">
+      <c r="K53" s="264" t="s">
         <v>22</v>
       </c>
-      <c r="L53" s="207" t="s">
+      <c r="L53" s="221" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="54" spans="1:13" ht="56.45" customHeight="1">
-      <c r="A54" s="291"/>
-      <c r="B54" s="294"/>
-      <c r="C54" s="269"/>
-      <c r="D54" s="269"/>
-      <c r="E54" s="269"/>
-      <c r="F54" s="227"/>
+      <c r="A54" s="297"/>
+      <c r="B54" s="300"/>
+      <c r="C54" s="275"/>
+      <c r="D54" s="275"/>
+      <c r="E54" s="275"/>
+      <c r="F54" s="235"/>
       <c r="G54" s="26" t="s">
         <v>111</v>
       </c>
@@ -6087,16 +6143,16 @@
       <c r="J54" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="K54" s="256"/>
-      <c r="L54" s="207"/>
+      <c r="K54" s="264"/>
+      <c r="L54" s="221"/>
     </row>
     <row r="55" spans="1:13" ht="56.45" customHeight="1">
-      <c r="A55" s="291"/>
-      <c r="B55" s="294"/>
-      <c r="C55" s="269"/>
-      <c r="D55" s="269"/>
-      <c r="E55" s="269"/>
-      <c r="F55" s="227"/>
+      <c r="A55" s="297"/>
+      <c r="B55" s="300"/>
+      <c r="C55" s="275"/>
+      <c r="D55" s="275"/>
+      <c r="E55" s="275"/>
+      <c r="F55" s="235"/>
       <c r="G55" s="26" t="s">
         <v>112</v>
       </c>
@@ -6109,16 +6165,16 @@
       <c r="J55" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="K55" s="256"/>
-      <c r="L55" s="207"/>
+      <c r="K55" s="264"/>
+      <c r="L55" s="221"/>
     </row>
     <row r="56" spans="1:13" ht="56.45" customHeight="1">
-      <c r="A56" s="291"/>
-      <c r="B56" s="294"/>
-      <c r="C56" s="269"/>
-      <c r="D56" s="269"/>
-      <c r="E56" s="269"/>
-      <c r="F56" s="227"/>
+      <c r="A56" s="297"/>
+      <c r="B56" s="300"/>
+      <c r="C56" s="275"/>
+      <c r="D56" s="275"/>
+      <c r="E56" s="275"/>
+      <c r="F56" s="235"/>
       <c r="G56" s="26" t="s">
         <v>113</v>
       </c>
@@ -6131,16 +6187,16 @@
       <c r="J56" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K56" s="256"/>
-      <c r="L56" s="207"/>
+      <c r="K56" s="264"/>
+      <c r="L56" s="221"/>
     </row>
     <row r="57" spans="1:13" ht="75.599999999999994" customHeight="1">
-      <c r="A57" s="291"/>
-      <c r="B57" s="294"/>
-      <c r="C57" s="269"/>
-      <c r="D57" s="269"/>
-      <c r="E57" s="269"/>
-      <c r="F57" s="227"/>
+      <c r="A57" s="297"/>
+      <c r="B57" s="300"/>
+      <c r="C57" s="275"/>
+      <c r="D57" s="275"/>
+      <c r="E57" s="275"/>
+      <c r="F57" s="235"/>
       <c r="G57" s="28" t="s">
         <v>114</v>
       </c>
@@ -6153,26 +6209,26 @@
       <c r="J57" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K57" s="256"/>
-      <c r="L57" s="212"/>
+      <c r="K57" s="264"/>
+      <c r="L57" s="200"/>
     </row>
     <row r="58" spans="1:13" ht="58.5" customHeight="1">
-      <c r="A58" s="291">
+      <c r="A58" s="297">
         <v>17</v>
       </c>
-      <c r="B58" s="269">
+      <c r="B58" s="275">
         <v>45809</v>
       </c>
-      <c r="C58" s="269" t="s">
+      <c r="C58" s="275" t="s">
         <v>14</v>
       </c>
-      <c r="D58" s="269" t="s">
+      <c r="D58" s="275" t="s">
         <v>115</v>
       </c>
-      <c r="E58" s="269" t="s">
+      <c r="E58" s="275" t="s">
         <v>47</v>
       </c>
-      <c r="F58" s="299" t="s">
+      <c r="F58" s="305" t="s">
         <v>116</v>
       </c>
       <c r="G58" s="26" t="s">
@@ -6187,21 +6243,21 @@
       <c r="J58" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K58" s="243" t="s">
+      <c r="K58" s="251" t="s">
         <v>22</v>
       </c>
-      <c r="L58" s="207" t="s">
+      <c r="L58" s="221" t="s">
         <v>22</v>
       </c>
       <c r="M58" s="12"/>
     </row>
     <row r="59" spans="1:13" ht="58.5" customHeight="1">
-      <c r="A59" s="291"/>
-      <c r="B59" s="269"/>
-      <c r="C59" s="269"/>
-      <c r="D59" s="269"/>
-      <c r="E59" s="269"/>
-      <c r="F59" s="299"/>
+      <c r="A59" s="297"/>
+      <c r="B59" s="275"/>
+      <c r="C59" s="275"/>
+      <c r="D59" s="275"/>
+      <c r="E59" s="275"/>
+      <c r="F59" s="305"/>
       <c r="G59" s="26" t="s">
         <v>119</v>
       </c>
@@ -6214,17 +6270,17 @@
       <c r="J59" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K59" s="243"/>
-      <c r="L59" s="207"/>
+      <c r="K59" s="251"/>
+      <c r="L59" s="221"/>
       <c r="M59" s="12"/>
     </row>
     <row r="60" spans="1:13" ht="58.5" customHeight="1">
-      <c r="A60" s="291"/>
-      <c r="B60" s="269"/>
-      <c r="C60" s="269"/>
-      <c r="D60" s="269"/>
-      <c r="E60" s="269"/>
-      <c r="F60" s="299"/>
+      <c r="A60" s="297"/>
+      <c r="B60" s="275"/>
+      <c r="C60" s="275"/>
+      <c r="D60" s="275"/>
+      <c r="E60" s="275"/>
+      <c r="F60" s="305"/>
       <c r="G60" s="26" t="s">
         <v>121</v>
       </c>
@@ -6237,17 +6293,17 @@
       <c r="J60" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K60" s="243"/>
-      <c r="L60" s="207"/>
+      <c r="K60" s="251"/>
+      <c r="L60" s="221"/>
       <c r="M60" s="12"/>
     </row>
     <row r="61" spans="1:13" ht="58.5" customHeight="1">
-      <c r="A61" s="291"/>
-      <c r="B61" s="294"/>
-      <c r="C61" s="269"/>
-      <c r="D61" s="269"/>
-      <c r="E61" s="269"/>
-      <c r="F61" s="299"/>
+      <c r="A61" s="297"/>
+      <c r="B61" s="300"/>
+      <c r="C61" s="275"/>
+      <c r="D61" s="275"/>
+      <c r="E61" s="275"/>
+      <c r="F61" s="305"/>
       <c r="G61" s="26" t="s">
         <v>122</v>
       </c>
@@ -6260,17 +6316,17 @@
       <c r="J61" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="K61" s="243"/>
-      <c r="L61" s="207"/>
+      <c r="K61" s="251"/>
+      <c r="L61" s="221"/>
       <c r="M61" s="12"/>
     </row>
     <row r="62" spans="1:13" ht="58.5" customHeight="1">
-      <c r="A62" s="291"/>
-      <c r="B62" s="294"/>
-      <c r="C62" s="269"/>
-      <c r="D62" s="269"/>
-      <c r="E62" s="269"/>
-      <c r="F62" s="299"/>
+      <c r="A62" s="297"/>
+      <c r="B62" s="300"/>
+      <c r="C62" s="275"/>
+      <c r="D62" s="275"/>
+      <c r="E62" s="275"/>
+      <c r="F62" s="305"/>
       <c r="G62" s="26" t="s">
         <v>123</v>
       </c>
@@ -6283,17 +6339,17 @@
       <c r="J62" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="K62" s="243"/>
-      <c r="L62" s="207"/>
+      <c r="K62" s="251"/>
+      <c r="L62" s="221"/>
       <c r="M62" s="12"/>
     </row>
     <row r="63" spans="1:13" ht="58.5" customHeight="1">
-      <c r="A63" s="291"/>
-      <c r="B63" s="294"/>
-      <c r="C63" s="269"/>
-      <c r="D63" s="269"/>
-      <c r="E63" s="269"/>
-      <c r="F63" s="299"/>
+      <c r="A63" s="297"/>
+      <c r="B63" s="300"/>
+      <c r="C63" s="275"/>
+      <c r="D63" s="275"/>
+      <c r="E63" s="275"/>
+      <c r="F63" s="305"/>
       <c r="G63" s="26" t="s">
         <v>124</v>
       </c>
@@ -6306,142 +6362,142 @@
       <c r="J63" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="K63" s="243"/>
-      <c r="L63" s="207"/>
+      <c r="K63" s="251"/>
+      <c r="L63" s="221"/>
       <c r="M63" s="12"/>
     </row>
     <row r="64" spans="1:13" ht="58.5" customHeight="1">
-      <c r="A64" s="288">
+      <c r="A64" s="294">
         <v>18</v>
       </c>
-      <c r="B64" s="263">
+      <c r="B64" s="269">
         <v>45816</v>
       </c>
-      <c r="C64" s="206" t="s">
+      <c r="C64" s="220" t="s">
         <v>125</v>
       </c>
-      <c r="D64" s="206" t="s">
+      <c r="D64" s="220" t="s">
         <v>126</v>
       </c>
-      <c r="E64" s="206" t="s">
+      <c r="E64" s="220" t="s">
         <v>27</v>
       </c>
-      <c r="F64" s="227" t="s">
+      <c r="F64" s="235" t="s">
         <v>127</v>
       </c>
-      <c r="G64" s="297" t="s">
+      <c r="G64" s="303" t="s">
         <v>29</v>
       </c>
-      <c r="H64" s="298" t="s">
+      <c r="H64" s="304" t="s">
         <v>30</v>
       </c>
-      <c r="I64" s="278" t="s">
+      <c r="I64" s="284" t="s">
         <v>31</v>
       </c>
-      <c r="J64" s="241"/>
-      <c r="K64" s="237"/>
-      <c r="L64" s="207"/>
+      <c r="J64" s="249"/>
+      <c r="K64" s="245"/>
+      <c r="L64" s="221"/>
       <c r="M64" s="12"/>
     </row>
     <row r="65" spans="1:13" ht="58.5" customHeight="1">
-      <c r="A65" s="288"/>
-      <c r="B65" s="258"/>
-      <c r="C65" s="206"/>
-      <c r="D65" s="206"/>
-      <c r="E65" s="206"/>
-      <c r="F65" s="227"/>
-      <c r="G65" s="297"/>
-      <c r="H65" s="298"/>
-      <c r="I65" s="266"/>
-      <c r="J65" s="241"/>
-      <c r="K65" s="237"/>
-      <c r="L65" s="207"/>
+      <c r="A65" s="294"/>
+      <c r="B65" s="266"/>
+      <c r="C65" s="220"/>
+      <c r="D65" s="220"/>
+      <c r="E65" s="220"/>
+      <c r="F65" s="235"/>
+      <c r="G65" s="303"/>
+      <c r="H65" s="304"/>
+      <c r="I65" s="272"/>
+      <c r="J65" s="249"/>
+      <c r="K65" s="245"/>
+      <c r="L65" s="221"/>
       <c r="M65" s="12"/>
     </row>
     <row r="66" spans="1:13" ht="73.5" customHeight="1">
-      <c r="A66" s="288">
+      <c r="A66" s="294">
         <v>19</v>
       </c>
-      <c r="B66" s="263">
+      <c r="B66" s="269">
         <v>45817</v>
       </c>
-      <c r="C66" s="206" t="s">
+      <c r="C66" s="220" t="s">
         <v>32</v>
       </c>
-      <c r="D66" s="206" t="s">
+      <c r="D66" s="220" t="s">
         <v>128</v>
       </c>
-      <c r="E66" s="206" t="s">
+      <c r="E66" s="220" t="s">
         <v>78</v>
       </c>
-      <c r="F66" s="227" t="s">
+      <c r="F66" s="235" t="s">
         <v>129</v>
       </c>
-      <c r="G66" s="296" t="s">
+      <c r="G66" s="302" t="s">
         <v>130</v>
       </c>
       <c r="H66" s="29" t="s">
         <v>131</v>
       </c>
-      <c r="I66" s="254"/>
-      <c r="J66" s="272"/>
-      <c r="K66" s="238"/>
-      <c r="L66" s="239" t="s">
+      <c r="I66" s="262"/>
+      <c r="J66" s="278"/>
+      <c r="K66" s="246"/>
+      <c r="L66" s="247" t="s">
         <v>132</v>
       </c>
       <c r="M66" s="12"/>
     </row>
     <row r="67" spans="1:13" ht="99.75" customHeight="1">
-      <c r="A67" s="288"/>
-      <c r="B67" s="263"/>
-      <c r="C67" s="206"/>
-      <c r="D67" s="206"/>
-      <c r="E67" s="206"/>
-      <c r="F67" s="227"/>
-      <c r="G67" s="296"/>
+      <c r="A67" s="294"/>
+      <c r="B67" s="269"/>
+      <c r="C67" s="220"/>
+      <c r="D67" s="220"/>
+      <c r="E67" s="220"/>
+      <c r="F67" s="235"/>
+      <c r="G67" s="302"/>
       <c r="H67" s="29" t="s">
         <v>133</v>
       </c>
-      <c r="I67" s="254"/>
-      <c r="J67" s="272"/>
-      <c r="K67" s="238"/>
-      <c r="L67" s="239"/>
+      <c r="I67" s="262"/>
+      <c r="J67" s="278"/>
+      <c r="K67" s="246"/>
+      <c r="L67" s="247"/>
       <c r="M67" s="12"/>
     </row>
     <row r="68" spans="1:13" ht="73.5" customHeight="1">
-      <c r="A68" s="288"/>
-      <c r="B68" s="258"/>
-      <c r="C68" s="206"/>
-      <c r="D68" s="206"/>
-      <c r="E68" s="206"/>
-      <c r="F68" s="227"/>
-      <c r="G68" s="296"/>
+      <c r="A68" s="294"/>
+      <c r="B68" s="266"/>
+      <c r="C68" s="220"/>
+      <c r="D68" s="220"/>
+      <c r="E68" s="220"/>
+      <c r="F68" s="235"/>
+      <c r="G68" s="302"/>
       <c r="H68" s="29" t="s">
         <v>131</v>
       </c>
-      <c r="I68" s="254"/>
-      <c r="J68" s="272"/>
-      <c r="K68" s="238"/>
-      <c r="L68" s="239"/>
+      <c r="I68" s="262"/>
+      <c r="J68" s="278"/>
+      <c r="K68" s="246"/>
+      <c r="L68" s="247"/>
       <c r="M68" s="12"/>
     </row>
     <row r="69" spans="1:13" ht="63" customHeight="1">
-      <c r="A69" s="288">
+      <c r="A69" s="294">
         <v>20</v>
       </c>
-      <c r="B69" s="226">
+      <c r="B69" s="234">
         <v>45818</v>
       </c>
-      <c r="C69" s="226" t="s">
+      <c r="C69" s="234" t="s">
         <v>32</v>
       </c>
-      <c r="D69" s="226" t="s">
+      <c r="D69" s="234" t="s">
         <v>134</v>
       </c>
-      <c r="E69" s="226" t="s">
+      <c r="E69" s="234" t="s">
         <v>27</v>
       </c>
-      <c r="F69" s="227" t="s">
+      <c r="F69" s="235" t="s">
         <v>135</v>
       </c>
       <c r="G69" s="31" t="s">
@@ -6456,21 +6512,21 @@
       <c r="J69" s="77" t="s">
         <v>20</v>
       </c>
-      <c r="K69" s="237" t="s">
+      <c r="K69" s="245" t="s">
         <v>22</v>
       </c>
-      <c r="L69" s="207" t="s">
+      <c r="L69" s="221" t="s">
         <v>22</v>
       </c>
       <c r="M69" s="12"/>
     </row>
     <row r="70" spans="1:13" ht="90.95" customHeight="1">
-      <c r="A70" s="288"/>
-      <c r="B70" s="206"/>
-      <c r="C70" s="226"/>
-      <c r="D70" s="226"/>
-      <c r="E70" s="226"/>
-      <c r="F70" s="227"/>
+      <c r="A70" s="294"/>
+      <c r="B70" s="220"/>
+      <c r="C70" s="234"/>
+      <c r="D70" s="234"/>
+      <c r="E70" s="234"/>
+      <c r="F70" s="235"/>
       <c r="G70" s="31" t="s">
         <v>72</v>
       </c>
@@ -6483,27 +6539,27 @@
       <c r="J70" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="K70" s="237"/>
-      <c r="L70" s="207"/>
+      <c r="K70" s="245"/>
+      <c r="L70" s="221"/>
       <c r="M70" s="12"/>
     </row>
     <row r="71" spans="1:13" ht="123.95" customHeight="1">
-      <c r="A71" s="288">
+      <c r="A71" s="294">
         <v>21</v>
       </c>
-      <c r="B71" s="208">
+      <c r="B71" s="222">
         <v>45821</v>
       </c>
-      <c r="C71" s="208" t="s">
+      <c r="C71" s="222" t="s">
         <v>32</v>
       </c>
-      <c r="D71" s="226" t="s">
+      <c r="D71" s="234" t="s">
         <v>138</v>
       </c>
-      <c r="E71" s="226" t="s">
+      <c r="E71" s="234" t="s">
         <v>27</v>
       </c>
-      <c r="F71" s="227" t="s">
+      <c r="F71" s="235" t="s">
         <v>139</v>
       </c>
       <c r="G71" s="31" t="s">
@@ -6518,21 +6574,21 @@
       <c r="J71" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="K71" s="224" t="s">
+      <c r="K71" s="232" t="s">
         <v>22</v>
       </c>
-      <c r="L71" s="207" t="s">
+      <c r="L71" s="221" t="s">
         <v>22</v>
       </c>
       <c r="M71" s="12"/>
     </row>
     <row r="72" spans="1:13" ht="78.599999999999994" customHeight="1">
-      <c r="A72" s="288"/>
-      <c r="B72" s="208"/>
-      <c r="C72" s="208"/>
-      <c r="D72" s="226"/>
-      <c r="E72" s="226"/>
-      <c r="F72" s="227"/>
+      <c r="A72" s="294"/>
+      <c r="B72" s="222"/>
+      <c r="C72" s="222"/>
+      <c r="D72" s="234"/>
+      <c r="E72" s="234"/>
+      <c r="F72" s="235"/>
       <c r="G72" s="31" t="s">
         <v>142</v>
       </c>
@@ -6545,17 +6601,17 @@
       <c r="J72" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="K72" s="224"/>
-      <c r="L72" s="207"/>
+      <c r="K72" s="232"/>
+      <c r="L72" s="221"/>
       <c r="M72" s="12"/>
     </row>
     <row r="73" spans="1:13" ht="47.1" customHeight="1">
-      <c r="A73" s="288"/>
-      <c r="B73" s="208"/>
-      <c r="C73" s="208"/>
-      <c r="D73" s="226"/>
-      <c r="E73" s="226"/>
-      <c r="F73" s="227"/>
+      <c r="A73" s="294"/>
+      <c r="B73" s="222"/>
+      <c r="C73" s="222"/>
+      <c r="D73" s="234"/>
+      <c r="E73" s="234"/>
+      <c r="F73" s="235"/>
       <c r="G73" s="31" t="s">
         <v>143</v>
       </c>
@@ -6568,27 +6624,27 @@
       <c r="J73" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="K73" s="224"/>
-      <c r="L73" s="207"/>
+      <c r="K73" s="232"/>
+      <c r="L73" s="221"/>
       <c r="M73" s="12"/>
     </row>
     <row r="74" spans="1:13" ht="45" customHeight="1">
-      <c r="A74" s="288">
+      <c r="A74" s="294">
         <v>22</v>
       </c>
-      <c r="B74" s="226">
+      <c r="B74" s="234">
         <v>45829</v>
       </c>
-      <c r="C74" s="226" t="s">
+      <c r="C74" s="234" t="s">
         <v>14</v>
       </c>
-      <c r="D74" s="226" t="s">
+      <c r="D74" s="234" t="s">
         <v>145</v>
       </c>
-      <c r="E74" s="226" t="s">
+      <c r="E74" s="234" t="s">
         <v>27</v>
       </c>
-      <c r="F74" s="227" t="s">
+      <c r="F74" s="235" t="s">
         <v>146</v>
       </c>
       <c r="G74" s="33" t="s">
@@ -6603,21 +6659,21 @@
       <c r="J74" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="K74" s="224" t="s">
+      <c r="K74" s="232" t="s">
         <v>22</v>
       </c>
-      <c r="L74" s="207" t="s">
+      <c r="L74" s="221" t="s">
         <v>22</v>
       </c>
       <c r="M74" s="12"/>
     </row>
     <row r="75" spans="1:13" ht="67.5" customHeight="1">
-      <c r="A75" s="288"/>
-      <c r="B75" s="206"/>
-      <c r="C75" s="226"/>
-      <c r="D75" s="226"/>
-      <c r="E75" s="226"/>
-      <c r="F75" s="227"/>
+      <c r="A75" s="294"/>
+      <c r="B75" s="220"/>
+      <c r="C75" s="234"/>
+      <c r="D75" s="234"/>
+      <c r="E75" s="234"/>
+      <c r="F75" s="235"/>
       <c r="G75" s="31" t="s">
         <v>149</v>
       </c>
@@ -6630,27 +6686,27 @@
       <c r="J75" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="K75" s="224"/>
-      <c r="L75" s="207"/>
+      <c r="K75" s="232"/>
+      <c r="L75" s="221"/>
       <c r="M75" s="12"/>
     </row>
     <row r="76" spans="1:13" ht="101.45" customHeight="1">
-      <c r="A76" s="288">
+      <c r="A76" s="294">
         <v>23</v>
       </c>
-      <c r="B76" s="226">
+      <c r="B76" s="234">
         <v>45838</v>
       </c>
-      <c r="C76" s="226" t="s">
+      <c r="C76" s="234" t="s">
         <v>32</v>
       </c>
-      <c r="D76" s="226" t="s">
+      <c r="D76" s="234" t="s">
         <v>151</v>
       </c>
-      <c r="E76" s="226" t="s">
+      <c r="E76" s="234" t="s">
         <v>27</v>
       </c>
-      <c r="F76" s="227" t="s">
+      <c r="F76" s="235" t="s">
         <v>152</v>
       </c>
       <c r="G76" s="31" t="s">
@@ -6665,21 +6721,21 @@
       <c r="J76" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="K76" s="224" t="s">
+      <c r="K76" s="232" t="s">
         <v>22</v>
       </c>
-      <c r="L76" s="207" t="s">
+      <c r="L76" s="221" t="s">
         <v>22</v>
       </c>
       <c r="M76" s="12"/>
     </row>
     <row r="77" spans="1:13" ht="67.5" customHeight="1">
-      <c r="A77" s="288"/>
-      <c r="B77" s="206"/>
-      <c r="C77" s="226"/>
-      <c r="D77" s="226"/>
-      <c r="E77" s="226"/>
-      <c r="F77" s="227"/>
+      <c r="A77" s="294"/>
+      <c r="B77" s="220"/>
+      <c r="C77" s="234"/>
+      <c r="D77" s="234"/>
+      <c r="E77" s="234"/>
+      <c r="F77" s="235"/>
       <c r="G77" s="31" t="s">
         <v>154</v>
       </c>
@@ -6692,27 +6748,27 @@
       <c r="J77" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="K77" s="224"/>
-      <c r="L77" s="207"/>
+      <c r="K77" s="232"/>
+      <c r="L77" s="221"/>
       <c r="M77" s="12"/>
     </row>
     <row r="78" spans="1:13" ht="321.95" customHeight="1">
-      <c r="A78" s="288">
+      <c r="A78" s="294">
         <v>24</v>
       </c>
-      <c r="B78" s="226">
+      <c r="B78" s="234">
         <v>45839</v>
       </c>
-      <c r="C78" s="226" t="s">
+      <c r="C78" s="234" t="s">
         <v>32</v>
       </c>
-      <c r="D78" s="226" t="s">
+      <c r="D78" s="234" t="s">
         <v>156</v>
       </c>
-      <c r="E78" s="226" t="s">
+      <c r="E78" s="234" t="s">
         <v>27</v>
       </c>
-      <c r="F78" s="227" t="s">
+      <c r="F78" s="235" t="s">
         <v>157</v>
       </c>
       <c r="G78" s="31" t="s">
@@ -6727,21 +6783,21 @@
       <c r="J78" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="K78" s="238" t="s">
+      <c r="K78" s="246" t="s">
         <v>22</v>
       </c>
-      <c r="L78" s="207" t="s">
+      <c r="L78" s="221" t="s">
         <v>22</v>
       </c>
       <c r="M78" s="12"/>
     </row>
     <row r="79" spans="1:13" ht="43.5" customHeight="1">
-      <c r="A79" s="288"/>
-      <c r="B79" s="226"/>
-      <c r="C79" s="226"/>
-      <c r="D79" s="226"/>
-      <c r="E79" s="226"/>
-      <c r="F79" s="227"/>
+      <c r="A79" s="294"/>
+      <c r="B79" s="234"/>
+      <c r="C79" s="234"/>
+      <c r="D79" s="234"/>
+      <c r="E79" s="234"/>
+      <c r="F79" s="235"/>
       <c r="G79" s="33" t="s">
         <v>160</v>
       </c>
@@ -6754,17 +6810,17 @@
       <c r="J79" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="K79" s="238"/>
-      <c r="L79" s="207"/>
+      <c r="K79" s="246"/>
+      <c r="L79" s="221"/>
       <c r="M79" s="12"/>
     </row>
     <row r="80" spans="1:13" ht="39.6" customHeight="1">
-      <c r="A80" s="288"/>
-      <c r="B80" s="226"/>
-      <c r="C80" s="226"/>
-      <c r="D80" s="226"/>
-      <c r="E80" s="226"/>
-      <c r="F80" s="227"/>
+      <c r="A80" s="294"/>
+      <c r="B80" s="234"/>
+      <c r="C80" s="234"/>
+      <c r="D80" s="234"/>
+      <c r="E80" s="234"/>
+      <c r="F80" s="235"/>
       <c r="G80" s="31" t="s">
         <v>162</v>
       </c>
@@ -6777,17 +6833,17 @@
       <c r="J80" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="K80" s="238"/>
-      <c r="L80" s="207"/>
+      <c r="K80" s="246"/>
+      <c r="L80" s="221"/>
       <c r="M80" s="12"/>
     </row>
     <row r="81" spans="1:13" ht="87.6" customHeight="1">
-      <c r="A81" s="288"/>
-      <c r="B81" s="206"/>
-      <c r="C81" s="226"/>
-      <c r="D81" s="226"/>
-      <c r="E81" s="226"/>
-      <c r="F81" s="227"/>
+      <c r="A81" s="294"/>
+      <c r="B81" s="220"/>
+      <c r="C81" s="234"/>
+      <c r="D81" s="234"/>
+      <c r="E81" s="234"/>
+      <c r="F81" s="235"/>
       <c r="G81" s="31" t="s">
         <v>163</v>
       </c>
@@ -6800,25 +6856,25 @@
       <c r="J81" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K81" s="238"/>
-      <c r="L81" s="207"/>
+      <c r="K81" s="246"/>
+      <c r="L81" s="221"/>
       <c r="M81" s="12"/>
     </row>
     <row r="82" spans="1:13" ht="76.5" customHeight="1">
-      <c r="A82" s="207">
+      <c r="A82" s="221">
         <v>25</v>
       </c>
-      <c r="B82" s="226">
+      <c r="B82" s="234">
         <v>45850</v>
       </c>
-      <c r="C82" s="226"/>
-      <c r="D82" s="226" t="s">
+      <c r="C82" s="234"/>
+      <c r="D82" s="234" t="s">
         <v>165</v>
       </c>
-      <c r="E82" s="226" t="s">
+      <c r="E82" s="234" t="s">
         <v>27</v>
       </c>
-      <c r="F82" s="227" t="s">
+      <c r="F82" s="235" t="s">
         <v>166</v>
       </c>
       <c r="G82" s="31" t="s">
@@ -6833,21 +6889,21 @@
       <c r="J82" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K82" s="224" t="s">
+      <c r="K82" s="232" t="s">
         <v>22</v>
       </c>
-      <c r="L82" s="207" t="s">
+      <c r="L82" s="221" t="s">
         <v>22</v>
       </c>
       <c r="M82" s="12"/>
     </row>
     <row r="83" spans="1:13" ht="76.5" customHeight="1">
-      <c r="A83" s="207"/>
-      <c r="B83" s="226"/>
-      <c r="C83" s="226"/>
-      <c r="D83" s="226"/>
-      <c r="E83" s="226"/>
-      <c r="F83" s="227"/>
+      <c r="A83" s="221"/>
+      <c r="B83" s="234"/>
+      <c r="C83" s="234"/>
+      <c r="D83" s="234"/>
+      <c r="E83" s="234"/>
+      <c r="F83" s="235"/>
       <c r="G83" s="31" t="s">
         <v>169</v>
       </c>
@@ -6860,17 +6916,17 @@
       <c r="J83" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K83" s="224"/>
-      <c r="L83" s="207"/>
+      <c r="K83" s="232"/>
+      <c r="L83" s="221"/>
       <c r="M83" s="12"/>
     </row>
     <row r="84" spans="1:13" ht="76.5" customHeight="1">
-      <c r="A84" s="207"/>
-      <c r="B84" s="206"/>
-      <c r="C84" s="226"/>
-      <c r="D84" s="226"/>
-      <c r="E84" s="226"/>
-      <c r="F84" s="227"/>
+      <c r="A84" s="221"/>
+      <c r="B84" s="220"/>
+      <c r="C84" s="234"/>
+      <c r="D84" s="234"/>
+      <c r="E84" s="234"/>
+      <c r="F84" s="235"/>
       <c r="G84" s="31" t="s">
         <v>171</v>
       </c>
@@ -6883,25 +6939,25 @@
       <c r="J84" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K84" s="224"/>
-      <c r="L84" s="207"/>
+      <c r="K84" s="232"/>
+      <c r="L84" s="221"/>
       <c r="M84" s="12"/>
     </row>
     <row r="85" spans="1:13" ht="84.75" customHeight="1">
-      <c r="A85" s="207">
+      <c r="A85" s="221">
         <v>26</v>
       </c>
-      <c r="B85" s="226">
+      <c r="B85" s="234">
         <v>45856</v>
       </c>
-      <c r="C85" s="226"/>
-      <c r="D85" s="226" t="s">
+      <c r="C85" s="234"/>
+      <c r="D85" s="234" t="s">
         <v>172</v>
       </c>
-      <c r="E85" s="226" t="s">
+      <c r="E85" s="234" t="s">
         <v>27</v>
       </c>
-      <c r="F85" s="227" t="s">
+      <c r="F85" s="235" t="s">
         <v>173</v>
       </c>
       <c r="G85" s="31" t="s">
@@ -6916,21 +6972,21 @@
       <c r="J85" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="K85" s="238" t="s">
+      <c r="K85" s="246" t="s">
         <v>22</v>
       </c>
-      <c r="L85" s="207" t="s">
+      <c r="L85" s="221" t="s">
         <v>22</v>
       </c>
       <c r="M85" s="12"/>
     </row>
     <row r="86" spans="1:13" ht="84.75" customHeight="1">
-      <c r="A86" s="207"/>
-      <c r="B86" s="206"/>
-      <c r="C86" s="226"/>
-      <c r="D86" s="226"/>
-      <c r="E86" s="226"/>
-      <c r="F86" s="227"/>
+      <c r="A86" s="221"/>
+      <c r="B86" s="220"/>
+      <c r="C86" s="234"/>
+      <c r="D86" s="234"/>
+      <c r="E86" s="234"/>
+      <c r="F86" s="235"/>
       <c r="G86" s="36" t="s">
         <v>171</v>
       </c>
@@ -6943,67 +6999,67 @@
       <c r="J86" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="K86" s="238"/>
-      <c r="L86" s="207"/>
+      <c r="K86" s="246"/>
+      <c r="L86" s="221"/>
       <c r="M86" s="12"/>
     </row>
     <row r="87" spans="1:13" ht="76.5" customHeight="1">
-      <c r="A87" s="207">
+      <c r="A87" s="221">
         <v>27</v>
       </c>
-      <c r="B87" s="263">
+      <c r="B87" s="269">
         <v>45860</v>
       </c>
-      <c r="C87" s="226"/>
-      <c r="D87" s="300" t="s">
+      <c r="C87" s="234"/>
+      <c r="D87" s="306" t="s">
         <v>175</v>
       </c>
-      <c r="E87" s="226" t="s">
+      <c r="E87" s="234" t="s">
         <v>27</v>
       </c>
-      <c r="F87" s="299" t="s">
+      <c r="F87" s="305" t="s">
         <v>176</v>
       </c>
-      <c r="G87" s="252" t="s">
+      <c r="G87" s="260" t="s">
         <v>177</v>
       </c>
-      <c r="H87" s="253" t="s">
+      <c r="H87" s="261" t="s">
         <v>30</v>
       </c>
-      <c r="I87" s="251" t="s">
+      <c r="I87" s="259" t="s">
         <v>30</v>
       </c>
-      <c r="J87" s="240" t="s">
+      <c r="J87" s="248" t="s">
         <v>20</v>
       </c>
-      <c r="K87" s="242" t="s">
+      <c r="K87" s="250" t="s">
         <v>178</v>
       </c>
-      <c r="L87" s="207"/>
+      <c r="L87" s="221"/>
       <c r="M87" s="12"/>
     </row>
     <row r="88" spans="1:13" ht="76.5" customHeight="1">
-      <c r="A88" s="207"/>
-      <c r="B88" s="263"/>
-      <c r="C88" s="226"/>
-      <c r="D88" s="226"/>
-      <c r="E88" s="226"/>
-      <c r="F88" s="299"/>
-      <c r="G88" s="252"/>
-      <c r="H88" s="253"/>
-      <c r="I88" s="251"/>
-      <c r="J88" s="240"/>
-      <c r="K88" s="242"/>
-      <c r="L88" s="207"/>
+      <c r="A88" s="221"/>
+      <c r="B88" s="269"/>
+      <c r="C88" s="234"/>
+      <c r="D88" s="234"/>
+      <c r="E88" s="234"/>
+      <c r="F88" s="305"/>
+      <c r="G88" s="260"/>
+      <c r="H88" s="261"/>
+      <c r="I88" s="259"/>
+      <c r="J88" s="248"/>
+      <c r="K88" s="250"/>
+      <c r="L88" s="221"/>
       <c r="M88" s="12"/>
     </row>
     <row r="89" spans="1:13" ht="76.5" customHeight="1">
-      <c r="A89" s="207"/>
-      <c r="B89" s="263"/>
-      <c r="C89" s="226"/>
-      <c r="D89" s="226"/>
-      <c r="E89" s="226"/>
-      <c r="F89" s="299"/>
+      <c r="A89" s="221"/>
+      <c r="B89" s="269"/>
+      <c r="C89" s="234"/>
+      <c r="D89" s="234"/>
+      <c r="E89" s="234"/>
+      <c r="F89" s="305"/>
       <c r="G89" s="130" t="s">
         <v>179</v>
       </c>
@@ -7014,45 +7070,45 @@
       <c r="J89" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="K89" s="242"/>
-      <c r="L89" s="207"/>
+      <c r="K89" s="250"/>
+      <c r="L89" s="221"/>
       <c r="M89" s="12"/>
     </row>
     <row r="90" spans="1:13" ht="76.5" customHeight="1">
-      <c r="A90" s="207">
+      <c r="A90" s="221">
         <v>28</v>
       </c>
-      <c r="B90" s="226">
+      <c r="B90" s="234">
         <v>45870</v>
       </c>
-      <c r="C90" s="226" t="s">
+      <c r="C90" s="234" t="s">
         <v>125</v>
       </c>
-      <c r="D90" s="226" t="s">
+      <c r="D90" s="234" t="s">
         <v>181</v>
       </c>
-      <c r="E90" s="226" t="s">
+      <c r="E90" s="234" t="s">
         <v>182</v>
       </c>
-      <c r="F90" s="227" t="s">
+      <c r="F90" s="235" t="s">
         <v>183</v>
       </c>
-      <c r="G90" s="273" t="s">
+      <c r="G90" s="279" t="s">
         <v>184</v>
       </c>
-      <c r="H90" s="244" t="s">
+      <c r="H90" s="252" t="s">
         <v>180</v>
       </c>
-      <c r="I90" s="266">
+      <c r="I90" s="272">
         <v>45900</v>
       </c>
-      <c r="J90" s="267" t="s">
+      <c r="J90" s="273" t="s">
         <v>20</v>
       </c>
-      <c r="K90" s="249" t="s">
+      <c r="K90" s="257" t="s">
         <v>20</v>
       </c>
-      <c r="L90" s="207" t="s">
+      <c r="L90" s="221" t="s">
         <v>20</v>
       </c>
       <c r="M90" s="12" t="s">
@@ -7060,37 +7116,37 @@
       </c>
     </row>
     <row r="91" spans="1:13" ht="76.5" customHeight="1">
-      <c r="A91" s="207"/>
-      <c r="B91" s="226"/>
-      <c r="C91" s="226"/>
-      <c r="D91" s="226"/>
-      <c r="E91" s="226"/>
-      <c r="F91" s="227"/>
-      <c r="G91" s="274"/>
-      <c r="H91" s="245"/>
-      <c r="I91" s="267"/>
-      <c r="J91" s="267"/>
-      <c r="K91" s="249"/>
-      <c r="L91" s="207"/>
+      <c r="A91" s="221"/>
+      <c r="B91" s="234"/>
+      <c r="C91" s="234"/>
+      <c r="D91" s="234"/>
+      <c r="E91" s="234"/>
+      <c r="F91" s="235"/>
+      <c r="G91" s="280"/>
+      <c r="H91" s="253"/>
+      <c r="I91" s="273"/>
+      <c r="J91" s="273"/>
+      <c r="K91" s="257"/>
+      <c r="L91" s="221"/>
       <c r="M91" s="12"/>
     </row>
     <row r="92" spans="1:13" ht="66" customHeight="1">
-      <c r="A92" s="207">
+      <c r="A92" s="221">
         <v>29</v>
       </c>
-      <c r="B92" s="226">
+      <c r="B92" s="234">
         <v>45879</v>
       </c>
-      <c r="C92" s="226" t="s">
+      <c r="C92" s="234" t="s">
         <v>125</v>
       </c>
-      <c r="D92" s="226" t="s">
+      <c r="D92" s="234" t="s">
         <v>186</v>
       </c>
-      <c r="E92" s="226" t="s">
+      <c r="E92" s="234" t="s">
         <v>182</v>
       </c>
-      <c r="F92" s="227" t="s">
+      <c r="F92" s="235" t="s">
         <v>187</v>
       </c>
       <c r="G92" s="131" t="s">
@@ -7105,10 +7161,10 @@
       <c r="J92" s="74" t="s">
         <v>20</v>
       </c>
-      <c r="K92" s="250" t="s">
+      <c r="K92" s="258" t="s">
         <v>20</v>
       </c>
-      <c r="L92" s="207" t="s">
+      <c r="L92" s="221" t="s">
         <v>20</v>
       </c>
       <c r="M92" s="12" t="s">
@@ -7116,12 +7172,12 @@
       </c>
     </row>
     <row r="93" spans="1:13" ht="66" customHeight="1">
-      <c r="A93" s="207"/>
-      <c r="B93" s="226"/>
-      <c r="C93" s="226"/>
-      <c r="D93" s="226"/>
-      <c r="E93" s="226"/>
-      <c r="F93" s="227"/>
+      <c r="A93" s="221"/>
+      <c r="B93" s="234"/>
+      <c r="C93" s="234"/>
+      <c r="D93" s="234"/>
+      <c r="E93" s="234"/>
+      <c r="F93" s="235"/>
       <c r="G93" s="131" t="s">
         <v>190</v>
       </c>
@@ -7134,17 +7190,17 @@
       <c r="J93" s="74" t="s">
         <v>20</v>
       </c>
-      <c r="K93" s="250"/>
-      <c r="L93" s="207"/>
+      <c r="K93" s="258"/>
+      <c r="L93" s="221"/>
       <c r="M93" s="12"/>
     </row>
     <row r="94" spans="1:13" ht="66" customHeight="1">
-      <c r="A94" s="207"/>
-      <c r="B94" s="226"/>
-      <c r="C94" s="226"/>
-      <c r="D94" s="226"/>
-      <c r="E94" s="226"/>
-      <c r="F94" s="227"/>
+      <c r="A94" s="221"/>
+      <c r="B94" s="234"/>
+      <c r="C94" s="234"/>
+      <c r="D94" s="234"/>
+      <c r="E94" s="234"/>
+      <c r="F94" s="235"/>
       <c r="G94" s="132" t="s">
         <v>192</v>
       </c>
@@ -7157,17 +7213,17 @@
       <c r="J94" s="77" t="s">
         <v>20</v>
       </c>
-      <c r="K94" s="250"/>
-      <c r="L94" s="207"/>
+      <c r="K94" s="258"/>
+      <c r="L94" s="221"/>
       <c r="M94" s="12"/>
     </row>
     <row r="95" spans="1:13" ht="66" customHeight="1">
-      <c r="A95" s="207"/>
-      <c r="B95" s="226"/>
-      <c r="C95" s="226"/>
-      <c r="D95" s="226"/>
-      <c r="E95" s="226"/>
-      <c r="F95" s="227"/>
+      <c r="A95" s="221"/>
+      <c r="B95" s="234"/>
+      <c r="C95" s="234"/>
+      <c r="D95" s="234"/>
+      <c r="E95" s="234"/>
+      <c r="F95" s="235"/>
       <c r="G95" s="132" t="s">
         <v>193</v>
       </c>
@@ -7180,17 +7236,17 @@
       <c r="J95" s="77" t="s">
         <v>20</v>
       </c>
-      <c r="K95" s="250"/>
-      <c r="L95" s="207"/>
+      <c r="K95" s="258"/>
+      <c r="L95" s="221"/>
       <c r="M95" s="12"/>
     </row>
     <row r="96" spans="1:13" ht="66" customHeight="1">
-      <c r="A96" s="207"/>
-      <c r="B96" s="226"/>
-      <c r="C96" s="226"/>
-      <c r="D96" s="226"/>
-      <c r="E96" s="226"/>
-      <c r="F96" s="227"/>
+      <c r="A96" s="221"/>
+      <c r="B96" s="234"/>
+      <c r="C96" s="234"/>
+      <c r="D96" s="234"/>
+      <c r="E96" s="234"/>
+      <c r="F96" s="235"/>
       <c r="G96" s="132" t="s">
         <v>194</v>
       </c>
@@ -7203,17 +7259,17 @@
       <c r="J96" s="77" t="s">
         <v>20</v>
       </c>
-      <c r="K96" s="250"/>
-      <c r="L96" s="207"/>
+      <c r="K96" s="258"/>
+      <c r="L96" s="221"/>
       <c r="M96" s="12"/>
     </row>
     <row r="97" spans="1:13" ht="66" customHeight="1">
-      <c r="A97" s="207"/>
-      <c r="B97" s="226"/>
-      <c r="C97" s="226"/>
-      <c r="D97" s="226"/>
-      <c r="E97" s="226"/>
-      <c r="F97" s="227"/>
+      <c r="A97" s="221"/>
+      <c r="B97" s="234"/>
+      <c r="C97" s="234"/>
+      <c r="D97" s="234"/>
+      <c r="E97" s="234"/>
+      <c r="F97" s="235"/>
       <c r="G97" s="132" t="s">
         <v>195</v>
       </c>
@@ -7226,201 +7282,201 @@
       <c r="J97" s="79" t="s">
         <v>196</v>
       </c>
-      <c r="K97" s="250"/>
-      <c r="L97" s="207"/>
+      <c r="K97" s="258"/>
+      <c r="L97" s="221"/>
       <c r="M97" s="12"/>
     </row>
     <row r="98" spans="1:13" ht="76.5" customHeight="1">
-      <c r="A98" s="207">
+      <c r="A98" s="221">
         <v>30</v>
       </c>
-      <c r="B98" s="226">
+      <c r="B98" s="234">
         <v>45885</v>
       </c>
-      <c r="C98" s="226" t="s">
+      <c r="C98" s="234" t="s">
         <v>197</v>
       </c>
-      <c r="D98" s="226" t="s">
+      <c r="D98" s="234" t="s">
         <v>198</v>
       </c>
-      <c r="E98" s="226" t="s">
+      <c r="E98" s="234" t="s">
         <v>199</v>
       </c>
-      <c r="F98" s="227" t="s">
+      <c r="F98" s="235" t="s">
         <v>200</v>
       </c>
       <c r="G98" s="132" t="s">
         <v>201</v>
       </c>
-      <c r="H98" s="265" t="s">
+      <c r="H98" s="271" t="s">
         <v>202</v>
       </c>
-      <c r="I98" s="264">
+      <c r="I98" s="270">
         <v>45886</v>
       </c>
-      <c r="J98" s="241" t="s">
+      <c r="J98" s="249" t="s">
         <v>20</v>
       </c>
-      <c r="K98" s="237" t="s">
+      <c r="K98" s="245" t="s">
         <v>178</v>
       </c>
-      <c r="L98" s="207" t="s">
+      <c r="L98" s="221" t="s">
         <v>178</v>
       </c>
       <c r="M98" s="12"/>
     </row>
     <row r="99" spans="1:13" ht="76.5" customHeight="1">
-      <c r="A99" s="207"/>
-      <c r="B99" s="226"/>
-      <c r="C99" s="226"/>
-      <c r="D99" s="226"/>
-      <c r="E99" s="226"/>
-      <c r="F99" s="227"/>
+      <c r="A99" s="221"/>
+      <c r="B99" s="234"/>
+      <c r="C99" s="234"/>
+      <c r="D99" s="234"/>
+      <c r="E99" s="234"/>
+      <c r="F99" s="235"/>
       <c r="G99" s="132" t="s">
         <v>203</v>
       </c>
-      <c r="H99" s="265"/>
-      <c r="I99" s="265"/>
-      <c r="J99" s="241"/>
-      <c r="K99" s="237"/>
-      <c r="L99" s="207"/>
+      <c r="H99" s="271"/>
+      <c r="I99" s="271"/>
+      <c r="J99" s="249"/>
+      <c r="K99" s="245"/>
+      <c r="L99" s="221"/>
       <c r="M99" s="12"/>
     </row>
     <row r="100" spans="1:13" ht="76.5" customHeight="1">
-      <c r="A100" s="207"/>
-      <c r="B100" s="226"/>
-      <c r="C100" s="226"/>
-      <c r="D100" s="226"/>
-      <c r="E100" s="226"/>
-      <c r="F100" s="227"/>
+      <c r="A100" s="221"/>
+      <c r="B100" s="234"/>
+      <c r="C100" s="234"/>
+      <c r="D100" s="234"/>
+      <c r="E100" s="234"/>
+      <c r="F100" s="235"/>
       <c r="G100" s="132" t="s">
         <v>204</v>
       </c>
-      <c r="H100" s="265"/>
-      <c r="I100" s="265"/>
-      <c r="J100" s="241"/>
-      <c r="K100" s="237"/>
-      <c r="L100" s="207"/>
+      <c r="H100" s="271"/>
+      <c r="I100" s="271"/>
+      <c r="J100" s="249"/>
+      <c r="K100" s="245"/>
+      <c r="L100" s="221"/>
       <c r="M100" s="12"/>
     </row>
     <row r="101" spans="1:13" ht="76.5" customHeight="1">
-      <c r="A101" s="207"/>
-      <c r="B101" s="226"/>
-      <c r="C101" s="226"/>
-      <c r="D101" s="226"/>
-      <c r="E101" s="226"/>
-      <c r="F101" s="227"/>
+      <c r="A101" s="221"/>
+      <c r="B101" s="234"/>
+      <c r="C101" s="234"/>
+      <c r="D101" s="234"/>
+      <c r="E101" s="234"/>
+      <c r="F101" s="235"/>
       <c r="G101" s="132" t="s">
         <v>205</v>
       </c>
-      <c r="H101" s="265"/>
-      <c r="I101" s="265"/>
-      <c r="J101" s="241"/>
-      <c r="K101" s="237"/>
-      <c r="L101" s="207"/>
+      <c r="H101" s="271"/>
+      <c r="I101" s="271"/>
+      <c r="J101" s="249"/>
+      <c r="K101" s="245"/>
+      <c r="L101" s="221"/>
       <c r="M101" s="12"/>
     </row>
     <row r="102" spans="1:13" ht="76.5" customHeight="1">
-      <c r="A102" s="207"/>
-      <c r="B102" s="226"/>
-      <c r="C102" s="226"/>
-      <c r="D102" s="226"/>
-      <c r="E102" s="226"/>
-      <c r="F102" s="227"/>
+      <c r="A102" s="221"/>
+      <c r="B102" s="234"/>
+      <c r="C102" s="234"/>
+      <c r="D102" s="234"/>
+      <c r="E102" s="234"/>
+      <c r="F102" s="235"/>
       <c r="G102" s="132" t="s">
         <v>206</v>
       </c>
-      <c r="H102" s="265"/>
-      <c r="I102" s="265"/>
-      <c r="J102" s="241"/>
-      <c r="K102" s="237"/>
-      <c r="L102" s="207"/>
+      <c r="H102" s="271"/>
+      <c r="I102" s="271"/>
+      <c r="J102" s="249"/>
+      <c r="K102" s="245"/>
+      <c r="L102" s="221"/>
       <c r="M102" s="12"/>
     </row>
     <row r="103" spans="1:13" ht="76.5" customHeight="1">
-      <c r="A103" s="207"/>
-      <c r="B103" s="226"/>
-      <c r="C103" s="226"/>
-      <c r="D103" s="226"/>
-      <c r="E103" s="226"/>
-      <c r="F103" s="227"/>
+      <c r="A103" s="221"/>
+      <c r="B103" s="234"/>
+      <c r="C103" s="234"/>
+      <c r="D103" s="234"/>
+      <c r="E103" s="234"/>
+      <c r="F103" s="235"/>
       <c r="G103" s="132" t="s">
         <v>207</v>
       </c>
-      <c r="H103" s="265"/>
-      <c r="I103" s="265"/>
-      <c r="J103" s="241"/>
-      <c r="K103" s="237"/>
-      <c r="L103" s="207"/>
+      <c r="H103" s="271"/>
+      <c r="I103" s="271"/>
+      <c r="J103" s="249"/>
+      <c r="K103" s="245"/>
+      <c r="L103" s="221"/>
       <c r="M103" s="12"/>
     </row>
     <row r="104" spans="1:13" ht="97.5" customHeight="1">
-      <c r="A104" s="207">
+      <c r="A104" s="221">
         <v>31</v>
       </c>
-      <c r="B104" s="226">
+      <c r="B104" s="234">
         <v>45887</v>
       </c>
-      <c r="C104" s="226"/>
-      <c r="D104" s="226" t="s">
+      <c r="C104" s="234"/>
+      <c r="D104" s="234" t="s">
         <v>208</v>
       </c>
-      <c r="E104" s="226" t="s">
+      <c r="E104" s="234" t="s">
         <v>209</v>
       </c>
-      <c r="F104" s="227" t="s">
+      <c r="F104" s="235" t="s">
         <v>210</v>
       </c>
-      <c r="G104" s="247" t="s">
+      <c r="G104" s="255" t="s">
         <v>211</v>
       </c>
-      <c r="H104" s="248" t="s">
+      <c r="H104" s="256" t="s">
         <v>30</v>
       </c>
-      <c r="I104" s="264" t="s">
+      <c r="I104" s="270" t="s">
         <v>30</v>
       </c>
-      <c r="J104" s="241" t="s">
+      <c r="J104" s="249" t="s">
         <v>20</v>
       </c>
-      <c r="K104" s="237" t="s">
+      <c r="K104" s="245" t="s">
         <v>178</v>
       </c>
-      <c r="L104" s="258" t="s">
+      <c r="L104" s="266" t="s">
         <v>212</v>
       </c>
       <c r="M104" s="12"/>
     </row>
     <row r="105" spans="1:13" ht="60" customHeight="1">
-      <c r="A105" s="207"/>
-      <c r="B105" s="206"/>
-      <c r="C105" s="226"/>
-      <c r="D105" s="226"/>
-      <c r="E105" s="226"/>
-      <c r="F105" s="227"/>
-      <c r="G105" s="247"/>
-      <c r="H105" s="248"/>
-      <c r="I105" s="264"/>
-      <c r="J105" s="241"/>
-      <c r="K105" s="237"/>
-      <c r="L105" s="258"/>
+      <c r="A105" s="221"/>
+      <c r="B105" s="220"/>
+      <c r="C105" s="234"/>
+      <c r="D105" s="234"/>
+      <c r="E105" s="234"/>
+      <c r="F105" s="235"/>
+      <c r="G105" s="255"/>
+      <c r="H105" s="256"/>
+      <c r="I105" s="270"/>
+      <c r="J105" s="249"/>
+      <c r="K105" s="245"/>
+      <c r="L105" s="266"/>
       <c r="M105" s="12"/>
     </row>
     <row r="106" spans="1:13" ht="113.25" customHeight="1">
-      <c r="A106" s="262">
+      <c r="A106" s="268">
         <v>32</v>
       </c>
-      <c r="B106" s="225">
+      <c r="B106" s="233">
         <v>45895</v>
       </c>
-      <c r="C106" s="225"/>
-      <c r="D106" s="225" t="s">
+      <c r="C106" s="233"/>
+      <c r="D106" s="233" t="s">
         <v>213</v>
       </c>
-      <c r="E106" s="207" t="s">
+      <c r="E106" s="221" t="s">
         <v>27</v>
       </c>
-      <c r="F106" s="227" t="s">
+      <c r="F106" s="235" t="s">
         <v>214</v>
       </c>
       <c r="G106" s="31" t="s">
@@ -7435,17 +7491,17 @@
       <c r="J106" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="K106" s="224"/>
-      <c r="L106" s="363"/>
+      <c r="K106" s="232"/>
+      <c r="L106" s="367"/>
       <c r="M106" s="12"/>
     </row>
     <row r="107" spans="1:13" ht="56.25" customHeight="1">
-      <c r="A107" s="262"/>
-      <c r="B107" s="225"/>
-      <c r="C107" s="225"/>
-      <c r="D107" s="225"/>
-      <c r="E107" s="207"/>
-      <c r="F107" s="246"/>
+      <c r="A107" s="268"/>
+      <c r="B107" s="233"/>
+      <c r="C107" s="233"/>
+      <c r="D107" s="233"/>
+      <c r="E107" s="221"/>
+      <c r="F107" s="254"/>
       <c r="G107" s="31" t="s">
         <v>217</v>
       </c>
@@ -7458,17 +7514,17 @@
       <c r="J107" s="78" t="s">
         <v>218</v>
       </c>
-      <c r="K107" s="224"/>
-      <c r="L107" s="363"/>
+      <c r="K107" s="232"/>
+      <c r="L107" s="367"/>
       <c r="M107" s="12"/>
     </row>
     <row r="108" spans="1:13" ht="81" customHeight="1">
-      <c r="A108" s="262"/>
-      <c r="B108" s="256"/>
-      <c r="C108" s="225"/>
-      <c r="D108" s="225"/>
-      <c r="E108" s="207"/>
-      <c r="F108" s="246"/>
+      <c r="A108" s="268"/>
+      <c r="B108" s="264"/>
+      <c r="C108" s="233"/>
+      <c r="D108" s="233"/>
+      <c r="E108" s="221"/>
+      <c r="F108" s="254"/>
       <c r="G108" s="31" t="s">
         <v>219</v>
       </c>
@@ -7481,17 +7537,17 @@
       <c r="J108" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K108" s="224"/>
-      <c r="L108" s="363"/>
+      <c r="K108" s="232"/>
+      <c r="L108" s="367"/>
       <c r="M108" s="12"/>
     </row>
     <row r="109" spans="1:13" ht="56.25" customHeight="1">
-      <c r="A109" s="262"/>
-      <c r="B109" s="256"/>
-      <c r="C109" s="225"/>
-      <c r="D109" s="225"/>
-      <c r="E109" s="207"/>
-      <c r="F109" s="268"/>
+      <c r="A109" s="268"/>
+      <c r="B109" s="264"/>
+      <c r="C109" s="233"/>
+      <c r="D109" s="233"/>
+      <c r="E109" s="221"/>
+      <c r="F109" s="274"/>
       <c r="G109" s="36" t="s">
         <v>221</v>
       </c>
@@ -7504,17 +7560,17 @@
       <c r="J109" s="76" t="s">
         <v>222</v>
       </c>
-      <c r="K109" s="224"/>
-      <c r="L109" s="363"/>
+      <c r="K109" s="232"/>
+      <c r="L109" s="367"/>
       <c r="M109" s="12"/>
     </row>
     <row r="110" spans="1:13" ht="56.25" customHeight="1">
-      <c r="A110" s="262"/>
-      <c r="B110" s="256"/>
-      <c r="C110" s="225"/>
-      <c r="D110" s="225"/>
-      <c r="E110" s="207"/>
-      <c r="F110" s="268"/>
+      <c r="A110" s="268"/>
+      <c r="B110" s="264"/>
+      <c r="C110" s="233"/>
+      <c r="D110" s="233"/>
+      <c r="E110" s="221"/>
+      <c r="F110" s="274"/>
       <c r="G110" s="31" t="s">
         <v>223</v>
       </c>
@@ -7527,27 +7583,27 @@
       <c r="J110" s="76" t="s">
         <v>222</v>
       </c>
-      <c r="K110" s="224"/>
-      <c r="L110" s="363"/>
+      <c r="K110" s="232"/>
+      <c r="L110" s="367"/>
       <c r="M110" s="12"/>
     </row>
     <row r="111" spans="1:13" ht="71.25" customHeight="1">
-      <c r="A111" s="262">
+      <c r="A111" s="268">
         <v>33</v>
       </c>
-      <c r="B111" s="225">
+      <c r="B111" s="233">
         <v>45900</v>
       </c>
-      <c r="C111" s="225" t="s">
+      <c r="C111" s="233" t="s">
         <v>125</v>
       </c>
-      <c r="D111" s="269" t="s">
+      <c r="D111" s="275" t="s">
         <v>224</v>
       </c>
-      <c r="E111" s="218" t="s">
+      <c r="E111" s="226" t="s">
         <v>182</v>
       </c>
-      <c r="F111" s="246" t="s">
+      <c r="F111" s="254" t="s">
         <v>225</v>
       </c>
       <c r="G111" s="31" t="s">
@@ -7562,10 +7618,10 @@
       <c r="J111" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="K111" s="232" t="s">
+      <c r="K111" s="240" t="s">
         <v>20</v>
       </c>
-      <c r="L111" s="207" t="s">
+      <c r="L111" s="221" t="s">
         <v>20</v>
       </c>
       <c r="M111" s="12" t="s">
@@ -7573,12 +7629,12 @@
       </c>
     </row>
     <row r="112" spans="1:13" ht="80.25" customHeight="1">
-      <c r="A112" s="262"/>
-      <c r="B112" s="256"/>
-      <c r="C112" s="225"/>
-      <c r="D112" s="226"/>
-      <c r="E112" s="207"/>
-      <c r="F112" s="246"/>
+      <c r="A112" s="268"/>
+      <c r="B112" s="264"/>
+      <c r="C112" s="233"/>
+      <c r="D112" s="234"/>
+      <c r="E112" s="221"/>
+      <c r="F112" s="254"/>
       <c r="G112" s="36" t="s">
         <v>228</v>
       </c>
@@ -7591,17 +7647,17 @@
       <c r="J112" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K112" s="232"/>
-      <c r="L112" s="207"/>
+      <c r="K112" s="240"/>
+      <c r="L112" s="221"/>
       <c r="M112" s="12"/>
     </row>
     <row r="113" spans="1:13" ht="96.75" customHeight="1">
-      <c r="A113" s="262"/>
-      <c r="B113" s="256"/>
-      <c r="C113" s="225"/>
-      <c r="D113" s="226"/>
-      <c r="E113" s="207"/>
-      <c r="F113" s="246"/>
+      <c r="A113" s="268"/>
+      <c r="B113" s="264"/>
+      <c r="C113" s="233"/>
+      <c r="D113" s="234"/>
+      <c r="E113" s="221"/>
+      <c r="F113" s="254"/>
       <c r="G113" s="36" t="s">
         <v>230</v>
       </c>
@@ -7614,17 +7670,17 @@
       <c r="J113" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K113" s="232"/>
-      <c r="L113" s="207"/>
+      <c r="K113" s="240"/>
+      <c r="L113" s="221"/>
       <c r="M113" s="12"/>
     </row>
     <row r="114" spans="1:13" ht="114.75" customHeight="1">
-      <c r="A114" s="262"/>
-      <c r="B114" s="256"/>
-      <c r="C114" s="225"/>
-      <c r="D114" s="226"/>
-      <c r="E114" s="207"/>
-      <c r="F114" s="246"/>
+      <c r="A114" s="268"/>
+      <c r="B114" s="264"/>
+      <c r="C114" s="233"/>
+      <c r="D114" s="234"/>
+      <c r="E114" s="221"/>
+      <c r="F114" s="254"/>
       <c r="G114" s="36" t="s">
         <v>232</v>
       </c>
@@ -7637,17 +7693,17 @@
       <c r="J114" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K114" s="232"/>
-      <c r="L114" s="207"/>
+      <c r="K114" s="240"/>
+      <c r="L114" s="221"/>
       <c r="M114" s="12"/>
     </row>
     <row r="115" spans="1:13" ht="87.75" customHeight="1">
-      <c r="A115" s="262"/>
-      <c r="B115" s="256"/>
-      <c r="C115" s="225"/>
-      <c r="D115" s="226"/>
-      <c r="E115" s="207"/>
-      <c r="F115" s="246"/>
+      <c r="A115" s="268"/>
+      <c r="B115" s="264"/>
+      <c r="C115" s="233"/>
+      <c r="D115" s="234"/>
+      <c r="E115" s="221"/>
+      <c r="F115" s="254"/>
       <c r="G115" s="36" t="s">
         <v>234</v>
       </c>
@@ -7660,27 +7716,27 @@
       <c r="J115" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K115" s="232"/>
-      <c r="L115" s="207"/>
+      <c r="K115" s="240"/>
+      <c r="L115" s="221"/>
       <c r="M115" s="12"/>
     </row>
     <row r="116" spans="1:13" ht="87.75" customHeight="1">
-      <c r="A116" s="262">
+      <c r="A116" s="268">
         <v>34</v>
       </c>
-      <c r="B116" s="225">
+      <c r="B116" s="233">
         <v>45906</v>
       </c>
-      <c r="C116" s="225" t="s">
+      <c r="C116" s="233" t="s">
         <v>32</v>
       </c>
-      <c r="D116" s="270" t="s">
+      <c r="D116" s="276" t="s">
         <v>236</v>
       </c>
-      <c r="E116" s="214" t="s">
+      <c r="E116" s="206" t="s">
         <v>78</v>
       </c>
-      <c r="F116" s="246" t="s">
+      <c r="F116" s="254" t="s">
         <v>237</v>
       </c>
       <c r="G116" s="36" t="s">
@@ -7695,19 +7751,19 @@
       <c r="J116" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K116" s="243" t="s">
+      <c r="K116" s="251" t="s">
         <v>240</v>
       </c>
-      <c r="L116" s="257"/>
+      <c r="L116" s="265"/>
       <c r="M116" s="12"/>
     </row>
     <row r="117" spans="1:13" ht="87.75" customHeight="1">
-      <c r="A117" s="262"/>
-      <c r="B117" s="256"/>
-      <c r="C117" s="225"/>
-      <c r="D117" s="270"/>
-      <c r="E117" s="303"/>
-      <c r="F117" s="246"/>
+      <c r="A117" s="268"/>
+      <c r="B117" s="264"/>
+      <c r="C117" s="233"/>
+      <c r="D117" s="276"/>
+      <c r="E117" s="207"/>
+      <c r="F117" s="254"/>
       <c r="G117" s="36" t="s">
         <v>241</v>
       </c>
@@ -7720,17 +7776,17 @@
       <c r="J117" s="76" t="s">
         <v>222</v>
       </c>
-      <c r="K117" s="243"/>
-      <c r="L117" s="257"/>
+      <c r="K117" s="251"/>
+      <c r="L117" s="265"/>
       <c r="M117" s="12"/>
     </row>
     <row r="118" spans="1:13" ht="87.75" customHeight="1">
-      <c r="A118" s="262"/>
-      <c r="B118" s="256"/>
-      <c r="C118" s="225"/>
-      <c r="D118" s="270"/>
-      <c r="E118" s="303"/>
-      <c r="F118" s="246"/>
+      <c r="A118" s="268"/>
+      <c r="B118" s="264"/>
+      <c r="C118" s="233"/>
+      <c r="D118" s="276"/>
+      <c r="E118" s="207"/>
+      <c r="F118" s="254"/>
       <c r="G118" s="36" t="s">
         <v>243</v>
       </c>
@@ -7743,17 +7799,17 @@
       <c r="J118" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K118" s="243"/>
-      <c r="L118" s="257"/>
+      <c r="K118" s="251"/>
+      <c r="L118" s="265"/>
       <c r="M118" s="12"/>
     </row>
     <row r="119" spans="1:13" ht="87.75" customHeight="1">
-      <c r="A119" s="262"/>
-      <c r="B119" s="256"/>
-      <c r="C119" s="225"/>
-      <c r="D119" s="270"/>
-      <c r="E119" s="303"/>
-      <c r="F119" s="246"/>
+      <c r="A119" s="268"/>
+      <c r="B119" s="264"/>
+      <c r="C119" s="233"/>
+      <c r="D119" s="276"/>
+      <c r="E119" s="207"/>
+      <c r="F119" s="254"/>
       <c r="G119" s="165" t="s">
         <v>244</v>
       </c>
@@ -7766,17 +7822,17 @@
       <c r="J119" s="76" t="s">
         <v>222</v>
       </c>
-      <c r="K119" s="243"/>
-      <c r="L119" s="257"/>
+      <c r="K119" s="251"/>
+      <c r="L119" s="265"/>
       <c r="M119" s="12"/>
     </row>
     <row r="120" spans="1:13" ht="87.75" customHeight="1">
-      <c r="A120" s="262"/>
-      <c r="B120" s="256"/>
-      <c r="C120" s="225"/>
-      <c r="D120" s="270"/>
-      <c r="E120" s="215"/>
-      <c r="F120" s="246"/>
+      <c r="A120" s="268"/>
+      <c r="B120" s="264"/>
+      <c r="C120" s="233"/>
+      <c r="D120" s="276"/>
+      <c r="E120" s="208"/>
+      <c r="F120" s="254"/>
       <c r="G120" s="36" t="s">
         <v>246</v>
       </c>
@@ -7789,25 +7845,25 @@
       <c r="J120" s="76" t="s">
         <v>222</v>
       </c>
-      <c r="K120" s="243"/>
-      <c r="L120" s="257"/>
+      <c r="K120" s="251"/>
+      <c r="L120" s="265"/>
       <c r="M120" s="12"/>
     </row>
     <row r="121" spans="1:13" ht="99.75" customHeight="1">
-      <c r="A121" s="218">
+      <c r="A121" s="226">
         <v>35</v>
       </c>
-      <c r="B121" s="226">
+      <c r="B121" s="234">
         <v>45911</v>
       </c>
-      <c r="C121" s="226"/>
-      <c r="D121" s="226" t="s">
+      <c r="C121" s="234"/>
+      <c r="D121" s="234" t="s">
         <v>247</v>
       </c>
-      <c r="E121" s="226" t="s">
+      <c r="E121" s="234" t="s">
         <v>27</v>
       </c>
-      <c r="F121" s="227" t="s">
+      <c r="F121" s="235" t="s">
         <v>248</v>
       </c>
       <c r="G121" s="44" t="s">
@@ -7822,19 +7878,19 @@
       <c r="J121" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K121" s="232" t="s">
+      <c r="K121" s="240" t="s">
         <v>240</v>
       </c>
-      <c r="L121" s="207"/>
+      <c r="L121" s="221"/>
       <c r="M121" s="12"/>
     </row>
     <row r="122" spans="1:13" ht="72" customHeight="1">
-      <c r="A122" s="218"/>
-      <c r="B122" s="206"/>
-      <c r="C122" s="226"/>
-      <c r="D122" s="226"/>
-      <c r="E122" s="226"/>
-      <c r="F122" s="227"/>
+      <c r="A122" s="226"/>
+      <c r="B122" s="220"/>
+      <c r="C122" s="234"/>
+      <c r="D122" s="234"/>
+      <c r="E122" s="234"/>
+      <c r="F122" s="235"/>
       <c r="G122" s="31" t="s">
         <v>219</v>
       </c>
@@ -7847,17 +7903,17 @@
       <c r="J122" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="K122" s="232"/>
-      <c r="L122" s="207"/>
+      <c r="K122" s="240"/>
+      <c r="L122" s="221"/>
       <c r="M122" s="12"/>
     </row>
     <row r="123" spans="1:13" ht="49.5" customHeight="1">
-      <c r="A123" s="218"/>
-      <c r="B123" s="206"/>
-      <c r="C123" s="226"/>
-      <c r="D123" s="226"/>
-      <c r="E123" s="226"/>
-      <c r="F123" s="227"/>
+      <c r="A123" s="226"/>
+      <c r="B123" s="220"/>
+      <c r="C123" s="234"/>
+      <c r="D123" s="234"/>
+      <c r="E123" s="234"/>
+      <c r="F123" s="235"/>
       <c r="G123" s="31" t="s">
         <v>250</v>
       </c>
@@ -7870,17 +7926,17 @@
       <c r="J123" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K123" s="232"/>
-      <c r="L123" s="207"/>
+      <c r="K123" s="240"/>
+      <c r="L123" s="221"/>
       <c r="M123" s="12"/>
     </row>
     <row r="124" spans="1:13" ht="71.25" customHeight="1">
-      <c r="A124" s="218"/>
-      <c r="B124" s="206"/>
-      <c r="C124" s="226"/>
-      <c r="D124" s="226"/>
-      <c r="E124" s="226"/>
-      <c r="F124" s="227"/>
+      <c r="A124" s="226"/>
+      <c r="B124" s="220"/>
+      <c r="C124" s="234"/>
+      <c r="D124" s="234"/>
+      <c r="E124" s="234"/>
+      <c r="F124" s="235"/>
       <c r="G124" s="31" t="s">
         <v>252</v>
       </c>
@@ -7893,25 +7949,25 @@
       <c r="J124" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K124" s="232"/>
-      <c r="L124" s="207"/>
+      <c r="K124" s="240"/>
+      <c r="L124" s="221"/>
       <c r="M124" s="12"/>
     </row>
     <row r="125" spans="1:13" ht="66.75" customHeight="1">
-      <c r="A125" s="218">
+      <c r="A125" s="226">
         <v>36</v>
       </c>
-      <c r="B125" s="226">
+      <c r="B125" s="234">
         <v>45917</v>
       </c>
-      <c r="C125" s="206"/>
-      <c r="D125" s="206" t="s">
+      <c r="C125" s="220"/>
+      <c r="D125" s="220" t="s">
         <v>253</v>
       </c>
-      <c r="E125" s="294" t="s">
+      <c r="E125" s="300" t="s">
         <v>47</v>
       </c>
-      <c r="F125" s="227" t="s">
+      <c r="F125" s="235" t="s">
         <v>254</v>
       </c>
       <c r="G125" s="36" t="s">
@@ -7926,21 +7982,21 @@
       <c r="J125" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="K125" s="232" t="s">
+      <c r="K125" s="240" t="s">
         <v>240</v>
       </c>
-      <c r="L125" s="207" t="s">
+      <c r="L125" s="221" t="s">
         <v>22</v>
       </c>
       <c r="M125" s="12"/>
     </row>
     <row r="126" spans="1:13" ht="66.75" customHeight="1">
-      <c r="A126" s="218"/>
-      <c r="B126" s="226"/>
-      <c r="C126" s="206"/>
-      <c r="D126" s="206"/>
-      <c r="E126" s="294"/>
-      <c r="F126" s="227"/>
+      <c r="A126" s="226"/>
+      <c r="B126" s="234"/>
+      <c r="C126" s="220"/>
+      <c r="D126" s="220"/>
+      <c r="E126" s="300"/>
+      <c r="F126" s="235"/>
       <c r="G126" s="36" t="s">
         <v>256</v>
       </c>
@@ -7953,17 +8009,17 @@
       <c r="J126" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="K126" s="232"/>
-      <c r="L126" s="207"/>
+      <c r="K126" s="240"/>
+      <c r="L126" s="221"/>
       <c r="M126" s="12"/>
     </row>
     <row r="127" spans="1:13" ht="66.75" customHeight="1">
-      <c r="A127" s="218"/>
-      <c r="B127" s="206"/>
-      <c r="C127" s="206"/>
-      <c r="D127" s="206"/>
-      <c r="E127" s="294"/>
-      <c r="F127" s="227"/>
+      <c r="A127" s="226"/>
+      <c r="B127" s="220"/>
+      <c r="C127" s="220"/>
+      <c r="D127" s="220"/>
+      <c r="E127" s="300"/>
+      <c r="F127" s="235"/>
       <c r="G127" s="36" t="s">
         <v>258</v>
       </c>
@@ -7976,8 +8032,8 @@
       <c r="J127" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K127" s="232"/>
-      <c r="L127" s="207"/>
+      <c r="K127" s="240"/>
+      <c r="L127" s="221"/>
       <c r="M127" s="12"/>
     </row>
     <row r="128" spans="1:13" ht="92.1" customHeight="1">
@@ -8020,72 +8076,72 @@
       <c r="M128" s="12"/>
     </row>
     <row r="129" spans="1:13" ht="112.5" customHeight="1">
-      <c r="A129" s="218">
+      <c r="A129" s="226">
         <v>38</v>
       </c>
-      <c r="B129" s="226">
+      <c r="B129" s="234">
         <v>45932</v>
       </c>
-      <c r="C129" s="226" t="s">
+      <c r="C129" s="234" t="s">
         <v>261</v>
       </c>
-      <c r="D129" s="226" t="s">
+      <c r="D129" s="234" t="s">
         <v>262</v>
       </c>
-      <c r="E129" s="226" t="s">
+      <c r="E129" s="234" t="s">
         <v>27</v>
       </c>
-      <c r="F129" s="227" t="s">
+      <c r="F129" s="235" t="s">
         <v>263</v>
       </c>
-      <c r="G129" s="301" t="s">
+      <c r="G129" s="307" t="s">
         <v>29</v>
       </c>
-      <c r="H129" s="248" t="s">
+      <c r="H129" s="256" t="s">
         <v>30</v>
       </c>
-      <c r="I129" s="302" t="s">
+      <c r="I129" s="308" t="s">
         <v>31</v>
       </c>
-      <c r="J129" s="276" t="s">
+      <c r="J129" s="282" t="s">
         <v>264</v>
       </c>
-      <c r="K129" s="237"/>
-      <c r="L129" s="207"/>
+      <c r="K129" s="245"/>
+      <c r="L129" s="221"/>
       <c r="M129" s="12"/>
     </row>
     <row r="130" spans="1:13" ht="58.5" customHeight="1">
-      <c r="A130" s="218"/>
-      <c r="B130" s="258"/>
-      <c r="C130" s="226"/>
-      <c r="D130" s="226"/>
-      <c r="E130" s="226"/>
-      <c r="F130" s="227"/>
-      <c r="G130" s="301"/>
-      <c r="H130" s="248"/>
-      <c r="I130" s="264"/>
-      <c r="J130" s="241"/>
-      <c r="K130" s="237"/>
-      <c r="L130" s="207"/>
+      <c r="A130" s="226"/>
+      <c r="B130" s="266"/>
+      <c r="C130" s="234"/>
+      <c r="D130" s="234"/>
+      <c r="E130" s="234"/>
+      <c r="F130" s="235"/>
+      <c r="G130" s="307"/>
+      <c r="H130" s="256"/>
+      <c r="I130" s="270"/>
+      <c r="J130" s="249"/>
+      <c r="K130" s="245"/>
+      <c r="L130" s="221"/>
       <c r="M130" s="12"/>
     </row>
     <row r="131" spans="1:13" ht="96" customHeight="1">
-      <c r="A131" s="261">
+      <c r="A131" s="267">
         <v>39</v>
       </c>
-      <c r="B131" s="225">
+      <c r="B131" s="233">
         <v>45948</v>
       </c>
-      <c r="C131" s="225" t="s">
+      <c r="C131" s="233" t="s">
         <v>265</v>
       </c>
-      <c r="D131" s="226" t="s">
+      <c r="D131" s="234" t="s">
         <v>266</v>
       </c>
-      <c r="E131" s="226" t="s">
+      <c r="E131" s="234" t="s">
         <v>27</v>
       </c>
-      <c r="F131" s="227" t="s">
+      <c r="F131" s="235" t="s">
         <v>267</v>
       </c>
       <c r="G131" s="45" t="s">
@@ -8100,21 +8156,21 @@
       <c r="J131" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K131" s="243" t="s">
+      <c r="K131" s="251" t="s">
         <v>240</v>
       </c>
-      <c r="L131" s="207" t="s">
+      <c r="L131" s="221" t="s">
         <v>22</v>
       </c>
       <c r="M131" s="12"/>
     </row>
     <row r="132" spans="1:13" ht="71.25" customHeight="1">
-      <c r="A132" s="261"/>
-      <c r="B132" s="225"/>
-      <c r="C132" s="225"/>
-      <c r="D132" s="226"/>
-      <c r="E132" s="226"/>
-      <c r="F132" s="227"/>
+      <c r="A132" s="267"/>
+      <c r="B132" s="233"/>
+      <c r="C132" s="233"/>
+      <c r="D132" s="234"/>
+      <c r="E132" s="234"/>
+      <c r="F132" s="235"/>
       <c r="G132" s="31" t="s">
         <v>270</v>
       </c>
@@ -8127,17 +8183,17 @@
       <c r="J132" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K132" s="243"/>
-      <c r="L132" s="207"/>
+      <c r="K132" s="251"/>
+      <c r="L132" s="221"/>
       <c r="M132" s="12"/>
     </row>
     <row r="133" spans="1:13" ht="71.25" customHeight="1">
-      <c r="A133" s="261"/>
-      <c r="B133" s="256"/>
-      <c r="C133" s="225"/>
-      <c r="D133" s="226"/>
-      <c r="E133" s="226"/>
-      <c r="F133" s="227"/>
+      <c r="A133" s="267"/>
+      <c r="B133" s="264"/>
+      <c r="C133" s="233"/>
+      <c r="D133" s="234"/>
+      <c r="E133" s="234"/>
+      <c r="F133" s="235"/>
       <c r="G133" s="31" t="s">
         <v>271</v>
       </c>
@@ -8150,8 +8206,8 @@
       <c r="J133" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="K133" s="243"/>
-      <c r="L133" s="207"/>
+      <c r="K133" s="251"/>
+      <c r="L133" s="221"/>
       <c r="M133" s="12"/>
     </row>
     <row r="134" spans="1:13" ht="145.5" customHeight="1">
@@ -8188,20 +8244,20 @@
       </c>
     </row>
     <row r="135" spans="1:13" ht="101.25" customHeight="1">
-      <c r="A135" s="218">
+      <c r="A135" s="226">
         <v>41</v>
       </c>
-      <c r="B135" s="226">
+      <c r="B135" s="234">
         <v>45952</v>
       </c>
-      <c r="C135" s="226"/>
-      <c r="D135" s="226" t="s">
+      <c r="C135" s="234"/>
+      <c r="D135" s="234" t="s">
         <v>276</v>
       </c>
-      <c r="E135" s="226" t="s">
+      <c r="E135" s="234" t="s">
         <v>27</v>
       </c>
-      <c r="F135" s="227" t="s">
+      <c r="F135" s="235" t="s">
         <v>277</v>
       </c>
       <c r="G135" s="44" t="s">
@@ -8216,19 +8272,19 @@
       <c r="J135" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K135" s="243" t="s">
+      <c r="K135" s="251" t="s">
         <v>240</v>
       </c>
-      <c r="L135" s="207"/>
+      <c r="L135" s="221"/>
       <c r="M135" s="12"/>
     </row>
     <row r="136" spans="1:13" ht="101.25" customHeight="1">
-      <c r="A136" s="218"/>
-      <c r="B136" s="206"/>
-      <c r="C136" s="226"/>
-      <c r="D136" s="226"/>
-      <c r="E136" s="226"/>
-      <c r="F136" s="227"/>
+      <c r="A136" s="226"/>
+      <c r="B136" s="220"/>
+      <c r="C136" s="234"/>
+      <c r="D136" s="234"/>
+      <c r="E136" s="234"/>
+      <c r="F136" s="235"/>
       <c r="G136" s="36" t="s">
         <v>279</v>
       </c>
@@ -8241,17 +8297,17 @@
       <c r="J136" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K136" s="243"/>
-      <c r="L136" s="207"/>
+      <c r="K136" s="251"/>
+      <c r="L136" s="221"/>
       <c r="M136" s="12"/>
     </row>
     <row r="137" spans="1:13" ht="101.25" customHeight="1">
-      <c r="A137" s="218"/>
-      <c r="B137" s="206"/>
-      <c r="C137" s="226"/>
-      <c r="D137" s="226"/>
-      <c r="E137" s="226"/>
-      <c r="F137" s="227"/>
+      <c r="A137" s="226"/>
+      <c r="B137" s="220"/>
+      <c r="C137" s="234"/>
+      <c r="D137" s="234"/>
+      <c r="E137" s="234"/>
+      <c r="F137" s="235"/>
       <c r="G137" s="36" t="s">
         <v>281</v>
       </c>
@@ -8264,111 +8320,111 @@
       <c r="J137" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K137" s="243"/>
-      <c r="L137" s="207"/>
+      <c r="K137" s="251"/>
+      <c r="L137" s="221"/>
       <c r="M137" s="12"/>
     </row>
     <row r="138" spans="1:13" ht="97.5" customHeight="1">
-      <c r="A138" s="218">
+      <c r="A138" s="226">
         <v>42</v>
       </c>
-      <c r="B138" s="226">
+      <c r="B138" s="234">
         <v>45962</v>
       </c>
-      <c r="C138" s="226" t="s">
+      <c r="C138" s="234" t="s">
         <v>14</v>
       </c>
-      <c r="D138" s="226" t="s">
+      <c r="D138" s="234" t="s">
         <v>282</v>
       </c>
-      <c r="E138" s="226" t="s">
+      <c r="E138" s="234" t="s">
         <v>47</v>
       </c>
-      <c r="F138" s="227" t="s">
+      <c r="F138" s="235" t="s">
         <v>283</v>
       </c>
-      <c r="G138" s="234" t="s">
+      <c r="G138" s="242" t="s">
         <v>284</v>
       </c>
-      <c r="H138" s="235" t="s">
+      <c r="H138" s="243" t="s">
         <v>120</v>
       </c>
-      <c r="I138" s="254">
+      <c r="I138" s="262">
         <v>45991</v>
       </c>
-      <c r="J138" s="255" t="s">
+      <c r="J138" s="263" t="s">
         <v>20</v>
       </c>
-      <c r="K138" s="232" t="s">
+      <c r="K138" s="240" t="s">
         <v>240</v>
       </c>
-      <c r="L138" s="207" t="s">
+      <c r="L138" s="221" t="s">
         <v>22</v>
       </c>
       <c r="M138" s="12"/>
     </row>
     <row r="139" spans="1:13" ht="28.5" customHeight="1">
-      <c r="A139" s="218"/>
-      <c r="B139" s="226"/>
-      <c r="C139" s="226"/>
-      <c r="D139" s="226"/>
-      <c r="E139" s="226"/>
-      <c r="F139" s="227"/>
-      <c r="G139" s="234"/>
-      <c r="H139" s="235"/>
-      <c r="I139" s="254"/>
-      <c r="J139" s="255"/>
-      <c r="K139" s="232"/>
-      <c r="L139" s="207"/>
+      <c r="A139" s="226"/>
+      <c r="B139" s="234"/>
+      <c r="C139" s="234"/>
+      <c r="D139" s="234"/>
+      <c r="E139" s="234"/>
+      <c r="F139" s="235"/>
+      <c r="G139" s="242"/>
+      <c r="H139" s="243"/>
+      <c r="I139" s="262"/>
+      <c r="J139" s="263"/>
+      <c r="K139" s="240"/>
+      <c r="L139" s="221"/>
       <c r="M139" s="12"/>
     </row>
     <row r="140" spans="1:13" ht="28.5" customHeight="1">
-      <c r="A140" s="218"/>
-      <c r="B140" s="226"/>
-      <c r="C140" s="226"/>
-      <c r="D140" s="226"/>
-      <c r="E140" s="226"/>
-      <c r="F140" s="227"/>
-      <c r="G140" s="234"/>
-      <c r="H140" s="235"/>
-      <c r="I140" s="254"/>
-      <c r="J140" s="255"/>
-      <c r="K140" s="232"/>
-      <c r="L140" s="207"/>
+      <c r="A140" s="226"/>
+      <c r="B140" s="234"/>
+      <c r="C140" s="234"/>
+      <c r="D140" s="234"/>
+      <c r="E140" s="234"/>
+      <c r="F140" s="235"/>
+      <c r="G140" s="242"/>
+      <c r="H140" s="243"/>
+      <c r="I140" s="262"/>
+      <c r="J140" s="263"/>
+      <c r="K140" s="240"/>
+      <c r="L140" s="221"/>
       <c r="M140" s="12"/>
     </row>
     <row r="141" spans="1:13" ht="28.5" customHeight="1">
-      <c r="A141" s="218"/>
-      <c r="B141" s="226"/>
-      <c r="C141" s="226"/>
-      <c r="D141" s="226"/>
-      <c r="E141" s="226"/>
-      <c r="F141" s="227"/>
-      <c r="G141" s="234"/>
-      <c r="H141" s="235"/>
-      <c r="I141" s="254"/>
-      <c r="J141" s="255"/>
-      <c r="K141" s="232"/>
-      <c r="L141" s="207"/>
+      <c r="A141" s="226"/>
+      <c r="B141" s="234"/>
+      <c r="C141" s="234"/>
+      <c r="D141" s="234"/>
+      <c r="E141" s="234"/>
+      <c r="F141" s="235"/>
+      <c r="G141" s="242"/>
+      <c r="H141" s="243"/>
+      <c r="I141" s="262"/>
+      <c r="J141" s="263"/>
+      <c r="K141" s="240"/>
+      <c r="L141" s="221"/>
       <c r="M141" s="12"/>
     </row>
     <row r="142" spans="1:13" ht="44.45" customHeight="1">
-      <c r="A142" s="218">
+      <c r="A142" s="226">
         <v>43</v>
       </c>
-      <c r="B142" s="226">
+      <c r="B142" s="234">
         <v>45964</v>
       </c>
-      <c r="C142" s="225" t="s">
+      <c r="C142" s="233" t="s">
         <v>14</v>
       </c>
-      <c r="D142" s="226" t="s">
+      <c r="D142" s="234" t="s">
         <v>285</v>
       </c>
-      <c r="E142" s="226" t="s">
+      <c r="E142" s="234" t="s">
         <v>78</v>
       </c>
-      <c r="F142" s="227" t="s">
+      <c r="F142" s="235" t="s">
         <v>286</v>
       </c>
       <c r="G142" s="31" t="s">
@@ -8383,19 +8439,19 @@
       <c r="J142" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="K142" s="233" t="s">
+      <c r="K142" s="241" t="s">
         <v>22</v>
       </c>
-      <c r="L142" s="257"/>
+      <c r="L142" s="265"/>
       <c r="M142" s="12"/>
     </row>
     <row r="143" spans="1:13" ht="44.45" customHeight="1">
-      <c r="A143" s="218"/>
-      <c r="B143" s="206"/>
-      <c r="C143" s="225"/>
-      <c r="D143" s="226"/>
-      <c r="E143" s="226"/>
-      <c r="F143" s="227"/>
+      <c r="A143" s="226"/>
+      <c r="B143" s="220"/>
+      <c r="C143" s="233"/>
+      <c r="D143" s="234"/>
+      <c r="E143" s="234"/>
+      <c r="F143" s="235"/>
       <c r="G143" s="31" t="s">
         <v>288</v>
       </c>
@@ -8408,17 +8464,17 @@
       <c r="J143" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="K143" s="233"/>
-      <c r="L143" s="257"/>
+      <c r="K143" s="241"/>
+      <c r="L143" s="265"/>
       <c r="M143" s="12"/>
     </row>
     <row r="144" spans="1:13" ht="44.45" customHeight="1">
-      <c r="A144" s="218"/>
-      <c r="B144" s="206"/>
-      <c r="C144" s="225"/>
-      <c r="D144" s="226"/>
-      <c r="E144" s="226"/>
-      <c r="F144" s="227"/>
+      <c r="A144" s="226"/>
+      <c r="B144" s="220"/>
+      <c r="C144" s="233"/>
+      <c r="D144" s="234"/>
+      <c r="E144" s="234"/>
+      <c r="F144" s="235"/>
       <c r="G144" s="31" t="s">
         <v>289</v>
       </c>
@@ -8431,27 +8487,27 @@
       <c r="J144" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="K144" s="233"/>
-      <c r="L144" s="257"/>
+      <c r="K144" s="241"/>
+      <c r="L144" s="265"/>
       <c r="M144" s="12"/>
     </row>
     <row r="145" spans="1:13" ht="57" customHeight="1">
-      <c r="A145" s="218">
+      <c r="A145" s="226">
         <v>44</v>
       </c>
-      <c r="B145" s="208">
+      <c r="B145" s="222">
         <v>45968</v>
       </c>
-      <c r="C145" s="226" t="s">
+      <c r="C145" s="234" t="s">
         <v>14</v>
       </c>
-      <c r="D145" s="206" t="s">
+      <c r="D145" s="220" t="s">
         <v>291</v>
       </c>
-      <c r="E145" s="207" t="s">
+      <c r="E145" s="221" t="s">
         <v>209</v>
       </c>
-      <c r="F145" s="227" t="s">
+      <c r="F145" s="235" t="s">
         <v>292</v>
       </c>
       <c r="G145" s="47" t="s">
@@ -8466,21 +8522,21 @@
       <c r="J145" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="K145" s="233" t="s">
+      <c r="K145" s="241" t="s">
         <v>178</v>
       </c>
-      <c r="L145" s="207" t="s">
+      <c r="L145" s="221" t="s">
         <v>178</v>
       </c>
       <c r="M145" s="12"/>
     </row>
     <row r="146" spans="1:13" ht="103.5" customHeight="1">
-      <c r="A146" s="218"/>
-      <c r="B146" s="208"/>
-      <c r="C146" s="226"/>
-      <c r="D146" s="206"/>
-      <c r="E146" s="207"/>
-      <c r="F146" s="227"/>
+      <c r="A146" s="226"/>
+      <c r="B146" s="222"/>
+      <c r="C146" s="234"/>
+      <c r="D146" s="220"/>
+      <c r="E146" s="221"/>
+      <c r="F146" s="235"/>
       <c r="G146" s="48" t="s">
         <v>294</v>
       </c>
@@ -8493,17 +8549,17 @@
       <c r="J146" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="K146" s="233"/>
-      <c r="L146" s="207"/>
+      <c r="K146" s="241"/>
+      <c r="L146" s="221"/>
       <c r="M146" s="12"/>
     </row>
     <row r="147" spans="1:13" ht="57" customHeight="1">
-      <c r="A147" s="218"/>
-      <c r="B147" s="208"/>
-      <c r="C147" s="226"/>
-      <c r="D147" s="206"/>
-      <c r="E147" s="207"/>
-      <c r="F147" s="227"/>
+      <c r="A147" s="226"/>
+      <c r="B147" s="222"/>
+      <c r="C147" s="234"/>
+      <c r="D147" s="220"/>
+      <c r="E147" s="221"/>
+      <c r="F147" s="235"/>
       <c r="G147" s="49" t="s">
         <v>296</v>
       </c>
@@ -8516,27 +8572,27 @@
       <c r="J147" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="K147" s="233"/>
-      <c r="L147" s="207"/>
+      <c r="K147" s="241"/>
+      <c r="L147" s="221"/>
       <c r="M147" s="12"/>
     </row>
     <row r="148" spans="1:13" ht="49.5" customHeight="1">
-      <c r="A148" s="218">
+      <c r="A148" s="226">
         <v>45</v>
       </c>
-      <c r="B148" s="208">
+      <c r="B148" s="222">
         <v>45970</v>
       </c>
-      <c r="C148" s="226" t="s">
+      <c r="C148" s="234" t="s">
         <v>14</v>
       </c>
-      <c r="D148" s="206" t="s">
+      <c r="D148" s="220" t="s">
         <v>297</v>
       </c>
-      <c r="E148" s="207" t="s">
+      <c r="E148" s="221" t="s">
         <v>298</v>
       </c>
-      <c r="F148" s="227" t="s">
+      <c r="F148" s="235" t="s">
         <v>299</v>
       </c>
       <c r="G148" s="13" t="s">
@@ -8551,19 +8607,19 @@
       <c r="J148" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="K148" s="228" t="s">
+      <c r="K148" s="236" t="s">
         <v>22</v>
       </c>
-      <c r="L148" s="207"/>
+      <c r="L148" s="221"/>
       <c r="M148" s="12"/>
     </row>
     <row r="149" spans="1:13" ht="43.5" customHeight="1">
-      <c r="A149" s="218"/>
-      <c r="B149" s="207"/>
-      <c r="C149" s="226"/>
-      <c r="D149" s="206"/>
-      <c r="E149" s="207"/>
-      <c r="F149" s="227"/>
+      <c r="A149" s="226"/>
+      <c r="B149" s="221"/>
+      <c r="C149" s="234"/>
+      <c r="D149" s="220"/>
+      <c r="E149" s="221"/>
+      <c r="F149" s="235"/>
       <c r="G149" s="14" t="s">
         <v>302</v>
       </c>
@@ -8576,17 +8632,17 @@
       <c r="J149" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="K149" s="229"/>
-      <c r="L149" s="207"/>
+      <c r="K149" s="237"/>
+      <c r="L149" s="221"/>
       <c r="M149" s="12"/>
     </row>
     <row r="150" spans="1:13" ht="43.5" customHeight="1">
-      <c r="A150" s="218"/>
-      <c r="B150" s="207"/>
-      <c r="C150" s="226"/>
-      <c r="D150" s="206"/>
-      <c r="E150" s="207"/>
-      <c r="F150" s="227"/>
+      <c r="A150" s="226"/>
+      <c r="B150" s="221"/>
+      <c r="C150" s="234"/>
+      <c r="D150" s="220"/>
+      <c r="E150" s="221"/>
+      <c r="F150" s="235"/>
       <c r="G150" s="14" t="s">
         <v>304</v>
       </c>
@@ -8599,27 +8655,27 @@
       <c r="J150" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="K150" s="229"/>
-      <c r="L150" s="207"/>
+      <c r="K150" s="237"/>
+      <c r="L150" s="221"/>
       <c r="M150" s="12"/>
     </row>
     <row r="151" spans="1:13" ht="43.5" customHeight="1">
-      <c r="A151" s="218">
+      <c r="A151" s="226">
         <v>46</v>
       </c>
-      <c r="B151" s="208">
+      <c r="B151" s="222">
         <v>45980</v>
       </c>
-      <c r="C151" s="226" t="s">
+      <c r="C151" s="234" t="s">
         <v>125</v>
       </c>
-      <c r="D151" s="206" t="s">
+      <c r="D151" s="220" t="s">
         <v>306</v>
       </c>
-      <c r="E151" s="207" t="s">
+      <c r="E151" s="221" t="s">
         <v>298</v>
       </c>
-      <c r="F151" s="227" t="s">
+      <c r="F151" s="235" t="s">
         <v>307</v>
       </c>
       <c r="G151" s="14" t="s">
@@ -8634,21 +8690,21 @@
       <c r="J151" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="K151" s="233" t="s">
+      <c r="K151" s="241" t="s">
         <v>20</v>
       </c>
-      <c r="L151" s="207" t="s">
+      <c r="L151" s="221" t="s">
         <v>22</v>
       </c>
       <c r="M151" s="12"/>
     </row>
     <row r="152" spans="1:13" ht="43.5" customHeight="1">
-      <c r="A152" s="218"/>
-      <c r="B152" s="208"/>
-      <c r="C152" s="226"/>
-      <c r="D152" s="206"/>
-      <c r="E152" s="207"/>
-      <c r="F152" s="227"/>
+      <c r="A152" s="226"/>
+      <c r="B152" s="222"/>
+      <c r="C152" s="234"/>
+      <c r="D152" s="220"/>
+      <c r="E152" s="221"/>
+      <c r="F152" s="235"/>
       <c r="G152" s="14" t="s">
         <v>309</v>
       </c>
@@ -8661,17 +8717,17 @@
       <c r="J152" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="K152" s="233"/>
-      <c r="L152" s="207"/>
+      <c r="K152" s="241"/>
+      <c r="L152" s="221"/>
       <c r="M152" s="12"/>
     </row>
     <row r="153" spans="1:13" ht="43.5" customHeight="1">
-      <c r="A153" s="218"/>
-      <c r="B153" s="208"/>
-      <c r="C153" s="226"/>
-      <c r="D153" s="206"/>
-      <c r="E153" s="207"/>
-      <c r="F153" s="227"/>
+      <c r="A153" s="226"/>
+      <c r="B153" s="222"/>
+      <c r="C153" s="234"/>
+      <c r="D153" s="220"/>
+      <c r="E153" s="221"/>
+      <c r="F153" s="235"/>
       <c r="G153" s="14" t="s">
         <v>310</v>
       </c>
@@ -8684,17 +8740,17 @@
       <c r="J153" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="K153" s="233"/>
-      <c r="L153" s="207"/>
+      <c r="K153" s="241"/>
+      <c r="L153" s="221"/>
       <c r="M153" s="12"/>
     </row>
     <row r="154" spans="1:13" ht="49.5" customHeight="1">
-      <c r="A154" s="218"/>
-      <c r="B154" s="208"/>
-      <c r="C154" s="226"/>
-      <c r="D154" s="206"/>
-      <c r="E154" s="207"/>
-      <c r="F154" s="227"/>
+      <c r="A154" s="226"/>
+      <c r="B154" s="222"/>
+      <c r="C154" s="234"/>
+      <c r="D154" s="220"/>
+      <c r="E154" s="221"/>
+      <c r="F154" s="235"/>
       <c r="G154" s="14" t="s">
         <v>311</v>
       </c>
@@ -8707,8 +8763,8 @@
       <c r="J154" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="K154" s="233"/>
-      <c r="L154" s="207"/>
+      <c r="K154" s="241"/>
+      <c r="L154" s="221"/>
       <c r="M154" s="12"/>
     </row>
     <row r="155" spans="1:13" s="1" customFormat="1" ht="91.5" customHeight="1">
@@ -8786,22 +8842,22 @@
       <c r="M156" s="12"/>
     </row>
     <row r="157" spans="1:13" ht="90.75" customHeight="1">
-      <c r="A157" s="218">
+      <c r="A157" s="226">
         <v>49</v>
       </c>
-      <c r="B157" s="208">
+      <c r="B157" s="222">
         <v>45994</v>
       </c>
-      <c r="C157" s="207" t="s">
+      <c r="C157" s="221" t="s">
         <v>125</v>
       </c>
-      <c r="D157" s="206" t="s">
+      <c r="D157" s="220" t="s">
         <v>319</v>
       </c>
-      <c r="E157" s="236" t="s">
+      <c r="E157" s="244" t="s">
         <v>320</v>
       </c>
-      <c r="F157" s="227" t="s">
+      <c r="F157" s="235" t="s">
         <v>321</v>
       </c>
       <c r="G157" s="14" t="s">
@@ -8816,10 +8872,10 @@
       <c r="J157" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="K157" s="230" t="s">
+      <c r="K157" s="238" t="s">
         <v>20</v>
       </c>
-      <c r="L157" s="207" t="s">
+      <c r="L157" s="221" t="s">
         <v>22</v>
       </c>
       <c r="M157" s="12" t="s">
@@ -8827,12 +8883,12 @@
       </c>
     </row>
     <row r="158" spans="1:13" ht="59.25" customHeight="1">
-      <c r="A158" s="218"/>
-      <c r="B158" s="208"/>
-      <c r="C158" s="207"/>
-      <c r="D158" s="206"/>
-      <c r="E158" s="236"/>
-      <c r="F158" s="227"/>
+      <c r="A158" s="226"/>
+      <c r="B158" s="222"/>
+      <c r="C158" s="221"/>
+      <c r="D158" s="220"/>
+      <c r="E158" s="244"/>
+      <c r="F158" s="235"/>
       <c r="G158" s="14" t="s">
         <v>324</v>
       </c>
@@ -8845,17 +8901,17 @@
       <c r="J158" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="K158" s="230"/>
-      <c r="L158" s="207"/>
+      <c r="K158" s="238"/>
+      <c r="L158" s="221"/>
       <c r="M158" s="12"/>
     </row>
     <row r="159" spans="1:13" ht="72.75" customHeight="1">
-      <c r="A159" s="218"/>
-      <c r="B159" s="208"/>
-      <c r="C159" s="207"/>
-      <c r="D159" s="206"/>
-      <c r="E159" s="236"/>
-      <c r="F159" s="227"/>
+      <c r="A159" s="226"/>
+      <c r="B159" s="222"/>
+      <c r="C159" s="221"/>
+      <c r="D159" s="220"/>
+      <c r="E159" s="244"/>
+      <c r="F159" s="235"/>
       <c r="G159" s="14" t="s">
         <v>326</v>
       </c>
@@ -8868,17 +8924,17 @@
       <c r="J159" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="K159" s="230"/>
-      <c r="L159" s="207"/>
+      <c r="K159" s="238"/>
+      <c r="L159" s="221"/>
       <c r="M159" s="12"/>
     </row>
     <row r="160" spans="1:13" ht="41.25" customHeight="1">
-      <c r="A160" s="218"/>
-      <c r="B160" s="208"/>
-      <c r="C160" s="207"/>
-      <c r="D160" s="206"/>
-      <c r="E160" s="236"/>
-      <c r="F160" s="227"/>
+      <c r="A160" s="226"/>
+      <c r="B160" s="222"/>
+      <c r="C160" s="221"/>
+      <c r="D160" s="220"/>
+      <c r="E160" s="244"/>
+      <c r="F160" s="235"/>
       <c r="G160" s="14" t="s">
         <v>201</v>
       </c>
@@ -8891,17 +8947,17 @@
       <c r="J160" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="K160" s="230"/>
-      <c r="L160" s="207"/>
+      <c r="K160" s="238"/>
+      <c r="L160" s="221"/>
       <c r="M160" s="12"/>
     </row>
     <row r="161" spans="1:13" ht="57" customHeight="1">
-      <c r="A161" s="218"/>
-      <c r="B161" s="208"/>
-      <c r="C161" s="207"/>
-      <c r="D161" s="206"/>
-      <c r="E161" s="236"/>
-      <c r="F161" s="227"/>
+      <c r="A161" s="226"/>
+      <c r="B161" s="222"/>
+      <c r="C161" s="221"/>
+      <c r="D161" s="220"/>
+      <c r="E161" s="244"/>
+      <c r="F161" s="235"/>
       <c r="G161" s="14" t="s">
         <v>329</v>
       </c>
@@ -8914,17 +8970,17 @@
       <c r="J161" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="K161" s="230"/>
-      <c r="L161" s="207"/>
+      <c r="K161" s="238"/>
+      <c r="L161" s="221"/>
       <c r="M161" s="12"/>
     </row>
     <row r="162" spans="1:13" ht="45" customHeight="1">
-      <c r="A162" s="218"/>
-      <c r="B162" s="208"/>
-      <c r="C162" s="207"/>
-      <c r="D162" s="206"/>
-      <c r="E162" s="236"/>
-      <c r="F162" s="227"/>
+      <c r="A162" s="226"/>
+      <c r="B162" s="222"/>
+      <c r="C162" s="221"/>
+      <c r="D162" s="220"/>
+      <c r="E162" s="244"/>
+      <c r="F162" s="235"/>
       <c r="G162" s="14" t="s">
         <v>331</v>
       </c>
@@ -8937,17 +8993,17 @@
       <c r="J162" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="K162" s="230"/>
-      <c r="L162" s="207"/>
+      <c r="K162" s="238"/>
+      <c r="L162" s="221"/>
       <c r="M162" s="12"/>
     </row>
     <row r="163" spans="1:13" ht="36.75" customHeight="1">
-      <c r="A163" s="218"/>
-      <c r="B163" s="208"/>
-      <c r="C163" s="207"/>
-      <c r="D163" s="206"/>
-      <c r="E163" s="236"/>
-      <c r="F163" s="227"/>
+      <c r="A163" s="226"/>
+      <c r="B163" s="222"/>
+      <c r="C163" s="221"/>
+      <c r="D163" s="220"/>
+      <c r="E163" s="244"/>
+      <c r="F163" s="235"/>
       <c r="G163" s="14" t="s">
         <v>333</v>
       </c>
@@ -8960,17 +9016,17 @@
       <c r="J163" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="K163" s="230"/>
-      <c r="L163" s="207"/>
+      <c r="K163" s="238"/>
+      <c r="L163" s="221"/>
       <c r="M163" s="12"/>
     </row>
     <row r="164" spans="1:13" ht="45.75" customHeight="1">
-      <c r="A164" s="218"/>
-      <c r="B164" s="208"/>
-      <c r="C164" s="207"/>
-      <c r="D164" s="206"/>
-      <c r="E164" s="236"/>
-      <c r="F164" s="227"/>
+      <c r="A164" s="226"/>
+      <c r="B164" s="222"/>
+      <c r="C164" s="221"/>
+      <c r="D164" s="220"/>
+      <c r="E164" s="244"/>
+      <c r="F164" s="235"/>
       <c r="G164" s="14" t="s">
         <v>335</v>
       </c>
@@ -8983,17 +9039,17 @@
       <c r="J164" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="K164" s="230"/>
-      <c r="L164" s="207"/>
+      <c r="K164" s="238"/>
+      <c r="L164" s="221"/>
       <c r="M164" s="12"/>
     </row>
     <row r="165" spans="1:13" ht="45.75" customHeight="1">
-      <c r="A165" s="218"/>
-      <c r="B165" s="208"/>
-      <c r="C165" s="207"/>
-      <c r="D165" s="206"/>
-      <c r="E165" s="236"/>
-      <c r="F165" s="227"/>
+      <c r="A165" s="226"/>
+      <c r="B165" s="222"/>
+      <c r="C165" s="221"/>
+      <c r="D165" s="220"/>
+      <c r="E165" s="244"/>
+      <c r="F165" s="235"/>
       <c r="G165" s="14" t="s">
         <v>336</v>
       </c>
@@ -9004,17 +9060,17 @@
       <c r="J165" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="K165" s="230"/>
-      <c r="L165" s="207"/>
+      <c r="K165" s="238"/>
+      <c r="L165" s="221"/>
       <c r="M165" s="12"/>
     </row>
     <row r="166" spans="1:13" ht="45.75" customHeight="1">
-      <c r="A166" s="218"/>
-      <c r="B166" s="208"/>
-      <c r="C166" s="207"/>
-      <c r="D166" s="206"/>
-      <c r="E166" s="236"/>
-      <c r="F166" s="227"/>
+      <c r="A166" s="226"/>
+      <c r="B166" s="222"/>
+      <c r="C166" s="221"/>
+      <c r="D166" s="220"/>
+      <c r="E166" s="244"/>
+      <c r="F166" s="235"/>
       <c r="G166" s="14" t="s">
         <v>337</v>
       </c>
@@ -9025,17 +9081,17 @@
       <c r="J166" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="K166" s="230"/>
-      <c r="L166" s="207"/>
+      <c r="K166" s="238"/>
+      <c r="L166" s="221"/>
       <c r="M166" s="12"/>
     </row>
     <row r="167" spans="1:13" ht="45.75" customHeight="1">
-      <c r="A167" s="218"/>
-      <c r="B167" s="208"/>
-      <c r="C167" s="207"/>
-      <c r="D167" s="206"/>
-      <c r="E167" s="236"/>
-      <c r="F167" s="227"/>
+      <c r="A167" s="226"/>
+      <c r="B167" s="222"/>
+      <c r="C167" s="221"/>
+      <c r="D167" s="220"/>
+      <c r="E167" s="244"/>
+      <c r="F167" s="235"/>
       <c r="G167" s="14" t="s">
         <v>338</v>
       </c>
@@ -9046,17 +9102,17 @@
       <c r="J167" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="K167" s="230"/>
-      <c r="L167" s="207"/>
+      <c r="K167" s="238"/>
+      <c r="L167" s="221"/>
       <c r="M167" s="12"/>
     </row>
     <row r="168" spans="1:13" ht="45.75" customHeight="1">
-      <c r="A168" s="218"/>
-      <c r="B168" s="208"/>
-      <c r="C168" s="207"/>
-      <c r="D168" s="206"/>
-      <c r="E168" s="236"/>
-      <c r="F168" s="227"/>
+      <c r="A168" s="226"/>
+      <c r="B168" s="222"/>
+      <c r="C168" s="221"/>
+      <c r="D168" s="220"/>
+      <c r="E168" s="244"/>
+      <c r="F168" s="235"/>
       <c r="G168" s="14" t="s">
         <v>339</v>
       </c>
@@ -9067,17 +9123,17 @@
       <c r="J168" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="K168" s="230"/>
-      <c r="L168" s="207"/>
+      <c r="K168" s="238"/>
+      <c r="L168" s="221"/>
       <c r="M168" s="12"/>
     </row>
     <row r="169" spans="1:13" ht="66.75" customHeight="1">
-      <c r="A169" s="218"/>
-      <c r="B169" s="208"/>
-      <c r="C169" s="207"/>
-      <c r="D169" s="206"/>
-      <c r="E169" s="236"/>
-      <c r="F169" s="227"/>
+      <c r="A169" s="226"/>
+      <c r="B169" s="222"/>
+      <c r="C169" s="221"/>
+      <c r="D169" s="220"/>
+      <c r="E169" s="244"/>
+      <c r="F169" s="235"/>
       <c r="G169" s="14" t="s">
         <v>340</v>
       </c>
@@ -9088,27 +9144,27 @@
       <c r="J169" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="K169" s="230"/>
-      <c r="L169" s="207"/>
+      <c r="K169" s="238"/>
+      <c r="L169" s="221"/>
       <c r="M169" s="12"/>
     </row>
     <row r="170" spans="1:13" ht="99" customHeight="1">
-      <c r="A170" s="207">
+      <c r="A170" s="221">
         <v>50</v>
       </c>
-      <c r="B170" s="208">
+      <c r="B170" s="222">
         <v>46011</v>
       </c>
-      <c r="C170" s="207" t="s">
+      <c r="C170" s="221" t="s">
         <v>265</v>
       </c>
-      <c r="D170" s="206" t="s">
+      <c r="D170" s="220" t="s">
         <v>341</v>
       </c>
-      <c r="E170" s="206" t="s">
+      <c r="E170" s="220" t="s">
         <v>298</v>
       </c>
-      <c r="F170" s="227" t="s">
+      <c r="F170" s="235" t="s">
         <v>342</v>
       </c>
       <c r="G170" s="71" t="s">
@@ -9123,21 +9179,21 @@
       <c r="J170" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="K170" s="230" t="s">
+      <c r="K170" s="238" t="s">
         <v>22</v>
       </c>
-      <c r="L170" s="207" t="s">
+      <c r="L170" s="221" t="s">
         <v>22</v>
       </c>
       <c r="M170" s="12"/>
     </row>
     <row r="171" spans="1:13" ht="78.75" customHeight="1">
-      <c r="A171" s="207"/>
-      <c r="B171" s="208"/>
-      <c r="C171" s="207"/>
-      <c r="D171" s="206"/>
-      <c r="E171" s="207"/>
-      <c r="F171" s="227"/>
+      <c r="A171" s="221"/>
+      <c r="B171" s="222"/>
+      <c r="C171" s="221"/>
+      <c r="D171" s="220"/>
+      <c r="E171" s="221"/>
+      <c r="F171" s="235"/>
       <c r="G171" s="72" t="s">
         <v>345</v>
       </c>
@@ -9150,17 +9206,17 @@
       <c r="J171" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="K171" s="230"/>
-      <c r="L171" s="207"/>
+      <c r="K171" s="238"/>
+      <c r="L171" s="221"/>
       <c r="M171" s="12"/>
     </row>
     <row r="172" spans="1:13" ht="105" customHeight="1">
-      <c r="A172" s="207"/>
-      <c r="B172" s="208"/>
-      <c r="C172" s="207"/>
-      <c r="D172" s="206"/>
-      <c r="E172" s="207"/>
-      <c r="F172" s="227"/>
+      <c r="A172" s="221"/>
+      <c r="B172" s="222"/>
+      <c r="C172" s="221"/>
+      <c r="D172" s="220"/>
+      <c r="E172" s="221"/>
+      <c r="F172" s="235"/>
       <c r="G172" s="71" t="s">
         <v>346</v>
       </c>
@@ -9173,17 +9229,17 @@
       <c r="J172" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="K172" s="230"/>
-      <c r="L172" s="207"/>
+      <c r="K172" s="238"/>
+      <c r="L172" s="221"/>
       <c r="M172" s="12"/>
     </row>
     <row r="173" spans="1:13" ht="86.25" customHeight="1">
-      <c r="A173" s="207"/>
-      <c r="B173" s="208"/>
-      <c r="C173" s="207"/>
-      <c r="D173" s="206"/>
-      <c r="E173" s="207"/>
-      <c r="F173" s="227"/>
+      <c r="A173" s="221"/>
+      <c r="B173" s="222"/>
+      <c r="C173" s="221"/>
+      <c r="D173" s="220"/>
+      <c r="E173" s="221"/>
+      <c r="F173" s="235"/>
       <c r="G173" s="71" t="s">
         <v>347</v>
       </c>
@@ -9196,17 +9252,17 @@
       <c r="J173" s="81" t="s">
         <v>20</v>
       </c>
-      <c r="K173" s="230"/>
-      <c r="L173" s="207"/>
+      <c r="K173" s="238"/>
+      <c r="L173" s="221"/>
       <c r="M173" s="12"/>
     </row>
     <row r="174" spans="1:13" ht="61.5" customHeight="1">
-      <c r="A174" s="207"/>
-      <c r="B174" s="208"/>
-      <c r="C174" s="207"/>
-      <c r="D174" s="206"/>
-      <c r="E174" s="207"/>
-      <c r="F174" s="227"/>
+      <c r="A174" s="221"/>
+      <c r="B174" s="222"/>
+      <c r="C174" s="221"/>
+      <c r="D174" s="220"/>
+      <c r="E174" s="221"/>
+      <c r="F174" s="235"/>
       <c r="G174" s="71" t="s">
         <v>348</v>
       </c>
@@ -9219,8 +9275,8 @@
       <c r="J174" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="K174" s="230"/>
-      <c r="L174" s="207"/>
+      <c r="K174" s="238"/>
+      <c r="L174" s="221"/>
       <c r="M174" s="12"/>
     </row>
     <row r="175" spans="1:13" ht="66" customHeight="1">
@@ -9265,22 +9321,22 @@
       </c>
     </row>
     <row r="176" spans="1:13" ht="65.25" customHeight="1">
-      <c r="A176" s="207">
+      <c r="A176" s="221">
         <v>52</v>
       </c>
-      <c r="B176" s="208">
+      <c r="B176" s="222">
         <v>46014</v>
       </c>
-      <c r="C176" s="207" t="s">
+      <c r="C176" s="221" t="s">
         <v>125</v>
       </c>
-      <c r="D176" s="206" t="s">
+      <c r="D176" s="220" t="s">
         <v>352</v>
       </c>
-      <c r="E176" s="207" t="s">
+      <c r="E176" s="221" t="s">
         <v>47</v>
       </c>
-      <c r="F176" s="227" t="s">
+      <c r="F176" s="235" t="s">
         <v>353</v>
       </c>
       <c r="G176" s="115" t="s">
@@ -9295,19 +9351,19 @@
       <c r="J176" s="50" t="s">
         <v>222</v>
       </c>
-      <c r="K176" s="231" t="s">
+      <c r="K176" s="239" t="s">
         <v>22</v>
       </c>
-      <c r="L176" s="207"/>
+      <c r="L176" s="221"/>
       <c r="M176" s="12"/>
     </row>
     <row r="177" spans="1:13" ht="45" customHeight="1">
-      <c r="A177" s="207"/>
-      <c r="B177" s="208"/>
-      <c r="C177" s="207"/>
-      <c r="D177" s="207"/>
-      <c r="E177" s="207"/>
-      <c r="F177" s="227"/>
+      <c r="A177" s="221"/>
+      <c r="B177" s="222"/>
+      <c r="C177" s="221"/>
+      <c r="D177" s="221"/>
+      <c r="E177" s="221"/>
+      <c r="F177" s="235"/>
       <c r="G177" s="115" t="s">
         <v>356</v>
       </c>
@@ -9320,17 +9376,17 @@
       <c r="J177" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="K177" s="231"/>
-      <c r="L177" s="207"/>
+      <c r="K177" s="239"/>
+      <c r="L177" s="221"/>
       <c r="M177" s="12"/>
     </row>
     <row r="178" spans="1:13" ht="45" customHeight="1">
-      <c r="A178" s="207"/>
-      <c r="B178" s="208"/>
-      <c r="C178" s="207"/>
-      <c r="D178" s="207"/>
-      <c r="E178" s="207"/>
-      <c r="F178" s="227"/>
+      <c r="A178" s="221"/>
+      <c r="B178" s="222"/>
+      <c r="C178" s="221"/>
+      <c r="D178" s="221"/>
+      <c r="E178" s="221"/>
+      <c r="F178" s="235"/>
       <c r="G178" s="115" t="s">
         <v>357</v>
       </c>
@@ -9343,27 +9399,27 @@
       <c r="J178" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="K178" s="231"/>
-      <c r="L178" s="207"/>
+      <c r="K178" s="239"/>
+      <c r="L178" s="221"/>
       <c r="M178" s="12"/>
     </row>
     <row r="179" spans="1:13" ht="90" customHeight="1">
-      <c r="A179" s="207">
+      <c r="A179" s="221">
         <v>53</v>
       </c>
-      <c r="B179" s="208">
+      <c r="B179" s="222">
         <v>46027</v>
       </c>
-      <c r="C179" s="207" t="s">
+      <c r="C179" s="221" t="s">
         <v>265</v>
       </c>
-      <c r="D179" s="206" t="s">
+      <c r="D179" s="220" t="s">
         <v>359</v>
       </c>
-      <c r="E179" s="207" t="s">
+      <c r="E179" s="221" t="s">
         <v>47</v>
       </c>
-      <c r="F179" s="227" t="s">
+      <c r="F179" s="235" t="s">
         <v>360</v>
       </c>
       <c r="G179" s="116" t="s">
@@ -9378,19 +9434,19 @@
       <c r="J179" s="50" t="s">
         <v>222</v>
       </c>
-      <c r="K179" s="231" t="s">
+      <c r="K179" s="239" t="s">
         <v>22</v>
       </c>
-      <c r="L179" s="207"/>
+      <c r="L179" s="221"/>
       <c r="M179" s="12"/>
     </row>
     <row r="180" spans="1:13" ht="76.5" customHeight="1">
-      <c r="A180" s="207"/>
-      <c r="B180" s="208"/>
-      <c r="C180" s="207"/>
-      <c r="D180" s="206"/>
-      <c r="E180" s="207"/>
-      <c r="F180" s="227"/>
+      <c r="A180" s="221"/>
+      <c r="B180" s="222"/>
+      <c r="C180" s="221"/>
+      <c r="D180" s="220"/>
+      <c r="E180" s="221"/>
+      <c r="F180" s="235"/>
       <c r="G180" s="116" t="s">
         <v>362</v>
       </c>
@@ -9403,17 +9459,17 @@
       <c r="J180" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="K180" s="231"/>
-      <c r="L180" s="207"/>
+      <c r="K180" s="239"/>
+      <c r="L180" s="221"/>
       <c r="M180" s="12"/>
     </row>
     <row r="181" spans="1:13" ht="49.5" customHeight="1">
-      <c r="A181" s="207"/>
-      <c r="B181" s="208"/>
-      <c r="C181" s="207"/>
-      <c r="D181" s="206"/>
-      <c r="E181" s="207"/>
-      <c r="F181" s="227"/>
+      <c r="A181" s="221"/>
+      <c r="B181" s="222"/>
+      <c r="C181" s="221"/>
+      <c r="D181" s="220"/>
+      <c r="E181" s="221"/>
+      <c r="F181" s="235"/>
       <c r="G181" s="116" t="s">
         <v>363</v>
       </c>
@@ -9426,27 +9482,27 @@
       <c r="J181" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="K181" s="231"/>
-      <c r="L181" s="207"/>
+      <c r="K181" s="239"/>
+      <c r="L181" s="221"/>
       <c r="M181" s="12"/>
     </row>
     <row r="182" spans="1:13" ht="81.75" customHeight="1">
-      <c r="A182" s="207">
+      <c r="A182" s="221">
         <v>54</v>
       </c>
-      <c r="B182" s="208">
+      <c r="B182" s="222">
         <v>46035</v>
       </c>
-      <c r="C182" s="207" t="s">
+      <c r="C182" s="221" t="s">
         <v>125</v>
       </c>
-      <c r="D182" s="206" t="s">
+      <c r="D182" s="220" t="s">
         <v>364</v>
       </c>
-      <c r="E182" s="207" t="s">
+      <c r="E182" s="221" t="s">
         <v>182</v>
       </c>
-      <c r="F182" s="227" t="s">
+      <c r="F182" s="235" t="s">
         <v>365</v>
       </c>
       <c r="G182" s="116" t="s">
@@ -9461,21 +9517,21 @@
       <c r="J182" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="K182" s="231" t="s">
+      <c r="K182" s="239" t="s">
         <v>20</v>
       </c>
-      <c r="L182" s="207"/>
+      <c r="L182" s="221"/>
       <c r="M182" s="12" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="183" spans="1:13" ht="84.75" customHeight="1">
-      <c r="A183" s="207"/>
-      <c r="B183" s="208"/>
-      <c r="C183" s="207"/>
-      <c r="D183" s="206"/>
-      <c r="E183" s="207"/>
-      <c r="F183" s="227"/>
+      <c r="A183" s="221"/>
+      <c r="B183" s="222"/>
+      <c r="C183" s="221"/>
+      <c r="D183" s="220"/>
+      <c r="E183" s="221"/>
+      <c r="F183" s="235"/>
       <c r="G183" s="71" t="s">
         <v>367</v>
       </c>
@@ -9488,17 +9544,17 @@
       <c r="J183" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="K183" s="231"/>
-      <c r="L183" s="207"/>
+      <c r="K183" s="239"/>
+      <c r="L183" s="221"/>
       <c r="M183" s="12"/>
     </row>
     <row r="184" spans="1:13" ht="68.25" customHeight="1">
-      <c r="A184" s="207"/>
-      <c r="B184" s="208"/>
-      <c r="C184" s="207"/>
-      <c r="D184" s="206"/>
-      <c r="E184" s="207"/>
-      <c r="F184" s="227"/>
+      <c r="A184" s="221"/>
+      <c r="B184" s="222"/>
+      <c r="C184" s="221"/>
+      <c r="D184" s="220"/>
+      <c r="E184" s="221"/>
+      <c r="F184" s="235"/>
       <c r="G184" s="71" t="s">
         <v>368</v>
       </c>
@@ -9511,27 +9567,27 @@
       <c r="J184" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="K184" s="231"/>
-      <c r="L184" s="207"/>
+      <c r="K184" s="239"/>
+      <c r="L184" s="221"/>
       <c r="M184" s="12"/>
     </row>
     <row r="185" spans="1:13" ht="111.75" customHeight="1">
-      <c r="A185" s="207">
+      <c r="A185" s="221">
         <v>55</v>
       </c>
-      <c r="B185" s="208">
+      <c r="B185" s="222">
         <v>46053</v>
       </c>
-      <c r="C185" s="207" t="s">
+      <c r="C185" s="221" t="s">
         <v>125</v>
       </c>
-      <c r="D185" s="206" t="s">
+      <c r="D185" s="220" t="s">
         <v>370</v>
       </c>
-      <c r="E185" s="207" t="s">
+      <c r="E185" s="221" t="s">
         <v>27</v>
       </c>
-      <c r="F185" s="227" t="s">
+      <c r="F185" s="235" t="s">
         <v>371</v>
       </c>
       <c r="G185" s="71" t="s">
@@ -9549,16 +9605,16 @@
       <c r="K185" s="98" t="s">
         <v>22</v>
       </c>
-      <c r="L185" s="207"/>
+      <c r="L185" s="221"/>
       <c r="M185" s="12"/>
     </row>
     <row r="186" spans="1:13" ht="116.25" customHeight="1">
-      <c r="A186" s="207"/>
-      <c r="B186" s="208"/>
-      <c r="C186" s="207"/>
-      <c r="D186" s="206"/>
-      <c r="E186" s="207"/>
-      <c r="F186" s="227"/>
+      <c r="A186" s="221"/>
+      <c r="B186" s="222"/>
+      <c r="C186" s="221"/>
+      <c r="D186" s="220"/>
+      <c r="E186" s="221"/>
+      <c r="F186" s="235"/>
       <c r="G186" s="146" t="s">
         <v>374</v>
       </c>
@@ -9572,26 +9628,26 @@
       <c r="K186" s="98" t="s">
         <v>22</v>
       </c>
-      <c r="L186" s="207"/>
+      <c r="L186" s="221"/>
       <c r="M186" s="12"/>
     </row>
     <row r="187" spans="1:13" ht="54.75" customHeight="1">
-      <c r="A187" s="207">
+      <c r="A187" s="221">
         <v>56</v>
       </c>
-      <c r="B187" s="208">
+      <c r="B187" s="222">
         <v>46059</v>
       </c>
-      <c r="C187" s="207" t="s">
+      <c r="C187" s="221" t="s">
         <v>125</v>
       </c>
-      <c r="D187" s="304" t="s">
+      <c r="D187" s="309" t="s">
         <v>375</v>
       </c>
-      <c r="E187" s="207" t="s">
+      <c r="E187" s="221" t="s">
         <v>47</v>
       </c>
-      <c r="F187" s="227" t="s">
+      <c r="F187" s="235" t="s">
         <v>376</v>
       </c>
       <c r="G187" s="71" t="s">
@@ -9604,19 +9660,19 @@
       <c r="J187" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="K187" s="224" t="s">
+      <c r="K187" s="232" t="s">
         <v>22</v>
       </c>
-      <c r="L187" s="257"/>
+      <c r="L187" s="265"/>
       <c r="M187" s="12"/>
     </row>
     <row r="188" spans="1:13" ht="83.25" customHeight="1">
-      <c r="A188" s="207"/>
-      <c r="B188" s="208"/>
-      <c r="C188" s="207"/>
-      <c r="D188" s="304"/>
-      <c r="E188" s="207"/>
-      <c r="F188" s="227"/>
+      <c r="A188" s="221"/>
+      <c r="B188" s="222"/>
+      <c r="C188" s="221"/>
+      <c r="D188" s="309"/>
+      <c r="E188" s="221"/>
+      <c r="F188" s="235"/>
       <c r="G188" s="116" t="s">
         <v>378</v>
       </c>
@@ -9627,17 +9683,17 @@
       <c r="J188" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="K188" s="224"/>
-      <c r="L188" s="257"/>
+      <c r="K188" s="232"/>
+      <c r="L188" s="265"/>
       <c r="M188" s="12"/>
     </row>
     <row r="189" spans="1:13" ht="136.5" customHeight="1">
-      <c r="A189" s="207"/>
-      <c r="B189" s="208"/>
-      <c r="C189" s="207"/>
-      <c r="D189" s="304"/>
-      <c r="E189" s="207"/>
-      <c r="F189" s="227"/>
+      <c r="A189" s="221"/>
+      <c r="B189" s="222"/>
+      <c r="C189" s="221"/>
+      <c r="D189" s="309"/>
+      <c r="E189" s="221"/>
+      <c r="F189" s="235"/>
       <c r="G189" s="116" t="s">
         <v>379</v>
       </c>
@@ -9650,27 +9706,27 @@
       <c r="J189" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="K189" s="209"/>
-      <c r="L189" s="257"/>
+      <c r="K189" s="223"/>
+      <c r="L189" s="265"/>
       <c r="M189" s="12"/>
     </row>
     <row r="190" spans="1:13" ht="52.5" customHeight="1">
-      <c r="A190" s="207">
+      <c r="A190" s="221">
         <v>57</v>
       </c>
-      <c r="B190" s="208">
+      <c r="B190" s="222">
         <v>46059</v>
       </c>
-      <c r="C190" s="207" t="s">
+      <c r="C190" s="221" t="s">
         <v>125</v>
       </c>
-      <c r="D190" s="206" t="s">
+      <c r="D190" s="220" t="s">
         <v>381</v>
       </c>
-      <c r="E190" s="207" t="s">
+      <c r="E190" s="221" t="s">
         <v>47</v>
       </c>
-      <c r="F190" s="227" t="s">
+      <c r="F190" s="235" t="s">
         <v>382</v>
       </c>
       <c r="G190" s="116" t="s">
@@ -9685,19 +9741,19 @@
       <c r="J190" s="82" t="s">
         <v>222</v>
       </c>
-      <c r="K190" s="224" t="s">
+      <c r="K190" s="232" t="s">
         <v>22</v>
       </c>
-      <c r="L190" s="207"/>
+      <c r="L190" s="221"/>
       <c r="M190" s="12"/>
     </row>
     <row r="191" spans="1:13" ht="51.75" customHeight="1">
-      <c r="A191" s="207"/>
-      <c r="B191" s="208"/>
-      <c r="C191" s="207"/>
-      <c r="D191" s="206"/>
-      <c r="E191" s="207"/>
-      <c r="F191" s="227"/>
+      <c r="A191" s="221"/>
+      <c r="B191" s="222"/>
+      <c r="C191" s="221"/>
+      <c r="D191" s="220"/>
+      <c r="E191" s="221"/>
+      <c r="F191" s="235"/>
       <c r="G191" s="116" t="s">
         <v>385</v>
       </c>
@@ -9710,27 +9766,27 @@
       <c r="J191" s="82" t="s">
         <v>196</v>
       </c>
-      <c r="K191" s="224"/>
-      <c r="L191" s="207"/>
+      <c r="K191" s="232"/>
+      <c r="L191" s="221"/>
       <c r="M191" s="12"/>
     </row>
     <row r="192" spans="1:13" ht="54" customHeight="1">
-      <c r="A192" s="207">
+      <c r="A192" s="221">
         <v>58</v>
       </c>
-      <c r="B192" s="208">
+      <c r="B192" s="222">
         <v>46068</v>
       </c>
-      <c r="C192" s="207" t="s">
+      <c r="C192" s="221" t="s">
         <v>312</v>
       </c>
-      <c r="D192" s="206" t="s">
+      <c r="D192" s="220" t="s">
         <v>386</v>
       </c>
-      <c r="E192" s="207" t="s">
+      <c r="E192" s="221" t="s">
         <v>47</v>
       </c>
-      <c r="F192" s="227" t="s">
+      <c r="F192" s="235" t="s">
         <v>387</v>
       </c>
       <c r="G192" s="117" t="s">
@@ -9745,19 +9801,19 @@
       <c r="J192" s="82" t="s">
         <v>196</v>
       </c>
-      <c r="K192" s="260" t="s">
+      <c r="K192" s="209" t="s">
         <v>390</v>
       </c>
-      <c r="L192" s="207"/>
+      <c r="L192" s="221"/>
       <c r="M192" s="12"/>
     </row>
     <row r="193" spans="1:2438" ht="50.25" customHeight="1">
-      <c r="A193" s="207"/>
-      <c r="B193" s="208"/>
-      <c r="C193" s="207"/>
-      <c r="D193" s="206"/>
-      <c r="E193" s="207"/>
-      <c r="F193" s="227"/>
+      <c r="A193" s="221"/>
+      <c r="B193" s="222"/>
+      <c r="C193" s="221"/>
+      <c r="D193" s="220"/>
+      <c r="E193" s="221"/>
+      <c r="F193" s="235"/>
       <c r="G193" s="116" t="s">
         <v>391</v>
       </c>
@@ -9770,17 +9826,17 @@
       <c r="J193" s="69" t="s">
         <v>222</v>
       </c>
-      <c r="K193" s="224"/>
-      <c r="L193" s="207"/>
+      <c r="K193" s="232"/>
+      <c r="L193" s="221"/>
       <c r="M193" s="12"/>
     </row>
     <row r="194" spans="1:2438" ht="55.5" customHeight="1">
-      <c r="A194" s="207"/>
-      <c r="B194" s="208"/>
-      <c r="C194" s="207"/>
-      <c r="D194" s="206"/>
-      <c r="E194" s="207"/>
-      <c r="F194" s="227"/>
+      <c r="A194" s="221"/>
+      <c r="B194" s="222"/>
+      <c r="C194" s="221"/>
+      <c r="D194" s="220"/>
+      <c r="E194" s="221"/>
+      <c r="F194" s="235"/>
       <c r="G194" s="116" t="s">
         <v>392</v>
       </c>
@@ -9793,8 +9849,8 @@
       <c r="J194" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="K194" s="224"/>
-      <c r="L194" s="207"/>
+      <c r="K194" s="232"/>
+      <c r="L194" s="221"/>
       <c r="M194" s="12"/>
     </row>
     <row r="195" spans="1:2438" ht="167.25" customHeight="1">
@@ -9837,22 +9893,22 @@
       <c r="M195" s="12"/>
     </row>
     <row r="196" spans="1:2438" ht="53.25" customHeight="1">
-      <c r="A196" s="212">
+      <c r="A196" s="200">
         <v>60</v>
       </c>
-      <c r="B196" s="216">
+      <c r="B196" s="203">
         <v>46075</v>
       </c>
-      <c r="C196" s="212" t="s">
+      <c r="C196" s="200" t="s">
         <v>125</v>
       </c>
-      <c r="D196" s="214" t="s">
+      <c r="D196" s="206" t="s">
         <v>398</v>
       </c>
-      <c r="E196" s="212" t="s">
+      <c r="E196" s="200" t="s">
         <v>47</v>
       </c>
-      <c r="F196" s="221" t="s">
+      <c r="F196" s="229" t="s">
         <v>399</v>
       </c>
       <c r="G196" s="73" t="s">
@@ -9872,12 +9928,12 @@
       <c r="M196" s="12"/>
     </row>
     <row r="197" spans="1:2438" ht="59.25" customHeight="1">
-      <c r="A197" s="259"/>
-      <c r="B197" s="305"/>
-      <c r="C197" s="259"/>
-      <c r="D197" s="303"/>
-      <c r="E197" s="259"/>
-      <c r="F197" s="222"/>
+      <c r="A197" s="201"/>
+      <c r="B197" s="204"/>
+      <c r="C197" s="201"/>
+      <c r="D197" s="207"/>
+      <c r="E197" s="201"/>
+      <c r="F197" s="230"/>
       <c r="G197" s="73" t="s">
         <v>402</v>
       </c>
@@ -9893,12 +9949,12 @@
       <c r="M197" s="12"/>
     </row>
     <row r="198" spans="1:2438" ht="57" customHeight="1">
-      <c r="A198" s="259"/>
-      <c r="B198" s="305"/>
-      <c r="C198" s="259"/>
-      <c r="D198" s="303"/>
-      <c r="E198" s="259"/>
-      <c r="F198" s="222"/>
+      <c r="A198" s="201"/>
+      <c r="B198" s="204"/>
+      <c r="C198" s="201"/>
+      <c r="D198" s="207"/>
+      <c r="E198" s="201"/>
+      <c r="F198" s="230"/>
       <c r="G198" s="73" t="s">
         <v>403</v>
       </c>
@@ -9914,12 +9970,12 @@
       <c r="M198" s="12"/>
     </row>
     <row r="199" spans="1:2438" ht="42.75" customHeight="1">
-      <c r="A199" s="213"/>
-      <c r="B199" s="217"/>
-      <c r="C199" s="213"/>
-      <c r="D199" s="215"/>
-      <c r="E199" s="213"/>
-      <c r="F199" s="223"/>
+      <c r="A199" s="202"/>
+      <c r="B199" s="205"/>
+      <c r="C199" s="202"/>
+      <c r="D199" s="208"/>
+      <c r="E199" s="202"/>
+      <c r="F199" s="231"/>
       <c r="G199" s="73" t="s">
         <v>404</v>
       </c>
@@ -10001,22 +10057,22 @@
       <c r="M201" s="12"/>
     </row>
     <row r="202" spans="1:2438" s="62" customFormat="1" ht="84.75" customHeight="1">
-      <c r="A202" s="312">
+      <c r="A202" s="316">
         <v>63</v>
       </c>
-      <c r="B202" s="313">
+      <c r="B202" s="317">
         <v>46082</v>
       </c>
-      <c r="C202" s="312" t="s">
+      <c r="C202" s="316" t="s">
         <v>409</v>
       </c>
-      <c r="D202" s="314" t="s">
+      <c r="D202" s="318" t="s">
         <v>410</v>
       </c>
-      <c r="E202" s="312" t="s">
+      <c r="E202" s="316" t="s">
         <v>47</v>
       </c>
-      <c r="F202" s="306" t="s">
+      <c r="F202" s="310" t="s">
         <v>411</v>
       </c>
       <c r="G202" s="119" t="s">
@@ -12461,12 +12517,12 @@
       <c r="COT202"/>
     </row>
     <row r="203" spans="1:2438" s="62" customFormat="1" ht="78" customHeight="1">
-      <c r="A203" s="312"/>
-      <c r="B203" s="313"/>
-      <c r="C203" s="312"/>
-      <c r="D203" s="314"/>
-      <c r="E203" s="312"/>
-      <c r="F203" s="307"/>
+      <c r="A203" s="316"/>
+      <c r="B203" s="317"/>
+      <c r="C203" s="316"/>
+      <c r="D203" s="318"/>
+      <c r="E203" s="316"/>
+      <c r="F203" s="311"/>
       <c r="G203" s="120" t="s">
         <v>414</v>
       </c>
@@ -14909,22 +14965,22 @@
       <c r="COT203"/>
     </row>
     <row r="204" spans="1:2438" s="62" customFormat="1" ht="78" customHeight="1">
-      <c r="A204" s="310">
+      <c r="A204" s="314">
         <v>64</v>
       </c>
-      <c r="B204" s="308">
+      <c r="B204" s="312">
         <v>46082</v>
       </c>
-      <c r="C204" s="310" t="s">
+      <c r="C204" s="314" t="s">
         <v>265</v>
       </c>
-      <c r="D204" s="315" t="s">
+      <c r="D204" s="319" t="s">
         <v>417</v>
       </c>
-      <c r="E204" s="310" t="s">
+      <c r="E204" s="314" t="s">
         <v>47</v>
       </c>
-      <c r="F204" s="306" t="s">
+      <c r="F204" s="310" t="s">
         <v>418</v>
       </c>
       <c r="G204" s="120" t="s">
@@ -17369,12 +17425,12 @@
       <c r="COT204"/>
     </row>
     <row r="205" spans="1:2438" s="62" customFormat="1" ht="142.5" customHeight="1">
-      <c r="A205" s="311"/>
-      <c r="B205" s="309"/>
-      <c r="C205" s="311"/>
-      <c r="D205" s="316"/>
-      <c r="E205" s="311"/>
-      <c r="F205" s="307"/>
+      <c r="A205" s="315"/>
+      <c r="B205" s="313"/>
+      <c r="C205" s="315"/>
+      <c r="D205" s="320"/>
+      <c r="E205" s="315"/>
+      <c r="F205" s="311"/>
       <c r="G205" s="120" t="s">
         <v>421</v>
       </c>
@@ -19817,22 +19873,22 @@
       <c r="COT205"/>
     </row>
     <row r="206" spans="1:2438" s="62" customFormat="1" ht="95.25" customHeight="1">
-      <c r="A206" s="310">
+      <c r="A206" s="314">
         <v>65</v>
       </c>
-      <c r="B206" s="308">
+      <c r="B206" s="312">
         <v>46096</v>
       </c>
-      <c r="C206" s="310" t="s">
+      <c r="C206" s="314" t="s">
         <v>265</v>
       </c>
-      <c r="D206" s="315" t="s">
+      <c r="D206" s="319" t="s">
         <v>423</v>
       </c>
-      <c r="E206" s="310" t="s">
+      <c r="E206" s="314" t="s">
         <v>47</v>
       </c>
-      <c r="F206" s="306" t="s">
+      <c r="F206" s="310" t="s">
         <v>424</v>
       </c>
       <c r="G206" s="120" t="s">
@@ -22277,12 +22333,12 @@
       <c r="COT206"/>
     </row>
     <row r="207" spans="1:2438" s="62" customFormat="1" ht="61.5" customHeight="1">
-      <c r="A207" s="311"/>
-      <c r="B207" s="309"/>
-      <c r="C207" s="311"/>
-      <c r="D207" s="316"/>
-      <c r="E207" s="311"/>
-      <c r="F207" s="307"/>
+      <c r="A207" s="315"/>
+      <c r="B207" s="313"/>
+      <c r="C207" s="315"/>
+      <c r="D207" s="320"/>
+      <c r="E207" s="315"/>
+      <c r="F207" s="311"/>
       <c r="G207" s="120" t="s">
         <v>427</v>
       </c>
@@ -24725,22 +24781,22 @@
       <c r="COT207"/>
     </row>
     <row r="208" spans="1:2438" s="62" customFormat="1" ht="87" customHeight="1">
-      <c r="A208" s="315">
+      <c r="A208" s="319">
         <v>66</v>
       </c>
-      <c r="B208" s="317">
+      <c r="B208" s="321">
         <v>46097</v>
       </c>
-      <c r="C208" s="315" t="s">
+      <c r="C208" s="319" t="s">
         <v>125</v>
       </c>
-      <c r="D208" s="323" t="s">
+      <c r="D208" s="327" t="s">
         <v>428</v>
       </c>
-      <c r="E208" s="315" t="s">
+      <c r="E208" s="319" t="s">
         <v>47</v>
       </c>
-      <c r="F208" s="306" t="s">
+      <c r="F208" s="310" t="s">
         <v>429</v>
       </c>
       <c r="G208" s="120" t="s">
@@ -27185,12 +27241,12 @@
       <c r="COT208"/>
     </row>
     <row r="209" spans="1:2438" s="62" customFormat="1" ht="87" customHeight="1">
-      <c r="A209" s="321"/>
-      <c r="B209" s="322"/>
-      <c r="C209" s="321"/>
-      <c r="D209" s="324"/>
-      <c r="E209" s="321"/>
-      <c r="F209" s="325"/>
+      <c r="A209" s="325"/>
+      <c r="B209" s="326"/>
+      <c r="C209" s="325"/>
+      <c r="D209" s="328"/>
+      <c r="E209" s="325"/>
+      <c r="F209" s="329"/>
       <c r="G209" s="120" t="s">
         <v>431</v>
       </c>
@@ -29633,12 +29689,12 @@
       <c r="COT209"/>
     </row>
     <row r="210" spans="1:2438" s="62" customFormat="1" ht="43.5" customHeight="1">
-      <c r="A210" s="321"/>
-      <c r="B210" s="322"/>
-      <c r="C210" s="321"/>
-      <c r="D210" s="324"/>
-      <c r="E210" s="321"/>
-      <c r="F210" s="325"/>
+      <c r="A210" s="325"/>
+      <c r="B210" s="326"/>
+      <c r="C210" s="325"/>
+      <c r="D210" s="328"/>
+      <c r="E210" s="325"/>
+      <c r="F210" s="329"/>
       <c r="G210" s="120" t="s">
         <v>433</v>
       </c>
@@ -32081,12 +32137,12 @@
       <c r="COT210"/>
     </row>
     <row r="211" spans="1:2438" s="63" customFormat="1" ht="96.75" customHeight="1">
-      <c r="A211" s="321"/>
-      <c r="B211" s="322"/>
-      <c r="C211" s="321"/>
-      <c r="D211" s="324"/>
-      <c r="E211" s="321"/>
-      <c r="F211" s="325"/>
+      <c r="A211" s="325"/>
+      <c r="B211" s="326"/>
+      <c r="C211" s="325"/>
+      <c r="D211" s="328"/>
+      <c r="E211" s="325"/>
+      <c r="F211" s="329"/>
       <c r="G211" s="120" t="s">
         <v>435</v>
       </c>
@@ -34529,22 +34585,22 @@
       <c r="COT211"/>
     </row>
     <row r="212" spans="1:2438" s="63" customFormat="1" ht="90" customHeight="1">
-      <c r="A212" s="206">
+      <c r="A212" s="220">
         <v>67</v>
       </c>
-      <c r="B212" s="226">
+      <c r="B212" s="234">
         <v>46099</v>
       </c>
-      <c r="C212" s="206" t="s">
+      <c r="C212" s="220" t="s">
         <v>125</v>
       </c>
-      <c r="D212" s="206" t="s">
+      <c r="D212" s="220" t="s">
         <v>436</v>
       </c>
-      <c r="E212" s="258" t="s">
+      <c r="E212" s="266" t="s">
         <v>182</v>
       </c>
-      <c r="F212" s="299" t="s">
+      <c r="F212" s="305" t="s">
         <v>437</v>
       </c>
       <c r="G212" s="121" t="s">
@@ -36993,12 +37049,12 @@
       <c r="COT212"/>
     </row>
     <row r="213" spans="1:2438" s="63" customFormat="1" ht="90" customHeight="1">
-      <c r="A213" s="321"/>
-      <c r="B213" s="322"/>
-      <c r="C213" s="321"/>
-      <c r="D213" s="321"/>
-      <c r="E213" s="321"/>
-      <c r="F213" s="326"/>
+      <c r="A213" s="325"/>
+      <c r="B213" s="326"/>
+      <c r="C213" s="325"/>
+      <c r="D213" s="325"/>
+      <c r="E213" s="325"/>
+      <c r="F213" s="330"/>
       <c r="G213" s="120" t="s">
         <v>441</v>
       </c>
@@ -39441,12 +39497,12 @@
       <c r="COT213"/>
     </row>
     <row r="214" spans="1:2438" s="65" customFormat="1" ht="34.5" customHeight="1">
-      <c r="A214" s="316"/>
-      <c r="B214" s="318"/>
-      <c r="C214" s="316"/>
-      <c r="D214" s="316"/>
-      <c r="E214" s="316"/>
-      <c r="F214" s="320"/>
+      <c r="A214" s="320"/>
+      <c r="B214" s="322"/>
+      <c r="C214" s="320"/>
+      <c r="D214" s="320"/>
+      <c r="E214" s="320"/>
+      <c r="F214" s="324"/>
       <c r="G214" s="120" t="s">
         <v>443</v>
       </c>
@@ -41889,22 +41945,22 @@
       <c r="COT214"/>
     </row>
     <row r="215" spans="1:2438" s="63" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A215" s="315">
+      <c r="A215" s="319">
         <v>68</v>
       </c>
-      <c r="B215" s="317">
+      <c r="B215" s="321">
         <v>46102</v>
       </c>
-      <c r="C215" s="315" t="s">
+      <c r="C215" s="319" t="s">
         <v>265</v>
       </c>
-      <c r="D215" s="315" t="s">
+      <c r="D215" s="319" t="s">
         <v>444</v>
       </c>
-      <c r="E215" s="315" t="s">
+      <c r="E215" s="319" t="s">
         <v>47</v>
       </c>
-      <c r="F215" s="319" t="s">
+      <c r="F215" s="323" t="s">
         <v>445</v>
       </c>
       <c r="G215" s="120" t="s">
@@ -44349,12 +44405,12 @@
       <c r="COT215"/>
     </row>
     <row r="216" spans="1:2438" s="63" customFormat="1" ht="90" customHeight="1">
-      <c r="A216" s="316"/>
-      <c r="B216" s="318"/>
-      <c r="C216" s="316"/>
-      <c r="D216" s="316"/>
-      <c r="E216" s="316"/>
-      <c r="F216" s="320"/>
+      <c r="A216" s="320"/>
+      <c r="B216" s="322"/>
+      <c r="C216" s="320"/>
+      <c r="D216" s="320"/>
+      <c r="E216" s="320"/>
+      <c r="F216" s="324"/>
       <c r="G216" s="122" t="s">
         <v>448</v>
       </c>
@@ -46797,22 +46853,22 @@
       <c r="COT216"/>
     </row>
     <row r="217" spans="1:2438" s="63" customFormat="1" ht="135" customHeight="1">
-      <c r="A217" s="315">
+      <c r="A217" s="319">
         <v>69</v>
       </c>
-      <c r="B217" s="317">
+      <c r="B217" s="321">
         <v>46106</v>
       </c>
-      <c r="C217" s="315" t="s">
+      <c r="C217" s="319" t="s">
         <v>265</v>
       </c>
-      <c r="D217" s="327" t="s">
+      <c r="D217" s="331" t="s">
         <v>449</v>
       </c>
-      <c r="E217" s="315" t="s">
+      <c r="E217" s="319" t="s">
         <v>47</v>
       </c>
-      <c r="F217" s="329" t="s">
+      <c r="F217" s="333" t="s">
         <v>450</v>
       </c>
       <c r="G217" s="71" t="s">
@@ -49257,12 +49313,12 @@
       <c r="COT217"/>
     </row>
     <row r="218" spans="1:2438" s="63" customFormat="1" ht="116.25" customHeight="1">
-      <c r="A218" s="316"/>
-      <c r="B218" s="318"/>
-      <c r="C218" s="316"/>
-      <c r="D218" s="328"/>
-      <c r="E218" s="316"/>
-      <c r="F218" s="330"/>
+      <c r="A218" s="320"/>
+      <c r="B218" s="322"/>
+      <c r="C218" s="320"/>
+      <c r="D218" s="332"/>
+      <c r="E218" s="320"/>
+      <c r="F218" s="334"/>
       <c r="G218" s="71" t="s">
         <v>454</v>
       </c>
@@ -51705,22 +51761,22 @@
       <c r="COT218"/>
     </row>
     <row r="219" spans="1:2438" s="63" customFormat="1" ht="86.45" customHeight="1">
-      <c r="A219" s="315">
+      <c r="A219" s="319">
         <v>70</v>
       </c>
-      <c r="B219" s="317">
+      <c r="B219" s="321">
         <v>46107</v>
       </c>
-      <c r="C219" s="315" t="s">
+      <c r="C219" s="319" t="s">
         <v>265</v>
       </c>
-      <c r="D219" s="315" t="s">
+      <c r="D219" s="319" t="s">
         <v>456</v>
       </c>
-      <c r="E219" s="315" t="s">
+      <c r="E219" s="319" t="s">
         <v>47</v>
       </c>
-      <c r="F219" s="319" t="s">
+      <c r="F219" s="323" t="s">
         <v>457</v>
       </c>
       <c r="G219" s="173" t="s">
@@ -54165,12 +54221,12 @@
       <c r="COT219"/>
     </row>
     <row r="220" spans="1:2438" s="63" customFormat="1" ht="86.45" customHeight="1">
-      <c r="A220" s="321"/>
-      <c r="B220" s="322"/>
-      <c r="C220" s="321"/>
-      <c r="D220" s="321"/>
-      <c r="E220" s="321"/>
-      <c r="F220" s="326"/>
+      <c r="A220" s="325"/>
+      <c r="B220" s="326"/>
+      <c r="C220" s="325"/>
+      <c r="D220" s="325"/>
+      <c r="E220" s="325"/>
+      <c r="F220" s="330"/>
       <c r="G220" s="140" t="s">
         <v>459</v>
       </c>
@@ -56613,12 +56669,12 @@
       <c r="COT220"/>
     </row>
     <row r="221" spans="1:2438" s="63" customFormat="1" ht="90" customHeight="1">
-      <c r="A221" s="321"/>
-      <c r="B221" s="322"/>
-      <c r="C221" s="321"/>
-      <c r="D221" s="321"/>
-      <c r="E221" s="321"/>
-      <c r="F221" s="326"/>
+      <c r="A221" s="325"/>
+      <c r="B221" s="326"/>
+      <c r="C221" s="325"/>
+      <c r="D221" s="325"/>
+      <c r="E221" s="325"/>
+      <c r="F221" s="330"/>
       <c r="G221" s="122" t="s">
         <v>460</v>
       </c>
@@ -59098,22 +59154,22 @@
       </c>
     </row>
     <row r="223" spans="1:2438" ht="147.75" customHeight="1">
-      <c r="A223" s="224">
+      <c r="A223" s="232">
         <v>72</v>
       </c>
-      <c r="B223" s="208">
+      <c r="B223" s="222">
         <v>46127</v>
       </c>
-      <c r="C223" s="207" t="s">
+      <c r="C223" s="221" t="s">
         <v>265</v>
       </c>
-      <c r="D223" s="206" t="s">
+      <c r="D223" s="220" t="s">
         <v>465</v>
       </c>
-      <c r="E223" s="218" t="s">
+      <c r="E223" s="226" t="s">
         <v>182</v>
       </c>
-      <c r="F223" s="227" t="s">
+      <c r="F223" s="235" t="s">
         <v>466</v>
       </c>
       <c r="G223" s="124" t="s">
@@ -59135,12 +59191,12 @@
       </c>
     </row>
     <row r="224" spans="1:2438" ht="84.75" customHeight="1">
-      <c r="A224" s="209"/>
-      <c r="B224" s="208"/>
-      <c r="C224" s="207"/>
-      <c r="D224" s="206"/>
-      <c r="E224" s="218"/>
-      <c r="F224" s="227"/>
+      <c r="A224" s="223"/>
+      <c r="B224" s="222"/>
+      <c r="C224" s="221"/>
+      <c r="D224" s="220"/>
+      <c r="E224" s="226"/>
+      <c r="F224" s="235"/>
       <c r="G224" s="125" t="s">
         <v>470</v>
       </c>
@@ -59158,22 +59214,22 @@
       <c r="M224" s="12"/>
     </row>
     <row r="225" spans="1:13" ht="87.75" customHeight="1">
-      <c r="A225" s="207">
+      <c r="A225" s="221">
         <v>73</v>
       </c>
-      <c r="B225" s="217">
+      <c r="B225" s="205">
         <v>46132</v>
       </c>
-      <c r="C225" s="213" t="s">
+      <c r="C225" s="202" t="s">
         <v>125</v>
       </c>
-      <c r="D225" s="215" t="s">
+      <c r="D225" s="208" t="s">
         <v>472</v>
       </c>
-      <c r="E225" s="213" t="s">
+      <c r="E225" s="202" t="s">
         <v>47</v>
       </c>
-      <c r="F225" s="331" t="s">
+      <c r="F225" s="335" t="s">
         <v>473</v>
       </c>
       <c r="G225" s="13" t="s">
@@ -59193,12 +59249,12 @@
       <c r="M225" s="12"/>
     </row>
     <row r="226" spans="1:13" ht="87.75" customHeight="1">
-      <c r="A226" s="207"/>
-      <c r="B226" s="208"/>
-      <c r="C226" s="207"/>
-      <c r="D226" s="206"/>
-      <c r="E226" s="207"/>
-      <c r="F226" s="227"/>
+      <c r="A226" s="221"/>
+      <c r="B226" s="222"/>
+      <c r="C226" s="221"/>
+      <c r="D226" s="220"/>
+      <c r="E226" s="221"/>
+      <c r="F226" s="235"/>
       <c r="G226" s="13" t="s">
         <v>476</v>
       </c>
@@ -59216,12 +59272,12 @@
       <c r="M226" s="12"/>
     </row>
     <row r="227" spans="1:13" ht="87.75" customHeight="1">
-      <c r="A227" s="212"/>
-      <c r="B227" s="216"/>
-      <c r="C227" s="212"/>
-      <c r="D227" s="214"/>
-      <c r="E227" s="212"/>
-      <c r="F227" s="332"/>
+      <c r="A227" s="200"/>
+      <c r="B227" s="203"/>
+      <c r="C227" s="200"/>
+      <c r="D227" s="206"/>
+      <c r="E227" s="200"/>
+      <c r="F227" s="336"/>
       <c r="G227" s="73" t="s">
         <v>477</v>
       </c>
@@ -59239,22 +59295,22 @@
       <c r="M227" s="12"/>
     </row>
     <row r="228" spans="1:13" ht="42" customHeight="1">
-      <c r="A228" s="207">
+      <c r="A228" s="221">
         <v>74</v>
       </c>
-      <c r="B228" s="208">
+      <c r="B228" s="222">
         <v>46135</v>
       </c>
-      <c r="C228" s="207" t="s">
+      <c r="C228" s="221" t="s">
         <v>125</v>
       </c>
-      <c r="D228" s="206" t="s">
+      <c r="D228" s="220" t="s">
         <v>478</v>
       </c>
-      <c r="E228" s="207" t="s">
+      <c r="E228" s="221" t="s">
         <v>47</v>
       </c>
-      <c r="F228" s="227" t="s">
+      <c r="F228" s="235" t="s">
         <v>479</v>
       </c>
       <c r="G228" s="13" t="s">
@@ -59274,12 +59330,12 @@
       <c r="M228" s="12"/>
     </row>
     <row r="229" spans="1:13" ht="54" customHeight="1">
-      <c r="A229" s="207"/>
-      <c r="B229" s="208"/>
-      <c r="C229" s="207"/>
-      <c r="D229" s="206"/>
-      <c r="E229" s="207"/>
-      <c r="F229" s="227"/>
+      <c r="A229" s="221"/>
+      <c r="B229" s="222"/>
+      <c r="C229" s="221"/>
+      <c r="D229" s="220"/>
+      <c r="E229" s="221"/>
+      <c r="F229" s="235"/>
       <c r="G229" s="13" t="s">
         <v>481</v>
       </c>
@@ -59297,12 +59353,12 @@
       <c r="M229" s="12"/>
     </row>
     <row r="230" spans="1:13" ht="42" customHeight="1">
-      <c r="A230" s="207"/>
-      <c r="B230" s="208"/>
-      <c r="C230" s="207"/>
-      <c r="D230" s="206"/>
-      <c r="E230" s="207"/>
-      <c r="F230" s="227"/>
+      <c r="A230" s="221"/>
+      <c r="B230" s="222"/>
+      <c r="C230" s="221"/>
+      <c r="D230" s="220"/>
+      <c r="E230" s="221"/>
+      <c r="F230" s="235"/>
       <c r="G230" s="115" t="s">
         <v>483</v>
       </c>
@@ -59320,12 +59376,12 @@
       <c r="M230" s="12"/>
     </row>
     <row r="231" spans="1:13" ht="44.25" customHeight="1">
-      <c r="A231" s="207"/>
-      <c r="B231" s="208"/>
-      <c r="C231" s="207"/>
-      <c r="D231" s="206"/>
-      <c r="E231" s="207"/>
-      <c r="F231" s="227"/>
+      <c r="A231" s="221"/>
+      <c r="B231" s="222"/>
+      <c r="C231" s="221"/>
+      <c r="D231" s="220"/>
+      <c r="E231" s="221"/>
+      <c r="F231" s="235"/>
       <c r="G231" s="115" t="s">
         <v>484</v>
       </c>
@@ -59343,22 +59399,22 @@
       <c r="M231" s="12"/>
     </row>
     <row r="232" spans="1:13" ht="77.25" customHeight="1">
-      <c r="A232" s="207">
+      <c r="A232" s="221">
         <v>75</v>
       </c>
-      <c r="B232" s="208">
+      <c r="B232" s="222">
         <v>46135</v>
       </c>
-      <c r="C232" s="207" t="s">
+      <c r="C232" s="221" t="s">
         <v>125</v>
       </c>
-      <c r="D232" s="206" t="s">
+      <c r="D232" s="220" t="s">
         <v>485</v>
       </c>
-      <c r="E232" s="207" t="s">
+      <c r="E232" s="221" t="s">
         <v>47</v>
       </c>
-      <c r="F232" s="227" t="s">
+      <c r="F232" s="235" t="s">
         <v>486</v>
       </c>
       <c r="G232" s="115" t="s">
@@ -59380,12 +59436,12 @@
       <c r="M232" s="12"/>
     </row>
     <row r="233" spans="1:13" ht="42" customHeight="1">
-      <c r="A233" s="207"/>
-      <c r="B233" s="207"/>
-      <c r="C233" s="207"/>
-      <c r="D233" s="206"/>
-      <c r="E233" s="207"/>
-      <c r="F233" s="227"/>
+      <c r="A233" s="221"/>
+      <c r="B233" s="221"/>
+      <c r="C233" s="221"/>
+      <c r="D233" s="220"/>
+      <c r="E233" s="221"/>
+      <c r="F233" s="235"/>
       <c r="G233" s="13" t="s">
         <v>489</v>
       </c>
@@ -59403,12 +59459,12 @@
       <c r="M233" s="12"/>
     </row>
     <row r="234" spans="1:13" ht="52.5" customHeight="1">
-      <c r="A234" s="212"/>
-      <c r="B234" s="212"/>
-      <c r="C234" s="212"/>
-      <c r="D234" s="214"/>
-      <c r="E234" s="212"/>
-      <c r="F234" s="332"/>
+      <c r="A234" s="200"/>
+      <c r="B234" s="200"/>
+      <c r="C234" s="200"/>
+      <c r="D234" s="206"/>
+      <c r="E234" s="200"/>
+      <c r="F234" s="336"/>
       <c r="G234" s="118" t="s">
         <v>491</v>
       </c>
@@ -59426,22 +59482,22 @@
       <c r="M234" s="12"/>
     </row>
     <row r="235" spans="1:13" ht="52.5" customHeight="1">
-      <c r="A235" s="212">
+      <c r="A235" s="200">
         <v>77</v>
       </c>
-      <c r="B235" s="216">
+      <c r="B235" s="203">
         <v>46140</v>
       </c>
-      <c r="C235" s="212" t="s">
+      <c r="C235" s="200" t="s">
         <v>493</v>
       </c>
-      <c r="D235" s="214" t="s">
+      <c r="D235" s="206" t="s">
         <v>494</v>
       </c>
-      <c r="E235" s="212" t="s">
+      <c r="E235" s="200" t="s">
         <v>47</v>
       </c>
-      <c r="F235" s="214" t="s">
+      <c r="F235" s="206" t="s">
         <v>495</v>
       </c>
       <c r="G235" s="118" t="s">
@@ -59461,12 +59517,12 @@
       <c r="M235" s="60"/>
     </row>
     <row r="236" spans="1:13" ht="53.25" customHeight="1">
-      <c r="A236" s="259"/>
-      <c r="B236" s="305"/>
-      <c r="C236" s="259"/>
-      <c r="D236" s="303"/>
-      <c r="E236" s="259"/>
-      <c r="F236" s="303"/>
+      <c r="A236" s="201"/>
+      <c r="B236" s="204"/>
+      <c r="C236" s="201"/>
+      <c r="D236" s="207"/>
+      <c r="E236" s="201"/>
+      <c r="F236" s="207"/>
       <c r="G236" s="133" t="s">
         <v>499</v>
       </c>
@@ -59484,22 +59540,22 @@
       <c r="M236" s="60"/>
     </row>
     <row r="237" spans="1:13" ht="149.25" customHeight="1">
-      <c r="A237" s="207">
+      <c r="A237" s="221">
         <v>78</v>
       </c>
-      <c r="B237" s="208">
+      <c r="B237" s="222">
         <v>46145</v>
       </c>
-      <c r="C237" s="206" t="s">
+      <c r="C237" s="220" t="s">
         <v>501</v>
       </c>
-      <c r="D237" s="206" t="s">
+      <c r="D237" s="220" t="s">
         <v>502</v>
       </c>
-      <c r="E237" s="207" t="s">
+      <c r="E237" s="221" t="s">
         <v>182</v>
       </c>
-      <c r="F237" s="333" t="s">
+      <c r="F237" s="337" t="s">
         <v>503</v>
       </c>
       <c r="G237" s="145" t="s">
@@ -59514,21 +59570,21 @@
       <c r="J237" s="127" t="s">
         <v>20</v>
       </c>
-      <c r="K237" s="364" t="s">
+      <c r="K237" s="368" t="s">
         <v>506</v>
       </c>
       <c r="L237" s="98"/>
-      <c r="M237" s="365" t="s">
+      <c r="M237" s="369" t="s">
         <v>507</v>
       </c>
     </row>
     <row r="238" spans="1:13" ht="82.5" customHeight="1">
-      <c r="A238" s="259"/>
-      <c r="B238" s="305"/>
-      <c r="C238" s="303"/>
-      <c r="D238" s="303"/>
-      <c r="E238" s="259"/>
-      <c r="F238" s="201"/>
+      <c r="A238" s="201"/>
+      <c r="B238" s="204"/>
+      <c r="C238" s="207"/>
+      <c r="D238" s="207"/>
+      <c r="E238" s="201"/>
+      <c r="F238" s="217"/>
       <c r="G238" s="126" t="s">
         <v>508</v>
       </c>
@@ -59543,15 +59599,15 @@
       </c>
       <c r="K238" s="5"/>
       <c r="L238" s="98"/>
-      <c r="M238" s="219"/>
+      <c r="M238" s="227"/>
     </row>
     <row r="239" spans="1:13" ht="54" customHeight="1">
-      <c r="A239" s="213"/>
-      <c r="B239" s="217"/>
-      <c r="C239" s="215"/>
-      <c r="D239" s="215"/>
-      <c r="E239" s="213"/>
-      <c r="F239" s="202"/>
+      <c r="A239" s="202"/>
+      <c r="B239" s="205"/>
+      <c r="C239" s="208"/>
+      <c r="D239" s="208"/>
+      <c r="E239" s="202"/>
+      <c r="F239" s="218"/>
       <c r="G239" s="128" t="s">
         <v>509</v>
       </c>
@@ -59566,25 +59622,25 @@
       </c>
       <c r="K239" s="60"/>
       <c r="L239" s="95"/>
-      <c r="M239" s="220"/>
+      <c r="M239" s="228"/>
     </row>
     <row r="240" spans="1:13" ht="66" customHeight="1">
-      <c r="A240" s="212">
+      <c r="A240" s="200">
         <v>79</v>
       </c>
-      <c r="B240" s="216">
+      <c r="B240" s="203">
         <v>46145</v>
       </c>
-      <c r="C240" s="214" t="s">
+      <c r="C240" s="206" t="s">
         <v>501</v>
       </c>
-      <c r="D240" s="214" t="s">
+      <c r="D240" s="206" t="s">
         <v>510</v>
       </c>
-      <c r="E240" s="212" t="s">
+      <c r="E240" s="200" t="s">
         <v>27</v>
       </c>
-      <c r="F240" s="200" t="s">
+      <c r="F240" s="216" t="s">
         <v>511</v>
       </c>
       <c r="G240" s="14" t="s">
@@ -59597,24 +59653,24 @@
         <v>46203</v>
       </c>
       <c r="J240" s="127" t="s">
-        <v>222</v>
+        <v>514</v>
       </c>
       <c r="K240" s="12"/>
       <c r="L240" s="12"/>
       <c r="M240" s="115"/>
     </row>
     <row r="241" spans="1:13" ht="81.75" customHeight="1">
-      <c r="A241" s="213"/>
-      <c r="B241" s="217"/>
-      <c r="C241" s="215"/>
-      <c r="D241" s="215"/>
-      <c r="E241" s="213"/>
-      <c r="F241" s="202"/>
+      <c r="A241" s="202"/>
+      <c r="B241" s="205"/>
+      <c r="C241" s="208"/>
+      <c r="D241" s="208"/>
+      <c r="E241" s="202"/>
+      <c r="F241" s="218"/>
       <c r="G241" s="139" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H241" s="129" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="I241" s="57">
         <v>46203</v>
@@ -59637,16 +59693,16 @@
         <v>501</v>
       </c>
       <c r="D242" s="134" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E242" s="91" t="s">
         <v>209</v>
       </c>
       <c r="F242" s="135" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="G242" s="118" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H242" s="60"/>
       <c r="I242" s="142"/>
@@ -59658,43 +59714,43 @@
       <c r="M242" s="60"/>
     </row>
     <row r="243" spans="1:13" ht="76.5" customHeight="1">
-      <c r="A243" s="212">
+      <c r="A243" s="200">
         <v>81</v>
       </c>
-      <c r="B243" s="216">
+      <c r="B243" s="203">
         <v>46154</v>
       </c>
-      <c r="C243" s="212" t="s">
+      <c r="C243" s="200" t="s">
         <v>125</v>
       </c>
-      <c r="D243" s="214" t="s">
-        <v>519</v>
-      </c>
-      <c r="E243" s="212" t="s">
+      <c r="D243" s="206" t="s">
         <v>520</v>
       </c>
-      <c r="F243" s="198" t="s">
+      <c r="E243" s="200" t="s">
         <v>521</v>
       </c>
+      <c r="F243" s="214" t="s">
+        <v>522</v>
+      </c>
       <c r="G243" s="137" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H243" s="60"/>
       <c r="I243" s="142"/>
       <c r="J243" s="129" t="s">
-        <v>523</v>
+        <v>514</v>
       </c>
       <c r="K243" s="60"/>
       <c r="L243" s="60"/>
       <c r="M243" s="60"/>
     </row>
     <row r="244" spans="1:13" ht="76.5" customHeight="1">
-      <c r="A244" s="259"/>
-      <c r="B244" s="305"/>
-      <c r="C244" s="259"/>
-      <c r="D244" s="303"/>
-      <c r="E244" s="259"/>
-      <c r="F244" s="334"/>
+      <c r="A244" s="201"/>
+      <c r="B244" s="204"/>
+      <c r="C244" s="201"/>
+      <c r="D244" s="207"/>
+      <c r="E244" s="201"/>
+      <c r="F244" s="338"/>
       <c r="G244" s="118" t="s">
         <v>524</v>
       </c>
@@ -59708,12 +59764,12 @@
       <c r="M244" s="60"/>
     </row>
     <row r="245" spans="1:13" ht="85.5" customHeight="1">
-      <c r="A245" s="213"/>
-      <c r="B245" s="217"/>
-      <c r="C245" s="213"/>
-      <c r="D245" s="215"/>
-      <c r="E245" s="213"/>
-      <c r="F245" s="199"/>
+      <c r="A245" s="202"/>
+      <c r="B245" s="205"/>
+      <c r="C245" s="202"/>
+      <c r="D245" s="208"/>
+      <c r="E245" s="202"/>
+      <c r="F245" s="215"/>
       <c r="G245" s="13" t="s">
         <v>525</v>
       </c>
@@ -59740,7 +59796,7 @@
         <v>526</v>
       </c>
       <c r="E246" s="5" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F246" s="13" t="s">
         <v>527</v>
@@ -59758,22 +59814,22 @@
       <c r="M246" s="5"/>
     </row>
     <row r="247" spans="1:13" ht="85.5" customHeight="1">
-      <c r="A247" s="212">
+      <c r="A247" s="200">
         <v>83</v>
       </c>
-      <c r="B247" s="216">
+      <c r="B247" s="203">
         <v>46158</v>
       </c>
-      <c r="C247" s="212" t="s">
+      <c r="C247" s="200" t="s">
         <v>125</v>
       </c>
-      <c r="D247" s="212" t="s">
+      <c r="D247" s="200" t="s">
         <v>529</v>
       </c>
-      <c r="E247" s="212" t="s">
-        <v>520</v>
-      </c>
-      <c r="F247" s="198" t="s">
+      <c r="E247" s="200" t="s">
+        <v>521</v>
+      </c>
+      <c r="F247" s="214" t="s">
         <v>530</v>
       </c>
       <c r="G247" s="58" t="s">
@@ -59793,12 +59849,12 @@
       <c r="M247" s="5"/>
     </row>
     <row r="248" spans="1:13" ht="125.25" customHeight="1">
-      <c r="A248" s="213"/>
-      <c r="B248" s="217"/>
-      <c r="C248" s="213"/>
-      <c r="D248" s="213"/>
-      <c r="E248" s="213"/>
-      <c r="F248" s="199"/>
+      <c r="A248" s="202"/>
+      <c r="B248" s="205"/>
+      <c r="C248" s="202"/>
+      <c r="D248" s="202"/>
+      <c r="E248" s="202"/>
+      <c r="F248" s="215"/>
       <c r="G248" s="58" t="s">
         <v>534</v>
       </c>
@@ -59809,29 +59865,29 @@
         <v>536</v>
       </c>
       <c r="J248" s="129" t="s">
-        <v>523</v>
+        <v>514</v>
       </c>
       <c r="K248" s="5"/>
       <c r="L248" s="5"/>
       <c r="M248" s="5"/>
     </row>
     <row r="249" spans="1:13" ht="62.25" customHeight="1">
-      <c r="A249" s="212">
+      <c r="A249" s="200">
         <v>84</v>
       </c>
-      <c r="B249" s="216">
+      <c r="B249" s="203">
         <v>46166</v>
       </c>
-      <c r="C249" s="214" t="s">
+      <c r="C249" s="206" t="s">
         <v>501</v>
       </c>
-      <c r="D249" s="214" t="s">
+      <c r="D249" s="206" t="s">
         <v>537</v>
       </c>
-      <c r="E249" s="212" t="s">
+      <c r="E249" s="200" t="s">
         <v>27</v>
       </c>
-      <c r="F249" s="198" t="s">
+      <c r="F249" s="214" t="s">
         <v>538</v>
       </c>
       <c r="G249" s="137" t="s">
@@ -59851,12 +59907,12 @@
       <c r="M249" s="5"/>
     </row>
     <row r="250" spans="1:13" ht="68.25" customHeight="1">
-      <c r="A250" s="213"/>
-      <c r="B250" s="217"/>
-      <c r="C250" s="215"/>
-      <c r="D250" s="215"/>
-      <c r="E250" s="213"/>
-      <c r="F250" s="199"/>
+      <c r="A250" s="202"/>
+      <c r="B250" s="205"/>
+      <c r="C250" s="208"/>
+      <c r="D250" s="208"/>
+      <c r="E250" s="202"/>
+      <c r="F250" s="215"/>
       <c r="G250" s="100" t="s">
         <v>541</v>
       </c>
@@ -59874,22 +59930,22 @@
       <c r="M250" s="5"/>
     </row>
     <row r="251" spans="1:13" ht="63.75" customHeight="1">
-      <c r="A251" s="212">
+      <c r="A251" s="200">
         <v>85</v>
       </c>
-      <c r="B251" s="336">
+      <c r="B251" s="340">
         <v>46166</v>
       </c>
-      <c r="C251" s="214" t="s">
+      <c r="C251" s="206" t="s">
         <v>501</v>
       </c>
-      <c r="D251" s="214" t="s">
+      <c r="D251" s="206" t="s">
         <v>543</v>
       </c>
-      <c r="E251" s="212" t="s">
-        <v>520</v>
-      </c>
-      <c r="F251" s="198" t="s">
+      <c r="E251" s="200" t="s">
+        <v>521</v>
+      </c>
+      <c r="F251" s="214" t="s">
         <v>544</v>
       </c>
       <c r="G251" s="14" t="s">
@@ -59909,12 +59965,12 @@
       <c r="M251" s="5"/>
     </row>
     <row r="252" spans="1:13" ht="63.75" customHeight="1">
-      <c r="A252" s="259"/>
-      <c r="B252" s="337"/>
-      <c r="C252" s="303"/>
-      <c r="D252" s="303"/>
-      <c r="E252" s="259"/>
-      <c r="F252" s="334"/>
+      <c r="A252" s="201"/>
+      <c r="B252" s="341"/>
+      <c r="C252" s="207"/>
+      <c r="D252" s="207"/>
+      <c r="E252" s="201"/>
+      <c r="F252" s="338"/>
       <c r="G252" s="100" t="s">
         <v>547</v>
       </c>
@@ -59932,12 +59988,12 @@
       <c r="M252" s="5"/>
     </row>
     <row r="253" spans="1:13" ht="63.75" customHeight="1">
-      <c r="A253" s="259"/>
-      <c r="B253" s="337"/>
-      <c r="C253" s="303"/>
-      <c r="D253" s="303"/>
-      <c r="E253" s="259"/>
-      <c r="F253" s="334"/>
+      <c r="A253" s="201"/>
+      <c r="B253" s="341"/>
+      <c r="C253" s="207"/>
+      <c r="D253" s="207"/>
+      <c r="E253" s="201"/>
+      <c r="F253" s="338"/>
       <c r="G253" s="100" t="s">
         <v>548</v>
       </c>
@@ -59955,12 +60011,12 @@
       <c r="M253" s="5"/>
     </row>
     <row r="254" spans="1:13" ht="63.75" customHeight="1">
-      <c r="A254" s="259"/>
-      <c r="B254" s="337"/>
-      <c r="C254" s="303"/>
-      <c r="D254" s="303"/>
-      <c r="E254" s="259"/>
-      <c r="F254" s="334"/>
+      <c r="A254" s="201"/>
+      <c r="B254" s="341"/>
+      <c r="C254" s="207"/>
+      <c r="D254" s="207"/>
+      <c r="E254" s="201"/>
+      <c r="F254" s="338"/>
       <c r="G254" s="100" t="s">
         <v>549</v>
       </c>
@@ -59978,12 +60034,12 @@
       <c r="M254" s="5"/>
     </row>
     <row r="255" spans="1:13" ht="63.75" customHeight="1">
-      <c r="A255" s="259"/>
-      <c r="B255" s="337"/>
-      <c r="C255" s="303"/>
-      <c r="D255" s="303"/>
-      <c r="E255" s="259"/>
-      <c r="F255" s="334"/>
+      <c r="A255" s="201"/>
+      <c r="B255" s="341"/>
+      <c r="C255" s="207"/>
+      <c r="D255" s="207"/>
+      <c r="E255" s="201"/>
+      <c r="F255" s="338"/>
       <c r="G255" s="100" t="s">
         <v>551</v>
       </c>
@@ -60001,22 +60057,22 @@
       <c r="M255" s="5"/>
     </row>
     <row r="256" spans="1:13" ht="59.25" customHeight="1">
-      <c r="A256" s="207">
+      <c r="A256" s="221">
         <v>86</v>
       </c>
-      <c r="B256" s="208">
+      <c r="B256" s="222">
         <v>46167</v>
       </c>
-      <c r="C256" s="206" t="s">
+      <c r="C256" s="220" t="s">
         <v>265</v>
       </c>
-      <c r="D256" s="206" t="s">
+      <c r="D256" s="220" t="s">
         <v>553</v>
       </c>
-      <c r="E256" s="207" t="s">
-        <v>520</v>
-      </c>
-      <c r="F256" s="335" t="s">
+      <c r="E256" s="221" t="s">
+        <v>521</v>
+      </c>
+      <c r="F256" s="339" t="s">
         <v>554</v>
       </c>
       <c r="G256" s="163" t="s">
@@ -60036,12 +60092,12 @@
       <c r="M256" s="5"/>
     </row>
     <row r="257" spans="1:13" ht="59.25" customHeight="1">
-      <c r="A257" s="207"/>
-      <c r="B257" s="208"/>
-      <c r="C257" s="206"/>
-      <c r="D257" s="206"/>
-      <c r="E257" s="207"/>
-      <c r="F257" s="219"/>
+      <c r="A257" s="221"/>
+      <c r="B257" s="222"/>
+      <c r="C257" s="220"/>
+      <c r="D257" s="220"/>
+      <c r="E257" s="221"/>
+      <c r="F257" s="227"/>
       <c r="G257" s="163" t="s">
         <v>557</v>
       </c>
@@ -60059,12 +60115,12 @@
       <c r="M257" s="5"/>
     </row>
     <row r="258" spans="1:13" ht="59.25" customHeight="1">
-      <c r="A258" s="207"/>
-      <c r="B258" s="208"/>
-      <c r="C258" s="206"/>
-      <c r="D258" s="206"/>
-      <c r="E258" s="207"/>
-      <c r="F258" s="219"/>
+      <c r="A258" s="221"/>
+      <c r="B258" s="222"/>
+      <c r="C258" s="220"/>
+      <c r="D258" s="220"/>
+      <c r="E258" s="221"/>
+      <c r="F258" s="227"/>
       <c r="G258" s="163" t="s">
         <v>558</v>
       </c>
@@ -60082,12 +60138,12 @@
       <c r="M258" s="5"/>
     </row>
     <row r="259" spans="1:13" ht="67.5" customHeight="1">
-      <c r="A259" s="212"/>
-      <c r="B259" s="216"/>
-      <c r="C259" s="214"/>
-      <c r="D259" s="214"/>
-      <c r="E259" s="212"/>
-      <c r="F259" s="220"/>
+      <c r="A259" s="200"/>
+      <c r="B259" s="203"/>
+      <c r="C259" s="206"/>
+      <c r="D259" s="206"/>
+      <c r="E259" s="200"/>
+      <c r="F259" s="228"/>
       <c r="G259" s="164" t="s">
         <v>559</v>
       </c>
@@ -60105,22 +60161,22 @@
       <c r="M259" s="56"/>
     </row>
     <row r="260" spans="1:13" ht="67.5" customHeight="1">
-      <c r="A260" s="207">
+      <c r="A260" s="221">
         <v>87</v>
       </c>
-      <c r="B260" s="208">
+      <c r="B260" s="222">
         <v>46172</v>
       </c>
-      <c r="C260" s="207" t="s">
+      <c r="C260" s="221" t="s">
         <v>32</v>
       </c>
-      <c r="D260" s="206" t="s">
+      <c r="D260" s="220" t="s">
         <v>560</v>
       </c>
-      <c r="E260" s="207" t="s">
+      <c r="E260" s="221" t="s">
         <v>27</v>
       </c>
-      <c r="F260" s="333" t="s">
+      <c r="F260" s="337" t="s">
         <v>561</v>
       </c>
       <c r="G260" s="13" t="s">
@@ -60136,12 +60192,12 @@
       <c r="M260" s="5"/>
     </row>
     <row r="261" spans="1:13" ht="64.5" customHeight="1">
-      <c r="A261" s="207"/>
-      <c r="B261" s="208"/>
-      <c r="C261" s="207"/>
-      <c r="D261" s="206"/>
-      <c r="E261" s="207"/>
-      <c r="F261" s="206"/>
+      <c r="A261" s="221"/>
+      <c r="B261" s="222"/>
+      <c r="C261" s="221"/>
+      <c r="D261" s="220"/>
+      <c r="E261" s="221"/>
+      <c r="F261" s="220"/>
       <c r="G261" s="13" t="s">
         <v>564</v>
       </c>
@@ -60170,7 +60226,7 @@
         <v>565</v>
       </c>
       <c r="E262" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F262" s="13" t="s">
         <v>566</v>
@@ -60225,22 +60281,22 @@
       </c>
     </row>
     <row r="264" spans="1:13" ht="81" customHeight="1">
-      <c r="A264" s="204">
+      <c r="A264" s="219">
         <v>90</v>
       </c>
-      <c r="B264" s="216">
+      <c r="B264" s="203">
         <v>46192</v>
       </c>
-      <c r="C264" s="214" t="s">
+      <c r="C264" s="206" t="s">
         <v>125</v>
       </c>
-      <c r="D264" s="214" t="s">
+      <c r="D264" s="206" t="s">
         <v>572</v>
       </c>
-      <c r="E264" s="212" t="s">
-        <v>520</v>
-      </c>
-      <c r="F264" s="198" t="s">
+      <c r="E264" s="200" t="s">
+        <v>521</v>
+      </c>
+      <c r="F264" s="214" t="s">
         <v>573</v>
       </c>
       <c r="G264" s="56" t="s">
@@ -60260,12 +60316,12 @@
       <c r="M264" s="58"/>
     </row>
     <row r="265" spans="1:13" ht="81" customHeight="1">
-      <c r="A265" s="204"/>
-      <c r="B265" s="305"/>
-      <c r="C265" s="303"/>
-      <c r="D265" s="303"/>
-      <c r="E265" s="259"/>
-      <c r="F265" s="334"/>
+      <c r="A265" s="219"/>
+      <c r="B265" s="204"/>
+      <c r="C265" s="207"/>
+      <c r="D265" s="207"/>
+      <c r="E265" s="201"/>
+      <c r="F265" s="338"/>
       <c r="G265" s="56" t="s">
         <v>576</v>
       </c>
@@ -60283,12 +60339,12 @@
       <c r="M265" s="58"/>
     </row>
     <row r="266" spans="1:13" ht="81" customHeight="1">
-      <c r="A266" s="205"/>
-      <c r="B266" s="217"/>
-      <c r="C266" s="215"/>
-      <c r="D266" s="215"/>
-      <c r="E266" s="213"/>
-      <c r="F266" s="199"/>
+      <c r="A266" s="213"/>
+      <c r="B266" s="205"/>
+      <c r="C266" s="208"/>
+      <c r="D266" s="208"/>
+      <c r="E266" s="202"/>
+      <c r="F266" s="215"/>
       <c r="G266" s="56" t="s">
         <v>578</v>
       </c>
@@ -60306,22 +60362,22 @@
       <c r="M266" s="58"/>
     </row>
     <row r="267" spans="1:13" ht="63.75" customHeight="1">
-      <c r="A267" s="212">
+      <c r="A267" s="200">
         <v>91</v>
       </c>
-      <c r="B267" s="208">
+      <c r="B267" s="222">
         <v>46201</v>
       </c>
-      <c r="C267" s="206" t="s">
+      <c r="C267" s="220" t="s">
         <v>580</v>
       </c>
-      <c r="D267" s="206" t="s">
+      <c r="D267" s="220" t="s">
         <v>581</v>
       </c>
-      <c r="E267" s="218" t="s">
+      <c r="E267" s="226" t="s">
         <v>199</v>
       </c>
-      <c r="F267" s="342" t="s">
+      <c r="F267" s="346" t="s">
         <v>582</v>
       </c>
       <c r="G267" s="150" t="s">
@@ -60338,17 +60394,17 @@
       </c>
       <c r="K267" s="111"/>
       <c r="L267" s="12"/>
-      <c r="M267" s="341" t="s">
+      <c r="M267" s="345" t="s">
         <v>585</v>
       </c>
     </row>
     <row r="268" spans="1:13" ht="44.25" customHeight="1">
-      <c r="A268" s="259"/>
-      <c r="B268" s="208"/>
-      <c r="C268" s="206"/>
-      <c r="D268" s="206"/>
-      <c r="E268" s="218"/>
-      <c r="F268" s="342"/>
+      <c r="A268" s="201"/>
+      <c r="B268" s="222"/>
+      <c r="C268" s="220"/>
+      <c r="D268" s="220"/>
+      <c r="E268" s="226"/>
+      <c r="F268" s="346"/>
       <c r="G268" s="14" t="s">
         <v>586</v>
       </c>
@@ -60363,15 +60419,15 @@
       </c>
       <c r="K268" s="169"/>
       <c r="L268" s="170"/>
-      <c r="M268" s="334"/>
+      <c r="M268" s="338"/>
     </row>
     <row r="269" spans="1:13" ht="54.75" customHeight="1">
-      <c r="A269" s="213"/>
-      <c r="B269" s="216"/>
-      <c r="C269" s="214"/>
-      <c r="D269" s="214"/>
-      <c r="E269" s="343"/>
-      <c r="F269" s="200"/>
+      <c r="A269" s="202"/>
+      <c r="B269" s="203"/>
+      <c r="C269" s="206"/>
+      <c r="D269" s="206"/>
+      <c r="E269" s="347"/>
+      <c r="F269" s="216"/>
       <c r="G269" s="139" t="s">
         <v>587</v>
       </c>
@@ -60386,25 +60442,25 @@
       </c>
       <c r="K269" s="60"/>
       <c r="L269" s="95"/>
-      <c r="M269" s="334"/>
+      <c r="M269" s="338"/>
     </row>
     <row r="270" spans="1:13" ht="63.75" customHeight="1">
-      <c r="A270" s="212">
+      <c r="A270" s="200">
         <v>92</v>
       </c>
-      <c r="B270" s="354">
+      <c r="B270" s="358">
         <v>46227</v>
       </c>
-      <c r="C270" s="352" t="s">
+      <c r="C270" s="356" t="s">
         <v>501</v>
       </c>
-      <c r="D270" s="352" t="s">
+      <c r="D270" s="356" t="s">
         <v>588</v>
       </c>
-      <c r="E270" s="351" t="s">
+      <c r="E270" s="355" t="s">
         <v>27</v>
       </c>
-      <c r="F270" s="349" t="s">
+      <c r="F270" s="353" t="s">
         <v>589</v>
       </c>
       <c r="G270" s="166" t="s">
@@ -60424,12 +60480,12 @@
       <c r="M270" s="58"/>
     </row>
     <row r="271" spans="1:13" ht="63.75" customHeight="1">
-      <c r="A271" s="259"/>
-      <c r="B271" s="355"/>
-      <c r="C271" s="353"/>
-      <c r="D271" s="353"/>
-      <c r="E271" s="203"/>
-      <c r="F271" s="350"/>
+      <c r="A271" s="201"/>
+      <c r="B271" s="359"/>
+      <c r="C271" s="357"/>
+      <c r="D271" s="357"/>
+      <c r="E271" s="212"/>
+      <c r="F271" s="354"/>
       <c r="G271" s="14" t="s">
         <v>592</v>
       </c>
@@ -60465,7 +60521,7 @@
       <c r="F272" s="13" t="s">
         <v>595</v>
       </c>
-      <c r="G272" s="191" t="s">
+      <c r="G272" s="190" t="s">
         <v>30</v>
       </c>
       <c r="H272" s="43" t="s">
@@ -60488,28 +60544,28 @@
       </c>
     </row>
     <row r="273" spans="1:13" ht="98.25" customHeight="1">
-      <c r="A273" s="210">
+      <c r="A273" s="224">
         <v>94</v>
       </c>
-      <c r="B273" s="208">
+      <c r="B273" s="222">
         <v>46242</v>
       </c>
-      <c r="C273" s="346" t="s">
+      <c r="C273" s="350" t="s">
         <v>265</v>
       </c>
-      <c r="D273" s="215" t="s">
+      <c r="D273" s="208" t="s">
         <v>596</v>
       </c>
-      <c r="E273" s="344" t="s">
+      <c r="E273" s="348" t="s">
         <v>320</v>
       </c>
-      <c r="F273" s="202" t="s">
+      <c r="F273" s="218" t="s">
         <v>597</v>
       </c>
       <c r="G273" s="13" t="s">
         <v>598</v>
       </c>
-      <c r="H273" s="190" t="s">
+      <c r="H273" s="189" t="s">
         <v>599</v>
       </c>
       <c r="I273" s="4">
@@ -60520,18 +60576,18 @@
       </c>
       <c r="K273" s="12"/>
       <c r="L273" s="12"/>
-      <c r="M273" s="333" t="s">
+      <c r="M273" s="337" t="s">
         <v>600</v>
       </c>
     </row>
     <row r="274" spans="1:13" ht="68.25" customHeight="1">
-      <c r="A274" s="210"/>
-      <c r="B274" s="208"/>
-      <c r="C274" s="347"/>
-      <c r="D274" s="206"/>
-      <c r="E274" s="258"/>
-      <c r="F274" s="342"/>
-      <c r="G274" s="188" t="s">
+      <c r="A274" s="224"/>
+      <c r="B274" s="222"/>
+      <c r="C274" s="351"/>
+      <c r="D274" s="220"/>
+      <c r="E274" s="266"/>
+      <c r="F274" s="346"/>
+      <c r="G274" s="187" t="s">
         <v>601</v>
       </c>
       <c r="H274" s="175" t="s">
@@ -60545,16 +60601,16 @@
       </c>
       <c r="K274" s="12"/>
       <c r="L274" s="12"/>
-      <c r="M274" s="333"/>
+      <c r="M274" s="337"/>
     </row>
     <row r="275" spans="1:13" ht="67.5" customHeight="1">
-      <c r="A275" s="210"/>
-      <c r="B275" s="208"/>
-      <c r="C275" s="347"/>
-      <c r="D275" s="206"/>
-      <c r="E275" s="258"/>
-      <c r="F275" s="333"/>
-      <c r="G275" s="192" t="s">
+      <c r="A275" s="224"/>
+      <c r="B275" s="222"/>
+      <c r="C275" s="351"/>
+      <c r="D275" s="220"/>
+      <c r="E275" s="266"/>
+      <c r="F275" s="337"/>
+      <c r="G275" s="191" t="s">
         <v>603</v>
       </c>
       <c r="H275" s="175" t="s">
@@ -60568,15 +60624,15 @@
       </c>
       <c r="K275" s="12"/>
       <c r="L275" s="12"/>
-      <c r="M275" s="333"/>
+      <c r="M275" s="337"/>
     </row>
     <row r="276" spans="1:13" ht="93.75" customHeight="1">
-      <c r="A276" s="210"/>
-      <c r="B276" s="208"/>
-      <c r="C276" s="347"/>
-      <c r="D276" s="206"/>
-      <c r="E276" s="258"/>
-      <c r="F276" s="342"/>
+      <c r="A276" s="224"/>
+      <c r="B276" s="222"/>
+      <c r="C276" s="351"/>
+      <c r="D276" s="220"/>
+      <c r="E276" s="266"/>
+      <c r="F276" s="346"/>
       <c r="G276" s="13" t="s">
         <v>605</v>
       </c>
@@ -60591,15 +60647,15 @@
       </c>
       <c r="K276" s="12"/>
       <c r="L276" s="12"/>
-      <c r="M276" s="333"/>
+      <c r="M276" s="337"/>
     </row>
     <row r="277" spans="1:13" ht="72" customHeight="1">
-      <c r="A277" s="210"/>
-      <c r="B277" s="208"/>
-      <c r="C277" s="347"/>
-      <c r="D277" s="206"/>
-      <c r="E277" s="258"/>
-      <c r="F277" s="342"/>
+      <c r="A277" s="224"/>
+      <c r="B277" s="222"/>
+      <c r="C277" s="351"/>
+      <c r="D277" s="220"/>
+      <c r="E277" s="266"/>
+      <c r="F277" s="346"/>
       <c r="G277" s="13" t="s">
         <v>606</v>
       </c>
@@ -60614,15 +60670,15 @@
       </c>
       <c r="K277" s="12"/>
       <c r="L277" s="12"/>
-      <c r="M277" s="333"/>
+      <c r="M277" s="337"/>
     </row>
     <row r="278" spans="1:13" ht="74.25" customHeight="1">
-      <c r="A278" s="210"/>
-      <c r="B278" s="208"/>
-      <c r="C278" s="347"/>
-      <c r="D278" s="206"/>
-      <c r="E278" s="258"/>
-      <c r="F278" s="342"/>
+      <c r="A278" s="224"/>
+      <c r="B278" s="222"/>
+      <c r="C278" s="351"/>
+      <c r="D278" s="220"/>
+      <c r="E278" s="266"/>
+      <c r="F278" s="346"/>
       <c r="G278" s="116" t="s">
         <v>608</v>
       </c>
@@ -60637,16 +60693,16 @@
       </c>
       <c r="K278" s="12"/>
       <c r="L278" s="12"/>
-      <c r="M278" s="333"/>
+      <c r="M278" s="337"/>
     </row>
     <row r="279" spans="1:13" ht="57" customHeight="1">
-      <c r="A279" s="210"/>
-      <c r="B279" s="208"/>
-      <c r="C279" s="347"/>
-      <c r="D279" s="206"/>
-      <c r="E279" s="258"/>
-      <c r="F279" s="342"/>
-      <c r="G279" s="188" t="s">
+      <c r="A279" s="224"/>
+      <c r="B279" s="222"/>
+      <c r="C279" s="351"/>
+      <c r="D279" s="220"/>
+      <c r="E279" s="266"/>
+      <c r="F279" s="346"/>
+      <c r="G279" s="187" t="s">
         <v>610</v>
       </c>
       <c r="H279" s="175" t="s">
@@ -60660,15 +60716,15 @@
       </c>
       <c r="K279" s="12"/>
       <c r="L279" s="12"/>
-      <c r="M279" s="333"/>
+      <c r="M279" s="337"/>
     </row>
     <row r="280" spans="1:13" ht="72" customHeight="1">
-      <c r="A280" s="210"/>
-      <c r="B280" s="216"/>
-      <c r="C280" s="348"/>
-      <c r="D280" s="214"/>
-      <c r="E280" s="345"/>
-      <c r="F280" s="200"/>
+      <c r="A280" s="224"/>
+      <c r="B280" s="203"/>
+      <c r="C280" s="352"/>
+      <c r="D280" s="206"/>
+      <c r="E280" s="349"/>
+      <c r="F280" s="216"/>
       <c r="G280" s="181" t="s">
         <v>612</v>
       </c>
@@ -60678,33 +60734,33 @@
       <c r="I280" s="4">
         <v>46295</v>
       </c>
-      <c r="J280" s="193" t="s">
+      <c r="J280" s="192" t="s">
         <v>614</v>
       </c>
       <c r="K280" s="12"/>
       <c r="L280" s="12"/>
-      <c r="M280" s="333"/>
+      <c r="M280" s="337"/>
     </row>
     <row r="281" spans="1:13" ht="90" customHeight="1">
-      <c r="A281" s="212">
+      <c r="A281" s="200">
         <v>95</v>
       </c>
-      <c r="B281" s="216">
+      <c r="B281" s="203">
         <v>46247</v>
       </c>
-      <c r="C281" s="214" t="s">
+      <c r="C281" s="206" t="s">
         <v>265</v>
       </c>
-      <c r="D281" s="214" t="s">
+      <c r="D281" s="206" t="s">
         <v>615</v>
       </c>
-      <c r="E281" s="338" t="s">
+      <c r="E281" s="342" t="s">
         <v>27</v>
       </c>
-      <c r="F281" s="200" t="s">
+      <c r="F281" s="216" t="s">
         <v>616</v>
       </c>
-      <c r="G281" s="189" t="s">
+      <c r="G281" s="188" t="s">
         <v>617</v>
       </c>
       <c r="H281" s="168" t="s">
@@ -60720,13 +60776,13 @@
       <c r="M281" s="159"/>
     </row>
     <row r="282" spans="1:13" ht="90.75" customHeight="1">
-      <c r="A282" s="259"/>
-      <c r="B282" s="305"/>
-      <c r="C282" s="303"/>
-      <c r="D282" s="303"/>
-      <c r="E282" s="339"/>
-      <c r="F282" s="201"/>
-      <c r="G282" s="189" t="s">
+      <c r="A282" s="201"/>
+      <c r="B282" s="204"/>
+      <c r="C282" s="207"/>
+      <c r="D282" s="207"/>
+      <c r="E282" s="343"/>
+      <c r="F282" s="217"/>
+      <c r="G282" s="188" t="s">
         <v>619</v>
       </c>
       <c r="H282" s="168" t="s">
@@ -60743,13 +60799,13 @@
       <c r="M282" s="137"/>
     </row>
     <row r="283" spans="1:13" ht="61.5" customHeight="1">
-      <c r="A283" s="213"/>
-      <c r="B283" s="305"/>
-      <c r="C283" s="303"/>
-      <c r="D283" s="303"/>
-      <c r="E283" s="340"/>
-      <c r="F283" s="202"/>
-      <c r="G283" s="189" t="s">
+      <c r="A283" s="202"/>
+      <c r="B283" s="204"/>
+      <c r="C283" s="207"/>
+      <c r="D283" s="207"/>
+      <c r="E283" s="344"/>
+      <c r="F283" s="218"/>
+      <c r="G283" s="188" t="s">
         <v>620</v>
       </c>
       <c r="H283" s="168" t="s">
@@ -60766,22 +60822,22 @@
       <c r="M283" s="137"/>
     </row>
     <row r="284" spans="1:13" ht="96.75" customHeight="1">
-      <c r="A284" s="212">
+      <c r="A284" s="200">
         <v>96</v>
       </c>
-      <c r="B284" s="216">
+      <c r="B284" s="203">
         <v>46265</v>
       </c>
-      <c r="C284" s="214" t="s">
+      <c r="C284" s="206" t="s">
         <v>265</v>
       </c>
-      <c r="D284" s="214" t="s">
+      <c r="D284" s="206" t="s">
         <v>621</v>
       </c>
-      <c r="E284" s="212" t="s">
+      <c r="E284" s="200" t="s">
         <v>182</v>
       </c>
-      <c r="F284" s="200" t="s">
+      <c r="F284" s="216" t="s">
         <v>622</v>
       </c>
       <c r="G284" s="13" t="s">
@@ -60796,19 +60852,19 @@
       <c r="J284" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="K284" s="195"/>
+      <c r="K284" s="193"/>
       <c r="L284" s="60"/>
-      <c r="M284" s="198" t="s">
+      <c r="M284" s="214" t="s">
         <v>625</v>
       </c>
     </row>
     <row r="285" spans="1:13" ht="96.75" customHeight="1">
-      <c r="A285" s="213"/>
-      <c r="B285" s="217"/>
-      <c r="C285" s="215"/>
-      <c r="D285" s="215"/>
-      <c r="E285" s="213"/>
-      <c r="F285" s="202"/>
+      <c r="A285" s="202"/>
+      <c r="B285" s="205"/>
+      <c r="C285" s="208"/>
+      <c r="D285" s="208"/>
+      <c r="E285" s="202"/>
+      <c r="F285" s="218"/>
       <c r="G285" s="14" t="s">
         <v>626</v>
       </c>
@@ -60823,25 +60879,25 @@
       </c>
       <c r="K285" s="174"/>
       <c r="L285" s="60"/>
-      <c r="M285" s="199"/>
+      <c r="M285" s="215"/>
     </row>
     <row r="286" spans="1:13" ht="54.75" customHeight="1">
-      <c r="A286" s="209">
+      <c r="A286" s="223">
         <v>97</v>
       </c>
-      <c r="B286" s="208">
+      <c r="B286" s="222">
         <v>46275</v>
       </c>
-      <c r="C286" s="207" t="s">
+      <c r="C286" s="221" t="s">
         <v>125</v>
       </c>
-      <c r="D286" s="206" t="s">
+      <c r="D286" s="220" t="s">
         <v>628</v>
       </c>
-      <c r="E286" s="203" t="s">
-        <v>520</v>
-      </c>
-      <c r="F286" s="200" t="s">
+      <c r="E286" s="212" t="s">
+        <v>521</v>
+      </c>
+      <c r="F286" s="216" t="s">
         <v>629</v>
       </c>
       <c r="G286" s="13" t="s">
@@ -60861,12 +60917,12 @@
       <c r="M286" s="139"/>
     </row>
     <row r="287" spans="1:13" ht="54.75" customHeight="1">
-      <c r="A287" s="210"/>
-      <c r="B287" s="208"/>
-      <c r="C287" s="207"/>
-      <c r="D287" s="206"/>
-      <c r="E287" s="204"/>
-      <c r="F287" s="201"/>
+      <c r="A287" s="224"/>
+      <c r="B287" s="222"/>
+      <c r="C287" s="221"/>
+      <c r="D287" s="220"/>
+      <c r="E287" s="219"/>
+      <c r="F287" s="217"/>
       <c r="G287" s="13" t="s">
         <v>632</v>
       </c>
@@ -60884,12 +60940,12 @@
       <c r="M287" s="139"/>
     </row>
     <row r="288" spans="1:13" ht="54.75" customHeight="1">
-      <c r="A288" s="211"/>
-      <c r="B288" s="208"/>
-      <c r="C288" s="207"/>
-      <c r="D288" s="206"/>
-      <c r="E288" s="205"/>
-      <c r="F288" s="202"/>
+      <c r="A288" s="225"/>
+      <c r="B288" s="222"/>
+      <c r="C288" s="221"/>
+      <c r="D288" s="220"/>
+      <c r="E288" s="213"/>
+      <c r="F288" s="218"/>
       <c r="G288" s="13" t="s">
         <v>634</v>
       </c>
@@ -60899,7 +60955,7 @@
       <c r="I288" s="171">
         <v>46285</v>
       </c>
-      <c r="J288" s="5" t="s">
+      <c r="J288" s="56" t="s">
         <v>20</v>
       </c>
       <c r="K288" s="174"/>
@@ -60907,120 +60963,264 @@
       <c r="M288" s="139"/>
     </row>
     <row r="289" spans="1:13" ht="50.25" customHeight="1">
-      <c r="A289" s="85">
+      <c r="A289" s="200">
         <v>98</v>
       </c>
-      <c r="B289" s="136">
+      <c r="B289" s="203">
         <v>46278</v>
       </c>
-      <c r="C289" s="97" t="s">
+      <c r="C289" s="200" t="s">
         <v>125</v>
       </c>
-      <c r="D289" s="97" t="s">
+      <c r="D289" s="200" t="s">
         <v>635</v>
       </c>
-      <c r="E289" s="56" t="s">
+      <c r="E289" s="200" t="s">
         <v>27</v>
       </c>
-      <c r="F289" s="135" t="s">
+      <c r="F289" s="206" t="s">
         <v>636</v>
       </c>
       <c r="G289" s="12"/>
       <c r="H289" s="167"/>
-      <c r="I289" s="60"/>
-      <c r="J289" s="177"/>
-      <c r="K289" s="60"/>
+      <c r="I289" s="95"/>
+      <c r="J289" s="12"/>
+      <c r="K289" s="167"/>
       <c r="L289" s="60"/>
       <c r="M289" s="60"/>
     </row>
-    <row r="290" spans="1:13" ht="75" customHeight="1">
-      <c r="A290" s="98">
-        <v>99</v>
-      </c>
-      <c r="B290" s="57">
-        <v>46280</v>
-      </c>
-      <c r="C290" s="93" t="s">
-        <v>125</v>
-      </c>
-      <c r="D290" s="56" t="s">
+    <row r="290" spans="1:13" ht="50.25" customHeight="1">
+      <c r="A290" s="201"/>
+      <c r="B290" s="204"/>
+      <c r="C290" s="201"/>
+      <c r="D290" s="201"/>
+      <c r="E290" s="201"/>
+      <c r="F290" s="207"/>
+      <c r="G290" s="194" t="s">
         <v>637</v>
       </c>
-      <c r="E290" s="93" t="s">
-        <v>182</v>
-      </c>
-      <c r="F290" s="187" t="s">
+      <c r="H290" s="195" t="s">
         <v>638</v>
       </c>
-      <c r="G290" s="60"/>
-      <c r="H290" s="167"/>
-      <c r="I290" s="60"/>
-      <c r="J290" s="60"/>
-      <c r="K290" s="60"/>
+      <c r="I290" s="95"/>
+      <c r="J290" s="12"/>
+      <c r="K290" s="167"/>
       <c r="L290" s="60"/>
       <c r="M290" s="60"/>
     </row>
-    <row r="291" spans="1:13" ht="73.5" customHeight="1">
-      <c r="A291" s="85">
-        <v>100</v>
-      </c>
-      <c r="B291" s="147">
-        <v>46289</v>
-      </c>
-      <c r="C291" s="56" t="s">
-        <v>265</v>
-      </c>
-      <c r="D291" s="58" t="s">
-        <v>639</v>
-      </c>
-      <c r="E291" s="58" t="s">
-        <v>27</v>
-      </c>
-      <c r="F291" s="137" t="s">
-        <v>640</v>
-      </c>
-      <c r="G291" s="197" t="s">
-        <v>641</v>
-      </c>
-      <c r="H291" s="60"/>
-      <c r="I291" s="60"/>
-      <c r="J291" s="60"/>
-      <c r="K291" s="60"/>
+    <row r="291" spans="1:13" ht="50.25" customHeight="1">
+      <c r="A291" s="202"/>
+      <c r="B291" s="205"/>
+      <c r="C291" s="202"/>
+      <c r="D291" s="202"/>
+      <c r="E291" s="202"/>
+      <c r="F291" s="208"/>
+      <c r="G291" s="60"/>
+      <c r="H291" s="167"/>
+      <c r="I291" s="95"/>
+      <c r="J291" s="12"/>
+      <c r="K291" s="167"/>
       <c r="L291" s="60"/>
       <c r="M291" s="60"/>
     </row>
-    <row r="292" spans="1:13" ht="92.25" customHeight="1">
-      <c r="A292" s="5">
+    <row r="292" spans="1:13" ht="75" customHeight="1">
+      <c r="A292" s="200">
+        <v>99</v>
+      </c>
+      <c r="B292" s="210">
+        <v>46280</v>
+      </c>
+      <c r="C292" s="212" t="s">
+        <v>125</v>
+      </c>
+      <c r="D292" s="200" t="s">
+        <v>639</v>
+      </c>
+      <c r="E292" s="200" t="s">
+        <v>182</v>
+      </c>
+      <c r="F292" s="206" t="s">
+        <v>640</v>
+      </c>
+      <c r="G292" s="194" t="s">
+        <v>641</v>
+      </c>
+      <c r="H292" s="196" t="s">
+        <v>642</v>
+      </c>
+      <c r="I292" s="197">
+        <v>46310</v>
+      </c>
+      <c r="J292" s="177" t="s">
+        <v>222</v>
+      </c>
+      <c r="K292" s="60" t="s">
+        <v>643</v>
+      </c>
+      <c r="L292" s="60"/>
+      <c r="M292" s="60"/>
+    </row>
+    <row r="293" spans="1:13" ht="75" customHeight="1">
+      <c r="A293" s="202"/>
+      <c r="B293" s="211"/>
+      <c r="C293" s="213"/>
+      <c r="D293" s="202"/>
+      <c r="E293" s="202"/>
+      <c r="F293" s="208"/>
+      <c r="G293" s="194" t="s">
+        <v>644</v>
+      </c>
+      <c r="H293" s="93" t="s">
+        <v>257</v>
+      </c>
+      <c r="I293" s="197">
+        <v>46310</v>
+      </c>
+      <c r="J293" s="60" t="s">
+        <v>222</v>
+      </c>
+      <c r="K293" s="60" t="s">
+        <v>645</v>
+      </c>
+      <c r="L293" s="60"/>
+      <c r="M293" s="60"/>
+    </row>
+    <row r="294" spans="1:13" ht="73.5" customHeight="1">
+      <c r="A294" s="200">
+        <v>100</v>
+      </c>
+      <c r="B294" s="203">
+        <v>46289</v>
+      </c>
+      <c r="C294" s="200" t="s">
+        <v>265</v>
+      </c>
+      <c r="D294" s="206" t="s">
+        <v>646</v>
+      </c>
+      <c r="E294" s="206" t="s">
+        <v>27</v>
+      </c>
+      <c r="F294" s="206" t="s">
+        <v>647</v>
+      </c>
+      <c r="G294" s="139" t="s">
+        <v>648</v>
+      </c>
+      <c r="H294" s="194" t="s">
+        <v>649</v>
+      </c>
+      <c r="I294" s="197">
+        <v>46325</v>
+      </c>
+      <c r="J294" s="60" t="s">
+        <v>222</v>
+      </c>
+      <c r="K294" s="60"/>
+      <c r="L294" s="60"/>
+      <c r="M294" s="60"/>
+    </row>
+    <row r="295" spans="1:13" ht="73.5" customHeight="1">
+      <c r="A295" s="201"/>
+      <c r="B295" s="204"/>
+      <c r="C295" s="201"/>
+      <c r="D295" s="207"/>
+      <c r="E295" s="207"/>
+      <c r="F295" s="207"/>
+      <c r="G295" s="139" t="s">
+        <v>650</v>
+      </c>
+      <c r="H295" s="194" t="s">
+        <v>649</v>
+      </c>
+      <c r="I295" s="197">
+        <v>46325</v>
+      </c>
+      <c r="J295" s="60" t="s">
+        <v>222</v>
+      </c>
+      <c r="K295" s="60"/>
+      <c r="L295" s="60"/>
+      <c r="M295" s="60"/>
+    </row>
+    <row r="296" spans="1:13" ht="43.5" customHeight="1">
+      <c r="A296" s="200">
         <v>101</v>
       </c>
-      <c r="B292" s="4">
+      <c r="B296" s="203">
         <v>46299</v>
       </c>
-      <c r="C292" s="98" t="s">
+      <c r="C296" s="200" t="s">
         <v>125</v>
       </c>
-      <c r="D292" s="2" t="s">
-        <v>642</v>
-      </c>
-      <c r="E292" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="F292" s="196" t="s">
-        <v>643</v>
-      </c>
-      <c r="G292" s="194" t="s">
-        <v>644</v>
-      </c>
-      <c r="H292" s="12"/>
-      <c r="I292" s="12"/>
-      <c r="J292" s="12"/>
-      <c r="K292" s="12"/>
-      <c r="L292" s="12"/>
-      <c r="M292" s="12"/>
+      <c r="D296" s="206" t="s">
+        <v>651</v>
+      </c>
+      <c r="E296" s="206" t="s">
+        <v>521</v>
+      </c>
+      <c r="F296" s="206" t="s">
+        <v>652</v>
+      </c>
+      <c r="G296" s="198" t="s">
+        <v>653</v>
+      </c>
+      <c r="H296" s="194" t="s">
+        <v>649</v>
+      </c>
+      <c r="I296" s="197">
+        <v>46325</v>
+      </c>
+      <c r="J296" s="60" t="s">
+        <v>222</v>
+      </c>
+      <c r="K296" s="12"/>
+      <c r="L296" s="12"/>
+      <c r="M296" s="12"/>
+    </row>
+    <row r="297" spans="1:13" ht="36.75" customHeight="1">
+      <c r="A297" s="201"/>
+      <c r="B297" s="204"/>
+      <c r="C297" s="201"/>
+      <c r="D297" s="207"/>
+      <c r="E297" s="207"/>
+      <c r="F297" s="207"/>
+      <c r="G297" s="114" t="s">
+        <v>654</v>
+      </c>
+      <c r="H297" s="194" t="s">
+        <v>649</v>
+      </c>
+      <c r="I297" s="197">
+        <v>46325</v>
+      </c>
+      <c r="J297" s="60" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="298" spans="1:13" ht="39.75" customHeight="1">
+      <c r="A298" s="202"/>
+      <c r="B298" s="205"/>
+      <c r="C298" s="202"/>
+      <c r="D298" s="208"/>
+      <c r="E298" s="208"/>
+      <c r="F298" s="209"/>
+      <c r="G298" s="14" t="s">
+        <v>655</v>
+      </c>
+      <c r="H298" s="100" t="s">
+        <v>649</v>
+      </c>
+      <c r="I298" s="199">
+        <v>46325</v>
+      </c>
+      <c r="J298" s="12" t="s">
+        <v>222</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:COT291" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <mergeCells count="647">
+  <autoFilter ref="A2:COT296" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <mergeCells count="671">
     <mergeCell ref="M273:M280"/>
     <mergeCell ref="A273:A280"/>
     <mergeCell ref="F273:F280"/>
@@ -61655,6 +61855,12 @@
     <mergeCell ref="C148:C150"/>
     <mergeCell ref="K190:K191"/>
     <mergeCell ref="K182:K184"/>
+    <mergeCell ref="F289:F291"/>
+    <mergeCell ref="E289:E291"/>
+    <mergeCell ref="D289:D291"/>
+    <mergeCell ref="C289:C291"/>
+    <mergeCell ref="B289:B291"/>
+    <mergeCell ref="A289:A291"/>
     <mergeCell ref="M284:M285"/>
     <mergeCell ref="F286:F288"/>
     <mergeCell ref="E286:E288"/>
@@ -61668,6 +61874,24 @@
     <mergeCell ref="B284:B285"/>
     <mergeCell ref="A284:A285"/>
     <mergeCell ref="F284:F285"/>
+    <mergeCell ref="A296:A298"/>
+    <mergeCell ref="B296:B298"/>
+    <mergeCell ref="C296:C298"/>
+    <mergeCell ref="D296:D298"/>
+    <mergeCell ref="E296:E298"/>
+    <mergeCell ref="F296:F298"/>
+    <mergeCell ref="A292:A293"/>
+    <mergeCell ref="B292:B293"/>
+    <mergeCell ref="C292:C293"/>
+    <mergeCell ref="D292:D293"/>
+    <mergeCell ref="E292:E293"/>
+    <mergeCell ref="F292:F293"/>
+    <mergeCell ref="A294:A295"/>
+    <mergeCell ref="B294:B295"/>
+    <mergeCell ref="C294:C295"/>
+    <mergeCell ref="D294:D295"/>
+    <mergeCell ref="E294:E295"/>
+    <mergeCell ref="F294:F295"/>
   </mergeCells>
   <conditionalFormatting sqref="J2:J66 J155:J170 I142:I145 J222 J227 J69:J138 J142:J150 J175:J214 J232:J271 J273:J1048576">
     <cfRule type="cellIs" dxfId="32" priority="36" operator="equal">
@@ -61836,128 +62060,128 @@
   </cols>
   <sheetData>
     <row r="5" spans="2:7" hidden="1">
-      <c r="B5" s="212">
+      <c r="B5" s="200">
         <v>84</v>
       </c>
-      <c r="C5" s="216">
+      <c r="C5" s="203">
         <v>46166</v>
       </c>
-      <c r="D5" s="214" t="s">
+      <c r="D5" s="206" t="s">
         <v>501</v>
       </c>
-      <c r="E5" s="214" t="s">
+      <c r="E5" s="206" t="s">
         <v>537</v>
       </c>
-      <c r="F5" s="212" t="s">
+      <c r="F5" s="200" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="198" t="s">
+      <c r="G5" s="214" t="s">
         <v>538</v>
       </c>
     </row>
     <row r="6" spans="2:7" ht="79.5" hidden="1" customHeight="1">
-      <c r="B6" s="213"/>
-      <c r="C6" s="217"/>
-      <c r="D6" s="215"/>
-      <c r="E6" s="215"/>
-      <c r="F6" s="213"/>
-      <c r="G6" s="199"/>
+      <c r="B6" s="202"/>
+      <c r="C6" s="205"/>
+      <c r="D6" s="208"/>
+      <c r="E6" s="208"/>
+      <c r="F6" s="202"/>
+      <c r="G6" s="215"/>
     </row>
     <row r="7" spans="2:7" hidden="1">
-      <c r="B7" s="212">
+      <c r="B7" s="200">
         <v>85</v>
       </c>
-      <c r="C7" s="336">
+      <c r="C7" s="340">
         <v>46166</v>
       </c>
-      <c r="D7" s="214" t="s">
+      <c r="D7" s="206" t="s">
         <v>501</v>
       </c>
-      <c r="E7" s="214" t="s">
+      <c r="E7" s="206" t="s">
         <v>543</v>
       </c>
-      <c r="F7" s="212" t="s">
-        <v>520</v>
-      </c>
-      <c r="G7" s="198" t="s">
+      <c r="F7" s="200" t="s">
+        <v>521</v>
+      </c>
+      <c r="G7" s="214" t="s">
         <v>544</v>
       </c>
     </row>
     <row r="8" spans="2:7" hidden="1">
-      <c r="B8" s="259"/>
-      <c r="C8" s="337"/>
-      <c r="D8" s="303"/>
-      <c r="E8" s="303"/>
-      <c r="F8" s="259"/>
-      <c r="G8" s="334"/>
+      <c r="B8" s="201"/>
+      <c r="C8" s="341"/>
+      <c r="D8" s="207"/>
+      <c r="E8" s="207"/>
+      <c r="F8" s="201"/>
+      <c r="G8" s="338"/>
     </row>
     <row r="9" spans="2:7" hidden="1">
-      <c r="B9" s="259"/>
-      <c r="C9" s="337"/>
-      <c r="D9" s="303"/>
-      <c r="E9" s="303"/>
-      <c r="F9" s="259"/>
-      <c r="G9" s="334"/>
+      <c r="B9" s="201"/>
+      <c r="C9" s="341"/>
+      <c r="D9" s="207"/>
+      <c r="E9" s="207"/>
+      <c r="F9" s="201"/>
+      <c r="G9" s="338"/>
     </row>
     <row r="10" spans="2:7" hidden="1">
-      <c r="B10" s="259"/>
-      <c r="C10" s="337"/>
-      <c r="D10" s="303"/>
-      <c r="E10" s="303"/>
-      <c r="F10" s="259"/>
-      <c r="G10" s="334"/>
+      <c r="B10" s="201"/>
+      <c r="C10" s="341"/>
+      <c r="D10" s="207"/>
+      <c r="E10" s="207"/>
+      <c r="F10" s="201"/>
+      <c r="G10" s="338"/>
     </row>
     <row r="11" spans="2:7" hidden="1">
-      <c r="B11" s="213"/>
-      <c r="C11" s="362"/>
-      <c r="D11" s="215"/>
-      <c r="E11" s="215"/>
-      <c r="F11" s="213"/>
-      <c r="G11" s="199"/>
+      <c r="B11" s="202"/>
+      <c r="C11" s="366"/>
+      <c r="D11" s="208"/>
+      <c r="E11" s="208"/>
+      <c r="F11" s="202"/>
+      <c r="G11" s="215"/>
     </row>
     <row r="12" spans="2:7" hidden="1">
-      <c r="B12" s="212">
+      <c r="B12" s="200">
         <v>86</v>
       </c>
-      <c r="C12" s="216">
+      <c r="C12" s="203">
         <v>46167</v>
       </c>
-      <c r="D12" s="214" t="s">
+      <c r="D12" s="206" t="s">
         <v>501</v>
       </c>
-      <c r="E12" s="214" t="s">
+      <c r="E12" s="206" t="s">
         <v>553</v>
       </c>
-      <c r="F12" s="212" t="s">
-        <v>520</v>
-      </c>
-      <c r="G12" s="198" t="s">
+      <c r="F12" s="200" t="s">
+        <v>521</v>
+      </c>
+      <c r="G12" s="214" t="s">
         <v>554</v>
       </c>
     </row>
     <row r="13" spans="2:7" hidden="1">
-      <c r="B13" s="259"/>
-      <c r="C13" s="305"/>
-      <c r="D13" s="303"/>
-      <c r="E13" s="303"/>
-      <c r="F13" s="259"/>
-      <c r="G13" s="334"/>
+      <c r="B13" s="201"/>
+      <c r="C13" s="204"/>
+      <c r="D13" s="207"/>
+      <c r="E13" s="207"/>
+      <c r="F13" s="201"/>
+      <c r="G13" s="338"/>
     </row>
     <row r="14" spans="2:7" hidden="1">
-      <c r="B14" s="259"/>
-      <c r="C14" s="305"/>
-      <c r="D14" s="303"/>
-      <c r="E14" s="303"/>
-      <c r="F14" s="259"/>
-      <c r="G14" s="334"/>
+      <c r="B14" s="201"/>
+      <c r="C14" s="204"/>
+      <c r="D14" s="207"/>
+      <c r="E14" s="207"/>
+      <c r="F14" s="201"/>
+      <c r="G14" s="338"/>
     </row>
     <row r="15" spans="2:7" hidden="1">
-      <c r="B15" s="259"/>
-      <c r="C15" s="305"/>
-      <c r="D15" s="303"/>
-      <c r="E15" s="303"/>
-      <c r="F15" s="259"/>
-      <c r="G15" s="334"/>
+      <c r="B15" s="201"/>
+      <c r="C15" s="204"/>
+      <c r="D15" s="207"/>
+      <c r="E15" s="207"/>
+      <c r="F15" s="201"/>
+      <c r="G15" s="338"/>
     </row>
     <row r="16" spans="2:7" ht="110.25" hidden="1" customHeight="1">
       <c r="B16" s="56">
@@ -61980,13 +62204,13 @@
       </c>
     </row>
     <row r="17" spans="2:8" ht="76.5" customHeight="1">
-      <c r="B17" s="356" t="s">
-        <v>645</v>
-      </c>
-      <c r="C17" s="357"/>
-      <c r="D17" s="357"/>
-      <c r="E17" s="357"/>
-      <c r="F17" s="358"/>
+      <c r="B17" s="360" t="s">
+        <v>656</v>
+      </c>
+      <c r="C17" s="361"/>
+      <c r="D17" s="361"/>
+      <c r="E17" s="361"/>
+      <c r="F17" s="362"/>
     </row>
     <row r="19" spans="2:8" ht="30.75">
       <c r="B19" s="5" t="s">
@@ -62223,7 +62447,7 @@
         <v>526</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F32" s="13" t="s">
         <v>527</v>
@@ -62240,7 +62464,7 @@
         <v>543</v>
       </c>
       <c r="E33" s="56" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F33" s="137" t="s">
         <v>544</v>
@@ -62257,20 +62481,20 @@
         <v>553</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F34" s="13" t="s">
         <v>554</v>
       </c>
     </row>
     <row r="36" spans="2:8">
-      <c r="B36" s="359" t="s">
-        <v>646</v>
-      </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="361"/>
+      <c r="B36" s="363" t="s">
+        <v>657</v>
+      </c>
+      <c r="C36" s="364"/>
+      <c r="D36" s="364"/>
+      <c r="E36" s="364"/>
+      <c r="F36" s="365"/>
     </row>
     <row r="37" spans="2:8" ht="30.75">
       <c r="B37" s="5" t="s">
@@ -62450,7 +62674,7 @@
         <v>45856</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>647</v>
+        <v>658</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>172</v>
@@ -62467,7 +62691,7 @@
         <v>45895</v>
       </c>
       <c r="C48" s="21" t="s">
-        <v>647</v>
+        <v>658</v>
       </c>
       <c r="D48" s="21" t="s">
         <v>213</v>
@@ -62484,7 +62708,7 @@
         <v>45911</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>648</v>
+        <v>659</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>247</v>
@@ -62535,7 +62759,7 @@
         <v>45952</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>647</v>
+        <v>658</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>276</v>
@@ -62661,6 +62885,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="bfc16dd4-e730-4177-bed2-044dda2bf77d">
@@ -62673,7 +62906,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100799CEE48EDF530489491C09C05FAF2D7" ma:contentTypeVersion="20" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="8588156f1272411709cab45f0014b8ca">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="8acf4dff-38b4-4dda-b9e7-848f633fa258" xmlns:ns3="bfc16dd4-e730-4177-bed2-044dda2bf77d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6b9b282de669aac180207b5a56aa065f" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -62951,23 +63184,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25712F2C-DE3C-493E-8600-BB452D2E9876}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{941F4B03-BBAE-4269-A23B-CFCC16098CF0}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{297525D0-4F49-4A23-9B84-BFA8F7140960}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25712F2C-DE3C-493E-8600-BB452D2E9876}"/>
 </file>
--- a/Consolidado Incidentes y Medidas Correctivas (Formato Interno).xlsx
+++ b/Consolidado Incidentes y Medidas Correctivas (Formato Interno).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Entrega de turno 09.04.2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9F8D4187-88E1-4B9B-8F2C-07618ACD9B07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F54D5589-6F21-4ADD-85CF-8B5124A2B070}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -138,7 +138,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1491" uniqueCount="660">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1492" uniqueCount="661">
   <si>
     <t xml:space="preserve">INCIDENTES CONTRATO </t>
   </si>
@@ -854,9 +854,6 @@
     <t xml:space="preserve">Difundir informe técnico donde se han identificado los posibles escenarios que puedan ocurrir este tipo de eventos </t>
   </si>
   <si>
-    <t>ABIERTO</t>
-  </si>
-  <si>
     <t xml:space="preserve">Reforzamiento sobre la comunicación en caso de eventos, a quienes de debe dar aviso y acción a seguir posterior a un evento que involucre a equipos. </t>
   </si>
   <si>
@@ -921,6 +918,9 @@
 Supte. General de faena SKIC 
 Cristian Ramirez 
 Codelco</t>
+  </si>
+  <si>
+    <t>ABIERTO</t>
   </si>
   <si>
     <t>Se realizara la actualización del Procedimiento de Perforación manual 4600029025-000000-PROCI-00004 e IPER en donde se incluirán las medidas de control para la exposición a caída de rocas y/o material suelto</t>
@@ -1959,6 +1959,9 @@
 Gerente de construcción
 Hernán Cortes – Mauricio González
 Jefe Deysu.</t>
+  </si>
+  <si>
+    <t>Pendiente Turno B</t>
   </si>
   <si>
     <t>SEGREGACIÓN MANIPULADOR TELESCÓPICO</t>
@@ -7557,8 +7560,8 @@
       <c r="I109" s="35">
         <v>45930</v>
       </c>
-      <c r="J109" s="76" t="s">
-        <v>222</v>
+      <c r="J109" s="78" t="s">
+        <v>218</v>
       </c>
       <c r="K109" s="232"/>
       <c r="L109" s="367"/>
@@ -7572,7 +7575,7 @@
       <c r="E110" s="221"/>
       <c r="F110" s="274"/>
       <c r="G110" s="31" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H110" s="34" t="s">
         <v>220</v>
@@ -7580,8 +7583,8 @@
       <c r="I110" s="35">
         <v>45915</v>
       </c>
-      <c r="J110" s="76" t="s">
-        <v>222</v>
+      <c r="J110" s="78" t="s">
+        <v>218</v>
       </c>
       <c r="K110" s="232"/>
       <c r="L110" s="367"/>
@@ -7598,19 +7601,19 @@
         <v>125</v>
       </c>
       <c r="D111" s="275" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E111" s="226" t="s">
         <v>182</v>
       </c>
       <c r="F111" s="254" t="s">
+        <v>224</v>
+      </c>
+      <c r="G111" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="G111" s="31" t="s">
+      <c r="H111" s="32" t="s">
         <v>226</v>
-      </c>
-      <c r="H111" s="32" t="s">
-        <v>227</v>
       </c>
       <c r="I111" s="35">
         <v>45960</v>
@@ -7636,10 +7639,10 @@
       <c r="E112" s="221"/>
       <c r="F112" s="254"/>
       <c r="G112" s="36" t="s">
+        <v>227</v>
+      </c>
+      <c r="H112" s="34" t="s">
         <v>228</v>
-      </c>
-      <c r="H112" s="34" t="s">
-        <v>229</v>
       </c>
       <c r="I112" s="35">
         <v>45960</v>
@@ -7659,10 +7662,10 @@
       <c r="E113" s="221"/>
       <c r="F113" s="254"/>
       <c r="G113" s="36" t="s">
+        <v>229</v>
+      </c>
+      <c r="H113" s="34" t="s">
         <v>230</v>
-      </c>
-      <c r="H113" s="34" t="s">
-        <v>231</v>
       </c>
       <c r="I113" s="35">
         <v>45951</v>
@@ -7682,10 +7685,10 @@
       <c r="E114" s="221"/>
       <c r="F114" s="254"/>
       <c r="G114" s="36" t="s">
+        <v>231</v>
+      </c>
+      <c r="H114" s="34" t="s">
         <v>232</v>
-      </c>
-      <c r="H114" s="34" t="s">
-        <v>233</v>
       </c>
       <c r="I114" s="35">
         <v>45960</v>
@@ -7705,10 +7708,10 @@
       <c r="E115" s="221"/>
       <c r="F115" s="254"/>
       <c r="G115" s="36" t="s">
+        <v>233</v>
+      </c>
+      <c r="H115" s="34" t="s">
         <v>234</v>
-      </c>
-      <c r="H115" s="34" t="s">
-        <v>235</v>
       </c>
       <c r="I115" s="35">
         <v>45960</v>
@@ -7731,19 +7734,19 @@
         <v>32</v>
       </c>
       <c r="D116" s="276" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E116" s="206" t="s">
         <v>78</v>
       </c>
       <c r="F116" s="254" t="s">
+        <v>236</v>
+      </c>
+      <c r="G116" s="36" t="s">
         <v>237</v>
       </c>
-      <c r="G116" s="36" t="s">
+      <c r="H116" s="34" t="s">
         <v>238</v>
-      </c>
-      <c r="H116" s="34" t="s">
-        <v>239</v>
       </c>
       <c r="I116" s="35">
         <v>45909</v>
@@ -7752,7 +7755,7 @@
         <v>20</v>
       </c>
       <c r="K116" s="251" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="L116" s="265"/>
       <c r="M116" s="12"/>
@@ -7765,16 +7768,16 @@
       <c r="E117" s="207"/>
       <c r="F117" s="254"/>
       <c r="G117" s="36" t="s">
+        <v>240</v>
+      </c>
+      <c r="H117" s="34" t="s">
         <v>241</v>
-      </c>
-      <c r="H117" s="34" t="s">
-        <v>242</v>
       </c>
       <c r="I117" s="35">
         <v>45930</v>
       </c>
       <c r="J117" s="76" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K117" s="251"/>
       <c r="L117" s="265"/>
@@ -7791,7 +7794,7 @@
         <v>243</v>
       </c>
       <c r="H118" s="34" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I118" s="35">
         <v>45930</v>
@@ -7820,7 +7823,7 @@
         <v>45930</v>
       </c>
       <c r="J119" s="76" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K119" s="251"/>
       <c r="L119" s="265"/>
@@ -7843,7 +7846,7 @@
         <v>45930</v>
       </c>
       <c r="J120" s="76" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K120" s="251"/>
       <c r="L120" s="265"/>
@@ -7879,7 +7882,7 @@
         <v>20</v>
       </c>
       <c r="K121" s="240" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="L121" s="221"/>
       <c r="M121" s="12"/>
@@ -7983,7 +7986,7 @@
         <v>20</v>
       </c>
       <c r="K125" s="240" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="L125" s="221" t="s">
         <v>22</v>
@@ -8157,7 +8160,7 @@
         <v>20</v>
       </c>
       <c r="K131" s="251" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="L131" s="221" t="s">
         <v>22</v>
@@ -8273,7 +8276,7 @@
         <v>20</v>
       </c>
       <c r="K135" s="251" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="L135" s="221"/>
       <c r="M135" s="12"/>
@@ -8356,7 +8359,7 @@
         <v>20</v>
       </c>
       <c r="K138" s="240" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="L138" s="221" t="s">
         <v>22</v>
@@ -8431,7 +8434,7 @@
         <v>287</v>
       </c>
       <c r="H142" s="32" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I142" s="6">
         <v>45996</v>
@@ -8456,7 +8459,7 @@
         <v>288</v>
       </c>
       <c r="H143" s="32" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I143" s="6">
         <v>45996</v>
@@ -9290,7 +9293,7 @@
         <v>125</v>
       </c>
       <c r="D175" s="7" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E175" s="89" t="s">
         <v>182</v>
@@ -9302,7 +9305,7 @@
         <v>350</v>
       </c>
       <c r="H175" s="32" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I175" s="4">
         <v>46061</v>
@@ -9349,7 +9352,7 @@
         <v>46380</v>
       </c>
       <c r="J176" s="50" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K176" s="239" t="s">
         <v>22</v>
@@ -9432,7 +9435,7 @@
         <v>46079</v>
       </c>
       <c r="J179" s="50" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K179" s="239" t="s">
         <v>22</v>
@@ -9600,7 +9603,7 @@
         <v>46081</v>
       </c>
       <c r="J185" s="69" t="s">
-        <v>222</v>
+        <v>20</v>
       </c>
       <c r="K185" s="98" t="s">
         <v>22</v>
@@ -9623,7 +9626,7 @@
         <v>46140</v>
       </c>
       <c r="J186" s="69" t="s">
-        <v>222</v>
+        <v>20</v>
       </c>
       <c r="K186" s="98" t="s">
         <v>22</v>
@@ -9739,7 +9742,7 @@
         <v>46069</v>
       </c>
       <c r="J190" s="82" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K190" s="232" t="s">
         <v>22</v>
@@ -9824,7 +9827,7 @@
         <v>46082</v>
       </c>
       <c r="J193" s="69" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K193" s="232"/>
       <c r="L193" s="221"/>
@@ -9882,7 +9885,7 @@
         <v>46111</v>
       </c>
       <c r="J195" s="69" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K195" s="85" t="s">
         <v>22</v>
@@ -9942,7 +9945,7 @@
         <v>46111</v>
       </c>
       <c r="J197" s="69" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K197" s="85"/>
       <c r="L197" s="12"/>
@@ -9963,7 +9966,7 @@
         <v>46111</v>
       </c>
       <c r="J198" s="69" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K198" s="85"/>
       <c r="L198" s="12"/>
@@ -10017,7 +10020,7 @@
         <v>46080</v>
       </c>
       <c r="J200" s="83" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K200" s="95"/>
       <c r="L200" s="12"/>
@@ -10085,7 +10088,7 @@
         <v>46147</v>
       </c>
       <c r="J202" s="69" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K202" s="107"/>
       <c r="L202" s="5"/>
@@ -17441,7 +17444,7 @@
         <v>420</v>
       </c>
       <c r="J205" s="69" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K205" s="107"/>
       <c r="L205" s="5"/>
@@ -22349,7 +22352,7 @@
         <v>420</v>
       </c>
       <c r="J207" s="69" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K207" s="107"/>
       <c r="L207" s="5"/>
@@ -24809,7 +24812,7 @@
         <v>46142</v>
       </c>
       <c r="J208" s="69" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K208" s="107"/>
       <c r="L208" s="5"/>
@@ -32153,7 +32156,7 @@
         <v>46143</v>
       </c>
       <c r="J211" s="69" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K211" s="108"/>
       <c r="L211" s="2"/>
@@ -34613,7 +34616,7 @@
         <v>46142</v>
       </c>
       <c r="J212" s="69" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K212" s="108" t="s">
         <v>440</v>
@@ -44421,7 +44424,7 @@
         <v>447</v>
       </c>
       <c r="J216" s="87" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K216" s="108"/>
       <c r="L216" s="2"/>
@@ -54237,7 +54240,7 @@
         <v>46137</v>
       </c>
       <c r="J220" s="87" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K220" s="108"/>
       <c r="L220" s="2"/>
@@ -56685,7 +56688,7 @@
         <v>46137</v>
       </c>
       <c r="J221" s="92" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K221" s="90"/>
       <c r="L221" s="2"/>
@@ -59207,7 +59210,7 @@
         <v>469</v>
       </c>
       <c r="J224" s="83" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K224" s="95"/>
       <c r="L224" s="12"/>
@@ -59323,7 +59326,7 @@
         <v>46142</v>
       </c>
       <c r="J228" s="69" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K228" s="110"/>
       <c r="L228" s="12"/>
@@ -59427,7 +59430,7 @@
         <v>46141</v>
       </c>
       <c r="J232" s="5" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K232" s="110" t="s">
         <v>22</v>
@@ -59510,7 +59513,7 @@
         <v>498</v>
       </c>
       <c r="J235" s="5" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K235" s="128"/>
       <c r="L235" s="60"/>
@@ -59533,7 +59536,7 @@
         <v>498</v>
       </c>
       <c r="J236" s="5" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K236" s="85"/>
       <c r="L236" s="56"/>
@@ -59595,7 +59598,7 @@
         <v>46172</v>
       </c>
       <c r="J238" s="98" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K238" s="5"/>
       <c r="L238" s="98"/>
@@ -59757,7 +59760,7 @@
       <c r="H244" s="60"/>
       <c r="I244" s="142"/>
       <c r="J244" s="129" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K244" s="60"/>
       <c r="L244" s="60"/>
@@ -59776,7 +59779,7 @@
       <c r="H245" s="5"/>
       <c r="I245" s="4"/>
       <c r="J245" s="129" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K245" s="5"/>
       <c r="L245" s="5"/>
@@ -59807,7 +59810,7 @@
       <c r="H246" s="5"/>
       <c r="I246" s="4"/>
       <c r="J246" s="129" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K246" s="5"/>
       <c r="L246" s="5"/>
@@ -59923,9 +59926,11 @@
         <v>46164</v>
       </c>
       <c r="J250" s="129" t="s">
-        <v>222</v>
-      </c>
-      <c r="K250" s="5"/>
+        <v>242</v>
+      </c>
+      <c r="K250" s="5" t="s">
+        <v>543</v>
+      </c>
       <c r="L250" s="5"/>
       <c r="M250" s="5"/>
     </row>
@@ -59940,25 +59945,25 @@
         <v>501</v>
       </c>
       <c r="D251" s="206" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="E251" s="200" t="s">
         <v>521</v>
       </c>
       <c r="F251" s="214" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="G251" s="14" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H251" s="144" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="I251" s="4">
         <v>46188</v>
       </c>
       <c r="J251" s="129" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K251" s="5"/>
       <c r="L251" s="5"/>
@@ -59972,16 +59977,16 @@
       <c r="E252" s="201"/>
       <c r="F252" s="338"/>
       <c r="G252" s="100" t="s">
+        <v>548</v>
+      </c>
+      <c r="H252" s="144" t="s">
         <v>547</v>
-      </c>
-      <c r="H252" s="144" t="s">
-        <v>546</v>
       </c>
       <c r="I252" s="4">
         <v>46188</v>
       </c>
       <c r="J252" s="129" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K252" s="5"/>
       <c r="L252" s="5"/>
@@ -59995,10 +60000,10 @@
       <c r="E253" s="201"/>
       <c r="F253" s="338"/>
       <c r="G253" s="100" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H253" s="144" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="I253" s="4">
         <v>46188</v>
@@ -60018,16 +60023,16 @@
       <c r="E254" s="201"/>
       <c r="F254" s="338"/>
       <c r="G254" s="100" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H254" s="144" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="I254" s="4">
         <v>46188</v>
       </c>
       <c r="J254" s="129" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K254" s="5"/>
       <c r="L254" s="5"/>
@@ -60041,16 +60046,16 @@
       <c r="E255" s="201"/>
       <c r="F255" s="338"/>
       <c r="G255" s="100" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H255" s="144" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="I255" s="4">
         <v>46188</v>
       </c>
       <c r="J255" s="129" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K255" s="5"/>
       <c r="L255" s="5"/>
@@ -60067,25 +60072,25 @@
         <v>265</v>
       </c>
       <c r="D256" s="220" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E256" s="221" t="s">
         <v>521</v>
       </c>
       <c r="F256" s="339" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="G256" s="163" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H256" s="144" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="I256" s="143">
         <v>46203</v>
       </c>
       <c r="J256" s="129" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K256" s="138"/>
       <c r="L256" s="5"/>
@@ -60099,16 +60104,16 @@
       <c r="E257" s="221"/>
       <c r="F257" s="227"/>
       <c r="G257" s="163" t="s">
+        <v>558</v>
+      </c>
+      <c r="H257" s="144" t="s">
         <v>557</v>
-      </c>
-      <c r="H257" s="144" t="s">
-        <v>556</v>
       </c>
       <c r="I257" s="143">
         <v>46203</v>
       </c>
       <c r="J257" s="129" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K257" s="138"/>
       <c r="L257" s="5"/>
@@ -60122,7 +60127,7 @@
       <c r="E258" s="221"/>
       <c r="F258" s="227"/>
       <c r="G258" s="163" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H258" s="144" t="s">
         <v>540</v>
@@ -60131,7 +60136,7 @@
         <v>46203</v>
       </c>
       <c r="J258" s="129" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K258" s="138"/>
       <c r="L258" s="5"/>
@@ -60145,7 +60150,7 @@
       <c r="E259" s="200"/>
       <c r="F259" s="228"/>
       <c r="G259" s="164" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H259" s="58" t="s">
         <v>540</v>
@@ -60171,19 +60176,19 @@
         <v>32</v>
       </c>
       <c r="D260" s="220" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E260" s="221" t="s">
         <v>27</v>
       </c>
       <c r="F260" s="337" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="G260" s="13" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H260" s="2" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="I260" s="4"/>
       <c r="J260" s="5"/>
@@ -60199,14 +60204,14 @@
       <c r="E261" s="221"/>
       <c r="F261" s="220"/>
       <c r="G261" s="13" t="s">
+        <v>565</v>
+      </c>
+      <c r="H261" s="2" t="s">
         <v>564</v>
-      </c>
-      <c r="H261" s="2" t="s">
-        <v>563</v>
       </c>
       <c r="I261" s="5"/>
       <c r="J261" s="5" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K261" s="5"/>
       <c r="L261" s="5"/>
@@ -60223,25 +60228,25 @@
         <v>32</v>
       </c>
       <c r="D262" s="2" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E262" s="2" t="s">
         <v>521</v>
       </c>
       <c r="F262" s="13" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="G262" s="2" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H262" s="2" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="I262" s="4">
         <v>46193</v>
       </c>
       <c r="J262" s="5" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K262" s="5"/>
       <c r="L262" s="5"/>
@@ -60258,16 +60263,16 @@
         <v>501</v>
       </c>
       <c r="D263" s="58" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E263" s="56" t="s">
         <v>27</v>
       </c>
       <c r="F263" s="137" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="G263" s="56" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H263" s="56"/>
       <c r="I263" s="56"/>
@@ -60277,7 +60282,7 @@
       <c r="K263" s="5"/>
       <c r="L263" s="5"/>
       <c r="M263" s="58" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="264" spans="1:13" ht="81" customHeight="1">
@@ -60291,22 +60296,22 @@
         <v>125</v>
       </c>
       <c r="D264" s="206" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E264" s="200" t="s">
         <v>521</v>
       </c>
       <c r="F264" s="214" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="G264" s="56" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H264" s="56" t="s">
         <v>358</v>
       </c>
       <c r="I264" s="56" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="J264" s="93" t="s">
         <v>20</v>
@@ -60323,16 +60328,16 @@
       <c r="E265" s="201"/>
       <c r="F265" s="338"/>
       <c r="G265" s="56" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H265" s="56" t="s">
         <v>358</v>
       </c>
       <c r="I265" s="56" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="J265" s="93" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K265" s="56"/>
       <c r="L265" s="85"/>
@@ -60346,13 +60351,13 @@
       <c r="E266" s="202"/>
       <c r="F266" s="215"/>
       <c r="G266" s="56" t="s">
+        <v>579</v>
+      </c>
+      <c r="H266" s="56" t="s">
+        <v>580</v>
+      </c>
+      <c r="I266" s="56" t="s">
         <v>578</v>
-      </c>
-      <c r="H266" s="56" t="s">
-        <v>579</v>
-      </c>
-      <c r="I266" s="56" t="s">
-        <v>577</v>
       </c>
       <c r="J266" s="93" t="s">
         <v>20</v>
@@ -60369,33 +60374,33 @@
         <v>46201</v>
       </c>
       <c r="C267" s="220" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D267" s="220" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E267" s="226" t="s">
         <v>199</v>
       </c>
       <c r="F267" s="346" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="G267" s="150" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H267" s="2" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="I267" s="4">
         <v>46223</v>
       </c>
       <c r="J267" s="129" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K267" s="111"/>
       <c r="L267" s="12"/>
       <c r="M267" s="345" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="268" spans="1:13" ht="44.25" customHeight="1">
@@ -60406,16 +60411,16 @@
       <c r="E268" s="226"/>
       <c r="F268" s="346"/>
       <c r="G268" s="14" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H268" s="2" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="I268" s="4">
         <v>46223</v>
       </c>
       <c r="J268" s="138" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K268" s="169"/>
       <c r="L268" s="170"/>
@@ -60429,10 +60434,10 @@
       <c r="E269" s="347"/>
       <c r="F269" s="216"/>
       <c r="G269" s="139" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H269" s="58" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="I269" s="57">
         <v>46223</v>
@@ -60455,25 +60460,25 @@
         <v>501</v>
       </c>
       <c r="D270" s="356" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E270" s="355" t="s">
         <v>27</v>
       </c>
       <c r="F270" s="353" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="G270" s="166" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H270" s="58" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="I270" s="57">
         <v>46233</v>
       </c>
       <c r="J270" s="56" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K270" s="56"/>
       <c r="L270" s="56"/>
@@ -60487,16 +60492,16 @@
       <c r="E271" s="212"/>
       <c r="F271" s="354"/>
       <c r="G271" s="14" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H271" s="176" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="I271" s="57">
         <v>46233</v>
       </c>
       <c r="J271" s="56" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K271" s="167"/>
       <c r="L271" s="60"/>
@@ -60513,13 +60518,13 @@
         <v>265</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E272" s="5" t="s">
         <v>199</v>
       </c>
       <c r="F272" s="13" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="G272" s="190" t="s">
         <v>30</v>
@@ -60554,19 +60559,19 @@
         <v>265</v>
       </c>
       <c r="D273" s="208" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="E273" s="348" t="s">
         <v>320</v>
       </c>
       <c r="F273" s="218" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="G273" s="13" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H273" s="189" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="I273" s="4">
         <v>46280</v>
@@ -60577,7 +60582,7 @@
       <c r="K273" s="12"/>
       <c r="L273" s="12"/>
       <c r="M273" s="337" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="274" spans="1:13" ht="68.25" customHeight="1">
@@ -60588,16 +60593,16 @@
       <c r="E274" s="266"/>
       <c r="F274" s="346"/>
       <c r="G274" s="187" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H274" s="175" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="I274" s="4">
         <v>46295</v>
       </c>
       <c r="J274" s="5" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K274" s="12"/>
       <c r="L274" s="12"/>
@@ -60611,10 +60616,10 @@
       <c r="E275" s="266"/>
       <c r="F275" s="337"/>
       <c r="G275" s="191" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H275" s="175" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="I275" s="4">
         <v>46265</v>
@@ -60634,10 +60639,10 @@
       <c r="E276" s="266"/>
       <c r="F276" s="346"/>
       <c r="G276" s="13" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H276" s="175" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="I276" s="4">
         <v>46295</v>
@@ -60657,10 +60662,10 @@
       <c r="E277" s="266"/>
       <c r="F277" s="346"/>
       <c r="G277" s="13" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H277" s="176" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="I277" s="4">
         <v>46295</v>
@@ -60680,10 +60685,10 @@
       <c r="E278" s="266"/>
       <c r="F278" s="346"/>
       <c r="G278" s="116" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H278" s="127" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="I278" s="4">
         <v>46295</v>
@@ -60703,16 +60708,16 @@
       <c r="E279" s="266"/>
       <c r="F279" s="346"/>
       <c r="G279" s="187" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H279" s="175" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="I279" s="4">
         <v>46295</v>
       </c>
       <c r="J279" s="5" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K279" s="12"/>
       <c r="L279" s="12"/>
@@ -60726,16 +60731,16 @@
       <c r="E280" s="349"/>
       <c r="F280" s="216"/>
       <c r="G280" s="181" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H280" s="175" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="I280" s="4">
         <v>46295</v>
       </c>
       <c r="J280" s="192" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="K280" s="12"/>
       <c r="L280" s="12"/>
@@ -60752,19 +60757,19 @@
         <v>265</v>
       </c>
       <c r="D281" s="206" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="E281" s="342" t="s">
         <v>27</v>
       </c>
       <c r="F281" s="216" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="G281" s="188" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H281" s="168" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="I281" s="179">
         <v>46315</v>
@@ -60783,16 +60788,16 @@
       <c r="E282" s="343"/>
       <c r="F282" s="217"/>
       <c r="G282" s="188" t="s">
+        <v>620</v>
+      </c>
+      <c r="H282" s="168" t="s">
         <v>619</v>
-      </c>
-      <c r="H282" s="168" t="s">
-        <v>618</v>
       </c>
       <c r="I282" s="171">
         <v>46315</v>
       </c>
       <c r="J282" s="5" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K282" s="174"/>
       <c r="L282" s="95"/>
@@ -60806,7 +60811,7 @@
       <c r="E283" s="344"/>
       <c r="F283" s="218"/>
       <c r="G283" s="188" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H283" s="168" t="s">
         <v>88</v>
@@ -60815,7 +60820,7 @@
         <v>46315</v>
       </c>
       <c r="J283" s="56" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K283" s="174"/>
       <c r="L283" s="95"/>
@@ -60832,19 +60837,19 @@
         <v>265</v>
       </c>
       <c r="D284" s="206" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="E284" s="200" t="s">
         <v>182</v>
       </c>
       <c r="F284" s="216" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="G284" s="13" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H284" s="134" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="I284" s="147">
         <v>46295</v>
@@ -60855,7 +60860,7 @@
       <c r="K284" s="193"/>
       <c r="L284" s="60"/>
       <c r="M284" s="214" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="285" spans="1:13" ht="96.75" customHeight="1">
@@ -60866,16 +60871,16 @@
       <c r="E285" s="202"/>
       <c r="F285" s="218"/>
       <c r="G285" s="14" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H285" s="134" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="I285" s="171">
         <v>46295</v>
       </c>
       <c r="J285" s="5" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K285" s="174"/>
       <c r="L285" s="60"/>
@@ -60892,19 +60897,19 @@
         <v>125</v>
       </c>
       <c r="D286" s="220" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="E286" s="212" t="s">
         <v>521</v>
       </c>
       <c r="F286" s="216" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="G286" s="13" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H286" s="93" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="I286" s="171">
         <v>46285</v>
@@ -60924,10 +60929,10 @@
       <c r="E287" s="219"/>
       <c r="F287" s="217"/>
       <c r="G287" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H287" s="93" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="I287" s="171">
         <v>46285</v>
@@ -60947,10 +60952,10 @@
       <c r="E288" s="213"/>
       <c r="F288" s="218"/>
       <c r="G288" s="13" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H288" s="93" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="I288" s="171">
         <v>46285</v>
@@ -60973,13 +60978,13 @@
         <v>125</v>
       </c>
       <c r="D289" s="200" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="E289" s="200" t="s">
         <v>27</v>
       </c>
       <c r="F289" s="206" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="G289" s="12"/>
       <c r="H289" s="167"/>
@@ -60997,10 +61002,10 @@
       <c r="E290" s="201"/>
       <c r="F290" s="207"/>
       <c r="G290" s="194" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H290" s="195" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="I290" s="95"/>
       <c r="J290" s="12"/>
@@ -61034,28 +61039,28 @@
         <v>125</v>
       </c>
       <c r="D292" s="200" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="E292" s="200" t="s">
         <v>182</v>
       </c>
       <c r="F292" s="206" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="G292" s="194" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H292" s="196" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="I292" s="197">
         <v>46310</v>
       </c>
       <c r="J292" s="177" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K292" s="60" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="L292" s="60"/>
       <c r="M292" s="60"/>
@@ -61068,7 +61073,7 @@
       <c r="E293" s="202"/>
       <c r="F293" s="208"/>
       <c r="G293" s="194" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H293" s="93" t="s">
         <v>257</v>
@@ -61077,10 +61082,10 @@
         <v>46310</v>
       </c>
       <c r="J293" s="60" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K293" s="60" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="L293" s="60"/>
       <c r="M293" s="60"/>
@@ -61096,25 +61101,25 @@
         <v>265</v>
       </c>
       <c r="D294" s="206" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="E294" s="206" t="s">
         <v>27</v>
       </c>
       <c r="F294" s="206" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="G294" s="139" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H294" s="194" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I294" s="197">
         <v>46325</v>
       </c>
       <c r="J294" s="60" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K294" s="60"/>
       <c r="L294" s="60"/>
@@ -61128,16 +61133,16 @@
       <c r="E295" s="207"/>
       <c r="F295" s="207"/>
       <c r="G295" s="139" t="s">
+        <v>651</v>
+      </c>
+      <c r="H295" s="194" t="s">
         <v>650</v>
-      </c>
-      <c r="H295" s="194" t="s">
-        <v>649</v>
       </c>
       <c r="I295" s="197">
         <v>46325</v>
       </c>
       <c r="J295" s="60" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K295" s="60"/>
       <c r="L295" s="60"/>
@@ -61154,25 +61159,25 @@
         <v>125</v>
       </c>
       <c r="D296" s="206" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E296" s="206" t="s">
         <v>521</v>
       </c>
       <c r="F296" s="206" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="G296" s="198" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H296" s="194" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I296" s="197">
         <v>46325</v>
       </c>
       <c r="J296" s="60" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="K296" s="12"/>
       <c r="L296" s="12"/>
@@ -61186,16 +61191,16 @@
       <c r="E297" s="207"/>
       <c r="F297" s="207"/>
       <c r="G297" s="114" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H297" s="194" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I297" s="197">
         <v>46325</v>
       </c>
       <c r="J297" s="60" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
     </row>
     <row r="298" spans="1:13" ht="39.75" customHeight="1">
@@ -61206,16 +61211,16 @@
       <c r="E298" s="208"/>
       <c r="F298" s="209"/>
       <c r="G298" s="14" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H298" s="100" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I298" s="199">
         <v>46325</v>
       </c>
       <c r="J298" s="12" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -61893,7 +61898,7 @@
     <mergeCell ref="E294:E295"/>
     <mergeCell ref="F294:F295"/>
   </mergeCells>
-  <conditionalFormatting sqref="J2:J66 J155:J170 I142:I145 J222 J227 J69:J138 J142:J150 J175:J214 J232:J271 J273:J1048576">
+  <conditionalFormatting sqref="J2:J66 J155:J170 I142:I145 J222 J227 J142:J150 J175:J214 J232:J271 J273:J1048576 J69:J138">
     <cfRule type="cellIs" dxfId="32" priority="36" operator="equal">
       <formula>"ABIERTO"</formula>
     </cfRule>
@@ -61901,7 +61906,7 @@
       <formula>NOT(ISERROR(SEARCH("ABIERTO",I2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J66 J222 J227 J69:J138 J142:J170 J175:J214 J232:J271 J273:J1048576">
+  <conditionalFormatting sqref="J2:J66 J222 J227 J142:J170 J175:J214 J232:J271 J273:J1048576 J69:J138">
     <cfRule type="containsText" dxfId="30" priority="35" operator="containsText" text="ABIERTO">
       <formula>NOT(ISERROR(SEARCH("ABIERTO",J2)))</formula>
     </cfRule>
@@ -62098,13 +62103,13 @@
         <v>501</v>
       </c>
       <c r="E7" s="206" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="F7" s="200" t="s">
         <v>521</v>
       </c>
       <c r="G7" s="214" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="8" spans="2:7" hidden="1">
@@ -62150,13 +62155,13 @@
         <v>501</v>
       </c>
       <c r="E12" s="206" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="F12" s="200" t="s">
         <v>521</v>
       </c>
       <c r="G12" s="214" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="13" spans="2:7" hidden="1">
@@ -62194,18 +62199,18 @@
         <v>32</v>
       </c>
       <c r="E16" s="58" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F16" s="56" t="s">
         <v>27</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="76.5" customHeight="1">
       <c r="B17" s="360" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C17" s="361"/>
       <c r="D17" s="361"/>
@@ -62461,13 +62466,13 @@
         <v>501</v>
       </c>
       <c r="D33" s="58" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="E33" s="56" t="s">
         <v>521</v>
       </c>
       <c r="F33" s="137" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="34" spans="2:8" ht="76.5">
@@ -62478,18 +62483,18 @@
         <v>501</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E34" s="5" t="s">
         <v>521</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="36" spans="2:8">
       <c r="B36" s="363" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C36" s="364"/>
       <c r="D36" s="364"/>
@@ -62674,7 +62679,7 @@
         <v>45856</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>172</v>
@@ -62691,7 +62696,7 @@
         <v>45895</v>
       </c>
       <c r="C48" s="21" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="D48" s="21" t="s">
         <v>213</v>
@@ -62708,7 +62713,7 @@
         <v>45911</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>247</v>
@@ -62759,7 +62764,7 @@
         <v>45952</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>276</v>
@@ -62847,13 +62852,13 @@
         <v>32</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E57" s="5" t="s">
         <v>27</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
   </sheetData>

--- a/Consolidado Incidentes y Medidas Correctivas (Formato Interno).xlsx
+++ b/Consolidado Incidentes y Medidas Correctivas (Formato Interno).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30621"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Entrega de turno 09.04.2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F54D5589-6F21-4ADD-85CF-8B5124A2B070}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{95C39D66-F1BF-4305-9B7A-F887CABA2A26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -118,27 +118,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="G280" authorId="0" shapeId="0" xr:uid="{85886566-760A-4FEC-9249-CB118B61FFCA}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Tamara Riquelme Salinas:
-PENDIENTE BUSCAR Y ESCANEAR LOS REGISTROS DEL TALLER REALIZADO AL TURNO B NOCHE</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1492" uniqueCount="661">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1492" uniqueCount="660">
   <si>
     <t xml:space="preserve">INCIDENTES CONTRATO </t>
   </si>
@@ -2232,10 +2217,6 @@
   <si>
     <t xml:space="preserve">Gerente de Proyecto / Jose Luis Maira
 </t>
-  </si>
-  <si>
-    <t>PENDIENTE TA 
-TB NOCHE</t>
   </si>
   <si>
     <t>DAÑO MATERIAL CAMIÓN DE IZAJE</t>
@@ -3029,7 +3010,7 @@
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="370">
+  <cellXfs count="368">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3550,9 +3531,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="33" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3582,9 +3560,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4533,7 +4508,7 @@
 <file path=xl/namedSheetViews/namedSheetView1.xml><?xml version="1.0" encoding="utf-8"?>
 <namedSheetViews xmlns="http://schemas.microsoft.com/office/spreadsheetml/2019/namedsheetviews" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <namedSheetView name="Vista 1" id="{CE0CDC46-C5E0-48C3-BF10-36800D88BDCE}">
-    <nsvFilter filterId="{00000000-0001-0000-0000-000000000000}" ref="A2:COT296" tableId="0"/>
+    <nsvFilter filterId="{00000000-0001-0000-0000-000000000000}" ref="A2:COT298" tableId="0"/>
   </namedSheetView>
 </namedSheetViews>
 </file>
@@ -4818,19 +4793,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="29.25" customHeight="1">
-      <c r="A1" s="289" t="s">
+      <c r="A1" s="287" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="290"/>
-      <c r="C1" s="290"/>
-      <c r="D1" s="290"/>
-      <c r="E1" s="290"/>
-      <c r="F1" s="290"/>
-      <c r="G1" s="290"/>
-      <c r="H1" s="290"/>
-      <c r="I1" s="290"/>
-      <c r="J1" s="290"/>
-      <c r="K1" s="291"/>
+      <c r="B1" s="288"/>
+      <c r="C1" s="288"/>
+      <c r="D1" s="288"/>
+      <c r="E1" s="288"/>
+      <c r="F1" s="288"/>
+      <c r="G1" s="288"/>
+      <c r="H1" s="288"/>
+      <c r="I1" s="288"/>
+      <c r="J1" s="288"/>
+      <c r="K1" s="289"/>
     </row>
     <row r="2" spans="1:13" ht="25.5" customHeight="1">
       <c r="A2" s="51" t="s">
@@ -4874,22 +4849,22 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="30" customHeight="1">
-      <c r="A3" s="294">
+      <c r="A3" s="292">
         <v>1</v>
       </c>
-      <c r="B3" s="222">
+      <c r="B3" s="220">
         <v>45709</v>
       </c>
-      <c r="C3" s="222" t="s">
+      <c r="C3" s="220" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="234" t="s">
+      <c r="D3" s="232" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="234" t="s">
+      <c r="E3" s="232" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="235" t="s">
+      <c r="F3" s="233" t="s">
         <v>17</v>
       </c>
       <c r="G3" s="13" t="s">
@@ -4904,20 +4879,20 @@
       <c r="J3" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="K3" s="221" t="s">
+      <c r="K3" s="219" t="s">
         <v>21</v>
       </c>
-      <c r="L3" s="202" t="s">
+      <c r="L3" s="200" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="39.950000000000003" customHeight="1">
-      <c r="A4" s="294"/>
-      <c r="B4" s="221"/>
-      <c r="C4" s="222"/>
-      <c r="D4" s="234"/>
-      <c r="E4" s="234"/>
-      <c r="F4" s="235"/>
+      <c r="A4" s="292"/>
+      <c r="B4" s="219"/>
+      <c r="C4" s="220"/>
+      <c r="D4" s="232"/>
+      <c r="E4" s="232"/>
+      <c r="F4" s="233"/>
       <c r="G4" s="13" t="s">
         <v>23</v>
       </c>
@@ -4930,16 +4905,16 @@
       <c r="J4" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="K4" s="221"/>
-      <c r="L4" s="221"/>
+      <c r="K4" s="219"/>
+      <c r="L4" s="219"/>
     </row>
     <row r="5" spans="1:13" ht="39.950000000000003" customHeight="1">
-      <c r="A5" s="294"/>
-      <c r="B5" s="221"/>
-      <c r="C5" s="222"/>
-      <c r="D5" s="234"/>
-      <c r="E5" s="234"/>
-      <c r="F5" s="235"/>
+      <c r="A5" s="292"/>
+      <c r="B5" s="219"/>
+      <c r="C5" s="220"/>
+      <c r="D5" s="232"/>
+      <c r="E5" s="232"/>
+      <c r="F5" s="233"/>
       <c r="G5" s="13" t="s">
         <v>24</v>
       </c>
@@ -4952,16 +4927,16 @@
       <c r="J5" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="K5" s="221"/>
-      <c r="L5" s="221"/>
+      <c r="K5" s="219"/>
+      <c r="L5" s="219"/>
     </row>
     <row r="6" spans="1:13" ht="38.25" customHeight="1">
-      <c r="A6" s="294"/>
-      <c r="B6" s="221"/>
-      <c r="C6" s="222"/>
-      <c r="D6" s="234"/>
-      <c r="E6" s="234"/>
-      <c r="F6" s="235"/>
+      <c r="A6" s="292"/>
+      <c r="B6" s="219"/>
+      <c r="C6" s="220"/>
+      <c r="D6" s="232"/>
+      <c r="E6" s="232"/>
+      <c r="F6" s="233"/>
       <c r="G6" s="14" t="s">
         <v>25</v>
       </c>
@@ -4974,72 +4949,72 @@
       <c r="J6" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="K6" s="221"/>
-      <c r="L6" s="221"/>
+      <c r="K6" s="219"/>
+      <c r="L6" s="219"/>
     </row>
     <row r="7" spans="1:13" ht="69.75" customHeight="1">
-      <c r="A7" s="294">
+      <c r="A7" s="292">
         <v>2</v>
       </c>
-      <c r="B7" s="286">
+      <c r="B7" s="284">
         <v>45731</v>
       </c>
-      <c r="C7" s="221" t="s">
+      <c r="C7" s="219" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="220" t="s">
+      <c r="D7" s="218" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="220" t="s">
+      <c r="E7" s="218" t="s">
         <v>27</v>
       </c>
-      <c r="F7" s="235" t="s">
+      <c r="F7" s="233" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="287" t="s">
+      <c r="G7" s="285" t="s">
         <v>29</v>
       </c>
-      <c r="H7" s="285" t="s">
+      <c r="H7" s="283" t="s">
         <v>30</v>
       </c>
-      <c r="I7" s="269" t="s">
+      <c r="I7" s="267" t="s">
         <v>31</v>
       </c>
-      <c r="J7" s="298"/>
-      <c r="K7" s="292"/>
-      <c r="L7" s="221"/>
+      <c r="J7" s="296"/>
+      <c r="K7" s="290"/>
+      <c r="L7" s="219"/>
     </row>
     <row r="8" spans="1:13" ht="39.950000000000003" customHeight="1">
-      <c r="A8" s="294"/>
-      <c r="B8" s="296"/>
-      <c r="C8" s="221"/>
-      <c r="D8" s="220"/>
-      <c r="E8" s="220"/>
-      <c r="F8" s="235"/>
-      <c r="G8" s="287"/>
-      <c r="H8" s="285"/>
-      <c r="I8" s="286"/>
-      <c r="J8" s="298"/>
-      <c r="K8" s="292"/>
-      <c r="L8" s="221"/>
+      <c r="A8" s="292"/>
+      <c r="B8" s="294"/>
+      <c r="C8" s="219"/>
+      <c r="D8" s="218"/>
+      <c r="E8" s="218"/>
+      <c r="F8" s="233"/>
+      <c r="G8" s="285"/>
+      <c r="H8" s="283"/>
+      <c r="I8" s="284"/>
+      <c r="J8" s="296"/>
+      <c r="K8" s="290"/>
+      <c r="L8" s="219"/>
     </row>
     <row r="9" spans="1:13" ht="115.5" customHeight="1">
-      <c r="A9" s="294">
+      <c r="A9" s="292">
         <v>3</v>
       </c>
-      <c r="B9" s="222">
+      <c r="B9" s="220">
         <v>45739</v>
       </c>
-      <c r="C9" s="222" t="s">
+      <c r="C9" s="220" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="234" t="s">
+      <c r="D9" s="232" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="234" t="s">
+      <c r="E9" s="232" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="235" t="s">
+      <c r="F9" s="233" t="s">
         <v>34</v>
       </c>
       <c r="G9" s="13" t="s">
@@ -5054,20 +5029,20 @@
       <c r="J9" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="K9" s="221" t="s">
+      <c r="K9" s="219" t="s">
         <v>21</v>
       </c>
-      <c r="L9" s="221" t="s">
+      <c r="L9" s="219" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="63.6" customHeight="1">
-      <c r="A10" s="294"/>
-      <c r="B10" s="221"/>
-      <c r="C10" s="222"/>
-      <c r="D10" s="234"/>
-      <c r="E10" s="234"/>
-      <c r="F10" s="235"/>
+      <c r="A10" s="292"/>
+      <c r="B10" s="219"/>
+      <c r="C10" s="220"/>
+      <c r="D10" s="232"/>
+      <c r="E10" s="232"/>
+      <c r="F10" s="233"/>
       <c r="G10" s="13" t="s">
         <v>36</v>
       </c>
@@ -5080,26 +5055,26 @@
       <c r="J10" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="K10" s="221"/>
-      <c r="L10" s="221"/>
+      <c r="K10" s="219"/>
+      <c r="L10" s="219"/>
     </row>
     <row r="11" spans="1:13" ht="81" customHeight="1">
-      <c r="A11" s="294">
+      <c r="A11" s="292">
         <v>4</v>
       </c>
-      <c r="B11" s="222">
+      <c r="B11" s="220">
         <v>45744</v>
       </c>
-      <c r="C11" s="222" t="s">
+      <c r="C11" s="220" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="234" t="s">
+      <c r="D11" s="232" t="s">
         <v>38</v>
       </c>
-      <c r="E11" s="234" t="s">
+      <c r="E11" s="232" t="s">
         <v>27</v>
       </c>
-      <c r="F11" s="235" t="s">
+      <c r="F11" s="233" t="s">
         <v>39</v>
       </c>
       <c r="G11" s="14" t="s">
@@ -5114,20 +5089,20 @@
       <c r="J11" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="K11" s="221" t="s">
+      <c r="K11" s="219" t="s">
         <v>42</v>
       </c>
-      <c r="L11" s="200" t="s">
+      <c r="L11" s="198" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="54.6" customHeight="1">
-      <c r="A12" s="294"/>
-      <c r="B12" s="221"/>
-      <c r="C12" s="222"/>
-      <c r="D12" s="234"/>
-      <c r="E12" s="234"/>
-      <c r="F12" s="235"/>
+      <c r="A12" s="292"/>
+      <c r="B12" s="219"/>
+      <c r="C12" s="220"/>
+      <c r="D12" s="232"/>
+      <c r="E12" s="232"/>
+      <c r="F12" s="233"/>
       <c r="G12" s="14" t="s">
         <v>43</v>
       </c>
@@ -5140,16 +5115,16 @@
       <c r="J12" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="K12" s="221"/>
-      <c r="L12" s="201"/>
+      <c r="K12" s="219"/>
+      <c r="L12" s="199"/>
     </row>
     <row r="13" spans="1:13" ht="54.6" customHeight="1">
-      <c r="A13" s="294"/>
-      <c r="B13" s="221"/>
-      <c r="C13" s="222"/>
-      <c r="D13" s="234"/>
-      <c r="E13" s="234"/>
-      <c r="F13" s="235"/>
+      <c r="A13" s="292"/>
+      <c r="B13" s="219"/>
+      <c r="C13" s="220"/>
+      <c r="D13" s="232"/>
+      <c r="E13" s="232"/>
+      <c r="F13" s="233"/>
       <c r="G13" s="14" t="s">
         <v>45</v>
       </c>
@@ -5162,26 +5137,26 @@
       <c r="J13" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="K13" s="221"/>
-      <c r="L13" s="202"/>
+      <c r="K13" s="219"/>
+      <c r="L13" s="200"/>
     </row>
     <row r="14" spans="1:13" ht="40.5" customHeight="1">
-      <c r="A14" s="297">
+      <c r="A14" s="295">
         <v>5</v>
       </c>
-      <c r="B14" s="222">
+      <c r="B14" s="220">
         <v>45746</v>
       </c>
-      <c r="C14" s="222" t="s">
+      <c r="C14" s="220" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="275" t="s">
+      <c r="D14" s="273" t="s">
         <v>46</v>
       </c>
-      <c r="E14" s="275" t="s">
+      <c r="E14" s="273" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="235" t="s">
+      <c r="F14" s="233" t="s">
         <v>48</v>
       </c>
       <c r="G14" s="13" t="s">
@@ -5196,20 +5171,20 @@
       <c r="J14" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="K14" s="221" t="s">
+      <c r="K14" s="219" t="s">
         <v>22</v>
       </c>
-      <c r="L14" s="200" t="s">
+      <c r="L14" s="198" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="48" customHeight="1">
-      <c r="A15" s="297"/>
-      <c r="B15" s="221"/>
-      <c r="C15" s="222"/>
-      <c r="D15" s="275"/>
-      <c r="E15" s="275"/>
-      <c r="F15" s="235"/>
+      <c r="A15" s="295"/>
+      <c r="B15" s="219"/>
+      <c r="C15" s="220"/>
+      <c r="D15" s="273"/>
+      <c r="E15" s="273"/>
+      <c r="F15" s="233"/>
       <c r="G15" s="13" t="s">
         <v>51</v>
       </c>
@@ -5222,16 +5197,16 @@
       <c r="J15" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="K15" s="221"/>
-      <c r="L15" s="201"/>
+      <c r="K15" s="219"/>
+      <c r="L15" s="199"/>
     </row>
     <row r="16" spans="1:13" ht="48" customHeight="1">
-      <c r="A16" s="297"/>
-      <c r="B16" s="221"/>
-      <c r="C16" s="222"/>
-      <c r="D16" s="275"/>
-      <c r="E16" s="275"/>
-      <c r="F16" s="235"/>
+      <c r="A16" s="295"/>
+      <c r="B16" s="219"/>
+      <c r="C16" s="220"/>
+      <c r="D16" s="273"/>
+      <c r="E16" s="273"/>
+      <c r="F16" s="233"/>
       <c r="G16" s="13" t="s">
         <v>53</v>
       </c>
@@ -5244,16 +5219,16 @@
       <c r="J16" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="K16" s="221"/>
-      <c r="L16" s="201"/>
+      <c r="K16" s="219"/>
+      <c r="L16" s="199"/>
     </row>
     <row r="17" spans="1:12" ht="48" customHeight="1">
-      <c r="A17" s="297"/>
-      <c r="B17" s="221"/>
-      <c r="C17" s="222"/>
-      <c r="D17" s="275"/>
-      <c r="E17" s="275"/>
-      <c r="F17" s="235"/>
+      <c r="A17" s="295"/>
+      <c r="B17" s="219"/>
+      <c r="C17" s="220"/>
+      <c r="D17" s="273"/>
+      <c r="E17" s="273"/>
+      <c r="F17" s="233"/>
       <c r="G17" s="13" t="s">
         <v>54</v>
       </c>
@@ -5266,142 +5241,142 @@
       <c r="J17" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="K17" s="221"/>
-      <c r="L17" s="202"/>
+      <c r="K17" s="219"/>
+      <c r="L17" s="200"/>
     </row>
     <row r="18" spans="1:12" ht="70.5" customHeight="1">
-      <c r="A18" s="294">
+      <c r="A18" s="292">
         <v>6</v>
       </c>
-      <c r="B18" s="286">
+      <c r="B18" s="284">
         <v>45756</v>
       </c>
-      <c r="C18" s="222" t="s">
+      <c r="C18" s="220" t="s">
         <v>32</v>
       </c>
-      <c r="D18" s="234" t="s">
+      <c r="D18" s="232" t="s">
         <v>56</v>
       </c>
-      <c r="E18" s="234" t="s">
+      <c r="E18" s="232" t="s">
         <v>27</v>
       </c>
-      <c r="F18" s="235" t="s">
+      <c r="F18" s="233" t="s">
         <v>57</v>
       </c>
-      <c r="G18" s="287" t="s">
+      <c r="G18" s="285" t="s">
         <v>29</v>
       </c>
-      <c r="H18" s="285" t="s">
+      <c r="H18" s="283" t="s">
         <v>30</v>
       </c>
-      <c r="I18" s="269" t="s">
+      <c r="I18" s="267" t="s">
         <v>31</v>
       </c>
-      <c r="J18" s="298"/>
-      <c r="K18" s="292"/>
-      <c r="L18" s="265"/>
+      <c r="J18" s="296"/>
+      <c r="K18" s="290"/>
+      <c r="L18" s="263"/>
     </row>
     <row r="19" spans="1:12" ht="33.6" customHeight="1">
-      <c r="A19" s="294"/>
-      <c r="B19" s="296"/>
-      <c r="C19" s="222"/>
-      <c r="D19" s="234"/>
-      <c r="E19" s="234"/>
-      <c r="F19" s="235"/>
-      <c r="G19" s="287"/>
-      <c r="H19" s="285"/>
-      <c r="I19" s="288"/>
-      <c r="J19" s="298"/>
-      <c r="K19" s="292"/>
-      <c r="L19" s="265"/>
+      <c r="A19" s="292"/>
+      <c r="B19" s="294"/>
+      <c r="C19" s="220"/>
+      <c r="D19" s="232"/>
+      <c r="E19" s="232"/>
+      <c r="F19" s="233"/>
+      <c r="G19" s="285"/>
+      <c r="H19" s="283"/>
+      <c r="I19" s="286"/>
+      <c r="J19" s="296"/>
+      <c r="K19" s="290"/>
+      <c r="L19" s="263"/>
     </row>
     <row r="20" spans="1:12" ht="33.6" customHeight="1">
-      <c r="A20" s="294"/>
-      <c r="B20" s="296"/>
-      <c r="C20" s="222"/>
-      <c r="D20" s="234"/>
-      <c r="E20" s="234"/>
-      <c r="F20" s="235"/>
-      <c r="G20" s="287"/>
-      <c r="H20" s="285"/>
-      <c r="I20" s="288"/>
-      <c r="J20" s="298"/>
-      <c r="K20" s="292"/>
-      <c r="L20" s="265"/>
+      <c r="A20" s="292"/>
+      <c r="B20" s="294"/>
+      <c r="C20" s="220"/>
+      <c r="D20" s="232"/>
+      <c r="E20" s="232"/>
+      <c r="F20" s="233"/>
+      <c r="G20" s="285"/>
+      <c r="H20" s="283"/>
+      <c r="I20" s="286"/>
+      <c r="J20" s="296"/>
+      <c r="K20" s="290"/>
+      <c r="L20" s="263"/>
     </row>
     <row r="21" spans="1:12" ht="33.6" customHeight="1">
-      <c r="A21" s="294"/>
-      <c r="B21" s="296"/>
-      <c r="C21" s="222"/>
-      <c r="D21" s="234"/>
-      <c r="E21" s="234"/>
-      <c r="F21" s="235"/>
-      <c r="G21" s="287"/>
-      <c r="H21" s="285"/>
-      <c r="I21" s="288"/>
-      <c r="J21" s="298"/>
-      <c r="K21" s="292"/>
-      <c r="L21" s="265"/>
+      <c r="A21" s="292"/>
+      <c r="B21" s="294"/>
+      <c r="C21" s="220"/>
+      <c r="D21" s="232"/>
+      <c r="E21" s="232"/>
+      <c r="F21" s="233"/>
+      <c r="G21" s="285"/>
+      <c r="H21" s="283"/>
+      <c r="I21" s="286"/>
+      <c r="J21" s="296"/>
+      <c r="K21" s="290"/>
+      <c r="L21" s="263"/>
     </row>
     <row r="22" spans="1:12" ht="33.6" customHeight="1">
-      <c r="A22" s="294"/>
-      <c r="B22" s="296"/>
-      <c r="C22" s="222"/>
-      <c r="D22" s="234"/>
-      <c r="E22" s="234"/>
-      <c r="F22" s="235"/>
-      <c r="G22" s="287"/>
-      <c r="H22" s="285"/>
-      <c r="I22" s="288"/>
-      <c r="J22" s="298"/>
-      <c r="K22" s="292"/>
-      <c r="L22" s="265"/>
+      <c r="A22" s="292"/>
+      <c r="B22" s="294"/>
+      <c r="C22" s="220"/>
+      <c r="D22" s="232"/>
+      <c r="E22" s="232"/>
+      <c r="F22" s="233"/>
+      <c r="G22" s="285"/>
+      <c r="H22" s="283"/>
+      <c r="I22" s="286"/>
+      <c r="J22" s="296"/>
+      <c r="K22" s="290"/>
+      <c r="L22" s="263"/>
     </row>
     <row r="23" spans="1:12" ht="33.6" customHeight="1">
-      <c r="A23" s="294"/>
-      <c r="B23" s="296"/>
-      <c r="C23" s="222"/>
-      <c r="D23" s="234"/>
-      <c r="E23" s="234"/>
-      <c r="F23" s="235"/>
-      <c r="G23" s="287"/>
-      <c r="H23" s="285"/>
-      <c r="I23" s="288"/>
-      <c r="J23" s="298"/>
-      <c r="K23" s="292"/>
-      <c r="L23" s="265"/>
+      <c r="A23" s="292"/>
+      <c r="B23" s="294"/>
+      <c r="C23" s="220"/>
+      <c r="D23" s="232"/>
+      <c r="E23" s="232"/>
+      <c r="F23" s="233"/>
+      <c r="G23" s="285"/>
+      <c r="H23" s="283"/>
+      <c r="I23" s="286"/>
+      <c r="J23" s="296"/>
+      <c r="K23" s="290"/>
+      <c r="L23" s="263"/>
     </row>
     <row r="24" spans="1:12" ht="33.6" customHeight="1">
-      <c r="A24" s="294"/>
-      <c r="B24" s="296"/>
-      <c r="C24" s="222"/>
-      <c r="D24" s="234"/>
-      <c r="E24" s="234"/>
-      <c r="F24" s="235"/>
-      <c r="G24" s="287"/>
-      <c r="H24" s="285"/>
-      <c r="I24" s="288"/>
-      <c r="J24" s="298"/>
-      <c r="K24" s="292"/>
-      <c r="L24" s="265"/>
+      <c r="A24" s="292"/>
+      <c r="B24" s="294"/>
+      <c r="C24" s="220"/>
+      <c r="D24" s="232"/>
+      <c r="E24" s="232"/>
+      <c r="F24" s="233"/>
+      <c r="G24" s="285"/>
+      <c r="H24" s="283"/>
+      <c r="I24" s="286"/>
+      <c r="J24" s="296"/>
+      <c r="K24" s="290"/>
+      <c r="L24" s="263"/>
     </row>
     <row r="25" spans="1:12" ht="97.5" customHeight="1">
-      <c r="A25" s="278">
+      <c r="A25" s="276">
         <v>7</v>
       </c>
-      <c r="B25" s="295">
+      <c r="B25" s="293">
         <v>45757</v>
       </c>
-      <c r="C25" s="295" t="s">
+      <c r="C25" s="293" t="s">
         <v>32</v>
       </c>
-      <c r="D25" s="233" t="s">
+      <c r="D25" s="231" t="s">
         <v>58</v>
       </c>
-      <c r="E25" s="233" t="s">
+      <c r="E25" s="231" t="s">
         <v>27</v>
       </c>
-      <c r="F25" s="254" t="s">
+      <c r="F25" s="252" t="s">
         <v>59</v>
       </c>
       <c r="G25" s="22" t="s">
@@ -5416,20 +5391,20 @@
       <c r="J25" s="74" t="s">
         <v>20</v>
       </c>
-      <c r="K25" s="293" t="s">
+      <c r="K25" s="291" t="s">
         <v>42</v>
       </c>
-      <c r="L25" s="221" t="s">
+      <c r="L25" s="219" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="68.099999999999994" customHeight="1">
-      <c r="A26" s="278"/>
-      <c r="B26" s="268"/>
-      <c r="C26" s="295"/>
-      <c r="D26" s="233"/>
-      <c r="E26" s="233"/>
-      <c r="F26" s="254"/>
+      <c r="A26" s="276"/>
+      <c r="B26" s="266"/>
+      <c r="C26" s="293"/>
+      <c r="D26" s="231"/>
+      <c r="E26" s="231"/>
+      <c r="F26" s="252"/>
       <c r="G26" s="14" t="s">
         <v>62</v>
       </c>
@@ -5442,26 +5417,26 @@
       <c r="J26" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="K26" s="293"/>
-      <c r="L26" s="221"/>
+      <c r="K26" s="291"/>
+      <c r="L26" s="219"/>
     </row>
     <row r="27" spans="1:12" ht="88.5" customHeight="1">
-      <c r="A27" s="294">
+      <c r="A27" s="292">
         <v>8</v>
       </c>
-      <c r="B27" s="222">
+      <c r="B27" s="220">
         <v>45760</v>
       </c>
-      <c r="C27" s="222" t="s">
+      <c r="C27" s="220" t="s">
         <v>32</v>
       </c>
-      <c r="D27" s="234" t="s">
+      <c r="D27" s="232" t="s">
         <v>63</v>
       </c>
-      <c r="E27" s="234" t="s">
+      <c r="E27" s="232" t="s">
         <v>27</v>
       </c>
-      <c r="F27" s="235" t="s">
+      <c r="F27" s="233" t="s">
         <v>64</v>
       </c>
       <c r="G27" s="14" t="s">
@@ -5476,20 +5451,20 @@
       <c r="J27" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="K27" s="220" t="s">
+      <c r="K27" s="218" t="s">
         <v>42</v>
       </c>
-      <c r="L27" s="221" t="s">
+      <c r="L27" s="219" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="88.5" customHeight="1">
-      <c r="A28" s="294"/>
-      <c r="B28" s="221"/>
-      <c r="C28" s="222"/>
-      <c r="D28" s="234"/>
-      <c r="E28" s="234"/>
-      <c r="F28" s="235"/>
+      <c r="A28" s="292"/>
+      <c r="B28" s="219"/>
+      <c r="C28" s="220"/>
+      <c r="D28" s="232"/>
+      <c r="E28" s="232"/>
+      <c r="F28" s="233"/>
       <c r="G28" s="14" t="s">
         <v>62</v>
       </c>
@@ -5502,26 +5477,26 @@
       <c r="J28" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="K28" s="220"/>
-      <c r="L28" s="221"/>
+      <c r="K28" s="218"/>
+      <c r="L28" s="219"/>
     </row>
     <row r="29" spans="1:12" ht="72" customHeight="1">
-      <c r="A29" s="294">
+      <c r="A29" s="292">
         <v>9</v>
       </c>
-      <c r="B29" s="222">
+      <c r="B29" s="220">
         <v>45764</v>
       </c>
-      <c r="C29" s="222" t="s">
+      <c r="C29" s="220" t="s">
         <v>14</v>
       </c>
-      <c r="D29" s="234" t="s">
+      <c r="D29" s="232" t="s">
         <v>66</v>
       </c>
-      <c r="E29" s="234" t="s">
+      <c r="E29" s="232" t="s">
         <v>27</v>
       </c>
-      <c r="F29" s="235" t="s">
+      <c r="F29" s="233" t="s">
         <v>67</v>
       </c>
       <c r="G29" s="14" t="s">
@@ -5536,20 +5511,20 @@
       <c r="J29" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="K29" s="220" t="s">
+      <c r="K29" s="218" t="s">
         <v>22</v>
       </c>
-      <c r="L29" s="221" t="s">
+      <c r="L29" s="219" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="72" customHeight="1">
-      <c r="A30" s="294"/>
-      <c r="B30" s="222"/>
-      <c r="C30" s="222"/>
-      <c r="D30" s="234"/>
-      <c r="E30" s="234"/>
-      <c r="F30" s="235"/>
+      <c r="A30" s="292"/>
+      <c r="B30" s="220"/>
+      <c r="C30" s="220"/>
+      <c r="D30" s="232"/>
+      <c r="E30" s="232"/>
+      <c r="F30" s="233"/>
       <c r="G30" s="14" t="s">
         <v>70</v>
       </c>
@@ -5562,16 +5537,16 @@
       <c r="J30" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="K30" s="220"/>
-      <c r="L30" s="221"/>
+      <c r="K30" s="218"/>
+      <c r="L30" s="219"/>
     </row>
     <row r="31" spans="1:12" ht="72" customHeight="1">
-      <c r="A31" s="294"/>
-      <c r="B31" s="222"/>
-      <c r="C31" s="222"/>
-      <c r="D31" s="234"/>
-      <c r="E31" s="234"/>
-      <c r="F31" s="235"/>
+      <c r="A31" s="292"/>
+      <c r="B31" s="220"/>
+      <c r="C31" s="220"/>
+      <c r="D31" s="232"/>
+      <c r="E31" s="232"/>
+      <c r="F31" s="233"/>
       <c r="G31" s="14" t="s">
         <v>72</v>
       </c>
@@ -5584,26 +5559,26 @@
       <c r="J31" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="K31" s="220"/>
-      <c r="L31" s="221"/>
+      <c r="K31" s="218"/>
+      <c r="L31" s="219"/>
     </row>
     <row r="32" spans="1:12" ht="81" customHeight="1">
-      <c r="A32" s="294">
+      <c r="A32" s="292">
         <v>10</v>
       </c>
-      <c r="B32" s="222">
+      <c r="B32" s="220">
         <v>45771</v>
       </c>
-      <c r="C32" s="222" t="s">
+      <c r="C32" s="220" t="s">
         <v>14</v>
       </c>
-      <c r="D32" s="234" t="s">
+      <c r="D32" s="232" t="s">
         <v>73</v>
       </c>
-      <c r="E32" s="234" t="s">
+      <c r="E32" s="232" t="s">
         <v>27</v>
       </c>
-      <c r="F32" s="235" t="s">
+      <c r="F32" s="233" t="s">
         <v>74</v>
       </c>
       <c r="G32" s="14" t="s">
@@ -5618,20 +5593,20 @@
       <c r="J32" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="K32" s="220" t="s">
+      <c r="K32" s="218" t="s">
         <v>22</v>
       </c>
-      <c r="L32" s="221" t="s">
+      <c r="L32" s="219" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="33" spans="1:12" ht="57.6" customHeight="1">
-      <c r="A33" s="294"/>
-      <c r="B33" s="222"/>
-      <c r="C33" s="222"/>
-      <c r="D33" s="234"/>
-      <c r="E33" s="234"/>
-      <c r="F33" s="235"/>
+      <c r="A33" s="292"/>
+      <c r="B33" s="220"/>
+      <c r="C33" s="220"/>
+      <c r="D33" s="232"/>
+      <c r="E33" s="232"/>
+      <c r="F33" s="233"/>
       <c r="G33" s="14" t="s">
         <v>76</v>
       </c>
@@ -5644,26 +5619,26 @@
       <c r="J33" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="K33" s="220"/>
-      <c r="L33" s="221"/>
+      <c r="K33" s="218"/>
+      <c r="L33" s="219"/>
     </row>
     <row r="34" spans="1:12" ht="56.45" customHeight="1">
-      <c r="A34" s="294">
+      <c r="A34" s="292">
         <v>11</v>
       </c>
-      <c r="B34" s="222">
+      <c r="B34" s="220">
         <v>45773</v>
       </c>
-      <c r="C34" s="222" t="s">
+      <c r="C34" s="220" t="s">
         <v>32</v>
       </c>
-      <c r="D34" s="234" t="s">
+      <c r="D34" s="232" t="s">
         <v>77</v>
       </c>
-      <c r="E34" s="234" t="s">
+      <c r="E34" s="232" t="s">
         <v>78</v>
       </c>
-      <c r="F34" s="235" t="s">
+      <c r="F34" s="233" t="s">
         <v>79</v>
       </c>
       <c r="G34" s="14" t="s">
@@ -5678,20 +5653,20 @@
       <c r="J34" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="K34" s="264" t="s">
+      <c r="K34" s="262" t="s">
         <v>42</v>
       </c>
-      <c r="L34" s="221" t="s">
+      <c r="L34" s="219" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:12" ht="56.45" customHeight="1">
-      <c r="A35" s="294"/>
-      <c r="B35" s="222"/>
-      <c r="C35" s="222"/>
-      <c r="D35" s="234"/>
-      <c r="E35" s="234"/>
-      <c r="F35" s="235"/>
+      <c r="A35" s="292"/>
+      <c r="B35" s="220"/>
+      <c r="C35" s="220"/>
+      <c r="D35" s="232"/>
+      <c r="E35" s="232"/>
+      <c r="F35" s="233"/>
       <c r="G35" s="14" t="s">
         <v>81</v>
       </c>
@@ -5704,16 +5679,16 @@
       <c r="J35" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="K35" s="264"/>
-      <c r="L35" s="221"/>
+      <c r="K35" s="262"/>
+      <c r="L35" s="219"/>
     </row>
     <row r="36" spans="1:12" ht="56.45" customHeight="1">
-      <c r="A36" s="294"/>
-      <c r="B36" s="222"/>
-      <c r="C36" s="222"/>
-      <c r="D36" s="234"/>
-      <c r="E36" s="234"/>
-      <c r="F36" s="235"/>
+      <c r="A36" s="292"/>
+      <c r="B36" s="220"/>
+      <c r="C36" s="220"/>
+      <c r="D36" s="232"/>
+      <c r="E36" s="232"/>
+      <c r="F36" s="233"/>
       <c r="G36" s="14" t="s">
         <v>82</v>
       </c>
@@ -5726,26 +5701,26 @@
       <c r="J36" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="K36" s="264"/>
-      <c r="L36" s="221"/>
+      <c r="K36" s="262"/>
+      <c r="L36" s="219"/>
     </row>
     <row r="37" spans="1:12" ht="58.5" customHeight="1">
-      <c r="A37" s="294">
+      <c r="A37" s="292">
         <v>12</v>
       </c>
-      <c r="B37" s="222">
+      <c r="B37" s="220">
         <v>45776</v>
       </c>
-      <c r="C37" s="222" t="s">
+      <c r="C37" s="220" t="s">
         <v>32</v>
       </c>
-      <c r="D37" s="220" t="s">
+      <c r="D37" s="218" t="s">
         <v>83</v>
       </c>
-      <c r="E37" s="220" t="s">
+      <c r="E37" s="218" t="s">
         <v>78</v>
       </c>
-      <c r="F37" s="235" t="s">
+      <c r="F37" s="233" t="s">
         <v>84</v>
       </c>
       <c r="G37" s="14" t="s">
@@ -5760,7 +5735,7 @@
       <c r="J37" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="K37" s="268" t="s">
+      <c r="K37" s="266" t="s">
         <v>22</v>
       </c>
       <c r="L37" s="24" t="s">
@@ -5768,12 +5743,12 @@
       </c>
     </row>
     <row r="38" spans="1:12" ht="58.5" customHeight="1">
-      <c r="A38" s="294"/>
-      <c r="B38" s="221"/>
-      <c r="C38" s="222"/>
-      <c r="D38" s="220"/>
-      <c r="E38" s="220"/>
-      <c r="F38" s="235"/>
+      <c r="A38" s="292"/>
+      <c r="B38" s="219"/>
+      <c r="C38" s="220"/>
+      <c r="D38" s="218"/>
+      <c r="E38" s="218"/>
+      <c r="F38" s="233"/>
       <c r="G38" s="14" t="s">
         <v>62</v>
       </c>
@@ -5786,18 +5761,18 @@
       <c r="J38" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K38" s="268"/>
+      <c r="K38" s="266"/>
       <c r="L38" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="58.5" customHeight="1">
-      <c r="A39" s="294"/>
-      <c r="B39" s="221"/>
-      <c r="C39" s="222"/>
-      <c r="D39" s="220"/>
-      <c r="E39" s="220"/>
-      <c r="F39" s="235"/>
+      <c r="A39" s="292"/>
+      <c r="B39" s="219"/>
+      <c r="C39" s="220"/>
+      <c r="D39" s="218"/>
+      <c r="E39" s="218"/>
+      <c r="F39" s="233"/>
       <c r="G39" s="14" t="s">
         <v>90</v>
       </c>
@@ -5810,176 +5785,176 @@
       <c r="J39" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K39" s="268"/>
+      <c r="K39" s="266"/>
       <c r="L39" s="12"/>
     </row>
     <row r="40" spans="1:12" ht="97.5" customHeight="1">
-      <c r="A40" s="294">
+      <c r="A40" s="292">
         <v>13</v>
       </c>
-      <c r="B40" s="222">
+      <c r="B40" s="220">
         <v>45781</v>
       </c>
-      <c r="C40" s="222" t="s">
+      <c r="C40" s="220" t="s">
         <v>14</v>
       </c>
-      <c r="D40" s="234" t="s">
+      <c r="D40" s="232" t="s">
         <v>92</v>
       </c>
-      <c r="E40" s="234" t="s">
+      <c r="E40" s="232" t="s">
         <v>27</v>
       </c>
-      <c r="F40" s="235" t="s">
+      <c r="F40" s="233" t="s">
         <v>93</v>
       </c>
-      <c r="G40" s="287" t="s">
+      <c r="G40" s="285" t="s">
         <v>29</v>
       </c>
-      <c r="H40" s="301" t="s">
+      <c r="H40" s="299" t="s">
         <v>30</v>
       </c>
-      <c r="I40" s="269" t="s">
+      <c r="I40" s="267" t="s">
         <v>31</v>
       </c>
-      <c r="J40" s="282"/>
-      <c r="K40" s="277"/>
-      <c r="L40" s="265"/>
+      <c r="J40" s="280"/>
+      <c r="K40" s="275"/>
+      <c r="L40" s="263"/>
     </row>
     <row r="41" spans="1:12" ht="33.6" customHeight="1">
-      <c r="A41" s="294"/>
-      <c r="B41" s="296"/>
-      <c r="C41" s="222"/>
-      <c r="D41" s="234"/>
-      <c r="E41" s="234"/>
-      <c r="F41" s="235"/>
-      <c r="G41" s="287"/>
-      <c r="H41" s="301"/>
-      <c r="I41" s="288"/>
-      <c r="J41" s="282"/>
-      <c r="K41" s="277"/>
-      <c r="L41" s="265"/>
+      <c r="A41" s="292"/>
+      <c r="B41" s="294"/>
+      <c r="C41" s="220"/>
+      <c r="D41" s="232"/>
+      <c r="E41" s="232"/>
+      <c r="F41" s="233"/>
+      <c r="G41" s="285"/>
+      <c r="H41" s="299"/>
+      <c r="I41" s="286"/>
+      <c r="J41" s="280"/>
+      <c r="K41" s="275"/>
+      <c r="L41" s="263"/>
     </row>
     <row r="42" spans="1:12" ht="33.6" customHeight="1">
-      <c r="A42" s="294"/>
-      <c r="B42" s="296"/>
-      <c r="C42" s="222"/>
-      <c r="D42" s="234"/>
-      <c r="E42" s="234"/>
-      <c r="F42" s="235"/>
-      <c r="G42" s="287"/>
-      <c r="H42" s="301"/>
-      <c r="I42" s="288"/>
-      <c r="J42" s="282"/>
-      <c r="K42" s="277"/>
-      <c r="L42" s="265"/>
+      <c r="A42" s="292"/>
+      <c r="B42" s="294"/>
+      <c r="C42" s="220"/>
+      <c r="D42" s="232"/>
+      <c r="E42" s="232"/>
+      <c r="F42" s="233"/>
+      <c r="G42" s="285"/>
+      <c r="H42" s="299"/>
+      <c r="I42" s="286"/>
+      <c r="J42" s="280"/>
+      <c r="K42" s="275"/>
+      <c r="L42" s="263"/>
     </row>
     <row r="43" spans="1:12" ht="33.6" customHeight="1">
-      <c r="A43" s="294"/>
-      <c r="B43" s="296"/>
-      <c r="C43" s="222"/>
-      <c r="D43" s="234"/>
-      <c r="E43" s="234"/>
-      <c r="F43" s="235"/>
-      <c r="G43" s="287"/>
-      <c r="H43" s="301"/>
-      <c r="I43" s="288"/>
-      <c r="J43" s="282"/>
-      <c r="K43" s="277"/>
-      <c r="L43" s="265"/>
+      <c r="A43" s="292"/>
+      <c r="B43" s="294"/>
+      <c r="C43" s="220"/>
+      <c r="D43" s="232"/>
+      <c r="E43" s="232"/>
+      <c r="F43" s="233"/>
+      <c r="G43" s="285"/>
+      <c r="H43" s="299"/>
+      <c r="I43" s="286"/>
+      <c r="J43" s="280"/>
+      <c r="K43" s="275"/>
+      <c r="L43" s="263"/>
     </row>
     <row r="44" spans="1:12" ht="33.6" customHeight="1">
-      <c r="A44" s="294">
+      <c r="A44" s="292">
         <v>14</v>
       </c>
-      <c r="B44" s="286">
+      <c r="B44" s="284">
         <v>45786</v>
       </c>
-      <c r="C44" s="221" t="s">
+      <c r="C44" s="219" t="s">
         <v>14</v>
       </c>
-      <c r="D44" s="220" t="s">
+      <c r="D44" s="218" t="s">
         <v>94</v>
       </c>
-      <c r="E44" s="220" t="s">
+      <c r="E44" s="218" t="s">
         <v>95</v>
       </c>
-      <c r="F44" s="235" t="s">
+      <c r="F44" s="233" t="s">
         <v>96</v>
       </c>
-      <c r="G44" s="283" t="s">
+      <c r="G44" s="281" t="s">
         <v>97</v>
       </c>
-      <c r="H44" s="285" t="s">
+      <c r="H44" s="283" t="s">
         <v>30</v>
       </c>
-      <c r="I44" s="281" t="s">
+      <c r="I44" s="279" t="s">
         <v>30</v>
       </c>
-      <c r="J44" s="282" t="s">
+      <c r="J44" s="280" t="s">
         <v>20</v>
       </c>
-      <c r="K44" s="277"/>
-      <c r="L44" s="265"/>
+      <c r="K44" s="275"/>
+      <c r="L44" s="263"/>
     </row>
     <row r="45" spans="1:12" ht="33.6" customHeight="1">
-      <c r="A45" s="294"/>
-      <c r="B45" s="296"/>
-      <c r="C45" s="221"/>
-      <c r="D45" s="220"/>
-      <c r="E45" s="220"/>
-      <c r="F45" s="235"/>
-      <c r="G45" s="283"/>
-      <c r="H45" s="285"/>
-      <c r="I45" s="281"/>
-      <c r="J45" s="282"/>
-      <c r="K45" s="277"/>
-      <c r="L45" s="265"/>
+      <c r="A45" s="292"/>
+      <c r="B45" s="294"/>
+      <c r="C45" s="219"/>
+      <c r="D45" s="218"/>
+      <c r="E45" s="218"/>
+      <c r="F45" s="233"/>
+      <c r="G45" s="281"/>
+      <c r="H45" s="283"/>
+      <c r="I45" s="279"/>
+      <c r="J45" s="280"/>
+      <c r="K45" s="275"/>
+      <c r="L45" s="263"/>
     </row>
     <row r="46" spans="1:12" ht="33.6" customHeight="1">
-      <c r="A46" s="294"/>
-      <c r="B46" s="296"/>
-      <c r="C46" s="221"/>
-      <c r="D46" s="220"/>
-      <c r="E46" s="220"/>
-      <c r="F46" s="235"/>
-      <c r="G46" s="283"/>
-      <c r="H46" s="285"/>
-      <c r="I46" s="281"/>
-      <c r="J46" s="282"/>
-      <c r="K46" s="277"/>
-      <c r="L46" s="265"/>
+      <c r="A46" s="292"/>
+      <c r="B46" s="294"/>
+      <c r="C46" s="219"/>
+      <c r="D46" s="218"/>
+      <c r="E46" s="218"/>
+      <c r="F46" s="233"/>
+      <c r="G46" s="281"/>
+      <c r="H46" s="283"/>
+      <c r="I46" s="279"/>
+      <c r="J46" s="280"/>
+      <c r="K46" s="275"/>
+      <c r="L46" s="263"/>
     </row>
     <row r="47" spans="1:12" ht="33.6" customHeight="1">
-      <c r="A47" s="294"/>
-      <c r="B47" s="296"/>
-      <c r="C47" s="221"/>
-      <c r="D47" s="220"/>
-      <c r="E47" s="220"/>
-      <c r="F47" s="235"/>
-      <c r="G47" s="283"/>
-      <c r="H47" s="285"/>
-      <c r="I47" s="281"/>
-      <c r="J47" s="282"/>
-      <c r="K47" s="277"/>
-      <c r="L47" s="265"/>
+      <c r="A47" s="292"/>
+      <c r="B47" s="294"/>
+      <c r="C47" s="219"/>
+      <c r="D47" s="218"/>
+      <c r="E47" s="218"/>
+      <c r="F47" s="233"/>
+      <c r="G47" s="281"/>
+      <c r="H47" s="283"/>
+      <c r="I47" s="279"/>
+      <c r="J47" s="280"/>
+      <c r="K47" s="275"/>
+      <c r="L47" s="263"/>
     </row>
     <row r="48" spans="1:12" ht="46.5" customHeight="1">
-      <c r="A48" s="297">
+      <c r="A48" s="295">
         <v>15</v>
       </c>
-      <c r="B48" s="299">
+      <c r="B48" s="297">
         <v>45787</v>
       </c>
-      <c r="C48" s="299" t="s">
+      <c r="C48" s="297" t="s">
         <v>14</v>
       </c>
-      <c r="D48" s="275" t="s">
+      <c r="D48" s="273" t="s">
         <v>98</v>
       </c>
-      <c r="E48" s="275" t="s">
+      <c r="E48" s="273" t="s">
         <v>47</v>
       </c>
-      <c r="F48" s="235" t="s">
+      <c r="F48" s="233" t="s">
         <v>99</v>
       </c>
       <c r="G48" s="14" t="s">
@@ -5994,20 +5969,20 @@
       <c r="J48" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K48" s="264" t="s">
+      <c r="K48" s="262" t="s">
         <v>22</v>
       </c>
-      <c r="L48" s="221" t="s">
+      <c r="L48" s="219" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="49" spans="1:13" ht="46.5" customHeight="1">
-      <c r="A49" s="297"/>
-      <c r="B49" s="226"/>
-      <c r="C49" s="299"/>
-      <c r="D49" s="275"/>
-      <c r="E49" s="275"/>
-      <c r="F49" s="235"/>
+      <c r="A49" s="295"/>
+      <c r="B49" s="224"/>
+      <c r="C49" s="297"/>
+      <c r="D49" s="273"/>
+      <c r="E49" s="273"/>
+      <c r="F49" s="233"/>
       <c r="G49" s="14" t="s">
         <v>102</v>
       </c>
@@ -6020,16 +5995,16 @@
       <c r="J49" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K49" s="264"/>
-      <c r="L49" s="221"/>
+      <c r="K49" s="262"/>
+      <c r="L49" s="219"/>
     </row>
     <row r="50" spans="1:13" ht="46.5" customHeight="1">
-      <c r="A50" s="297"/>
-      <c r="B50" s="226"/>
-      <c r="C50" s="299"/>
-      <c r="D50" s="275"/>
-      <c r="E50" s="275"/>
-      <c r="F50" s="235"/>
+      <c r="A50" s="295"/>
+      <c r="B50" s="224"/>
+      <c r="C50" s="297"/>
+      <c r="D50" s="273"/>
+      <c r="E50" s="273"/>
+      <c r="F50" s="233"/>
       <c r="G50" s="14" t="s">
         <v>104</v>
       </c>
@@ -6042,16 +6017,16 @@
       <c r="J50" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K50" s="264"/>
-      <c r="L50" s="221"/>
+      <c r="K50" s="262"/>
+      <c r="L50" s="219"/>
     </row>
     <row r="51" spans="1:13" ht="46.5" customHeight="1">
-      <c r="A51" s="297"/>
-      <c r="B51" s="226"/>
-      <c r="C51" s="299"/>
-      <c r="D51" s="275"/>
-      <c r="E51" s="275"/>
-      <c r="F51" s="235"/>
+      <c r="A51" s="295"/>
+      <c r="B51" s="224"/>
+      <c r="C51" s="297"/>
+      <c r="D51" s="273"/>
+      <c r="E51" s="273"/>
+      <c r="F51" s="233"/>
       <c r="G51" s="14" t="s">
         <v>105</v>
       </c>
@@ -6064,16 +6039,16 @@
       <c r="J51" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K51" s="264"/>
-      <c r="L51" s="221"/>
+      <c r="K51" s="262"/>
+      <c r="L51" s="219"/>
     </row>
     <row r="52" spans="1:13" ht="46.5" customHeight="1">
-      <c r="A52" s="297"/>
-      <c r="B52" s="226"/>
-      <c r="C52" s="299"/>
-      <c r="D52" s="275"/>
-      <c r="E52" s="275"/>
-      <c r="F52" s="235"/>
+      <c r="A52" s="295"/>
+      <c r="B52" s="224"/>
+      <c r="C52" s="297"/>
+      <c r="D52" s="273"/>
+      <c r="E52" s="273"/>
+      <c r="F52" s="233"/>
       <c r="G52" s="14" t="s">
         <v>107</v>
       </c>
@@ -6086,26 +6061,26 @@
       <c r="J52" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K52" s="264"/>
-      <c r="L52" s="221"/>
+      <c r="K52" s="262"/>
+      <c r="L52" s="219"/>
     </row>
     <row r="53" spans="1:13" ht="78" customHeight="1">
-      <c r="A53" s="297">
+      <c r="A53" s="295">
         <v>16</v>
       </c>
-      <c r="B53" s="275">
+      <c r="B53" s="273">
         <v>45800</v>
       </c>
-      <c r="C53" s="275" t="s">
+      <c r="C53" s="273" t="s">
         <v>32</v>
       </c>
-      <c r="D53" s="275" t="s">
+      <c r="D53" s="273" t="s">
         <v>108</v>
       </c>
-      <c r="E53" s="275" t="s">
+      <c r="E53" s="273" t="s">
         <v>47</v>
       </c>
-      <c r="F53" s="235" t="s">
+      <c r="F53" s="233" t="s">
         <v>109</v>
       </c>
       <c r="G53" s="26" t="s">
@@ -6120,20 +6095,20 @@
       <c r="J53" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K53" s="264" t="s">
+      <c r="K53" s="262" t="s">
         <v>22</v>
       </c>
-      <c r="L53" s="221" t="s">
+      <c r="L53" s="219" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="54" spans="1:13" ht="56.45" customHeight="1">
-      <c r="A54" s="297"/>
-      <c r="B54" s="300"/>
-      <c r="C54" s="275"/>
-      <c r="D54" s="275"/>
-      <c r="E54" s="275"/>
-      <c r="F54" s="235"/>
+      <c r="A54" s="295"/>
+      <c r="B54" s="298"/>
+      <c r="C54" s="273"/>
+      <c r="D54" s="273"/>
+      <c r="E54" s="273"/>
+      <c r="F54" s="233"/>
       <c r="G54" s="26" t="s">
         <v>111</v>
       </c>
@@ -6146,16 +6121,16 @@
       <c r="J54" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="K54" s="264"/>
-      <c r="L54" s="221"/>
+      <c r="K54" s="262"/>
+      <c r="L54" s="219"/>
     </row>
     <row r="55" spans="1:13" ht="56.45" customHeight="1">
-      <c r="A55" s="297"/>
-      <c r="B55" s="300"/>
-      <c r="C55" s="275"/>
-      <c r="D55" s="275"/>
-      <c r="E55" s="275"/>
-      <c r="F55" s="235"/>
+      <c r="A55" s="295"/>
+      <c r="B55" s="298"/>
+      <c r="C55" s="273"/>
+      <c r="D55" s="273"/>
+      <c r="E55" s="273"/>
+      <c r="F55" s="233"/>
       <c r="G55" s="26" t="s">
         <v>112</v>
       </c>
@@ -6168,16 +6143,16 @@
       <c r="J55" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="K55" s="264"/>
-      <c r="L55" s="221"/>
+      <c r="K55" s="262"/>
+      <c r="L55" s="219"/>
     </row>
     <row r="56" spans="1:13" ht="56.45" customHeight="1">
-      <c r="A56" s="297"/>
-      <c r="B56" s="300"/>
-      <c r="C56" s="275"/>
-      <c r="D56" s="275"/>
-      <c r="E56" s="275"/>
-      <c r="F56" s="235"/>
+      <c r="A56" s="295"/>
+      <c r="B56" s="298"/>
+      <c r="C56" s="273"/>
+      <c r="D56" s="273"/>
+      <c r="E56" s="273"/>
+      <c r="F56" s="233"/>
       <c r="G56" s="26" t="s">
         <v>113</v>
       </c>
@@ -6190,16 +6165,16 @@
       <c r="J56" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K56" s="264"/>
-      <c r="L56" s="221"/>
+      <c r="K56" s="262"/>
+      <c r="L56" s="219"/>
     </row>
     <row r="57" spans="1:13" ht="75.599999999999994" customHeight="1">
-      <c r="A57" s="297"/>
-      <c r="B57" s="300"/>
-      <c r="C57" s="275"/>
-      <c r="D57" s="275"/>
-      <c r="E57" s="275"/>
-      <c r="F57" s="235"/>
+      <c r="A57" s="295"/>
+      <c r="B57" s="298"/>
+      <c r="C57" s="273"/>
+      <c r="D57" s="273"/>
+      <c r="E57" s="273"/>
+      <c r="F57" s="233"/>
       <c r="G57" s="28" t="s">
         <v>114</v>
       </c>
@@ -6212,26 +6187,26 @@
       <c r="J57" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K57" s="264"/>
-      <c r="L57" s="200"/>
+      <c r="K57" s="262"/>
+      <c r="L57" s="198"/>
     </row>
     <row r="58" spans="1:13" ht="58.5" customHeight="1">
-      <c r="A58" s="297">
+      <c r="A58" s="295">
         <v>17</v>
       </c>
-      <c r="B58" s="275">
+      <c r="B58" s="273">
         <v>45809</v>
       </c>
-      <c r="C58" s="275" t="s">
+      <c r="C58" s="273" t="s">
         <v>14</v>
       </c>
-      <c r="D58" s="275" t="s">
+      <c r="D58" s="273" t="s">
         <v>115</v>
       </c>
-      <c r="E58" s="275" t="s">
+      <c r="E58" s="273" t="s">
         <v>47</v>
       </c>
-      <c r="F58" s="305" t="s">
+      <c r="F58" s="303" t="s">
         <v>116</v>
       </c>
       <c r="G58" s="26" t="s">
@@ -6246,21 +6221,21 @@
       <c r="J58" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K58" s="251" t="s">
+      <c r="K58" s="249" t="s">
         <v>22</v>
       </c>
-      <c r="L58" s="221" t="s">
+      <c r="L58" s="219" t="s">
         <v>22</v>
       </c>
       <c r="M58" s="12"/>
     </row>
     <row r="59" spans="1:13" ht="58.5" customHeight="1">
-      <c r="A59" s="297"/>
-      <c r="B59" s="275"/>
-      <c r="C59" s="275"/>
-      <c r="D59" s="275"/>
-      <c r="E59" s="275"/>
-      <c r="F59" s="305"/>
+      <c r="A59" s="295"/>
+      <c r="B59" s="273"/>
+      <c r="C59" s="273"/>
+      <c r="D59" s="273"/>
+      <c r="E59" s="273"/>
+      <c r="F59" s="303"/>
       <c r="G59" s="26" t="s">
         <v>119</v>
       </c>
@@ -6273,17 +6248,17 @@
       <c r="J59" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K59" s="251"/>
-      <c r="L59" s="221"/>
+      <c r="K59" s="249"/>
+      <c r="L59" s="219"/>
       <c r="M59" s="12"/>
     </row>
     <row r="60" spans="1:13" ht="58.5" customHeight="1">
-      <c r="A60" s="297"/>
-      <c r="B60" s="275"/>
-      <c r="C60" s="275"/>
-      <c r="D60" s="275"/>
-      <c r="E60" s="275"/>
-      <c r="F60" s="305"/>
+      <c r="A60" s="295"/>
+      <c r="B60" s="273"/>
+      <c r="C60" s="273"/>
+      <c r="D60" s="273"/>
+      <c r="E60" s="273"/>
+      <c r="F60" s="303"/>
       <c r="G60" s="26" t="s">
         <v>121</v>
       </c>
@@ -6296,17 +6271,17 @@
       <c r="J60" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K60" s="251"/>
-      <c r="L60" s="221"/>
+      <c r="K60" s="249"/>
+      <c r="L60" s="219"/>
       <c r="M60" s="12"/>
     </row>
     <row r="61" spans="1:13" ht="58.5" customHeight="1">
-      <c r="A61" s="297"/>
-      <c r="B61" s="300"/>
-      <c r="C61" s="275"/>
-      <c r="D61" s="275"/>
-      <c r="E61" s="275"/>
-      <c r="F61" s="305"/>
+      <c r="A61" s="295"/>
+      <c r="B61" s="298"/>
+      <c r="C61" s="273"/>
+      <c r="D61" s="273"/>
+      <c r="E61" s="273"/>
+      <c r="F61" s="303"/>
       <c r="G61" s="26" t="s">
         <v>122</v>
       </c>
@@ -6319,17 +6294,17 @@
       <c r="J61" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="K61" s="251"/>
-      <c r="L61" s="221"/>
+      <c r="K61" s="249"/>
+      <c r="L61" s="219"/>
       <c r="M61" s="12"/>
     </row>
     <row r="62" spans="1:13" ht="58.5" customHeight="1">
-      <c r="A62" s="297"/>
-      <c r="B62" s="300"/>
-      <c r="C62" s="275"/>
-      <c r="D62" s="275"/>
-      <c r="E62" s="275"/>
-      <c r="F62" s="305"/>
+      <c r="A62" s="295"/>
+      <c r="B62" s="298"/>
+      <c r="C62" s="273"/>
+      <c r="D62" s="273"/>
+      <c r="E62" s="273"/>
+      <c r="F62" s="303"/>
       <c r="G62" s="26" t="s">
         <v>123</v>
       </c>
@@ -6342,17 +6317,17 @@
       <c r="J62" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="K62" s="251"/>
-      <c r="L62" s="221"/>
+      <c r="K62" s="249"/>
+      <c r="L62" s="219"/>
       <c r="M62" s="12"/>
     </row>
     <row r="63" spans="1:13" ht="58.5" customHeight="1">
-      <c r="A63" s="297"/>
-      <c r="B63" s="300"/>
-      <c r="C63" s="275"/>
-      <c r="D63" s="275"/>
-      <c r="E63" s="275"/>
-      <c r="F63" s="305"/>
+      <c r="A63" s="295"/>
+      <c r="B63" s="298"/>
+      <c r="C63" s="273"/>
+      <c r="D63" s="273"/>
+      <c r="E63" s="273"/>
+      <c r="F63" s="303"/>
       <c r="G63" s="26" t="s">
         <v>124</v>
       </c>
@@ -6365,142 +6340,142 @@
       <c r="J63" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="K63" s="251"/>
-      <c r="L63" s="221"/>
+      <c r="K63" s="249"/>
+      <c r="L63" s="219"/>
       <c r="M63" s="12"/>
     </row>
     <row r="64" spans="1:13" ht="58.5" customHeight="1">
-      <c r="A64" s="294">
+      <c r="A64" s="292">
         <v>18</v>
       </c>
-      <c r="B64" s="269">
+      <c r="B64" s="267">
         <v>45816</v>
       </c>
-      <c r="C64" s="220" t="s">
+      <c r="C64" s="218" t="s">
         <v>125</v>
       </c>
-      <c r="D64" s="220" t="s">
+      <c r="D64" s="218" t="s">
         <v>126</v>
       </c>
-      <c r="E64" s="220" t="s">
+      <c r="E64" s="218" t="s">
         <v>27</v>
       </c>
-      <c r="F64" s="235" t="s">
+      <c r="F64" s="233" t="s">
         <v>127</v>
       </c>
-      <c r="G64" s="303" t="s">
+      <c r="G64" s="301" t="s">
         <v>29</v>
       </c>
-      <c r="H64" s="304" t="s">
+      <c r="H64" s="302" t="s">
         <v>30</v>
       </c>
-      <c r="I64" s="284" t="s">
+      <c r="I64" s="282" t="s">
         <v>31</v>
       </c>
-      <c r="J64" s="249"/>
-      <c r="K64" s="245"/>
-      <c r="L64" s="221"/>
+      <c r="J64" s="247"/>
+      <c r="K64" s="243"/>
+      <c r="L64" s="219"/>
       <c r="M64" s="12"/>
     </row>
     <row r="65" spans="1:13" ht="58.5" customHeight="1">
-      <c r="A65" s="294"/>
-      <c r="B65" s="266"/>
-      <c r="C65" s="220"/>
-      <c r="D65" s="220"/>
-      <c r="E65" s="220"/>
-      <c r="F65" s="235"/>
-      <c r="G65" s="303"/>
-      <c r="H65" s="304"/>
-      <c r="I65" s="272"/>
-      <c r="J65" s="249"/>
-      <c r="K65" s="245"/>
-      <c r="L65" s="221"/>
+      <c r="A65" s="292"/>
+      <c r="B65" s="264"/>
+      <c r="C65" s="218"/>
+      <c r="D65" s="218"/>
+      <c r="E65" s="218"/>
+      <c r="F65" s="233"/>
+      <c r="G65" s="301"/>
+      <c r="H65" s="302"/>
+      <c r="I65" s="270"/>
+      <c r="J65" s="247"/>
+      <c r="K65" s="243"/>
+      <c r="L65" s="219"/>
       <c r="M65" s="12"/>
     </row>
     <row r="66" spans="1:13" ht="73.5" customHeight="1">
-      <c r="A66" s="294">
+      <c r="A66" s="292">
         <v>19</v>
       </c>
-      <c r="B66" s="269">
+      <c r="B66" s="267">
         <v>45817</v>
       </c>
-      <c r="C66" s="220" t="s">
+      <c r="C66" s="218" t="s">
         <v>32</v>
       </c>
-      <c r="D66" s="220" t="s">
+      <c r="D66" s="218" t="s">
         <v>128</v>
       </c>
-      <c r="E66" s="220" t="s">
+      <c r="E66" s="218" t="s">
         <v>78</v>
       </c>
-      <c r="F66" s="235" t="s">
+      <c r="F66" s="233" t="s">
         <v>129</v>
       </c>
-      <c r="G66" s="302" t="s">
+      <c r="G66" s="300" t="s">
         <v>130</v>
       </c>
       <c r="H66" s="29" t="s">
         <v>131</v>
       </c>
-      <c r="I66" s="262"/>
-      <c r="J66" s="278"/>
-      <c r="K66" s="246"/>
-      <c r="L66" s="247" t="s">
+      <c r="I66" s="260"/>
+      <c r="J66" s="276"/>
+      <c r="K66" s="244"/>
+      <c r="L66" s="245" t="s">
         <v>132</v>
       </c>
       <c r="M66" s="12"/>
     </row>
     <row r="67" spans="1:13" ht="99.75" customHeight="1">
-      <c r="A67" s="294"/>
-      <c r="B67" s="269"/>
-      <c r="C67" s="220"/>
-      <c r="D67" s="220"/>
-      <c r="E67" s="220"/>
-      <c r="F67" s="235"/>
-      <c r="G67" s="302"/>
+      <c r="A67" s="292"/>
+      <c r="B67" s="267"/>
+      <c r="C67" s="218"/>
+      <c r="D67" s="218"/>
+      <c r="E67" s="218"/>
+      <c r="F67" s="233"/>
+      <c r="G67" s="300"/>
       <c r="H67" s="29" t="s">
         <v>133</v>
       </c>
-      <c r="I67" s="262"/>
-      <c r="J67" s="278"/>
-      <c r="K67" s="246"/>
-      <c r="L67" s="247"/>
+      <c r="I67" s="260"/>
+      <c r="J67" s="276"/>
+      <c r="K67" s="244"/>
+      <c r="L67" s="245"/>
       <c r="M67" s="12"/>
     </row>
     <row r="68" spans="1:13" ht="73.5" customHeight="1">
-      <c r="A68" s="294"/>
-      <c r="B68" s="266"/>
-      <c r="C68" s="220"/>
-      <c r="D68" s="220"/>
-      <c r="E68" s="220"/>
-      <c r="F68" s="235"/>
-      <c r="G68" s="302"/>
+      <c r="A68" s="292"/>
+      <c r="B68" s="264"/>
+      <c r="C68" s="218"/>
+      <c r="D68" s="218"/>
+      <c r="E68" s="218"/>
+      <c r="F68" s="233"/>
+      <c r="G68" s="300"/>
       <c r="H68" s="29" t="s">
         <v>131</v>
       </c>
-      <c r="I68" s="262"/>
-      <c r="J68" s="278"/>
-      <c r="K68" s="246"/>
-      <c r="L68" s="247"/>
+      <c r="I68" s="260"/>
+      <c r="J68" s="276"/>
+      <c r="K68" s="244"/>
+      <c r="L68" s="245"/>
       <c r="M68" s="12"/>
     </row>
     <row r="69" spans="1:13" ht="63" customHeight="1">
-      <c r="A69" s="294">
+      <c r="A69" s="292">
         <v>20</v>
       </c>
-      <c r="B69" s="234">
+      <c r="B69" s="232">
         <v>45818</v>
       </c>
-      <c r="C69" s="234" t="s">
+      <c r="C69" s="232" t="s">
         <v>32</v>
       </c>
-      <c r="D69" s="234" t="s">
+      <c r="D69" s="232" t="s">
         <v>134</v>
       </c>
-      <c r="E69" s="234" t="s">
+      <c r="E69" s="232" t="s">
         <v>27</v>
       </c>
-      <c r="F69" s="235" t="s">
+      <c r="F69" s="233" t="s">
         <v>135</v>
       </c>
       <c r="G69" s="31" t="s">
@@ -6515,21 +6490,21 @@
       <c r="J69" s="77" t="s">
         <v>20</v>
       </c>
-      <c r="K69" s="245" t="s">
+      <c r="K69" s="243" t="s">
         <v>22</v>
       </c>
-      <c r="L69" s="221" t="s">
+      <c r="L69" s="219" t="s">
         <v>22</v>
       </c>
       <c r="M69" s="12"/>
     </row>
     <row r="70" spans="1:13" ht="90.95" customHeight="1">
-      <c r="A70" s="294"/>
-      <c r="B70" s="220"/>
-      <c r="C70" s="234"/>
-      <c r="D70" s="234"/>
-      <c r="E70" s="234"/>
-      <c r="F70" s="235"/>
+      <c r="A70" s="292"/>
+      <c r="B70" s="218"/>
+      <c r="C70" s="232"/>
+      <c r="D70" s="232"/>
+      <c r="E70" s="232"/>
+      <c r="F70" s="233"/>
       <c r="G70" s="31" t="s">
         <v>72</v>
       </c>
@@ -6542,27 +6517,27 @@
       <c r="J70" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="K70" s="245"/>
-      <c r="L70" s="221"/>
+      <c r="K70" s="243"/>
+      <c r="L70" s="219"/>
       <c r="M70" s="12"/>
     </row>
     <row r="71" spans="1:13" ht="123.95" customHeight="1">
-      <c r="A71" s="294">
+      <c r="A71" s="292">
         <v>21</v>
       </c>
-      <c r="B71" s="222">
+      <c r="B71" s="220">
         <v>45821</v>
       </c>
-      <c r="C71" s="222" t="s">
+      <c r="C71" s="220" t="s">
         <v>32</v>
       </c>
-      <c r="D71" s="234" t="s">
+      <c r="D71" s="232" t="s">
         <v>138</v>
       </c>
-      <c r="E71" s="234" t="s">
+      <c r="E71" s="232" t="s">
         <v>27</v>
       </c>
-      <c r="F71" s="235" t="s">
+      <c r="F71" s="233" t="s">
         <v>139</v>
       </c>
       <c r="G71" s="31" t="s">
@@ -6577,21 +6552,21 @@
       <c r="J71" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="K71" s="232" t="s">
+      <c r="K71" s="230" t="s">
         <v>22</v>
       </c>
-      <c r="L71" s="221" t="s">
+      <c r="L71" s="219" t="s">
         <v>22</v>
       </c>
       <c r="M71" s="12"/>
     </row>
     <row r="72" spans="1:13" ht="78.599999999999994" customHeight="1">
-      <c r="A72" s="294"/>
-      <c r="B72" s="222"/>
-      <c r="C72" s="222"/>
-      <c r="D72" s="234"/>
-      <c r="E72" s="234"/>
-      <c r="F72" s="235"/>
+      <c r="A72" s="292"/>
+      <c r="B72" s="220"/>
+      <c r="C72" s="220"/>
+      <c r="D72" s="232"/>
+      <c r="E72" s="232"/>
+      <c r="F72" s="233"/>
       <c r="G72" s="31" t="s">
         <v>142</v>
       </c>
@@ -6604,17 +6579,17 @@
       <c r="J72" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="K72" s="232"/>
-      <c r="L72" s="221"/>
+      <c r="K72" s="230"/>
+      <c r="L72" s="219"/>
       <c r="M72" s="12"/>
     </row>
     <row r="73" spans="1:13" ht="47.1" customHeight="1">
-      <c r="A73" s="294"/>
-      <c r="B73" s="222"/>
-      <c r="C73" s="222"/>
-      <c r="D73" s="234"/>
-      <c r="E73" s="234"/>
-      <c r="F73" s="235"/>
+      <c r="A73" s="292"/>
+      <c r="B73" s="220"/>
+      <c r="C73" s="220"/>
+      <c r="D73" s="232"/>
+      <c r="E73" s="232"/>
+      <c r="F73" s="233"/>
       <c r="G73" s="31" t="s">
         <v>143</v>
       </c>
@@ -6627,27 +6602,27 @@
       <c r="J73" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="K73" s="232"/>
-      <c r="L73" s="221"/>
+      <c r="K73" s="230"/>
+      <c r="L73" s="219"/>
       <c r="M73" s="12"/>
     </row>
     <row r="74" spans="1:13" ht="45" customHeight="1">
-      <c r="A74" s="294">
+      <c r="A74" s="292">
         <v>22</v>
       </c>
-      <c r="B74" s="234">
+      <c r="B74" s="232">
         <v>45829</v>
       </c>
-      <c r="C74" s="234" t="s">
+      <c r="C74" s="232" t="s">
         <v>14</v>
       </c>
-      <c r="D74" s="234" t="s">
+      <c r="D74" s="232" t="s">
         <v>145</v>
       </c>
-      <c r="E74" s="234" t="s">
+      <c r="E74" s="232" t="s">
         <v>27</v>
       </c>
-      <c r="F74" s="235" t="s">
+      <c r="F74" s="233" t="s">
         <v>146</v>
       </c>
       <c r="G74" s="33" t="s">
@@ -6662,21 +6637,21 @@
       <c r="J74" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="K74" s="232" t="s">
+      <c r="K74" s="230" t="s">
         <v>22</v>
       </c>
-      <c r="L74" s="221" t="s">
+      <c r="L74" s="219" t="s">
         <v>22</v>
       </c>
       <c r="M74" s="12"/>
     </row>
     <row r="75" spans="1:13" ht="67.5" customHeight="1">
-      <c r="A75" s="294"/>
-      <c r="B75" s="220"/>
-      <c r="C75" s="234"/>
-      <c r="D75" s="234"/>
-      <c r="E75" s="234"/>
-      <c r="F75" s="235"/>
+      <c r="A75" s="292"/>
+      <c r="B75" s="218"/>
+      <c r="C75" s="232"/>
+      <c r="D75" s="232"/>
+      <c r="E75" s="232"/>
+      <c r="F75" s="233"/>
       <c r="G75" s="31" t="s">
         <v>149</v>
       </c>
@@ -6689,27 +6664,27 @@
       <c r="J75" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="K75" s="232"/>
-      <c r="L75" s="221"/>
+      <c r="K75" s="230"/>
+      <c r="L75" s="219"/>
       <c r="M75" s="12"/>
     </row>
     <row r="76" spans="1:13" ht="101.45" customHeight="1">
-      <c r="A76" s="294">
+      <c r="A76" s="292">
         <v>23</v>
       </c>
-      <c r="B76" s="234">
+      <c r="B76" s="232">
         <v>45838</v>
       </c>
-      <c r="C76" s="234" t="s">
+      <c r="C76" s="232" t="s">
         <v>32</v>
       </c>
-      <c r="D76" s="234" t="s">
+      <c r="D76" s="232" t="s">
         <v>151</v>
       </c>
-      <c r="E76" s="234" t="s">
+      <c r="E76" s="232" t="s">
         <v>27</v>
       </c>
-      <c r="F76" s="235" t="s">
+      <c r="F76" s="233" t="s">
         <v>152</v>
       </c>
       <c r="G76" s="31" t="s">
@@ -6724,21 +6699,21 @@
       <c r="J76" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="K76" s="232" t="s">
+      <c r="K76" s="230" t="s">
         <v>22</v>
       </c>
-      <c r="L76" s="221" t="s">
+      <c r="L76" s="219" t="s">
         <v>22</v>
       </c>
       <c r="M76" s="12"/>
     </row>
     <row r="77" spans="1:13" ht="67.5" customHeight="1">
-      <c r="A77" s="294"/>
-      <c r="B77" s="220"/>
-      <c r="C77" s="234"/>
-      <c r="D77" s="234"/>
-      <c r="E77" s="234"/>
-      <c r="F77" s="235"/>
+      <c r="A77" s="292"/>
+      <c r="B77" s="218"/>
+      <c r="C77" s="232"/>
+      <c r="D77" s="232"/>
+      <c r="E77" s="232"/>
+      <c r="F77" s="233"/>
       <c r="G77" s="31" t="s">
         <v>154</v>
       </c>
@@ -6751,27 +6726,27 @@
       <c r="J77" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="K77" s="232"/>
-      <c r="L77" s="221"/>
+      <c r="K77" s="230"/>
+      <c r="L77" s="219"/>
       <c r="M77" s="12"/>
     </row>
     <row r="78" spans="1:13" ht="321.95" customHeight="1">
-      <c r="A78" s="294">
+      <c r="A78" s="292">
         <v>24</v>
       </c>
-      <c r="B78" s="234">
+      <c r="B78" s="232">
         <v>45839</v>
       </c>
-      <c r="C78" s="234" t="s">
+      <c r="C78" s="232" t="s">
         <v>32</v>
       </c>
-      <c r="D78" s="234" t="s">
+      <c r="D78" s="232" t="s">
         <v>156</v>
       </c>
-      <c r="E78" s="234" t="s">
+      <c r="E78" s="232" t="s">
         <v>27</v>
       </c>
-      <c r="F78" s="235" t="s">
+      <c r="F78" s="233" t="s">
         <v>157</v>
       </c>
       <c r="G78" s="31" t="s">
@@ -6786,21 +6761,21 @@
       <c r="J78" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="K78" s="246" t="s">
+      <c r="K78" s="244" t="s">
         <v>22</v>
       </c>
-      <c r="L78" s="221" t="s">
+      <c r="L78" s="219" t="s">
         <v>22</v>
       </c>
       <c r="M78" s="12"/>
     </row>
     <row r="79" spans="1:13" ht="43.5" customHeight="1">
-      <c r="A79" s="294"/>
-      <c r="B79" s="234"/>
-      <c r="C79" s="234"/>
-      <c r="D79" s="234"/>
-      <c r="E79" s="234"/>
-      <c r="F79" s="235"/>
+      <c r="A79" s="292"/>
+      <c r="B79" s="232"/>
+      <c r="C79" s="232"/>
+      <c r="D79" s="232"/>
+      <c r="E79" s="232"/>
+      <c r="F79" s="233"/>
       <c r="G79" s="33" t="s">
         <v>160</v>
       </c>
@@ -6813,17 +6788,17 @@
       <c r="J79" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="K79" s="246"/>
-      <c r="L79" s="221"/>
+      <c r="K79" s="244"/>
+      <c r="L79" s="219"/>
       <c r="M79" s="12"/>
     </row>
     <row r="80" spans="1:13" ht="39.6" customHeight="1">
-      <c r="A80" s="294"/>
-      <c r="B80" s="234"/>
-      <c r="C80" s="234"/>
-      <c r="D80" s="234"/>
-      <c r="E80" s="234"/>
-      <c r="F80" s="235"/>
+      <c r="A80" s="292"/>
+      <c r="B80" s="232"/>
+      <c r="C80" s="232"/>
+      <c r="D80" s="232"/>
+      <c r="E80" s="232"/>
+      <c r="F80" s="233"/>
       <c r="G80" s="31" t="s">
         <v>162</v>
       </c>
@@ -6836,17 +6811,17 @@
       <c r="J80" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="K80" s="246"/>
-      <c r="L80" s="221"/>
+      <c r="K80" s="244"/>
+      <c r="L80" s="219"/>
       <c r="M80" s="12"/>
     </row>
     <row r="81" spans="1:13" ht="87.6" customHeight="1">
-      <c r="A81" s="294"/>
-      <c r="B81" s="220"/>
-      <c r="C81" s="234"/>
-      <c r="D81" s="234"/>
-      <c r="E81" s="234"/>
-      <c r="F81" s="235"/>
+      <c r="A81" s="292"/>
+      <c r="B81" s="218"/>
+      <c r="C81" s="232"/>
+      <c r="D81" s="232"/>
+      <c r="E81" s="232"/>
+      <c r="F81" s="233"/>
       <c r="G81" s="31" t="s">
         <v>163</v>
       </c>
@@ -6859,25 +6834,25 @@
       <c r="J81" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K81" s="246"/>
-      <c r="L81" s="221"/>
+      <c r="K81" s="244"/>
+      <c r="L81" s="219"/>
       <c r="M81" s="12"/>
     </row>
     <row r="82" spans="1:13" ht="76.5" customHeight="1">
-      <c r="A82" s="221">
+      <c r="A82" s="219">
         <v>25</v>
       </c>
-      <c r="B82" s="234">
+      <c r="B82" s="232">
         <v>45850</v>
       </c>
-      <c r="C82" s="234"/>
-      <c r="D82" s="234" t="s">
+      <c r="C82" s="232"/>
+      <c r="D82" s="232" t="s">
         <v>165</v>
       </c>
-      <c r="E82" s="234" t="s">
+      <c r="E82" s="232" t="s">
         <v>27</v>
       </c>
-      <c r="F82" s="235" t="s">
+      <c r="F82" s="233" t="s">
         <v>166</v>
       </c>
       <c r="G82" s="31" t="s">
@@ -6892,21 +6867,21 @@
       <c r="J82" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K82" s="232" t="s">
+      <c r="K82" s="230" t="s">
         <v>22</v>
       </c>
-      <c r="L82" s="221" t="s">
+      <c r="L82" s="219" t="s">
         <v>22</v>
       </c>
       <c r="M82" s="12"/>
     </row>
     <row r="83" spans="1:13" ht="76.5" customHeight="1">
-      <c r="A83" s="221"/>
-      <c r="B83" s="234"/>
-      <c r="C83" s="234"/>
-      <c r="D83" s="234"/>
-      <c r="E83" s="234"/>
-      <c r="F83" s="235"/>
+      <c r="A83" s="219"/>
+      <c r="B83" s="232"/>
+      <c r="C83" s="232"/>
+      <c r="D83" s="232"/>
+      <c r="E83" s="232"/>
+      <c r="F83" s="233"/>
       <c r="G83" s="31" t="s">
         <v>169</v>
       </c>
@@ -6919,17 +6894,17 @@
       <c r="J83" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K83" s="232"/>
-      <c r="L83" s="221"/>
+      <c r="K83" s="230"/>
+      <c r="L83" s="219"/>
       <c r="M83" s="12"/>
     </row>
     <row r="84" spans="1:13" ht="76.5" customHeight="1">
-      <c r="A84" s="221"/>
-      <c r="B84" s="220"/>
-      <c r="C84" s="234"/>
-      <c r="D84" s="234"/>
-      <c r="E84" s="234"/>
-      <c r="F84" s="235"/>
+      <c r="A84" s="219"/>
+      <c r="B84" s="218"/>
+      <c r="C84" s="232"/>
+      <c r="D84" s="232"/>
+      <c r="E84" s="232"/>
+      <c r="F84" s="233"/>
       <c r="G84" s="31" t="s">
         <v>171</v>
       </c>
@@ -6942,25 +6917,25 @@
       <c r="J84" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K84" s="232"/>
-      <c r="L84" s="221"/>
+      <c r="K84" s="230"/>
+      <c r="L84" s="219"/>
       <c r="M84" s="12"/>
     </row>
     <row r="85" spans="1:13" ht="84.75" customHeight="1">
-      <c r="A85" s="221">
+      <c r="A85" s="219">
         <v>26</v>
       </c>
-      <c r="B85" s="234">
+      <c r="B85" s="232">
         <v>45856</v>
       </c>
-      <c r="C85" s="234"/>
-      <c r="D85" s="234" t="s">
+      <c r="C85" s="232"/>
+      <c r="D85" s="232" t="s">
         <v>172</v>
       </c>
-      <c r="E85" s="234" t="s">
+      <c r="E85" s="232" t="s">
         <v>27</v>
       </c>
-      <c r="F85" s="235" t="s">
+      <c r="F85" s="233" t="s">
         <v>173</v>
       </c>
       <c r="G85" s="31" t="s">
@@ -6975,21 +6950,21 @@
       <c r="J85" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="K85" s="246" t="s">
+      <c r="K85" s="244" t="s">
         <v>22</v>
       </c>
-      <c r="L85" s="221" t="s">
+      <c r="L85" s="219" t="s">
         <v>22</v>
       </c>
       <c r="M85" s="12"/>
     </row>
     <row r="86" spans="1:13" ht="84.75" customHeight="1">
-      <c r="A86" s="221"/>
-      <c r="B86" s="220"/>
-      <c r="C86" s="234"/>
-      <c r="D86" s="234"/>
-      <c r="E86" s="234"/>
-      <c r="F86" s="235"/>
+      <c r="A86" s="219"/>
+      <c r="B86" s="218"/>
+      <c r="C86" s="232"/>
+      <c r="D86" s="232"/>
+      <c r="E86" s="232"/>
+      <c r="F86" s="233"/>
       <c r="G86" s="36" t="s">
         <v>171</v>
       </c>
@@ -7002,67 +6977,67 @@
       <c r="J86" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="K86" s="246"/>
-      <c r="L86" s="221"/>
+      <c r="K86" s="244"/>
+      <c r="L86" s="219"/>
       <c r="M86" s="12"/>
     </row>
     <row r="87" spans="1:13" ht="76.5" customHeight="1">
-      <c r="A87" s="221">
+      <c r="A87" s="219">
         <v>27</v>
       </c>
-      <c r="B87" s="269">
+      <c r="B87" s="267">
         <v>45860</v>
       </c>
-      <c r="C87" s="234"/>
-      <c r="D87" s="306" t="s">
+      <c r="C87" s="232"/>
+      <c r="D87" s="304" t="s">
         <v>175</v>
       </c>
-      <c r="E87" s="234" t="s">
+      <c r="E87" s="232" t="s">
         <v>27</v>
       </c>
-      <c r="F87" s="305" t="s">
+      <c r="F87" s="303" t="s">
         <v>176</v>
       </c>
-      <c r="G87" s="260" t="s">
+      <c r="G87" s="258" t="s">
         <v>177</v>
       </c>
-      <c r="H87" s="261" t="s">
+      <c r="H87" s="259" t="s">
         <v>30</v>
       </c>
-      <c r="I87" s="259" t="s">
+      <c r="I87" s="257" t="s">
         <v>30</v>
       </c>
-      <c r="J87" s="248" t="s">
+      <c r="J87" s="246" t="s">
         <v>20</v>
       </c>
-      <c r="K87" s="250" t="s">
+      <c r="K87" s="248" t="s">
         <v>178</v>
       </c>
-      <c r="L87" s="221"/>
+      <c r="L87" s="219"/>
       <c r="M87" s="12"/>
     </row>
     <row r="88" spans="1:13" ht="76.5" customHeight="1">
-      <c r="A88" s="221"/>
-      <c r="B88" s="269"/>
-      <c r="C88" s="234"/>
-      <c r="D88" s="234"/>
-      <c r="E88" s="234"/>
-      <c r="F88" s="305"/>
-      <c r="G88" s="260"/>
-      <c r="H88" s="261"/>
-      <c r="I88" s="259"/>
-      <c r="J88" s="248"/>
-      <c r="K88" s="250"/>
-      <c r="L88" s="221"/>
+      <c r="A88" s="219"/>
+      <c r="B88" s="267"/>
+      <c r="C88" s="232"/>
+      <c r="D88" s="232"/>
+      <c r="E88" s="232"/>
+      <c r="F88" s="303"/>
+      <c r="G88" s="258"/>
+      <c r="H88" s="259"/>
+      <c r="I88" s="257"/>
+      <c r="J88" s="246"/>
+      <c r="K88" s="248"/>
+      <c r="L88" s="219"/>
       <c r="M88" s="12"/>
     </row>
     <row r="89" spans="1:13" ht="76.5" customHeight="1">
-      <c r="A89" s="221"/>
-      <c r="B89" s="269"/>
-      <c r="C89" s="234"/>
-      <c r="D89" s="234"/>
-      <c r="E89" s="234"/>
-      <c r="F89" s="305"/>
+      <c r="A89" s="219"/>
+      <c r="B89" s="267"/>
+      <c r="C89" s="232"/>
+      <c r="D89" s="232"/>
+      <c r="E89" s="232"/>
+      <c r="F89" s="303"/>
       <c r="G89" s="130" t="s">
         <v>179</v>
       </c>
@@ -7073,45 +7048,45 @@
       <c r="J89" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="K89" s="250"/>
-      <c r="L89" s="221"/>
+      <c r="K89" s="248"/>
+      <c r="L89" s="219"/>
       <c r="M89" s="12"/>
     </row>
     <row r="90" spans="1:13" ht="76.5" customHeight="1">
-      <c r="A90" s="221">
+      <c r="A90" s="219">
         <v>28</v>
       </c>
-      <c r="B90" s="234">
+      <c r="B90" s="232">
         <v>45870</v>
       </c>
-      <c r="C90" s="234" t="s">
+      <c r="C90" s="232" t="s">
         <v>125</v>
       </c>
-      <c r="D90" s="234" t="s">
+      <c r="D90" s="232" t="s">
         <v>181</v>
       </c>
-      <c r="E90" s="234" t="s">
+      <c r="E90" s="232" t="s">
         <v>182</v>
       </c>
-      <c r="F90" s="235" t="s">
+      <c r="F90" s="233" t="s">
         <v>183</v>
       </c>
-      <c r="G90" s="279" t="s">
+      <c r="G90" s="277" t="s">
         <v>184</v>
       </c>
-      <c r="H90" s="252" t="s">
+      <c r="H90" s="250" t="s">
         <v>180</v>
       </c>
-      <c r="I90" s="272">
+      <c r="I90" s="270">
         <v>45900</v>
       </c>
-      <c r="J90" s="273" t="s">
+      <c r="J90" s="271" t="s">
         <v>20</v>
       </c>
-      <c r="K90" s="257" t="s">
+      <c r="K90" s="255" t="s">
         <v>20</v>
       </c>
-      <c r="L90" s="221" t="s">
+      <c r="L90" s="219" t="s">
         <v>20</v>
       </c>
       <c r="M90" s="12" t="s">
@@ -7119,37 +7094,37 @@
       </c>
     </row>
     <row r="91" spans="1:13" ht="76.5" customHeight="1">
-      <c r="A91" s="221"/>
-      <c r="B91" s="234"/>
-      <c r="C91" s="234"/>
-      <c r="D91" s="234"/>
-      <c r="E91" s="234"/>
-      <c r="F91" s="235"/>
-      <c r="G91" s="280"/>
-      <c r="H91" s="253"/>
-      <c r="I91" s="273"/>
-      <c r="J91" s="273"/>
-      <c r="K91" s="257"/>
-      <c r="L91" s="221"/>
+      <c r="A91" s="219"/>
+      <c r="B91" s="232"/>
+      <c r="C91" s="232"/>
+      <c r="D91" s="232"/>
+      <c r="E91" s="232"/>
+      <c r="F91" s="233"/>
+      <c r="G91" s="278"/>
+      <c r="H91" s="251"/>
+      <c r="I91" s="271"/>
+      <c r="J91" s="271"/>
+      <c r="K91" s="255"/>
+      <c r="L91" s="219"/>
       <c r="M91" s="12"/>
     </row>
     <row r="92" spans="1:13" ht="66" customHeight="1">
-      <c r="A92" s="221">
+      <c r="A92" s="219">
         <v>29</v>
       </c>
-      <c r="B92" s="234">
+      <c r="B92" s="232">
         <v>45879</v>
       </c>
-      <c r="C92" s="234" t="s">
+      <c r="C92" s="232" t="s">
         <v>125</v>
       </c>
-      <c r="D92" s="234" t="s">
+      <c r="D92" s="232" t="s">
         <v>186</v>
       </c>
-      <c r="E92" s="234" t="s">
+      <c r="E92" s="232" t="s">
         <v>182</v>
       </c>
-      <c r="F92" s="235" t="s">
+      <c r="F92" s="233" t="s">
         <v>187</v>
       </c>
       <c r="G92" s="131" t="s">
@@ -7164,10 +7139,10 @@
       <c r="J92" s="74" t="s">
         <v>20</v>
       </c>
-      <c r="K92" s="258" t="s">
+      <c r="K92" s="256" t="s">
         <v>20</v>
       </c>
-      <c r="L92" s="221" t="s">
+      <c r="L92" s="219" t="s">
         <v>20</v>
       </c>
       <c r="M92" s="12" t="s">
@@ -7175,12 +7150,12 @@
       </c>
     </row>
     <row r="93" spans="1:13" ht="66" customHeight="1">
-      <c r="A93" s="221"/>
-      <c r="B93" s="234"/>
-      <c r="C93" s="234"/>
-      <c r="D93" s="234"/>
-      <c r="E93" s="234"/>
-      <c r="F93" s="235"/>
+      <c r="A93" s="219"/>
+      <c r="B93" s="232"/>
+      <c r="C93" s="232"/>
+      <c r="D93" s="232"/>
+      <c r="E93" s="232"/>
+      <c r="F93" s="233"/>
       <c r="G93" s="131" t="s">
         <v>190</v>
       </c>
@@ -7193,17 +7168,17 @@
       <c r="J93" s="74" t="s">
         <v>20</v>
       </c>
-      <c r="K93" s="258"/>
-      <c r="L93" s="221"/>
+      <c r="K93" s="256"/>
+      <c r="L93" s="219"/>
       <c r="M93" s="12"/>
     </row>
     <row r="94" spans="1:13" ht="66" customHeight="1">
-      <c r="A94" s="221"/>
-      <c r="B94" s="234"/>
-      <c r="C94" s="234"/>
-      <c r="D94" s="234"/>
-      <c r="E94" s="234"/>
-      <c r="F94" s="235"/>
+      <c r="A94" s="219"/>
+      <c r="B94" s="232"/>
+      <c r="C94" s="232"/>
+      <c r="D94" s="232"/>
+      <c r="E94" s="232"/>
+      <c r="F94" s="233"/>
       <c r="G94" s="132" t="s">
         <v>192</v>
       </c>
@@ -7216,17 +7191,17 @@
       <c r="J94" s="77" t="s">
         <v>20</v>
       </c>
-      <c r="K94" s="258"/>
-      <c r="L94" s="221"/>
+      <c r="K94" s="256"/>
+      <c r="L94" s="219"/>
       <c r="M94" s="12"/>
     </row>
     <row r="95" spans="1:13" ht="66" customHeight="1">
-      <c r="A95" s="221"/>
-      <c r="B95" s="234"/>
-      <c r="C95" s="234"/>
-      <c r="D95" s="234"/>
-      <c r="E95" s="234"/>
-      <c r="F95" s="235"/>
+      <c r="A95" s="219"/>
+      <c r="B95" s="232"/>
+      <c r="C95" s="232"/>
+      <c r="D95" s="232"/>
+      <c r="E95" s="232"/>
+      <c r="F95" s="233"/>
       <c r="G95" s="132" t="s">
         <v>193</v>
       </c>
@@ -7239,17 +7214,17 @@
       <c r="J95" s="77" t="s">
         <v>20</v>
       </c>
-      <c r="K95" s="258"/>
-      <c r="L95" s="221"/>
+      <c r="K95" s="256"/>
+      <c r="L95" s="219"/>
       <c r="M95" s="12"/>
     </row>
     <row r="96" spans="1:13" ht="66" customHeight="1">
-      <c r="A96" s="221"/>
-      <c r="B96" s="234"/>
-      <c r="C96" s="234"/>
-      <c r="D96" s="234"/>
-      <c r="E96" s="234"/>
-      <c r="F96" s="235"/>
+      <c r="A96" s="219"/>
+      <c r="B96" s="232"/>
+      <c r="C96" s="232"/>
+      <c r="D96" s="232"/>
+      <c r="E96" s="232"/>
+      <c r="F96" s="233"/>
       <c r="G96" s="132" t="s">
         <v>194</v>
       </c>
@@ -7262,17 +7237,17 @@
       <c r="J96" s="77" t="s">
         <v>20</v>
       </c>
-      <c r="K96" s="258"/>
-      <c r="L96" s="221"/>
+      <c r="K96" s="256"/>
+      <c r="L96" s="219"/>
       <c r="M96" s="12"/>
     </row>
     <row r="97" spans="1:13" ht="66" customHeight="1">
-      <c r="A97" s="221"/>
-      <c r="B97" s="234"/>
-      <c r="C97" s="234"/>
-      <c r="D97" s="234"/>
-      <c r="E97" s="234"/>
-      <c r="F97" s="235"/>
+      <c r="A97" s="219"/>
+      <c r="B97" s="232"/>
+      <c r="C97" s="232"/>
+      <c r="D97" s="232"/>
+      <c r="E97" s="232"/>
+      <c r="F97" s="233"/>
       <c r="G97" s="132" t="s">
         <v>195</v>
       </c>
@@ -7285,201 +7260,201 @@
       <c r="J97" s="79" t="s">
         <v>196</v>
       </c>
-      <c r="K97" s="258"/>
-      <c r="L97" s="221"/>
+      <c r="K97" s="256"/>
+      <c r="L97" s="219"/>
       <c r="M97" s="12"/>
     </row>
     <row r="98" spans="1:13" ht="76.5" customHeight="1">
-      <c r="A98" s="221">
+      <c r="A98" s="219">
         <v>30</v>
       </c>
-      <c r="B98" s="234">
+      <c r="B98" s="232">
         <v>45885</v>
       </c>
-      <c r="C98" s="234" t="s">
+      <c r="C98" s="232" t="s">
         <v>197</v>
       </c>
-      <c r="D98" s="234" t="s">
+      <c r="D98" s="232" t="s">
         <v>198</v>
       </c>
-      <c r="E98" s="234" t="s">
+      <c r="E98" s="232" t="s">
         <v>199</v>
       </c>
-      <c r="F98" s="235" t="s">
+      <c r="F98" s="233" t="s">
         <v>200</v>
       </c>
       <c r="G98" s="132" t="s">
         <v>201</v>
       </c>
-      <c r="H98" s="271" t="s">
+      <c r="H98" s="269" t="s">
         <v>202</v>
       </c>
-      <c r="I98" s="270">
+      <c r="I98" s="268">
         <v>45886</v>
       </c>
-      <c r="J98" s="249" t="s">
+      <c r="J98" s="247" t="s">
         <v>20</v>
       </c>
-      <c r="K98" s="245" t="s">
+      <c r="K98" s="243" t="s">
         <v>178</v>
       </c>
-      <c r="L98" s="221" t="s">
+      <c r="L98" s="219" t="s">
         <v>178</v>
       </c>
       <c r="M98" s="12"/>
     </row>
     <row r="99" spans="1:13" ht="76.5" customHeight="1">
-      <c r="A99" s="221"/>
-      <c r="B99" s="234"/>
-      <c r="C99" s="234"/>
-      <c r="D99" s="234"/>
-      <c r="E99" s="234"/>
-      <c r="F99" s="235"/>
+      <c r="A99" s="219"/>
+      <c r="B99" s="232"/>
+      <c r="C99" s="232"/>
+      <c r="D99" s="232"/>
+      <c r="E99" s="232"/>
+      <c r="F99" s="233"/>
       <c r="G99" s="132" t="s">
         <v>203</v>
       </c>
-      <c r="H99" s="271"/>
-      <c r="I99" s="271"/>
-      <c r="J99" s="249"/>
-      <c r="K99" s="245"/>
-      <c r="L99" s="221"/>
+      <c r="H99" s="269"/>
+      <c r="I99" s="269"/>
+      <c r="J99" s="247"/>
+      <c r="K99" s="243"/>
+      <c r="L99" s="219"/>
       <c r="M99" s="12"/>
     </row>
     <row r="100" spans="1:13" ht="76.5" customHeight="1">
-      <c r="A100" s="221"/>
-      <c r="B100" s="234"/>
-      <c r="C100" s="234"/>
-      <c r="D100" s="234"/>
-      <c r="E100" s="234"/>
-      <c r="F100" s="235"/>
+      <c r="A100" s="219"/>
+      <c r="B100" s="232"/>
+      <c r="C100" s="232"/>
+      <c r="D100" s="232"/>
+      <c r="E100" s="232"/>
+      <c r="F100" s="233"/>
       <c r="G100" s="132" t="s">
         <v>204</v>
       </c>
-      <c r="H100" s="271"/>
-      <c r="I100" s="271"/>
-      <c r="J100" s="249"/>
-      <c r="K100" s="245"/>
-      <c r="L100" s="221"/>
+      <c r="H100" s="269"/>
+      <c r="I100" s="269"/>
+      <c r="J100" s="247"/>
+      <c r="K100" s="243"/>
+      <c r="L100" s="219"/>
       <c r="M100" s="12"/>
     </row>
     <row r="101" spans="1:13" ht="76.5" customHeight="1">
-      <c r="A101" s="221"/>
-      <c r="B101" s="234"/>
-      <c r="C101" s="234"/>
-      <c r="D101" s="234"/>
-      <c r="E101" s="234"/>
-      <c r="F101" s="235"/>
+      <c r="A101" s="219"/>
+      <c r="B101" s="232"/>
+      <c r="C101" s="232"/>
+      <c r="D101" s="232"/>
+      <c r="E101" s="232"/>
+      <c r="F101" s="233"/>
       <c r="G101" s="132" t="s">
         <v>205</v>
       </c>
-      <c r="H101" s="271"/>
-      <c r="I101" s="271"/>
-      <c r="J101" s="249"/>
-      <c r="K101" s="245"/>
-      <c r="L101" s="221"/>
+      <c r="H101" s="269"/>
+      <c r="I101" s="269"/>
+      <c r="J101" s="247"/>
+      <c r="K101" s="243"/>
+      <c r="L101" s="219"/>
       <c r="M101" s="12"/>
     </row>
     <row r="102" spans="1:13" ht="76.5" customHeight="1">
-      <c r="A102" s="221"/>
-      <c r="B102" s="234"/>
-      <c r="C102" s="234"/>
-      <c r="D102" s="234"/>
-      <c r="E102" s="234"/>
-      <c r="F102" s="235"/>
+      <c r="A102" s="219"/>
+      <c r="B102" s="232"/>
+      <c r="C102" s="232"/>
+      <c r="D102" s="232"/>
+      <c r="E102" s="232"/>
+      <c r="F102" s="233"/>
       <c r="G102" s="132" t="s">
         <v>206</v>
       </c>
-      <c r="H102" s="271"/>
-      <c r="I102" s="271"/>
-      <c r="J102" s="249"/>
-      <c r="K102" s="245"/>
-      <c r="L102" s="221"/>
+      <c r="H102" s="269"/>
+      <c r="I102" s="269"/>
+      <c r="J102" s="247"/>
+      <c r="K102" s="243"/>
+      <c r="L102" s="219"/>
       <c r="M102" s="12"/>
     </row>
     <row r="103" spans="1:13" ht="76.5" customHeight="1">
-      <c r="A103" s="221"/>
-      <c r="B103" s="234"/>
-      <c r="C103" s="234"/>
-      <c r="D103" s="234"/>
-      <c r="E103" s="234"/>
-      <c r="F103" s="235"/>
+      <c r="A103" s="219"/>
+      <c r="B103" s="232"/>
+      <c r="C103" s="232"/>
+      <c r="D103" s="232"/>
+      <c r="E103" s="232"/>
+      <c r="F103" s="233"/>
       <c r="G103" s="132" t="s">
         <v>207</v>
       </c>
-      <c r="H103" s="271"/>
-      <c r="I103" s="271"/>
-      <c r="J103" s="249"/>
-      <c r="K103" s="245"/>
-      <c r="L103" s="221"/>
+      <c r="H103" s="269"/>
+      <c r="I103" s="269"/>
+      <c r="J103" s="247"/>
+      <c r="K103" s="243"/>
+      <c r="L103" s="219"/>
       <c r="M103" s="12"/>
     </row>
     <row r="104" spans="1:13" ht="97.5" customHeight="1">
-      <c r="A104" s="221">
+      <c r="A104" s="219">
         <v>31</v>
       </c>
-      <c r="B104" s="234">
+      <c r="B104" s="232">
         <v>45887</v>
       </c>
-      <c r="C104" s="234"/>
-      <c r="D104" s="234" t="s">
+      <c r="C104" s="232"/>
+      <c r="D104" s="232" t="s">
         <v>208</v>
       </c>
-      <c r="E104" s="234" t="s">
+      <c r="E104" s="232" t="s">
         <v>209</v>
       </c>
-      <c r="F104" s="235" t="s">
+      <c r="F104" s="233" t="s">
         <v>210</v>
       </c>
-      <c r="G104" s="255" t="s">
+      <c r="G104" s="253" t="s">
         <v>211</v>
       </c>
-      <c r="H104" s="256" t="s">
+      <c r="H104" s="254" t="s">
         <v>30</v>
       </c>
-      <c r="I104" s="270" t="s">
+      <c r="I104" s="268" t="s">
         <v>30</v>
       </c>
-      <c r="J104" s="249" t="s">
+      <c r="J104" s="247" t="s">
         <v>20</v>
       </c>
-      <c r="K104" s="245" t="s">
+      <c r="K104" s="243" t="s">
         <v>178</v>
       </c>
-      <c r="L104" s="266" t="s">
+      <c r="L104" s="264" t="s">
         <v>212</v>
       </c>
       <c r="M104" s="12"/>
     </row>
     <row r="105" spans="1:13" ht="60" customHeight="1">
-      <c r="A105" s="221"/>
-      <c r="B105" s="220"/>
-      <c r="C105" s="234"/>
-      <c r="D105" s="234"/>
-      <c r="E105" s="234"/>
-      <c r="F105" s="235"/>
-      <c r="G105" s="255"/>
-      <c r="H105" s="256"/>
-      <c r="I105" s="270"/>
-      <c r="J105" s="249"/>
-      <c r="K105" s="245"/>
-      <c r="L105" s="266"/>
+      <c r="A105" s="219"/>
+      <c r="B105" s="218"/>
+      <c r="C105" s="232"/>
+      <c r="D105" s="232"/>
+      <c r="E105" s="232"/>
+      <c r="F105" s="233"/>
+      <c r="G105" s="253"/>
+      <c r="H105" s="254"/>
+      <c r="I105" s="268"/>
+      <c r="J105" s="247"/>
+      <c r="K105" s="243"/>
+      <c r="L105" s="264"/>
       <c r="M105" s="12"/>
     </row>
     <row r="106" spans="1:13" ht="113.25" customHeight="1">
-      <c r="A106" s="268">
+      <c r="A106" s="266">
         <v>32</v>
       </c>
-      <c r="B106" s="233">
+      <c r="B106" s="231">
         <v>45895</v>
       </c>
-      <c r="C106" s="233"/>
-      <c r="D106" s="233" t="s">
+      <c r="C106" s="231"/>
+      <c r="D106" s="231" t="s">
         <v>213</v>
       </c>
-      <c r="E106" s="221" t="s">
+      <c r="E106" s="219" t="s">
         <v>27</v>
       </c>
-      <c r="F106" s="235" t="s">
+      <c r="F106" s="233" t="s">
         <v>214</v>
       </c>
       <c r="G106" s="31" t="s">
@@ -7494,17 +7469,17 @@
       <c r="J106" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="K106" s="232"/>
-      <c r="L106" s="367"/>
+      <c r="K106" s="230"/>
+      <c r="L106" s="365"/>
       <c r="M106" s="12"/>
     </row>
     <row r="107" spans="1:13" ht="56.25" customHeight="1">
-      <c r="A107" s="268"/>
-      <c r="B107" s="233"/>
-      <c r="C107" s="233"/>
-      <c r="D107" s="233"/>
-      <c r="E107" s="221"/>
-      <c r="F107" s="254"/>
+      <c r="A107" s="266"/>
+      <c r="B107" s="231"/>
+      <c r="C107" s="231"/>
+      <c r="D107" s="231"/>
+      <c r="E107" s="219"/>
+      <c r="F107" s="252"/>
       <c r="G107" s="31" t="s">
         <v>217</v>
       </c>
@@ -7517,17 +7492,17 @@
       <c r="J107" s="78" t="s">
         <v>218</v>
       </c>
-      <c r="K107" s="232"/>
-      <c r="L107" s="367"/>
+      <c r="K107" s="230"/>
+      <c r="L107" s="365"/>
       <c r="M107" s="12"/>
     </row>
     <row r="108" spans="1:13" ht="81" customHeight="1">
-      <c r="A108" s="268"/>
-      <c r="B108" s="264"/>
-      <c r="C108" s="233"/>
-      <c r="D108" s="233"/>
-      <c r="E108" s="221"/>
-      <c r="F108" s="254"/>
+      <c r="A108" s="266"/>
+      <c r="B108" s="262"/>
+      <c r="C108" s="231"/>
+      <c r="D108" s="231"/>
+      <c r="E108" s="219"/>
+      <c r="F108" s="252"/>
       <c r="G108" s="31" t="s">
         <v>219</v>
       </c>
@@ -7540,17 +7515,17 @@
       <c r="J108" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K108" s="232"/>
-      <c r="L108" s="367"/>
+      <c r="K108" s="230"/>
+      <c r="L108" s="365"/>
       <c r="M108" s="12"/>
     </row>
     <row r="109" spans="1:13" ht="56.25" customHeight="1">
-      <c r="A109" s="268"/>
-      <c r="B109" s="264"/>
-      <c r="C109" s="233"/>
-      <c r="D109" s="233"/>
-      <c r="E109" s="221"/>
-      <c r="F109" s="274"/>
+      <c r="A109" s="266"/>
+      <c r="B109" s="262"/>
+      <c r="C109" s="231"/>
+      <c r="D109" s="231"/>
+      <c r="E109" s="219"/>
+      <c r="F109" s="272"/>
       <c r="G109" s="36" t="s">
         <v>221</v>
       </c>
@@ -7563,17 +7538,17 @@
       <c r="J109" s="78" t="s">
         <v>218</v>
       </c>
-      <c r="K109" s="232"/>
-      <c r="L109" s="367"/>
+      <c r="K109" s="230"/>
+      <c r="L109" s="365"/>
       <c r="M109" s="12"/>
     </row>
     <row r="110" spans="1:13" ht="56.25" customHeight="1">
-      <c r="A110" s="268"/>
-      <c r="B110" s="264"/>
-      <c r="C110" s="233"/>
-      <c r="D110" s="233"/>
-      <c r="E110" s="221"/>
-      <c r="F110" s="274"/>
+      <c r="A110" s="266"/>
+      <c r="B110" s="262"/>
+      <c r="C110" s="231"/>
+      <c r="D110" s="231"/>
+      <c r="E110" s="219"/>
+      <c r="F110" s="272"/>
       <c r="G110" s="31" t="s">
         <v>222</v>
       </c>
@@ -7586,27 +7561,27 @@
       <c r="J110" s="78" t="s">
         <v>218</v>
       </c>
-      <c r="K110" s="232"/>
-      <c r="L110" s="367"/>
+      <c r="K110" s="230"/>
+      <c r="L110" s="365"/>
       <c r="M110" s="12"/>
     </row>
     <row r="111" spans="1:13" ht="71.25" customHeight="1">
-      <c r="A111" s="268">
+      <c r="A111" s="266">
         <v>33</v>
       </c>
-      <c r="B111" s="233">
+      <c r="B111" s="231">
         <v>45900</v>
       </c>
-      <c r="C111" s="233" t="s">
+      <c r="C111" s="231" t="s">
         <v>125</v>
       </c>
-      <c r="D111" s="275" t="s">
+      <c r="D111" s="273" t="s">
         <v>223</v>
       </c>
-      <c r="E111" s="226" t="s">
+      <c r="E111" s="224" t="s">
         <v>182</v>
       </c>
-      <c r="F111" s="254" t="s">
+      <c r="F111" s="252" t="s">
         <v>224</v>
       </c>
       <c r="G111" s="31" t="s">
@@ -7621,10 +7596,10 @@
       <c r="J111" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="K111" s="240" t="s">
+      <c r="K111" s="238" t="s">
         <v>20</v>
       </c>
-      <c r="L111" s="221" t="s">
+      <c r="L111" s="219" t="s">
         <v>20</v>
       </c>
       <c r="M111" s="12" t="s">
@@ -7632,12 +7607,12 @@
       </c>
     </row>
     <row r="112" spans="1:13" ht="80.25" customHeight="1">
-      <c r="A112" s="268"/>
-      <c r="B112" s="264"/>
-      <c r="C112" s="233"/>
-      <c r="D112" s="234"/>
-      <c r="E112" s="221"/>
-      <c r="F112" s="254"/>
+      <c r="A112" s="266"/>
+      <c r="B112" s="262"/>
+      <c r="C112" s="231"/>
+      <c r="D112" s="232"/>
+      <c r="E112" s="219"/>
+      <c r="F112" s="252"/>
       <c r="G112" s="36" t="s">
         <v>227</v>
       </c>
@@ -7650,17 +7625,17 @@
       <c r="J112" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K112" s="240"/>
-      <c r="L112" s="221"/>
+      <c r="K112" s="238"/>
+      <c r="L112" s="219"/>
       <c r="M112" s="12"/>
     </row>
     <row r="113" spans="1:13" ht="96.75" customHeight="1">
-      <c r="A113" s="268"/>
-      <c r="B113" s="264"/>
-      <c r="C113" s="233"/>
-      <c r="D113" s="234"/>
-      <c r="E113" s="221"/>
-      <c r="F113" s="254"/>
+      <c r="A113" s="266"/>
+      <c r="B113" s="262"/>
+      <c r="C113" s="231"/>
+      <c r="D113" s="232"/>
+      <c r="E113" s="219"/>
+      <c r="F113" s="252"/>
       <c r="G113" s="36" t="s">
         <v>229</v>
       </c>
@@ -7673,17 +7648,17 @@
       <c r="J113" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K113" s="240"/>
-      <c r="L113" s="221"/>
+      <c r="K113" s="238"/>
+      <c r="L113" s="219"/>
       <c r="M113" s="12"/>
     </row>
     <row r="114" spans="1:13" ht="114.75" customHeight="1">
-      <c r="A114" s="268"/>
-      <c r="B114" s="264"/>
-      <c r="C114" s="233"/>
-      <c r="D114" s="234"/>
-      <c r="E114" s="221"/>
-      <c r="F114" s="254"/>
+      <c r="A114" s="266"/>
+      <c r="B114" s="262"/>
+      <c r="C114" s="231"/>
+      <c r="D114" s="232"/>
+      <c r="E114" s="219"/>
+      <c r="F114" s="252"/>
       <c r="G114" s="36" t="s">
         <v>231</v>
       </c>
@@ -7696,17 +7671,17 @@
       <c r="J114" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K114" s="240"/>
-      <c r="L114" s="221"/>
+      <c r="K114" s="238"/>
+      <c r="L114" s="219"/>
       <c r="M114" s="12"/>
     </row>
     <row r="115" spans="1:13" ht="87.75" customHeight="1">
-      <c r="A115" s="268"/>
-      <c r="B115" s="264"/>
-      <c r="C115" s="233"/>
-      <c r="D115" s="234"/>
-      <c r="E115" s="221"/>
-      <c r="F115" s="254"/>
+      <c r="A115" s="266"/>
+      <c r="B115" s="262"/>
+      <c r="C115" s="231"/>
+      <c r="D115" s="232"/>
+      <c r="E115" s="219"/>
+      <c r="F115" s="252"/>
       <c r="G115" s="36" t="s">
         <v>233</v>
       </c>
@@ -7719,27 +7694,27 @@
       <c r="J115" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K115" s="240"/>
-      <c r="L115" s="221"/>
+      <c r="K115" s="238"/>
+      <c r="L115" s="219"/>
       <c r="M115" s="12"/>
     </row>
     <row r="116" spans="1:13" ht="87.75" customHeight="1">
-      <c r="A116" s="268">
+      <c r="A116" s="266">
         <v>34</v>
       </c>
-      <c r="B116" s="233">
+      <c r="B116" s="231">
         <v>45906</v>
       </c>
-      <c r="C116" s="233" t="s">
+      <c r="C116" s="231" t="s">
         <v>32</v>
       </c>
-      <c r="D116" s="276" t="s">
+      <c r="D116" s="274" t="s">
         <v>235</v>
       </c>
-      <c r="E116" s="206" t="s">
+      <c r="E116" s="204" t="s">
         <v>78</v>
       </c>
-      <c r="F116" s="254" t="s">
+      <c r="F116" s="252" t="s">
         <v>236</v>
       </c>
       <c r="G116" s="36" t="s">
@@ -7754,19 +7729,19 @@
       <c r="J116" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K116" s="251" t="s">
+      <c r="K116" s="249" t="s">
         <v>239</v>
       </c>
-      <c r="L116" s="265"/>
+      <c r="L116" s="263"/>
       <c r="M116" s="12"/>
     </row>
     <row r="117" spans="1:13" ht="87.75" customHeight="1">
-      <c r="A117" s="268"/>
-      <c r="B117" s="264"/>
-      <c r="C117" s="233"/>
-      <c r="D117" s="276"/>
-      <c r="E117" s="207"/>
-      <c r="F117" s="254"/>
+      <c r="A117" s="266"/>
+      <c r="B117" s="262"/>
+      <c r="C117" s="231"/>
+      <c r="D117" s="274"/>
+      <c r="E117" s="205"/>
+      <c r="F117" s="252"/>
       <c r="G117" s="36" t="s">
         <v>240</v>
       </c>
@@ -7779,17 +7754,17 @@
       <c r="J117" s="76" t="s">
         <v>242</v>
       </c>
-      <c r="K117" s="251"/>
-      <c r="L117" s="265"/>
+      <c r="K117" s="249"/>
+      <c r="L117" s="263"/>
       <c r="M117" s="12"/>
     </row>
     <row r="118" spans="1:13" ht="87.75" customHeight="1">
-      <c r="A118" s="268"/>
-      <c r="B118" s="264"/>
-      <c r="C118" s="233"/>
-      <c r="D118" s="276"/>
-      <c r="E118" s="207"/>
-      <c r="F118" s="254"/>
+      <c r="A118" s="266"/>
+      <c r="B118" s="262"/>
+      <c r="C118" s="231"/>
+      <c r="D118" s="274"/>
+      <c r="E118" s="205"/>
+      <c r="F118" s="252"/>
       <c r="G118" s="36" t="s">
         <v>243</v>
       </c>
@@ -7802,17 +7777,17 @@
       <c r="J118" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K118" s="251"/>
-      <c r="L118" s="265"/>
+      <c r="K118" s="249"/>
+      <c r="L118" s="263"/>
       <c r="M118" s="12"/>
     </row>
     <row r="119" spans="1:13" ht="87.75" customHeight="1">
-      <c r="A119" s="268"/>
-      <c r="B119" s="264"/>
-      <c r="C119" s="233"/>
-      <c r="D119" s="276"/>
-      <c r="E119" s="207"/>
-      <c r="F119" s="254"/>
+      <c r="A119" s="266"/>
+      <c r="B119" s="262"/>
+      <c r="C119" s="231"/>
+      <c r="D119" s="274"/>
+      <c r="E119" s="205"/>
+      <c r="F119" s="252"/>
       <c r="G119" s="165" t="s">
         <v>244</v>
       </c>
@@ -7825,17 +7800,17 @@
       <c r="J119" s="76" t="s">
         <v>242</v>
       </c>
-      <c r="K119" s="251"/>
-      <c r="L119" s="265"/>
+      <c r="K119" s="249"/>
+      <c r="L119" s="263"/>
       <c r="M119" s="12"/>
     </row>
     <row r="120" spans="1:13" ht="87.75" customHeight="1">
-      <c r="A120" s="268"/>
-      <c r="B120" s="264"/>
-      <c r="C120" s="233"/>
-      <c r="D120" s="276"/>
-      <c r="E120" s="208"/>
-      <c r="F120" s="254"/>
+      <c r="A120" s="266"/>
+      <c r="B120" s="262"/>
+      <c r="C120" s="231"/>
+      <c r="D120" s="274"/>
+      <c r="E120" s="206"/>
+      <c r="F120" s="252"/>
       <c r="G120" s="36" t="s">
         <v>246</v>
       </c>
@@ -7848,25 +7823,25 @@
       <c r="J120" s="76" t="s">
         <v>242</v>
       </c>
-      <c r="K120" s="251"/>
-      <c r="L120" s="265"/>
+      <c r="K120" s="249"/>
+      <c r="L120" s="263"/>
       <c r="M120" s="12"/>
     </row>
     <row r="121" spans="1:13" ht="99.75" customHeight="1">
-      <c r="A121" s="226">
+      <c r="A121" s="224">
         <v>35</v>
       </c>
-      <c r="B121" s="234">
+      <c r="B121" s="232">
         <v>45911</v>
       </c>
-      <c r="C121" s="234"/>
-      <c r="D121" s="234" t="s">
+      <c r="C121" s="232"/>
+      <c r="D121" s="232" t="s">
         <v>247</v>
       </c>
-      <c r="E121" s="234" t="s">
+      <c r="E121" s="232" t="s">
         <v>27</v>
       </c>
-      <c r="F121" s="235" t="s">
+      <c r="F121" s="233" t="s">
         <v>248</v>
       </c>
       <c r="G121" s="44" t="s">
@@ -7881,19 +7856,19 @@
       <c r="J121" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K121" s="240" t="s">
+      <c r="K121" s="238" t="s">
         <v>239</v>
       </c>
-      <c r="L121" s="221"/>
+      <c r="L121" s="219"/>
       <c r="M121" s="12"/>
     </row>
     <row r="122" spans="1:13" ht="72" customHeight="1">
-      <c r="A122" s="226"/>
-      <c r="B122" s="220"/>
-      <c r="C122" s="234"/>
-      <c r="D122" s="234"/>
-      <c r="E122" s="234"/>
-      <c r="F122" s="235"/>
+      <c r="A122" s="224"/>
+      <c r="B122" s="218"/>
+      <c r="C122" s="232"/>
+      <c r="D122" s="232"/>
+      <c r="E122" s="232"/>
+      <c r="F122" s="233"/>
       <c r="G122" s="31" t="s">
         <v>219</v>
       </c>
@@ -7906,17 +7881,17 @@
       <c r="J122" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="K122" s="240"/>
-      <c r="L122" s="221"/>
+      <c r="K122" s="238"/>
+      <c r="L122" s="219"/>
       <c r="M122" s="12"/>
     </row>
     <row r="123" spans="1:13" ht="49.5" customHeight="1">
-      <c r="A123" s="226"/>
-      <c r="B123" s="220"/>
-      <c r="C123" s="234"/>
-      <c r="D123" s="234"/>
-      <c r="E123" s="234"/>
-      <c r="F123" s="235"/>
+      <c r="A123" s="224"/>
+      <c r="B123" s="218"/>
+      <c r="C123" s="232"/>
+      <c r="D123" s="232"/>
+      <c r="E123" s="232"/>
+      <c r="F123" s="233"/>
       <c r="G123" s="31" t="s">
         <v>250</v>
       </c>
@@ -7929,17 +7904,17 @@
       <c r="J123" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K123" s="240"/>
-      <c r="L123" s="221"/>
+      <c r="K123" s="238"/>
+      <c r="L123" s="219"/>
       <c r="M123" s="12"/>
     </row>
     <row r="124" spans="1:13" ht="71.25" customHeight="1">
-      <c r="A124" s="226"/>
-      <c r="B124" s="220"/>
-      <c r="C124" s="234"/>
-      <c r="D124" s="234"/>
-      <c r="E124" s="234"/>
-      <c r="F124" s="235"/>
+      <c r="A124" s="224"/>
+      <c r="B124" s="218"/>
+      <c r="C124" s="232"/>
+      <c r="D124" s="232"/>
+      <c r="E124" s="232"/>
+      <c r="F124" s="233"/>
       <c r="G124" s="31" t="s">
         <v>252</v>
       </c>
@@ -7952,25 +7927,25 @@
       <c r="J124" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K124" s="240"/>
-      <c r="L124" s="221"/>
+      <c r="K124" s="238"/>
+      <c r="L124" s="219"/>
       <c r="M124" s="12"/>
     </row>
     <row r="125" spans="1:13" ht="66.75" customHeight="1">
-      <c r="A125" s="226">
+      <c r="A125" s="224">
         <v>36</v>
       </c>
-      <c r="B125" s="234">
+      <c r="B125" s="232">
         <v>45917</v>
       </c>
-      <c r="C125" s="220"/>
-      <c r="D125" s="220" t="s">
+      <c r="C125" s="218"/>
+      <c r="D125" s="218" t="s">
         <v>253</v>
       </c>
-      <c r="E125" s="300" t="s">
+      <c r="E125" s="298" t="s">
         <v>47</v>
       </c>
-      <c r="F125" s="235" t="s">
+      <c r="F125" s="233" t="s">
         <v>254</v>
       </c>
       <c r="G125" s="36" t="s">
@@ -7985,21 +7960,21 @@
       <c r="J125" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="K125" s="240" t="s">
+      <c r="K125" s="238" t="s">
         <v>239</v>
       </c>
-      <c r="L125" s="221" t="s">
+      <c r="L125" s="219" t="s">
         <v>22</v>
       </c>
       <c r="M125" s="12"/>
     </row>
     <row r="126" spans="1:13" ht="66.75" customHeight="1">
-      <c r="A126" s="226"/>
-      <c r="B126" s="234"/>
-      <c r="C126" s="220"/>
-      <c r="D126" s="220"/>
-      <c r="E126" s="300"/>
-      <c r="F126" s="235"/>
+      <c r="A126" s="224"/>
+      <c r="B126" s="232"/>
+      <c r="C126" s="218"/>
+      <c r="D126" s="218"/>
+      <c r="E126" s="298"/>
+      <c r="F126" s="233"/>
       <c r="G126" s="36" t="s">
         <v>256</v>
       </c>
@@ -8012,17 +7987,17 @@
       <c r="J126" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="K126" s="240"/>
-      <c r="L126" s="221"/>
+      <c r="K126" s="238"/>
+      <c r="L126" s="219"/>
       <c r="M126" s="12"/>
     </row>
     <row r="127" spans="1:13" ht="66.75" customHeight="1">
-      <c r="A127" s="226"/>
-      <c r="B127" s="220"/>
-      <c r="C127" s="220"/>
-      <c r="D127" s="220"/>
-      <c r="E127" s="300"/>
-      <c r="F127" s="235"/>
+      <c r="A127" s="224"/>
+      <c r="B127" s="218"/>
+      <c r="C127" s="218"/>
+      <c r="D127" s="218"/>
+      <c r="E127" s="298"/>
+      <c r="F127" s="233"/>
       <c r="G127" s="36" t="s">
         <v>258</v>
       </c>
@@ -8035,8 +8010,8 @@
       <c r="J127" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K127" s="240"/>
-      <c r="L127" s="221"/>
+      <c r="K127" s="238"/>
+      <c r="L127" s="219"/>
       <c r="M127" s="12"/>
     </row>
     <row r="128" spans="1:13" ht="92.1" customHeight="1">
@@ -8079,72 +8054,72 @@
       <c r="M128" s="12"/>
     </row>
     <row r="129" spans="1:13" ht="112.5" customHeight="1">
-      <c r="A129" s="226">
+      <c r="A129" s="224">
         <v>38</v>
       </c>
-      <c r="B129" s="234">
+      <c r="B129" s="232">
         <v>45932</v>
       </c>
-      <c r="C129" s="234" t="s">
+      <c r="C129" s="232" t="s">
         <v>261</v>
       </c>
-      <c r="D129" s="234" t="s">
+      <c r="D129" s="232" t="s">
         <v>262</v>
       </c>
-      <c r="E129" s="234" t="s">
+      <c r="E129" s="232" t="s">
         <v>27</v>
       </c>
-      <c r="F129" s="235" t="s">
+      <c r="F129" s="233" t="s">
         <v>263</v>
       </c>
-      <c r="G129" s="307" t="s">
+      <c r="G129" s="305" t="s">
         <v>29</v>
       </c>
-      <c r="H129" s="256" t="s">
+      <c r="H129" s="254" t="s">
         <v>30</v>
       </c>
-      <c r="I129" s="308" t="s">
+      <c r="I129" s="306" t="s">
         <v>31</v>
       </c>
-      <c r="J129" s="282" t="s">
+      <c r="J129" s="280" t="s">
         <v>264</v>
       </c>
-      <c r="K129" s="245"/>
-      <c r="L129" s="221"/>
+      <c r="K129" s="243"/>
+      <c r="L129" s="219"/>
       <c r="M129" s="12"/>
     </row>
     <row r="130" spans="1:13" ht="58.5" customHeight="1">
-      <c r="A130" s="226"/>
-      <c r="B130" s="266"/>
-      <c r="C130" s="234"/>
-      <c r="D130" s="234"/>
-      <c r="E130" s="234"/>
-      <c r="F130" s="235"/>
-      <c r="G130" s="307"/>
-      <c r="H130" s="256"/>
-      <c r="I130" s="270"/>
-      <c r="J130" s="249"/>
-      <c r="K130" s="245"/>
-      <c r="L130" s="221"/>
+      <c r="A130" s="224"/>
+      <c r="B130" s="264"/>
+      <c r="C130" s="232"/>
+      <c r="D130" s="232"/>
+      <c r="E130" s="232"/>
+      <c r="F130" s="233"/>
+      <c r="G130" s="305"/>
+      <c r="H130" s="254"/>
+      <c r="I130" s="268"/>
+      <c r="J130" s="247"/>
+      <c r="K130" s="243"/>
+      <c r="L130" s="219"/>
       <c r="M130" s="12"/>
     </row>
     <row r="131" spans="1:13" ht="96" customHeight="1">
-      <c r="A131" s="267">
+      <c r="A131" s="265">
         <v>39</v>
       </c>
-      <c r="B131" s="233">
+      <c r="B131" s="231">
         <v>45948</v>
       </c>
-      <c r="C131" s="233" t="s">
+      <c r="C131" s="231" t="s">
         <v>265</v>
       </c>
-      <c r="D131" s="234" t="s">
+      <c r="D131" s="232" t="s">
         <v>266</v>
       </c>
-      <c r="E131" s="234" t="s">
+      <c r="E131" s="232" t="s">
         <v>27</v>
       </c>
-      <c r="F131" s="235" t="s">
+      <c r="F131" s="233" t="s">
         <v>267</v>
       </c>
       <c r="G131" s="45" t="s">
@@ -8159,21 +8134,21 @@
       <c r="J131" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K131" s="251" t="s">
+      <c r="K131" s="249" t="s">
         <v>239</v>
       </c>
-      <c r="L131" s="221" t="s">
+      <c r="L131" s="219" t="s">
         <v>22</v>
       </c>
       <c r="M131" s="12"/>
     </row>
     <row r="132" spans="1:13" ht="71.25" customHeight="1">
-      <c r="A132" s="267"/>
-      <c r="B132" s="233"/>
-      <c r="C132" s="233"/>
-      <c r="D132" s="234"/>
-      <c r="E132" s="234"/>
-      <c r="F132" s="235"/>
+      <c r="A132" s="265"/>
+      <c r="B132" s="231"/>
+      <c r="C132" s="231"/>
+      <c r="D132" s="232"/>
+      <c r="E132" s="232"/>
+      <c r="F132" s="233"/>
       <c r="G132" s="31" t="s">
         <v>270</v>
       </c>
@@ -8186,17 +8161,17 @@
       <c r="J132" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K132" s="251"/>
-      <c r="L132" s="221"/>
+      <c r="K132" s="249"/>
+      <c r="L132" s="219"/>
       <c r="M132" s="12"/>
     </row>
     <row r="133" spans="1:13" ht="71.25" customHeight="1">
-      <c r="A133" s="267"/>
-      <c r="B133" s="264"/>
-      <c r="C133" s="233"/>
-      <c r="D133" s="234"/>
-      <c r="E133" s="234"/>
-      <c r="F133" s="235"/>
+      <c r="A133" s="265"/>
+      <c r="B133" s="262"/>
+      <c r="C133" s="231"/>
+      <c r="D133" s="232"/>
+      <c r="E133" s="232"/>
+      <c r="F133" s="233"/>
       <c r="G133" s="31" t="s">
         <v>271</v>
       </c>
@@ -8209,8 +8184,8 @@
       <c r="J133" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="K133" s="251"/>
-      <c r="L133" s="221"/>
+      <c r="K133" s="249"/>
+      <c r="L133" s="219"/>
       <c r="M133" s="12"/>
     </row>
     <row r="134" spans="1:13" ht="145.5" customHeight="1">
@@ -8247,20 +8222,20 @@
       </c>
     </row>
     <row r="135" spans="1:13" ht="101.25" customHeight="1">
-      <c r="A135" s="226">
+      <c r="A135" s="224">
         <v>41</v>
       </c>
-      <c r="B135" s="234">
+      <c r="B135" s="232">
         <v>45952</v>
       </c>
-      <c r="C135" s="234"/>
-      <c r="D135" s="234" t="s">
+      <c r="C135" s="232"/>
+      <c r="D135" s="232" t="s">
         <v>276</v>
       </c>
-      <c r="E135" s="234" t="s">
+      <c r="E135" s="232" t="s">
         <v>27</v>
       </c>
-      <c r="F135" s="235" t="s">
+      <c r="F135" s="233" t="s">
         <v>277</v>
       </c>
       <c r="G135" s="44" t="s">
@@ -8275,19 +8250,19 @@
       <c r="J135" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K135" s="251" t="s">
+      <c r="K135" s="249" t="s">
         <v>239</v>
       </c>
-      <c r="L135" s="221"/>
+      <c r="L135" s="219"/>
       <c r="M135" s="12"/>
     </row>
     <row r="136" spans="1:13" ht="101.25" customHeight="1">
-      <c r="A136" s="226"/>
-      <c r="B136" s="220"/>
-      <c r="C136" s="234"/>
-      <c r="D136" s="234"/>
-      <c r="E136" s="234"/>
-      <c r="F136" s="235"/>
+      <c r="A136" s="224"/>
+      <c r="B136" s="218"/>
+      <c r="C136" s="232"/>
+      <c r="D136" s="232"/>
+      <c r="E136" s="232"/>
+      <c r="F136" s="233"/>
       <c r="G136" s="36" t="s">
         <v>279</v>
       </c>
@@ -8300,17 +8275,17 @@
       <c r="J136" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K136" s="251"/>
-      <c r="L136" s="221"/>
+      <c r="K136" s="249"/>
+      <c r="L136" s="219"/>
       <c r="M136" s="12"/>
     </row>
     <row r="137" spans="1:13" ht="101.25" customHeight="1">
-      <c r="A137" s="226"/>
-      <c r="B137" s="220"/>
-      <c r="C137" s="234"/>
-      <c r="D137" s="234"/>
-      <c r="E137" s="234"/>
-      <c r="F137" s="235"/>
+      <c r="A137" s="224"/>
+      <c r="B137" s="218"/>
+      <c r="C137" s="232"/>
+      <c r="D137" s="232"/>
+      <c r="E137" s="232"/>
+      <c r="F137" s="233"/>
       <c r="G137" s="36" t="s">
         <v>281</v>
       </c>
@@ -8323,111 +8298,111 @@
       <c r="J137" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="K137" s="251"/>
-      <c r="L137" s="221"/>
+      <c r="K137" s="249"/>
+      <c r="L137" s="219"/>
       <c r="M137" s="12"/>
     </row>
     <row r="138" spans="1:13" ht="97.5" customHeight="1">
-      <c r="A138" s="226">
+      <c r="A138" s="224">
         <v>42</v>
       </c>
-      <c r="B138" s="234">
+      <c r="B138" s="232">
         <v>45962</v>
       </c>
-      <c r="C138" s="234" t="s">
+      <c r="C138" s="232" t="s">
         <v>14</v>
       </c>
-      <c r="D138" s="234" t="s">
+      <c r="D138" s="232" t="s">
         <v>282</v>
       </c>
-      <c r="E138" s="234" t="s">
+      <c r="E138" s="232" t="s">
         <v>47</v>
       </c>
-      <c r="F138" s="235" t="s">
+      <c r="F138" s="233" t="s">
         <v>283</v>
       </c>
-      <c r="G138" s="242" t="s">
+      <c r="G138" s="240" t="s">
         <v>284</v>
       </c>
-      <c r="H138" s="243" t="s">
+      <c r="H138" s="241" t="s">
         <v>120</v>
       </c>
-      <c r="I138" s="262">
+      <c r="I138" s="260">
         <v>45991</v>
       </c>
-      <c r="J138" s="263" t="s">
+      <c r="J138" s="261" t="s">
         <v>20</v>
       </c>
-      <c r="K138" s="240" t="s">
+      <c r="K138" s="238" t="s">
         <v>239</v>
       </c>
-      <c r="L138" s="221" t="s">
+      <c r="L138" s="219" t="s">
         <v>22</v>
       </c>
       <c r="M138" s="12"/>
     </row>
     <row r="139" spans="1:13" ht="28.5" customHeight="1">
-      <c r="A139" s="226"/>
-      <c r="B139" s="234"/>
-      <c r="C139" s="234"/>
-      <c r="D139" s="234"/>
-      <c r="E139" s="234"/>
-      <c r="F139" s="235"/>
-      <c r="G139" s="242"/>
-      <c r="H139" s="243"/>
-      <c r="I139" s="262"/>
-      <c r="J139" s="263"/>
-      <c r="K139" s="240"/>
-      <c r="L139" s="221"/>
+      <c r="A139" s="224"/>
+      <c r="B139" s="232"/>
+      <c r="C139" s="232"/>
+      <c r="D139" s="232"/>
+      <c r="E139" s="232"/>
+      <c r="F139" s="233"/>
+      <c r="G139" s="240"/>
+      <c r="H139" s="241"/>
+      <c r="I139" s="260"/>
+      <c r="J139" s="261"/>
+      <c r="K139" s="238"/>
+      <c r="L139" s="219"/>
       <c r="M139" s="12"/>
     </row>
     <row r="140" spans="1:13" ht="28.5" customHeight="1">
-      <c r="A140" s="226"/>
-      <c r="B140" s="234"/>
-      <c r="C140" s="234"/>
-      <c r="D140" s="234"/>
-      <c r="E140" s="234"/>
-      <c r="F140" s="235"/>
-      <c r="G140" s="242"/>
-      <c r="H140" s="243"/>
-      <c r="I140" s="262"/>
-      <c r="J140" s="263"/>
-      <c r="K140" s="240"/>
-      <c r="L140" s="221"/>
+      <c r="A140" s="224"/>
+      <c r="B140" s="232"/>
+      <c r="C140" s="232"/>
+      <c r="D140" s="232"/>
+      <c r="E140" s="232"/>
+      <c r="F140" s="233"/>
+      <c r="G140" s="240"/>
+      <c r="H140" s="241"/>
+      <c r="I140" s="260"/>
+      <c r="J140" s="261"/>
+      <c r="K140" s="238"/>
+      <c r="L140" s="219"/>
       <c r="M140" s="12"/>
     </row>
     <row r="141" spans="1:13" ht="28.5" customHeight="1">
-      <c r="A141" s="226"/>
-      <c r="B141" s="234"/>
-      <c r="C141" s="234"/>
-      <c r="D141" s="234"/>
-      <c r="E141" s="234"/>
-      <c r="F141" s="235"/>
-      <c r="G141" s="242"/>
-      <c r="H141" s="243"/>
-      <c r="I141" s="262"/>
-      <c r="J141" s="263"/>
-      <c r="K141" s="240"/>
-      <c r="L141" s="221"/>
+      <c r="A141" s="224"/>
+      <c r="B141" s="232"/>
+      <c r="C141" s="232"/>
+      <c r="D141" s="232"/>
+      <c r="E141" s="232"/>
+      <c r="F141" s="233"/>
+      <c r="G141" s="240"/>
+      <c r="H141" s="241"/>
+      <c r="I141" s="260"/>
+      <c r="J141" s="261"/>
+      <c r="K141" s="238"/>
+      <c r="L141" s="219"/>
       <c r="M141" s="12"/>
     </row>
     <row r="142" spans="1:13" ht="44.45" customHeight="1">
-      <c r="A142" s="226">
+      <c r="A142" s="224">
         <v>43</v>
       </c>
-      <c r="B142" s="234">
+      <c r="B142" s="232">
         <v>45964</v>
       </c>
-      <c r="C142" s="233" t="s">
+      <c r="C142" s="231" t="s">
         <v>14</v>
       </c>
-      <c r="D142" s="234" t="s">
+      <c r="D142" s="232" t="s">
         <v>285</v>
       </c>
-      <c r="E142" s="234" t="s">
+      <c r="E142" s="232" t="s">
         <v>78</v>
       </c>
-      <c r="F142" s="235" t="s">
+      <c r="F142" s="233" t="s">
         <v>286</v>
       </c>
       <c r="G142" s="31" t="s">
@@ -8442,19 +8417,19 @@
       <c r="J142" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="K142" s="241" t="s">
+      <c r="K142" s="239" t="s">
         <v>22</v>
       </c>
-      <c r="L142" s="265"/>
+      <c r="L142" s="263"/>
       <c r="M142" s="12"/>
     </row>
     <row r="143" spans="1:13" ht="44.45" customHeight="1">
-      <c r="A143" s="226"/>
-      <c r="B143" s="220"/>
-      <c r="C143" s="233"/>
-      <c r="D143" s="234"/>
-      <c r="E143" s="234"/>
-      <c r="F143" s="235"/>
+      <c r="A143" s="224"/>
+      <c r="B143" s="218"/>
+      <c r="C143" s="231"/>
+      <c r="D143" s="232"/>
+      <c r="E143" s="232"/>
+      <c r="F143" s="233"/>
       <c r="G143" s="31" t="s">
         <v>288</v>
       </c>
@@ -8467,17 +8442,17 @@
       <c r="J143" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="K143" s="241"/>
-      <c r="L143" s="265"/>
+      <c r="K143" s="239"/>
+      <c r="L143" s="263"/>
       <c r="M143" s="12"/>
     </row>
     <row r="144" spans="1:13" ht="44.45" customHeight="1">
-      <c r="A144" s="226"/>
-      <c r="B144" s="220"/>
-      <c r="C144" s="233"/>
-      <c r="D144" s="234"/>
-      <c r="E144" s="234"/>
-      <c r="F144" s="235"/>
+      <c r="A144" s="224"/>
+      <c r="B144" s="218"/>
+      <c r="C144" s="231"/>
+      <c r="D144" s="232"/>
+      <c r="E144" s="232"/>
+      <c r="F144" s="233"/>
       <c r="G144" s="31" t="s">
         <v>289</v>
       </c>
@@ -8490,27 +8465,27 @@
       <c r="J144" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="K144" s="241"/>
-      <c r="L144" s="265"/>
+      <c r="K144" s="239"/>
+      <c r="L144" s="263"/>
       <c r="M144" s="12"/>
     </row>
     <row r="145" spans="1:13" ht="57" customHeight="1">
-      <c r="A145" s="226">
+      <c r="A145" s="224">
         <v>44</v>
       </c>
-      <c r="B145" s="222">
+      <c r="B145" s="220">
         <v>45968</v>
       </c>
-      <c r="C145" s="234" t="s">
+      <c r="C145" s="232" t="s">
         <v>14</v>
       </c>
-      <c r="D145" s="220" t="s">
+      <c r="D145" s="218" t="s">
         <v>291</v>
       </c>
-      <c r="E145" s="221" t="s">
+      <c r="E145" s="219" t="s">
         <v>209</v>
       </c>
-      <c r="F145" s="235" t="s">
+      <c r="F145" s="233" t="s">
         <v>292</v>
       </c>
       <c r="G145" s="47" t="s">
@@ -8525,21 +8500,21 @@
       <c r="J145" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="K145" s="241" t="s">
+      <c r="K145" s="239" t="s">
         <v>178</v>
       </c>
-      <c r="L145" s="221" t="s">
+      <c r="L145" s="219" t="s">
         <v>178</v>
       </c>
       <c r="M145" s="12"/>
     </row>
     <row r="146" spans="1:13" ht="103.5" customHeight="1">
-      <c r="A146" s="226"/>
-      <c r="B146" s="222"/>
-      <c r="C146" s="234"/>
-      <c r="D146" s="220"/>
-      <c r="E146" s="221"/>
-      <c r="F146" s="235"/>
+      <c r="A146" s="224"/>
+      <c r="B146" s="220"/>
+      <c r="C146" s="232"/>
+      <c r="D146" s="218"/>
+      <c r="E146" s="219"/>
+      <c r="F146" s="233"/>
       <c r="G146" s="48" t="s">
         <v>294</v>
       </c>
@@ -8552,17 +8527,17 @@
       <c r="J146" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="K146" s="241"/>
-      <c r="L146" s="221"/>
+      <c r="K146" s="239"/>
+      <c r="L146" s="219"/>
       <c r="M146" s="12"/>
     </row>
     <row r="147" spans="1:13" ht="57" customHeight="1">
-      <c r="A147" s="226"/>
-      <c r="B147" s="222"/>
-      <c r="C147" s="234"/>
-      <c r="D147" s="220"/>
-      <c r="E147" s="221"/>
-      <c r="F147" s="235"/>
+      <c r="A147" s="224"/>
+      <c r="B147" s="220"/>
+      <c r="C147" s="232"/>
+      <c r="D147" s="218"/>
+      <c r="E147" s="219"/>
+      <c r="F147" s="233"/>
       <c r="G147" s="49" t="s">
         <v>296</v>
       </c>
@@ -8575,27 +8550,27 @@
       <c r="J147" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="K147" s="241"/>
-      <c r="L147" s="221"/>
+      <c r="K147" s="239"/>
+      <c r="L147" s="219"/>
       <c r="M147" s="12"/>
     </row>
     <row r="148" spans="1:13" ht="49.5" customHeight="1">
-      <c r="A148" s="226">
+      <c r="A148" s="224">
         <v>45</v>
       </c>
-      <c r="B148" s="222">
+      <c r="B148" s="220">
         <v>45970</v>
       </c>
-      <c r="C148" s="234" t="s">
+      <c r="C148" s="232" t="s">
         <v>14</v>
       </c>
-      <c r="D148" s="220" t="s">
+      <c r="D148" s="218" t="s">
         <v>297</v>
       </c>
-      <c r="E148" s="221" t="s">
+      <c r="E148" s="219" t="s">
         <v>298</v>
       </c>
-      <c r="F148" s="235" t="s">
+      <c r="F148" s="233" t="s">
         <v>299</v>
       </c>
       <c r="G148" s="13" t="s">
@@ -8610,19 +8585,19 @@
       <c r="J148" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="K148" s="236" t="s">
+      <c r="K148" s="234" t="s">
         <v>22</v>
       </c>
-      <c r="L148" s="221"/>
+      <c r="L148" s="219"/>
       <c r="M148" s="12"/>
     </row>
     <row r="149" spans="1:13" ht="43.5" customHeight="1">
-      <c r="A149" s="226"/>
-      <c r="B149" s="221"/>
-      <c r="C149" s="234"/>
-      <c r="D149" s="220"/>
-      <c r="E149" s="221"/>
-      <c r="F149" s="235"/>
+      <c r="A149" s="224"/>
+      <c r="B149" s="219"/>
+      <c r="C149" s="232"/>
+      <c r="D149" s="218"/>
+      <c r="E149" s="219"/>
+      <c r="F149" s="233"/>
       <c r="G149" s="14" t="s">
         <v>302</v>
       </c>
@@ -8635,17 +8610,17 @@
       <c r="J149" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="K149" s="237"/>
-      <c r="L149" s="221"/>
+      <c r="K149" s="235"/>
+      <c r="L149" s="219"/>
       <c r="M149" s="12"/>
     </row>
     <row r="150" spans="1:13" ht="43.5" customHeight="1">
-      <c r="A150" s="226"/>
-      <c r="B150" s="221"/>
-      <c r="C150" s="234"/>
-      <c r="D150" s="220"/>
-      <c r="E150" s="221"/>
-      <c r="F150" s="235"/>
+      <c r="A150" s="224"/>
+      <c r="B150" s="219"/>
+      <c r="C150" s="232"/>
+      <c r="D150" s="218"/>
+      <c r="E150" s="219"/>
+      <c r="F150" s="233"/>
       <c r="G150" s="14" t="s">
         <v>304</v>
       </c>
@@ -8658,27 +8633,27 @@
       <c r="J150" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="K150" s="237"/>
-      <c r="L150" s="221"/>
+      <c r="K150" s="235"/>
+      <c r="L150" s="219"/>
       <c r="M150" s="12"/>
     </row>
     <row r="151" spans="1:13" ht="43.5" customHeight="1">
-      <c r="A151" s="226">
+      <c r="A151" s="224">
         <v>46</v>
       </c>
-      <c r="B151" s="222">
+      <c r="B151" s="220">
         <v>45980</v>
       </c>
-      <c r="C151" s="234" t="s">
+      <c r="C151" s="232" t="s">
         <v>125</v>
       </c>
-      <c r="D151" s="220" t="s">
+      <c r="D151" s="218" t="s">
         <v>306</v>
       </c>
-      <c r="E151" s="221" t="s">
+      <c r="E151" s="219" t="s">
         <v>298</v>
       </c>
-      <c r="F151" s="235" t="s">
+      <c r="F151" s="233" t="s">
         <v>307</v>
       </c>
       <c r="G151" s="14" t="s">
@@ -8693,21 +8668,21 @@
       <c r="J151" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="K151" s="241" t="s">
+      <c r="K151" s="239" t="s">
         <v>20</v>
       </c>
-      <c r="L151" s="221" t="s">
+      <c r="L151" s="219" t="s">
         <v>22</v>
       </c>
       <c r="M151" s="12"/>
     </row>
     <row r="152" spans="1:13" ht="43.5" customHeight="1">
-      <c r="A152" s="226"/>
-      <c r="B152" s="222"/>
-      <c r="C152" s="234"/>
-      <c r="D152" s="220"/>
-      <c r="E152" s="221"/>
-      <c r="F152" s="235"/>
+      <c r="A152" s="224"/>
+      <c r="B152" s="220"/>
+      <c r="C152" s="232"/>
+      <c r="D152" s="218"/>
+      <c r="E152" s="219"/>
+      <c r="F152" s="233"/>
       <c r="G152" s="14" t="s">
         <v>309</v>
       </c>
@@ -8720,17 +8695,17 @@
       <c r="J152" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="K152" s="241"/>
-      <c r="L152" s="221"/>
+      <c r="K152" s="239"/>
+      <c r="L152" s="219"/>
       <c r="M152" s="12"/>
     </row>
     <row r="153" spans="1:13" ht="43.5" customHeight="1">
-      <c r="A153" s="226"/>
-      <c r="B153" s="222"/>
-      <c r="C153" s="234"/>
-      <c r="D153" s="220"/>
-      <c r="E153" s="221"/>
-      <c r="F153" s="235"/>
+      <c r="A153" s="224"/>
+      <c r="B153" s="220"/>
+      <c r="C153" s="232"/>
+      <c r="D153" s="218"/>
+      <c r="E153" s="219"/>
+      <c r="F153" s="233"/>
       <c r="G153" s="14" t="s">
         <v>310</v>
       </c>
@@ -8743,17 +8718,17 @@
       <c r="J153" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="K153" s="241"/>
-      <c r="L153" s="221"/>
+      <c r="K153" s="239"/>
+      <c r="L153" s="219"/>
       <c r="M153" s="12"/>
     </row>
     <row r="154" spans="1:13" ht="49.5" customHeight="1">
-      <c r="A154" s="226"/>
-      <c r="B154" s="222"/>
-      <c r="C154" s="234"/>
-      <c r="D154" s="220"/>
-      <c r="E154" s="221"/>
-      <c r="F154" s="235"/>
+      <c r="A154" s="224"/>
+      <c r="B154" s="220"/>
+      <c r="C154" s="232"/>
+      <c r="D154" s="218"/>
+      <c r="E154" s="219"/>
+      <c r="F154" s="233"/>
       <c r="G154" s="14" t="s">
         <v>311</v>
       </c>
@@ -8766,8 +8741,8 @@
       <c r="J154" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="K154" s="241"/>
-      <c r="L154" s="221"/>
+      <c r="K154" s="239"/>
+      <c r="L154" s="219"/>
       <c r="M154" s="12"/>
     </row>
     <row r="155" spans="1:13" s="1" customFormat="1" ht="91.5" customHeight="1">
@@ -8845,22 +8820,22 @@
       <c r="M156" s="12"/>
     </row>
     <row r="157" spans="1:13" ht="90.75" customHeight="1">
-      <c r="A157" s="226">
+      <c r="A157" s="224">
         <v>49</v>
       </c>
-      <c r="B157" s="222">
+      <c r="B157" s="220">
         <v>45994</v>
       </c>
-      <c r="C157" s="221" t="s">
+      <c r="C157" s="219" t="s">
         <v>125</v>
       </c>
-      <c r="D157" s="220" t="s">
+      <c r="D157" s="218" t="s">
         <v>319</v>
       </c>
-      <c r="E157" s="244" t="s">
+      <c r="E157" s="242" t="s">
         <v>320</v>
       </c>
-      <c r="F157" s="235" t="s">
+      <c r="F157" s="233" t="s">
         <v>321</v>
       </c>
       <c r="G157" s="14" t="s">
@@ -8875,10 +8850,10 @@
       <c r="J157" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="K157" s="238" t="s">
+      <c r="K157" s="236" t="s">
         <v>20</v>
       </c>
-      <c r="L157" s="221" t="s">
+      <c r="L157" s="219" t="s">
         <v>22</v>
       </c>
       <c r="M157" s="12" t="s">
@@ -8886,12 +8861,12 @@
       </c>
     </row>
     <row r="158" spans="1:13" ht="59.25" customHeight="1">
-      <c r="A158" s="226"/>
-      <c r="B158" s="222"/>
-      <c r="C158" s="221"/>
-      <c r="D158" s="220"/>
-      <c r="E158" s="244"/>
-      <c r="F158" s="235"/>
+      <c r="A158" s="224"/>
+      <c r="B158" s="220"/>
+      <c r="C158" s="219"/>
+      <c r="D158" s="218"/>
+      <c r="E158" s="242"/>
+      <c r="F158" s="233"/>
       <c r="G158" s="14" t="s">
         <v>324</v>
       </c>
@@ -8904,17 +8879,17 @@
       <c r="J158" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="K158" s="238"/>
-      <c r="L158" s="221"/>
+      <c r="K158" s="236"/>
+      <c r="L158" s="219"/>
       <c r="M158" s="12"/>
     </row>
     <row r="159" spans="1:13" ht="72.75" customHeight="1">
-      <c r="A159" s="226"/>
-      <c r="B159" s="222"/>
-      <c r="C159" s="221"/>
-      <c r="D159" s="220"/>
-      <c r="E159" s="244"/>
-      <c r="F159" s="235"/>
+      <c r="A159" s="224"/>
+      <c r="B159" s="220"/>
+      <c r="C159" s="219"/>
+      <c r="D159" s="218"/>
+      <c r="E159" s="242"/>
+      <c r="F159" s="233"/>
       <c r="G159" s="14" t="s">
         <v>326</v>
       </c>
@@ -8927,17 +8902,17 @@
       <c r="J159" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="K159" s="238"/>
-      <c r="L159" s="221"/>
+      <c r="K159" s="236"/>
+      <c r="L159" s="219"/>
       <c r="M159" s="12"/>
     </row>
     <row r="160" spans="1:13" ht="41.25" customHeight="1">
-      <c r="A160" s="226"/>
-      <c r="B160" s="222"/>
-      <c r="C160" s="221"/>
-      <c r="D160" s="220"/>
-      <c r="E160" s="244"/>
-      <c r="F160" s="235"/>
+      <c r="A160" s="224"/>
+      <c r="B160" s="220"/>
+      <c r="C160" s="219"/>
+      <c r="D160" s="218"/>
+      <c r="E160" s="242"/>
+      <c r="F160" s="233"/>
       <c r="G160" s="14" t="s">
         <v>201</v>
       </c>
@@ -8950,17 +8925,17 @@
       <c r="J160" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="K160" s="238"/>
-      <c r="L160" s="221"/>
+      <c r="K160" s="236"/>
+      <c r="L160" s="219"/>
       <c r="M160" s="12"/>
     </row>
     <row r="161" spans="1:13" ht="57" customHeight="1">
-      <c r="A161" s="226"/>
-      <c r="B161" s="222"/>
-      <c r="C161" s="221"/>
-      <c r="D161" s="220"/>
-      <c r="E161" s="244"/>
-      <c r="F161" s="235"/>
+      <c r="A161" s="224"/>
+      <c r="B161" s="220"/>
+      <c r="C161" s="219"/>
+      <c r="D161" s="218"/>
+      <c r="E161" s="242"/>
+      <c r="F161" s="233"/>
       <c r="G161" s="14" t="s">
         <v>329</v>
       </c>
@@ -8973,17 +8948,17 @@
       <c r="J161" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="K161" s="238"/>
-      <c r="L161" s="221"/>
+      <c r="K161" s="236"/>
+      <c r="L161" s="219"/>
       <c r="M161" s="12"/>
     </row>
     <row r="162" spans="1:13" ht="45" customHeight="1">
-      <c r="A162" s="226"/>
-      <c r="B162" s="222"/>
-      <c r="C162" s="221"/>
-      <c r="D162" s="220"/>
-      <c r="E162" s="244"/>
-      <c r="F162" s="235"/>
+      <c r="A162" s="224"/>
+      <c r="B162" s="220"/>
+      <c r="C162" s="219"/>
+      <c r="D162" s="218"/>
+      <c r="E162" s="242"/>
+      <c r="F162" s="233"/>
       <c r="G162" s="14" t="s">
         <v>331</v>
       </c>
@@ -8996,17 +8971,17 @@
       <c r="J162" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="K162" s="238"/>
-      <c r="L162" s="221"/>
+      <c r="K162" s="236"/>
+      <c r="L162" s="219"/>
       <c r="M162" s="12"/>
     </row>
     <row r="163" spans="1:13" ht="36.75" customHeight="1">
-      <c r="A163" s="226"/>
-      <c r="B163" s="222"/>
-      <c r="C163" s="221"/>
-      <c r="D163" s="220"/>
-      <c r="E163" s="244"/>
-      <c r="F163" s="235"/>
+      <c r="A163" s="224"/>
+      <c r="B163" s="220"/>
+      <c r="C163" s="219"/>
+      <c r="D163" s="218"/>
+      <c r="E163" s="242"/>
+      <c r="F163" s="233"/>
       <c r="G163" s="14" t="s">
         <v>333</v>
       </c>
@@ -9019,17 +8994,17 @@
       <c r="J163" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="K163" s="238"/>
-      <c r="L163" s="221"/>
+      <c r="K163" s="236"/>
+      <c r="L163" s="219"/>
       <c r="M163" s="12"/>
     </row>
     <row r="164" spans="1:13" ht="45.75" customHeight="1">
-      <c r="A164" s="226"/>
-      <c r="B164" s="222"/>
-      <c r="C164" s="221"/>
-      <c r="D164" s="220"/>
-      <c r="E164" s="244"/>
-      <c r="F164" s="235"/>
+      <c r="A164" s="224"/>
+      <c r="B164" s="220"/>
+      <c r="C164" s="219"/>
+      <c r="D164" s="218"/>
+      <c r="E164" s="242"/>
+      <c r="F164" s="233"/>
       <c r="G164" s="14" t="s">
         <v>335</v>
       </c>
@@ -9042,17 +9017,17 @@
       <c r="J164" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="K164" s="238"/>
-      <c r="L164" s="221"/>
+      <c r="K164" s="236"/>
+      <c r="L164" s="219"/>
       <c r="M164" s="12"/>
     </row>
     <row r="165" spans="1:13" ht="45.75" customHeight="1">
-      <c r="A165" s="226"/>
-      <c r="B165" s="222"/>
-      <c r="C165" s="221"/>
-      <c r="D165" s="220"/>
-      <c r="E165" s="244"/>
-      <c r="F165" s="235"/>
+      <c r="A165" s="224"/>
+      <c r="B165" s="220"/>
+      <c r="C165" s="219"/>
+      <c r="D165" s="218"/>
+      <c r="E165" s="242"/>
+      <c r="F165" s="233"/>
       <c r="G165" s="14" t="s">
         <v>336</v>
       </c>
@@ -9063,17 +9038,17 @@
       <c r="J165" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="K165" s="238"/>
-      <c r="L165" s="221"/>
+      <c r="K165" s="236"/>
+      <c r="L165" s="219"/>
       <c r="M165" s="12"/>
     </row>
     <row r="166" spans="1:13" ht="45.75" customHeight="1">
-      <c r="A166" s="226"/>
-      <c r="B166" s="222"/>
-      <c r="C166" s="221"/>
-      <c r="D166" s="220"/>
-      <c r="E166" s="244"/>
-      <c r="F166" s="235"/>
+      <c r="A166" s="224"/>
+      <c r="B166" s="220"/>
+      <c r="C166" s="219"/>
+      <c r="D166" s="218"/>
+      <c r="E166" s="242"/>
+      <c r="F166" s="233"/>
       <c r="G166" s="14" t="s">
         <v>337</v>
       </c>
@@ -9084,17 +9059,17 @@
       <c r="J166" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="K166" s="238"/>
-      <c r="L166" s="221"/>
+      <c r="K166" s="236"/>
+      <c r="L166" s="219"/>
       <c r="M166" s="12"/>
     </row>
     <row r="167" spans="1:13" ht="45.75" customHeight="1">
-      <c r="A167" s="226"/>
-      <c r="B167" s="222"/>
-      <c r="C167" s="221"/>
-      <c r="D167" s="220"/>
-      <c r="E167" s="244"/>
-      <c r="F167" s="235"/>
+      <c r="A167" s="224"/>
+      <c r="B167" s="220"/>
+      <c r="C167" s="219"/>
+      <c r="D167" s="218"/>
+      <c r="E167" s="242"/>
+      <c r="F167" s="233"/>
       <c r="G167" s="14" t="s">
         <v>338</v>
       </c>
@@ -9105,17 +9080,17 @@
       <c r="J167" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="K167" s="238"/>
-      <c r="L167" s="221"/>
+      <c r="K167" s="236"/>
+      <c r="L167" s="219"/>
       <c r="M167" s="12"/>
     </row>
     <row r="168" spans="1:13" ht="45.75" customHeight="1">
-      <c r="A168" s="226"/>
-      <c r="B168" s="222"/>
-      <c r="C168" s="221"/>
-      <c r="D168" s="220"/>
-      <c r="E168" s="244"/>
-      <c r="F168" s="235"/>
+      <c r="A168" s="224"/>
+      <c r="B168" s="220"/>
+      <c r="C168" s="219"/>
+      <c r="D168" s="218"/>
+      <c r="E168" s="242"/>
+      <c r="F168" s="233"/>
       <c r="G168" s="14" t="s">
         <v>339</v>
       </c>
@@ -9126,17 +9101,17 @@
       <c r="J168" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="K168" s="238"/>
-      <c r="L168" s="221"/>
+      <c r="K168" s="236"/>
+      <c r="L168" s="219"/>
       <c r="M168" s="12"/>
     </row>
     <row r="169" spans="1:13" ht="66.75" customHeight="1">
-      <c r="A169" s="226"/>
-      <c r="B169" s="222"/>
-      <c r="C169" s="221"/>
-      <c r="D169" s="220"/>
-      <c r="E169" s="244"/>
-      <c r="F169" s="235"/>
+      <c r="A169" s="224"/>
+      <c r="B169" s="220"/>
+      <c r="C169" s="219"/>
+      <c r="D169" s="218"/>
+      <c r="E169" s="242"/>
+      <c r="F169" s="233"/>
       <c r="G169" s="14" t="s">
         <v>340</v>
       </c>
@@ -9147,27 +9122,27 @@
       <c r="J169" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="K169" s="238"/>
-      <c r="L169" s="221"/>
+      <c r="K169" s="236"/>
+      <c r="L169" s="219"/>
       <c r="M169" s="12"/>
     </row>
     <row r="170" spans="1:13" ht="99" customHeight="1">
-      <c r="A170" s="221">
+      <c r="A170" s="219">
         <v>50</v>
       </c>
-      <c r="B170" s="222">
+      <c r="B170" s="220">
         <v>46011</v>
       </c>
-      <c r="C170" s="221" t="s">
+      <c r="C170" s="219" t="s">
         <v>265</v>
       </c>
-      <c r="D170" s="220" t="s">
+      <c r="D170" s="218" t="s">
         <v>341</v>
       </c>
-      <c r="E170" s="220" t="s">
+      <c r="E170" s="218" t="s">
         <v>298</v>
       </c>
-      <c r="F170" s="235" t="s">
+      <c r="F170" s="233" t="s">
         <v>342</v>
       </c>
       <c r="G170" s="71" t="s">
@@ -9182,21 +9157,21 @@
       <c r="J170" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="K170" s="238" t="s">
+      <c r="K170" s="236" t="s">
         <v>22</v>
       </c>
-      <c r="L170" s="221" t="s">
+      <c r="L170" s="219" t="s">
         <v>22</v>
       </c>
       <c r="M170" s="12"/>
     </row>
     <row r="171" spans="1:13" ht="78.75" customHeight="1">
-      <c r="A171" s="221"/>
-      <c r="B171" s="222"/>
-      <c r="C171" s="221"/>
-      <c r="D171" s="220"/>
-      <c r="E171" s="221"/>
-      <c r="F171" s="235"/>
+      <c r="A171" s="219"/>
+      <c r="B171" s="220"/>
+      <c r="C171" s="219"/>
+      <c r="D171" s="218"/>
+      <c r="E171" s="219"/>
+      <c r="F171" s="233"/>
       <c r="G171" s="72" t="s">
         <v>345</v>
       </c>
@@ -9209,17 +9184,17 @@
       <c r="J171" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="K171" s="238"/>
-      <c r="L171" s="221"/>
+      <c r="K171" s="236"/>
+      <c r="L171" s="219"/>
       <c r="M171" s="12"/>
     </row>
     <row r="172" spans="1:13" ht="105" customHeight="1">
-      <c r="A172" s="221"/>
-      <c r="B172" s="222"/>
-      <c r="C172" s="221"/>
-      <c r="D172" s="220"/>
-      <c r="E172" s="221"/>
-      <c r="F172" s="235"/>
+      <c r="A172" s="219"/>
+      <c r="B172" s="220"/>
+      <c r="C172" s="219"/>
+      <c r="D172" s="218"/>
+      <c r="E172" s="219"/>
+      <c r="F172" s="233"/>
       <c r="G172" s="71" t="s">
         <v>346</v>
       </c>
@@ -9232,17 +9207,17 @@
       <c r="J172" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="K172" s="238"/>
-      <c r="L172" s="221"/>
+      <c r="K172" s="236"/>
+      <c r="L172" s="219"/>
       <c r="M172" s="12"/>
     </row>
     <row r="173" spans="1:13" ht="86.25" customHeight="1">
-      <c r="A173" s="221"/>
-      <c r="B173" s="222"/>
-      <c r="C173" s="221"/>
-      <c r="D173" s="220"/>
-      <c r="E173" s="221"/>
-      <c r="F173" s="235"/>
+      <c r="A173" s="219"/>
+      <c r="B173" s="220"/>
+      <c r="C173" s="219"/>
+      <c r="D173" s="218"/>
+      <c r="E173" s="219"/>
+      <c r="F173" s="233"/>
       <c r="G173" s="71" t="s">
         <v>347</v>
       </c>
@@ -9255,17 +9230,17 @@
       <c r="J173" s="81" t="s">
         <v>20</v>
       </c>
-      <c r="K173" s="238"/>
-      <c r="L173" s="221"/>
+      <c r="K173" s="236"/>
+      <c r="L173" s="219"/>
       <c r="M173" s="12"/>
     </row>
     <row r="174" spans="1:13" ht="61.5" customHeight="1">
-      <c r="A174" s="221"/>
-      <c r="B174" s="222"/>
-      <c r="C174" s="221"/>
-      <c r="D174" s="220"/>
-      <c r="E174" s="221"/>
-      <c r="F174" s="235"/>
+      <c r="A174" s="219"/>
+      <c r="B174" s="220"/>
+      <c r="C174" s="219"/>
+      <c r="D174" s="218"/>
+      <c r="E174" s="219"/>
+      <c r="F174" s="233"/>
       <c r="G174" s="71" t="s">
         <v>348</v>
       </c>
@@ -9278,8 +9253,8 @@
       <c r="J174" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="K174" s="238"/>
-      <c r="L174" s="221"/>
+      <c r="K174" s="236"/>
+      <c r="L174" s="219"/>
       <c r="M174" s="12"/>
     </row>
     <row r="175" spans="1:13" ht="66" customHeight="1">
@@ -9324,22 +9299,22 @@
       </c>
     </row>
     <row r="176" spans="1:13" ht="65.25" customHeight="1">
-      <c r="A176" s="221">
+      <c r="A176" s="219">
         <v>52</v>
       </c>
-      <c r="B176" s="222">
+      <c r="B176" s="220">
         <v>46014</v>
       </c>
-      <c r="C176" s="221" t="s">
+      <c r="C176" s="219" t="s">
         <v>125</v>
       </c>
-      <c r="D176" s="220" t="s">
+      <c r="D176" s="218" t="s">
         <v>352</v>
       </c>
-      <c r="E176" s="221" t="s">
+      <c r="E176" s="219" t="s">
         <v>47</v>
       </c>
-      <c r="F176" s="235" t="s">
+      <c r="F176" s="233" t="s">
         <v>353</v>
       </c>
       <c r="G176" s="115" t="s">
@@ -9354,19 +9329,19 @@
       <c r="J176" s="50" t="s">
         <v>242</v>
       </c>
-      <c r="K176" s="239" t="s">
+      <c r="K176" s="237" t="s">
         <v>22</v>
       </c>
-      <c r="L176" s="221"/>
+      <c r="L176" s="219"/>
       <c r="M176" s="12"/>
     </row>
     <row r="177" spans="1:13" ht="45" customHeight="1">
-      <c r="A177" s="221"/>
-      <c r="B177" s="222"/>
-      <c r="C177" s="221"/>
-      <c r="D177" s="221"/>
-      <c r="E177" s="221"/>
-      <c r="F177" s="235"/>
+      <c r="A177" s="219"/>
+      <c r="B177" s="220"/>
+      <c r="C177" s="219"/>
+      <c r="D177" s="219"/>
+      <c r="E177" s="219"/>
+      <c r="F177" s="233"/>
       <c r="G177" s="115" t="s">
         <v>356</v>
       </c>
@@ -9379,17 +9354,17 @@
       <c r="J177" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="K177" s="239"/>
-      <c r="L177" s="221"/>
+      <c r="K177" s="237"/>
+      <c r="L177" s="219"/>
       <c r="M177" s="12"/>
     </row>
     <row r="178" spans="1:13" ht="45" customHeight="1">
-      <c r="A178" s="221"/>
-      <c r="B178" s="222"/>
-      <c r="C178" s="221"/>
-      <c r="D178" s="221"/>
-      <c r="E178" s="221"/>
-      <c r="F178" s="235"/>
+      <c r="A178" s="219"/>
+      <c r="B178" s="220"/>
+      <c r="C178" s="219"/>
+      <c r="D178" s="219"/>
+      <c r="E178" s="219"/>
+      <c r="F178" s="233"/>
       <c r="G178" s="115" t="s">
         <v>357</v>
       </c>
@@ -9402,27 +9377,27 @@
       <c r="J178" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="K178" s="239"/>
-      <c r="L178" s="221"/>
+      <c r="K178" s="237"/>
+      <c r="L178" s="219"/>
       <c r="M178" s="12"/>
     </row>
     <row r="179" spans="1:13" ht="90" customHeight="1">
-      <c r="A179" s="221">
+      <c r="A179" s="219">
         <v>53</v>
       </c>
-      <c r="B179" s="222">
+      <c r="B179" s="220">
         <v>46027</v>
       </c>
-      <c r="C179" s="221" t="s">
+      <c r="C179" s="219" t="s">
         <v>265</v>
       </c>
-      <c r="D179" s="220" t="s">
+      <c r="D179" s="218" t="s">
         <v>359</v>
       </c>
-      <c r="E179" s="221" t="s">
+      <c r="E179" s="219" t="s">
         <v>47</v>
       </c>
-      <c r="F179" s="235" t="s">
+      <c r="F179" s="233" t="s">
         <v>360</v>
       </c>
       <c r="G179" s="116" t="s">
@@ -9437,19 +9412,19 @@
       <c r="J179" s="50" t="s">
         <v>242</v>
       </c>
-      <c r="K179" s="239" t="s">
+      <c r="K179" s="237" t="s">
         <v>22</v>
       </c>
-      <c r="L179" s="221"/>
+      <c r="L179" s="219"/>
       <c r="M179" s="12"/>
     </row>
     <row r="180" spans="1:13" ht="76.5" customHeight="1">
-      <c r="A180" s="221"/>
-      <c r="B180" s="222"/>
-      <c r="C180" s="221"/>
-      <c r="D180" s="220"/>
-      <c r="E180" s="221"/>
-      <c r="F180" s="235"/>
+      <c r="A180" s="219"/>
+      <c r="B180" s="220"/>
+      <c r="C180" s="219"/>
+      <c r="D180" s="218"/>
+      <c r="E180" s="219"/>
+      <c r="F180" s="233"/>
       <c r="G180" s="116" t="s">
         <v>362</v>
       </c>
@@ -9462,17 +9437,17 @@
       <c r="J180" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="K180" s="239"/>
-      <c r="L180" s="221"/>
+      <c r="K180" s="237"/>
+      <c r="L180" s="219"/>
       <c r="M180" s="12"/>
     </row>
     <row r="181" spans="1:13" ht="49.5" customHeight="1">
-      <c r="A181" s="221"/>
-      <c r="B181" s="222"/>
-      <c r="C181" s="221"/>
-      <c r="D181" s="220"/>
-      <c r="E181" s="221"/>
-      <c r="F181" s="235"/>
+      <c r="A181" s="219"/>
+      <c r="B181" s="220"/>
+      <c r="C181" s="219"/>
+      <c r="D181" s="218"/>
+      <c r="E181" s="219"/>
+      <c r="F181" s="233"/>
       <c r="G181" s="116" t="s">
         <v>363</v>
       </c>
@@ -9485,27 +9460,27 @@
       <c r="J181" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="K181" s="239"/>
-      <c r="L181" s="221"/>
+      <c r="K181" s="237"/>
+      <c r="L181" s="219"/>
       <c r="M181" s="12"/>
     </row>
     <row r="182" spans="1:13" ht="81.75" customHeight="1">
-      <c r="A182" s="221">
+      <c r="A182" s="219">
         <v>54</v>
       </c>
-      <c r="B182" s="222">
+      <c r="B182" s="220">
         <v>46035</v>
       </c>
-      <c r="C182" s="221" t="s">
+      <c r="C182" s="219" t="s">
         <v>125</v>
       </c>
-      <c r="D182" s="220" t="s">
+      <c r="D182" s="218" t="s">
         <v>364</v>
       </c>
-      <c r="E182" s="221" t="s">
+      <c r="E182" s="219" t="s">
         <v>182</v>
       </c>
-      <c r="F182" s="235" t="s">
+      <c r="F182" s="233" t="s">
         <v>365</v>
       </c>
       <c r="G182" s="116" t="s">
@@ -9520,21 +9495,21 @@
       <c r="J182" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="K182" s="239" t="s">
+      <c r="K182" s="237" t="s">
         <v>20</v>
       </c>
-      <c r="L182" s="221"/>
+      <c r="L182" s="219"/>
       <c r="M182" s="12" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="183" spans="1:13" ht="84.75" customHeight="1">
-      <c r="A183" s="221"/>
-      <c r="B183" s="222"/>
-      <c r="C183" s="221"/>
-      <c r="D183" s="220"/>
-      <c r="E183" s="221"/>
-      <c r="F183" s="235"/>
+      <c r="A183" s="219"/>
+      <c r="B183" s="220"/>
+      <c r="C183" s="219"/>
+      <c r="D183" s="218"/>
+      <c r="E183" s="219"/>
+      <c r="F183" s="233"/>
       <c r="G183" s="71" t="s">
         <v>367</v>
       </c>
@@ -9547,17 +9522,17 @@
       <c r="J183" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="K183" s="239"/>
-      <c r="L183" s="221"/>
+      <c r="K183" s="237"/>
+      <c r="L183" s="219"/>
       <c r="M183" s="12"/>
     </row>
     <row r="184" spans="1:13" ht="68.25" customHeight="1">
-      <c r="A184" s="221"/>
-      <c r="B184" s="222"/>
-      <c r="C184" s="221"/>
-      <c r="D184" s="220"/>
-      <c r="E184" s="221"/>
-      <c r="F184" s="235"/>
+      <c r="A184" s="219"/>
+      <c r="B184" s="220"/>
+      <c r="C184" s="219"/>
+      <c r="D184" s="218"/>
+      <c r="E184" s="219"/>
+      <c r="F184" s="233"/>
       <c r="G184" s="71" t="s">
         <v>368</v>
       </c>
@@ -9570,27 +9545,27 @@
       <c r="J184" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="K184" s="239"/>
-      <c r="L184" s="221"/>
+      <c r="K184" s="237"/>
+      <c r="L184" s="219"/>
       <c r="M184" s="12"/>
     </row>
     <row r="185" spans="1:13" ht="111.75" customHeight="1">
-      <c r="A185" s="221">
+      <c r="A185" s="219">
         <v>55</v>
       </c>
-      <c r="B185" s="222">
+      <c r="B185" s="220">
         <v>46053</v>
       </c>
-      <c r="C185" s="221" t="s">
+      <c r="C185" s="219" t="s">
         <v>125</v>
       </c>
-      <c r="D185" s="220" t="s">
+      <c r="D185" s="218" t="s">
         <v>370</v>
       </c>
-      <c r="E185" s="221" t="s">
+      <c r="E185" s="219" t="s">
         <v>27</v>
       </c>
-      <c r="F185" s="235" t="s">
+      <c r="F185" s="233" t="s">
         <v>371</v>
       </c>
       <c r="G185" s="71" t="s">
@@ -9608,16 +9583,16 @@
       <c r="K185" s="98" t="s">
         <v>22</v>
       </c>
-      <c r="L185" s="221"/>
+      <c r="L185" s="219"/>
       <c r="M185" s="12"/>
     </row>
     <row r="186" spans="1:13" ht="116.25" customHeight="1">
-      <c r="A186" s="221"/>
-      <c r="B186" s="222"/>
-      <c r="C186" s="221"/>
-      <c r="D186" s="220"/>
-      <c r="E186" s="221"/>
-      <c r="F186" s="235"/>
+      <c r="A186" s="219"/>
+      <c r="B186" s="220"/>
+      <c r="C186" s="219"/>
+      <c r="D186" s="218"/>
+      <c r="E186" s="219"/>
+      <c r="F186" s="233"/>
       <c r="G186" s="146" t="s">
         <v>374</v>
       </c>
@@ -9631,26 +9606,26 @@
       <c r="K186" s="98" t="s">
         <v>22</v>
       </c>
-      <c r="L186" s="221"/>
+      <c r="L186" s="219"/>
       <c r="M186" s="12"/>
     </row>
     <row r="187" spans="1:13" ht="54.75" customHeight="1">
-      <c r="A187" s="221">
+      <c r="A187" s="219">
         <v>56</v>
       </c>
-      <c r="B187" s="222">
+      <c r="B187" s="220">
         <v>46059</v>
       </c>
-      <c r="C187" s="221" t="s">
+      <c r="C187" s="219" t="s">
         <v>125</v>
       </c>
-      <c r="D187" s="309" t="s">
+      <c r="D187" s="307" t="s">
         <v>375</v>
       </c>
-      <c r="E187" s="221" t="s">
+      <c r="E187" s="219" t="s">
         <v>47</v>
       </c>
-      <c r="F187" s="235" t="s">
+      <c r="F187" s="233" t="s">
         <v>376</v>
       </c>
       <c r="G187" s="71" t="s">
@@ -9663,19 +9638,19 @@
       <c r="J187" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="K187" s="232" t="s">
+      <c r="K187" s="230" t="s">
         <v>22</v>
       </c>
-      <c r="L187" s="265"/>
+      <c r="L187" s="263"/>
       <c r="M187" s="12"/>
     </row>
     <row r="188" spans="1:13" ht="83.25" customHeight="1">
-      <c r="A188" s="221"/>
-      <c r="B188" s="222"/>
-      <c r="C188" s="221"/>
-      <c r="D188" s="309"/>
-      <c r="E188" s="221"/>
-      <c r="F188" s="235"/>
+      <c r="A188" s="219"/>
+      <c r="B188" s="220"/>
+      <c r="C188" s="219"/>
+      <c r="D188" s="307"/>
+      <c r="E188" s="219"/>
+      <c r="F188" s="233"/>
       <c r="G188" s="116" t="s">
         <v>378</v>
       </c>
@@ -9686,17 +9661,17 @@
       <c r="J188" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="K188" s="232"/>
-      <c r="L188" s="265"/>
+      <c r="K188" s="230"/>
+      <c r="L188" s="263"/>
       <c r="M188" s="12"/>
     </row>
     <row r="189" spans="1:13" ht="136.5" customHeight="1">
-      <c r="A189" s="221"/>
-      <c r="B189" s="222"/>
-      <c r="C189" s="221"/>
-      <c r="D189" s="309"/>
-      <c r="E189" s="221"/>
-      <c r="F189" s="235"/>
+      <c r="A189" s="219"/>
+      <c r="B189" s="220"/>
+      <c r="C189" s="219"/>
+      <c r="D189" s="307"/>
+      <c r="E189" s="219"/>
+      <c r="F189" s="233"/>
       <c r="G189" s="116" t="s">
         <v>379</v>
       </c>
@@ -9709,27 +9684,27 @@
       <c r="J189" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="K189" s="223"/>
-      <c r="L189" s="265"/>
+      <c r="K189" s="221"/>
+      <c r="L189" s="263"/>
       <c r="M189" s="12"/>
     </row>
     <row r="190" spans="1:13" ht="52.5" customHeight="1">
-      <c r="A190" s="221">
+      <c r="A190" s="219">
         <v>57</v>
       </c>
-      <c r="B190" s="222">
+      <c r="B190" s="220">
         <v>46059</v>
       </c>
-      <c r="C190" s="221" t="s">
+      <c r="C190" s="219" t="s">
         <v>125</v>
       </c>
-      <c r="D190" s="220" t="s">
+      <c r="D190" s="218" t="s">
         <v>381</v>
       </c>
-      <c r="E190" s="221" t="s">
+      <c r="E190" s="219" t="s">
         <v>47</v>
       </c>
-      <c r="F190" s="235" t="s">
+      <c r="F190" s="233" t="s">
         <v>382</v>
       </c>
       <c r="G190" s="116" t="s">
@@ -9744,19 +9719,19 @@
       <c r="J190" s="82" t="s">
         <v>242</v>
       </c>
-      <c r="K190" s="232" t="s">
+      <c r="K190" s="230" t="s">
         <v>22</v>
       </c>
-      <c r="L190" s="221"/>
+      <c r="L190" s="219"/>
       <c r="M190" s="12"/>
     </row>
     <row r="191" spans="1:13" ht="51.75" customHeight="1">
-      <c r="A191" s="221"/>
-      <c r="B191" s="222"/>
-      <c r="C191" s="221"/>
-      <c r="D191" s="220"/>
-      <c r="E191" s="221"/>
-      <c r="F191" s="235"/>
+      <c r="A191" s="219"/>
+      <c r="B191" s="220"/>
+      <c r="C191" s="219"/>
+      <c r="D191" s="218"/>
+      <c r="E191" s="219"/>
+      <c r="F191" s="233"/>
       <c r="G191" s="116" t="s">
         <v>385</v>
       </c>
@@ -9769,27 +9744,27 @@
       <c r="J191" s="82" t="s">
         <v>196</v>
       </c>
-      <c r="K191" s="232"/>
-      <c r="L191" s="221"/>
+      <c r="K191" s="230"/>
+      <c r="L191" s="219"/>
       <c r="M191" s="12"/>
     </row>
     <row r="192" spans="1:13" ht="54" customHeight="1">
-      <c r="A192" s="221">
+      <c r="A192" s="219">
         <v>58</v>
       </c>
-      <c r="B192" s="222">
+      <c r="B192" s="220">
         <v>46068</v>
       </c>
-      <c r="C192" s="221" t="s">
+      <c r="C192" s="219" t="s">
         <v>312</v>
       </c>
-      <c r="D192" s="220" t="s">
+      <c r="D192" s="218" t="s">
         <v>386</v>
       </c>
-      <c r="E192" s="221" t="s">
+      <c r="E192" s="219" t="s">
         <v>47</v>
       </c>
-      <c r="F192" s="235" t="s">
+      <c r="F192" s="233" t="s">
         <v>387</v>
       </c>
       <c r="G192" s="117" t="s">
@@ -9804,19 +9779,19 @@
       <c r="J192" s="82" t="s">
         <v>196</v>
       </c>
-      <c r="K192" s="209" t="s">
+      <c r="K192" s="207" t="s">
         <v>390</v>
       </c>
-      <c r="L192" s="221"/>
+      <c r="L192" s="219"/>
       <c r="M192" s="12"/>
     </row>
     <row r="193" spans="1:2438" ht="50.25" customHeight="1">
-      <c r="A193" s="221"/>
-      <c r="B193" s="222"/>
-      <c r="C193" s="221"/>
-      <c r="D193" s="220"/>
-      <c r="E193" s="221"/>
-      <c r="F193" s="235"/>
+      <c r="A193" s="219"/>
+      <c r="B193" s="220"/>
+      <c r="C193" s="219"/>
+      <c r="D193" s="218"/>
+      <c r="E193" s="219"/>
+      <c r="F193" s="233"/>
       <c r="G193" s="116" t="s">
         <v>391</v>
       </c>
@@ -9829,17 +9804,17 @@
       <c r="J193" s="69" t="s">
         <v>242</v>
       </c>
-      <c r="K193" s="232"/>
-      <c r="L193" s="221"/>
+      <c r="K193" s="230"/>
+      <c r="L193" s="219"/>
       <c r="M193" s="12"/>
     </row>
     <row r="194" spans="1:2438" ht="55.5" customHeight="1">
-      <c r="A194" s="221"/>
-      <c r="B194" s="222"/>
-      <c r="C194" s="221"/>
-      <c r="D194" s="220"/>
-      <c r="E194" s="221"/>
-      <c r="F194" s="235"/>
+      <c r="A194" s="219"/>
+      <c r="B194" s="220"/>
+      <c r="C194" s="219"/>
+      <c r="D194" s="218"/>
+      <c r="E194" s="219"/>
+      <c r="F194" s="233"/>
       <c r="G194" s="116" t="s">
         <v>392</v>
       </c>
@@ -9852,8 +9827,8 @@
       <c r="J194" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="K194" s="232"/>
-      <c r="L194" s="221"/>
+      <c r="K194" s="230"/>
+      <c r="L194" s="219"/>
       <c r="M194" s="12"/>
     </row>
     <row r="195" spans="1:2438" ht="167.25" customHeight="1">
@@ -9896,22 +9871,22 @@
       <c r="M195" s="12"/>
     </row>
     <row r="196" spans="1:2438" ht="53.25" customHeight="1">
-      <c r="A196" s="200">
+      <c r="A196" s="198">
         <v>60</v>
       </c>
-      <c r="B196" s="203">
+      <c r="B196" s="201">
         <v>46075</v>
       </c>
-      <c r="C196" s="200" t="s">
+      <c r="C196" s="198" t="s">
         <v>125</v>
       </c>
-      <c r="D196" s="206" t="s">
+      <c r="D196" s="204" t="s">
         <v>398</v>
       </c>
-      <c r="E196" s="200" t="s">
+      <c r="E196" s="198" t="s">
         <v>47</v>
       </c>
-      <c r="F196" s="229" t="s">
+      <c r="F196" s="227" t="s">
         <v>399</v>
       </c>
       <c r="G196" s="73" t="s">
@@ -9931,12 +9906,12 @@
       <c r="M196" s="12"/>
     </row>
     <row r="197" spans="1:2438" ht="59.25" customHeight="1">
-      <c r="A197" s="201"/>
-      <c r="B197" s="204"/>
-      <c r="C197" s="201"/>
-      <c r="D197" s="207"/>
-      <c r="E197" s="201"/>
-      <c r="F197" s="230"/>
+      <c r="A197" s="199"/>
+      <c r="B197" s="202"/>
+      <c r="C197" s="199"/>
+      <c r="D197" s="205"/>
+      <c r="E197" s="199"/>
+      <c r="F197" s="228"/>
       <c r="G197" s="73" t="s">
         <v>402</v>
       </c>
@@ -9952,12 +9927,12 @@
       <c r="M197" s="12"/>
     </row>
     <row r="198" spans="1:2438" ht="57" customHeight="1">
-      <c r="A198" s="201"/>
-      <c r="B198" s="204"/>
-      <c r="C198" s="201"/>
-      <c r="D198" s="207"/>
-      <c r="E198" s="201"/>
-      <c r="F198" s="230"/>
+      <c r="A198" s="199"/>
+      <c r="B198" s="202"/>
+      <c r="C198" s="199"/>
+      <c r="D198" s="205"/>
+      <c r="E198" s="199"/>
+      <c r="F198" s="228"/>
       <c r="G198" s="73" t="s">
         <v>403</v>
       </c>
@@ -9973,12 +9948,12 @@
       <c r="M198" s="12"/>
     </row>
     <row r="199" spans="1:2438" ht="42.75" customHeight="1">
-      <c r="A199" s="202"/>
-      <c r="B199" s="205"/>
-      <c r="C199" s="202"/>
-      <c r="D199" s="208"/>
-      <c r="E199" s="202"/>
-      <c r="F199" s="231"/>
+      <c r="A199" s="200"/>
+      <c r="B199" s="203"/>
+      <c r="C199" s="200"/>
+      <c r="D199" s="206"/>
+      <c r="E199" s="200"/>
+      <c r="F199" s="229"/>
       <c r="G199" s="73" t="s">
         <v>404</v>
       </c>
@@ -10060,22 +10035,22 @@
       <c r="M201" s="12"/>
     </row>
     <row r="202" spans="1:2438" s="62" customFormat="1" ht="84.75" customHeight="1">
-      <c r="A202" s="316">
+      <c r="A202" s="314">
         <v>63</v>
       </c>
-      <c r="B202" s="317">
+      <c r="B202" s="315">
         <v>46082</v>
       </c>
-      <c r="C202" s="316" t="s">
+      <c r="C202" s="314" t="s">
         <v>409</v>
       </c>
-      <c r="D202" s="318" t="s">
+      <c r="D202" s="316" t="s">
         <v>410</v>
       </c>
-      <c r="E202" s="316" t="s">
+      <c r="E202" s="314" t="s">
         <v>47</v>
       </c>
-      <c r="F202" s="310" t="s">
+      <c r="F202" s="308" t="s">
         <v>411</v>
       </c>
       <c r="G202" s="119" t="s">
@@ -12520,12 +12495,12 @@
       <c r="COT202"/>
     </row>
     <row r="203" spans="1:2438" s="62" customFormat="1" ht="78" customHeight="1">
-      <c r="A203" s="316"/>
-      <c r="B203" s="317"/>
-      <c r="C203" s="316"/>
-      <c r="D203" s="318"/>
-      <c r="E203" s="316"/>
-      <c r="F203" s="311"/>
+      <c r="A203" s="314"/>
+      <c r="B203" s="315"/>
+      <c r="C203" s="314"/>
+      <c r="D203" s="316"/>
+      <c r="E203" s="314"/>
+      <c r="F203" s="309"/>
       <c r="G203" s="120" t="s">
         <v>414</v>
       </c>
@@ -14968,22 +14943,22 @@
       <c r="COT203"/>
     </row>
     <row r="204" spans="1:2438" s="62" customFormat="1" ht="78" customHeight="1">
-      <c r="A204" s="314">
+      <c r="A204" s="312">
         <v>64</v>
       </c>
-      <c r="B204" s="312">
+      <c r="B204" s="310">
         <v>46082</v>
       </c>
-      <c r="C204" s="314" t="s">
+      <c r="C204" s="312" t="s">
         <v>265</v>
       </c>
-      <c r="D204" s="319" t="s">
+      <c r="D204" s="317" t="s">
         <v>417</v>
       </c>
-      <c r="E204" s="314" t="s">
+      <c r="E204" s="312" t="s">
         <v>47</v>
       </c>
-      <c r="F204" s="310" t="s">
+      <c r="F204" s="308" t="s">
         <v>418</v>
       </c>
       <c r="G204" s="120" t="s">
@@ -17428,12 +17403,12 @@
       <c r="COT204"/>
     </row>
     <row r="205" spans="1:2438" s="62" customFormat="1" ht="142.5" customHeight="1">
-      <c r="A205" s="315"/>
-      <c r="B205" s="313"/>
-      <c r="C205" s="315"/>
-      <c r="D205" s="320"/>
-      <c r="E205" s="315"/>
-      <c r="F205" s="311"/>
+      <c r="A205" s="313"/>
+      <c r="B205" s="311"/>
+      <c r="C205" s="313"/>
+      <c r="D205" s="318"/>
+      <c r="E205" s="313"/>
+      <c r="F205" s="309"/>
       <c r="G205" s="120" t="s">
         <v>421</v>
       </c>
@@ -19876,22 +19851,22 @@
       <c r="COT205"/>
     </row>
     <row r="206" spans="1:2438" s="62" customFormat="1" ht="95.25" customHeight="1">
-      <c r="A206" s="314">
+      <c r="A206" s="312">
         <v>65</v>
       </c>
-      <c r="B206" s="312">
+      <c r="B206" s="310">
         <v>46096</v>
       </c>
-      <c r="C206" s="314" t="s">
+      <c r="C206" s="312" t="s">
         <v>265</v>
       </c>
-      <c r="D206" s="319" t="s">
+      <c r="D206" s="317" t="s">
         <v>423</v>
       </c>
-      <c r="E206" s="314" t="s">
+      <c r="E206" s="312" t="s">
         <v>47</v>
       </c>
-      <c r="F206" s="310" t="s">
+      <c r="F206" s="308" t="s">
         <v>424</v>
       </c>
       <c r="G206" s="120" t="s">
@@ -22336,12 +22311,12 @@
       <c r="COT206"/>
     </row>
     <row r="207" spans="1:2438" s="62" customFormat="1" ht="61.5" customHeight="1">
-      <c r="A207" s="315"/>
-      <c r="B207" s="313"/>
-      <c r="C207" s="315"/>
-      <c r="D207" s="320"/>
-      <c r="E207" s="315"/>
-      <c r="F207" s="311"/>
+      <c r="A207" s="313"/>
+      <c r="B207" s="311"/>
+      <c r="C207" s="313"/>
+      <c r="D207" s="318"/>
+      <c r="E207" s="313"/>
+      <c r="F207" s="309"/>
       <c r="G207" s="120" t="s">
         <v>427</v>
       </c>
@@ -24784,22 +24759,22 @@
       <c r="COT207"/>
     </row>
     <row r="208" spans="1:2438" s="62" customFormat="1" ht="87" customHeight="1">
-      <c r="A208" s="319">
+      <c r="A208" s="317">
         <v>66</v>
       </c>
-      <c r="B208" s="321">
+      <c r="B208" s="319">
         <v>46097</v>
       </c>
-      <c r="C208" s="319" t="s">
+      <c r="C208" s="317" t="s">
         <v>125</v>
       </c>
-      <c r="D208" s="327" t="s">
+      <c r="D208" s="325" t="s">
         <v>428</v>
       </c>
-      <c r="E208" s="319" t="s">
+      <c r="E208" s="317" t="s">
         <v>47</v>
       </c>
-      <c r="F208" s="310" t="s">
+      <c r="F208" s="308" t="s">
         <v>429</v>
       </c>
       <c r="G208" s="120" t="s">
@@ -27244,12 +27219,12 @@
       <c r="COT208"/>
     </row>
     <row r="209" spans="1:2438" s="62" customFormat="1" ht="87" customHeight="1">
-      <c r="A209" s="325"/>
-      <c r="B209" s="326"/>
-      <c r="C209" s="325"/>
-      <c r="D209" s="328"/>
-      <c r="E209" s="325"/>
-      <c r="F209" s="329"/>
+      <c r="A209" s="323"/>
+      <c r="B209" s="324"/>
+      <c r="C209" s="323"/>
+      <c r="D209" s="326"/>
+      <c r="E209" s="323"/>
+      <c r="F209" s="327"/>
       <c r="G209" s="120" t="s">
         <v>431</v>
       </c>
@@ -29692,12 +29667,12 @@
       <c r="COT209"/>
     </row>
     <row r="210" spans="1:2438" s="62" customFormat="1" ht="43.5" customHeight="1">
-      <c r="A210" s="325"/>
-      <c r="B210" s="326"/>
-      <c r="C210" s="325"/>
-      <c r="D210" s="328"/>
-      <c r="E210" s="325"/>
-      <c r="F210" s="329"/>
+      <c r="A210" s="323"/>
+      <c r="B210" s="324"/>
+      <c r="C210" s="323"/>
+      <c r="D210" s="326"/>
+      <c r="E210" s="323"/>
+      <c r="F210" s="327"/>
       <c r="G210" s="120" t="s">
         <v>433</v>
       </c>
@@ -32140,12 +32115,12 @@
       <c r="COT210"/>
     </row>
     <row r="211" spans="1:2438" s="63" customFormat="1" ht="96.75" customHeight="1">
-      <c r="A211" s="325"/>
-      <c r="B211" s="326"/>
-      <c r="C211" s="325"/>
-      <c r="D211" s="328"/>
-      <c r="E211" s="325"/>
-      <c r="F211" s="329"/>
+      <c r="A211" s="323"/>
+      <c r="B211" s="324"/>
+      <c r="C211" s="323"/>
+      <c r="D211" s="326"/>
+      <c r="E211" s="323"/>
+      <c r="F211" s="327"/>
       <c r="G211" s="120" t="s">
         <v>435</v>
       </c>
@@ -34588,22 +34563,22 @@
       <c r="COT211"/>
     </row>
     <row r="212" spans="1:2438" s="63" customFormat="1" ht="90" customHeight="1">
-      <c r="A212" s="220">
+      <c r="A212" s="218">
         <v>67</v>
       </c>
-      <c r="B212" s="234">
+      <c r="B212" s="232">
         <v>46099</v>
       </c>
-      <c r="C212" s="220" t="s">
+      <c r="C212" s="218" t="s">
         <v>125</v>
       </c>
-      <c r="D212" s="220" t="s">
+      <c r="D212" s="218" t="s">
         <v>436</v>
       </c>
-      <c r="E212" s="266" t="s">
+      <c r="E212" s="264" t="s">
         <v>182</v>
       </c>
-      <c r="F212" s="305" t="s">
+      <c r="F212" s="303" t="s">
         <v>437</v>
       </c>
       <c r="G212" s="121" t="s">
@@ -37052,12 +37027,12 @@
       <c r="COT212"/>
     </row>
     <row r="213" spans="1:2438" s="63" customFormat="1" ht="90" customHeight="1">
-      <c r="A213" s="325"/>
-      <c r="B213" s="326"/>
-      <c r="C213" s="325"/>
-      <c r="D213" s="325"/>
-      <c r="E213" s="325"/>
-      <c r="F213" s="330"/>
+      <c r="A213" s="323"/>
+      <c r="B213" s="324"/>
+      <c r="C213" s="323"/>
+      <c r="D213" s="323"/>
+      <c r="E213" s="323"/>
+      <c r="F213" s="328"/>
       <c r="G213" s="120" t="s">
         <v>441</v>
       </c>
@@ -39500,12 +39475,12 @@
       <c r="COT213"/>
     </row>
     <row r="214" spans="1:2438" s="65" customFormat="1" ht="34.5" customHeight="1">
-      <c r="A214" s="320"/>
-      <c r="B214" s="322"/>
-      <c r="C214" s="320"/>
-      <c r="D214" s="320"/>
-      <c r="E214" s="320"/>
-      <c r="F214" s="324"/>
+      <c r="A214" s="318"/>
+      <c r="B214" s="320"/>
+      <c r="C214" s="318"/>
+      <c r="D214" s="318"/>
+      <c r="E214" s="318"/>
+      <c r="F214" s="322"/>
       <c r="G214" s="120" t="s">
         <v>443</v>
       </c>
@@ -41948,22 +41923,22 @@
       <c r="COT214"/>
     </row>
     <row r="215" spans="1:2438" s="63" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A215" s="319">
+      <c r="A215" s="317">
         <v>68</v>
       </c>
-      <c r="B215" s="321">
+      <c r="B215" s="319">
         <v>46102</v>
       </c>
-      <c r="C215" s="319" t="s">
+      <c r="C215" s="317" t="s">
         <v>265</v>
       </c>
-      <c r="D215" s="319" t="s">
+      <c r="D215" s="317" t="s">
         <v>444</v>
       </c>
-      <c r="E215" s="319" t="s">
+      <c r="E215" s="317" t="s">
         <v>47</v>
       </c>
-      <c r="F215" s="323" t="s">
+      <c r="F215" s="321" t="s">
         <v>445</v>
       </c>
       <c r="G215" s="120" t="s">
@@ -44408,12 +44383,12 @@
       <c r="COT215"/>
     </row>
     <row r="216" spans="1:2438" s="63" customFormat="1" ht="90" customHeight="1">
-      <c r="A216" s="320"/>
-      <c r="B216" s="322"/>
-      <c r="C216" s="320"/>
-      <c r="D216" s="320"/>
-      <c r="E216" s="320"/>
-      <c r="F216" s="324"/>
+      <c r="A216" s="318"/>
+      <c r="B216" s="320"/>
+      <c r="C216" s="318"/>
+      <c r="D216" s="318"/>
+      <c r="E216" s="318"/>
+      <c r="F216" s="322"/>
       <c r="G216" s="122" t="s">
         <v>448</v>
       </c>
@@ -46856,22 +46831,22 @@
       <c r="COT216"/>
     </row>
     <row r="217" spans="1:2438" s="63" customFormat="1" ht="135" customHeight="1">
-      <c r="A217" s="319">
+      <c r="A217" s="317">
         <v>69</v>
       </c>
-      <c r="B217" s="321">
+      <c r="B217" s="319">
         <v>46106</v>
       </c>
-      <c r="C217" s="319" t="s">
+      <c r="C217" s="317" t="s">
         <v>265</v>
       </c>
-      <c r="D217" s="331" t="s">
+      <c r="D217" s="329" t="s">
         <v>449</v>
       </c>
-      <c r="E217" s="319" t="s">
+      <c r="E217" s="317" t="s">
         <v>47</v>
       </c>
-      <c r="F217" s="333" t="s">
+      <c r="F217" s="331" t="s">
         <v>450</v>
       </c>
       <c r="G217" s="71" t="s">
@@ -49316,12 +49291,12 @@
       <c r="COT217"/>
     </row>
     <row r="218" spans="1:2438" s="63" customFormat="1" ht="116.25" customHeight="1">
-      <c r="A218" s="320"/>
-      <c r="B218" s="322"/>
-      <c r="C218" s="320"/>
-      <c r="D218" s="332"/>
-      <c r="E218" s="320"/>
-      <c r="F218" s="334"/>
+      <c r="A218" s="318"/>
+      <c r="B218" s="320"/>
+      <c r="C218" s="318"/>
+      <c r="D218" s="330"/>
+      <c r="E218" s="318"/>
+      <c r="F218" s="332"/>
       <c r="G218" s="71" t="s">
         <v>454</v>
       </c>
@@ -51764,22 +51739,22 @@
       <c r="COT218"/>
     </row>
     <row r="219" spans="1:2438" s="63" customFormat="1" ht="86.45" customHeight="1">
-      <c r="A219" s="319">
+      <c r="A219" s="317">
         <v>70</v>
       </c>
-      <c r="B219" s="321">
+      <c r="B219" s="319">
         <v>46107</v>
       </c>
-      <c r="C219" s="319" t="s">
+      <c r="C219" s="317" t="s">
         <v>265</v>
       </c>
-      <c r="D219" s="319" t="s">
+      <c r="D219" s="317" t="s">
         <v>456</v>
       </c>
-      <c r="E219" s="319" t="s">
+      <c r="E219" s="317" t="s">
         <v>47</v>
       </c>
-      <c r="F219" s="323" t="s">
+      <c r="F219" s="321" t="s">
         <v>457</v>
       </c>
       <c r="G219" s="173" t="s">
@@ -51788,7 +51763,7 @@
       <c r="H219" s="86" t="s">
         <v>415</v>
       </c>
-      <c r="I219" s="185">
+      <c r="I219" s="184">
         <v>46137</v>
       </c>
       <c r="J219" s="87" t="s">
@@ -54224,16 +54199,16 @@
       <c r="COT219"/>
     </row>
     <row r="220" spans="1:2438" s="63" customFormat="1" ht="86.45" customHeight="1">
-      <c r="A220" s="325"/>
-      <c r="B220" s="326"/>
-      <c r="C220" s="325"/>
-      <c r="D220" s="325"/>
-      <c r="E220" s="325"/>
-      <c r="F220" s="330"/>
+      <c r="A220" s="323"/>
+      <c r="B220" s="324"/>
+      <c r="C220" s="323"/>
+      <c r="D220" s="323"/>
+      <c r="E220" s="323"/>
+      <c r="F220" s="328"/>
       <c r="G220" s="140" t="s">
         <v>459</v>
       </c>
-      <c r="H220" s="183" t="s">
+      <c r="H220" s="182" t="s">
         <v>415</v>
       </c>
       <c r="I220" s="61">
@@ -56672,19 +56647,19 @@
       <c r="COT220"/>
     </row>
     <row r="221" spans="1:2438" s="63" customFormat="1" ht="90" customHeight="1">
-      <c r="A221" s="325"/>
-      <c r="B221" s="326"/>
-      <c r="C221" s="325"/>
-      <c r="D221" s="325"/>
-      <c r="E221" s="325"/>
-      <c r="F221" s="330"/>
+      <c r="A221" s="323"/>
+      <c r="B221" s="324"/>
+      <c r="C221" s="323"/>
+      <c r="D221" s="323"/>
+      <c r="E221" s="323"/>
+      <c r="F221" s="328"/>
       <c r="G221" s="122" t="s">
         <v>460</v>
       </c>
       <c r="H221" s="141" t="s">
         <v>415</v>
       </c>
-      <c r="I221" s="182">
+      <c r="I221" s="181">
         <v>46137</v>
       </c>
       <c r="J221" s="92" t="s">
@@ -59141,10 +59116,10 @@
       <c r="G222" s="123" t="s">
         <v>463</v>
       </c>
-      <c r="H222" s="184" t="s">
+      <c r="H222" s="183" t="s">
         <v>464</v>
       </c>
-      <c r="I222" s="182">
+      <c r="I222" s="181">
         <v>46137</v>
       </c>
       <c r="J222" s="92" t="s">
@@ -59157,22 +59132,22 @@
       </c>
     </row>
     <row r="223" spans="1:2438" ht="147.75" customHeight="1">
-      <c r="A223" s="232">
+      <c r="A223" s="230">
         <v>72</v>
       </c>
-      <c r="B223" s="222">
+      <c r="B223" s="220">
         <v>46127</v>
       </c>
-      <c r="C223" s="221" t="s">
+      <c r="C223" s="219" t="s">
         <v>265</v>
       </c>
-      <c r="D223" s="220" t="s">
+      <c r="D223" s="218" t="s">
         <v>465</v>
       </c>
-      <c r="E223" s="226" t="s">
+      <c r="E223" s="224" t="s">
         <v>182</v>
       </c>
-      <c r="F223" s="235" t="s">
+      <c r="F223" s="233" t="s">
         <v>466</v>
       </c>
       <c r="G223" s="124" t="s">
@@ -59181,7 +59156,7 @@
       <c r="H223" s="103" t="s">
         <v>468</v>
       </c>
-      <c r="I223" s="186" t="s">
+      <c r="I223" s="185" t="s">
         <v>469</v>
       </c>
       <c r="J223" s="87" t="s">
@@ -59194,12 +59169,12 @@
       </c>
     </row>
     <row r="224" spans="1:2438" ht="84.75" customHeight="1">
-      <c r="A224" s="223"/>
-      <c r="B224" s="222"/>
-      <c r="C224" s="221"/>
-      <c r="D224" s="220"/>
-      <c r="E224" s="226"/>
-      <c r="F224" s="235"/>
+      <c r="A224" s="221"/>
+      <c r="B224" s="220"/>
+      <c r="C224" s="219"/>
+      <c r="D224" s="218"/>
+      <c r="E224" s="224"/>
+      <c r="F224" s="233"/>
       <c r="G224" s="125" t="s">
         <v>470</v>
       </c>
@@ -59217,22 +59192,22 @@
       <c r="M224" s="12"/>
     </row>
     <row r="225" spans="1:13" ht="87.75" customHeight="1">
-      <c r="A225" s="221">
+      <c r="A225" s="219">
         <v>73</v>
       </c>
-      <c r="B225" s="205">
+      <c r="B225" s="203">
         <v>46132</v>
       </c>
-      <c r="C225" s="202" t="s">
+      <c r="C225" s="200" t="s">
         <v>125</v>
       </c>
-      <c r="D225" s="208" t="s">
+      <c r="D225" s="206" t="s">
         <v>472</v>
       </c>
-      <c r="E225" s="202" t="s">
+      <c r="E225" s="200" t="s">
         <v>47</v>
       </c>
-      <c r="F225" s="335" t="s">
+      <c r="F225" s="333" t="s">
         <v>473</v>
       </c>
       <c r="G225" s="13" t="s">
@@ -59252,12 +59227,12 @@
       <c r="M225" s="12"/>
     </row>
     <row r="226" spans="1:13" ht="87.75" customHeight="1">
-      <c r="A226" s="221"/>
-      <c r="B226" s="222"/>
-      <c r="C226" s="221"/>
-      <c r="D226" s="220"/>
-      <c r="E226" s="221"/>
-      <c r="F226" s="235"/>
+      <c r="A226" s="219"/>
+      <c r="B226" s="220"/>
+      <c r="C226" s="219"/>
+      <c r="D226" s="218"/>
+      <c r="E226" s="219"/>
+      <c r="F226" s="233"/>
       <c r="G226" s="13" t="s">
         <v>476</v>
       </c>
@@ -59275,12 +59250,12 @@
       <c r="M226" s="12"/>
     </row>
     <row r="227" spans="1:13" ht="87.75" customHeight="1">
-      <c r="A227" s="200"/>
-      <c r="B227" s="203"/>
-      <c r="C227" s="200"/>
-      <c r="D227" s="206"/>
-      <c r="E227" s="200"/>
-      <c r="F227" s="336"/>
+      <c r="A227" s="198"/>
+      <c r="B227" s="201"/>
+      <c r="C227" s="198"/>
+      <c r="D227" s="204"/>
+      <c r="E227" s="198"/>
+      <c r="F227" s="334"/>
       <c r="G227" s="73" t="s">
         <v>477</v>
       </c>
@@ -59298,22 +59273,22 @@
       <c r="M227" s="12"/>
     </row>
     <row r="228" spans="1:13" ht="42" customHeight="1">
-      <c r="A228" s="221">
+      <c r="A228" s="219">
         <v>74</v>
       </c>
-      <c r="B228" s="222">
+      <c r="B228" s="220">
         <v>46135</v>
       </c>
-      <c r="C228" s="221" t="s">
+      <c r="C228" s="219" t="s">
         <v>125</v>
       </c>
-      <c r="D228" s="220" t="s">
+      <c r="D228" s="218" t="s">
         <v>478</v>
       </c>
-      <c r="E228" s="221" t="s">
+      <c r="E228" s="219" t="s">
         <v>47</v>
       </c>
-      <c r="F228" s="235" t="s">
+      <c r="F228" s="233" t="s">
         <v>479</v>
       </c>
       <c r="G228" s="13" t="s">
@@ -59333,12 +59308,12 @@
       <c r="M228" s="12"/>
     </row>
     <row r="229" spans="1:13" ht="54" customHeight="1">
-      <c r="A229" s="221"/>
-      <c r="B229" s="222"/>
-      <c r="C229" s="221"/>
-      <c r="D229" s="220"/>
-      <c r="E229" s="221"/>
-      <c r="F229" s="235"/>
+      <c r="A229" s="219"/>
+      <c r="B229" s="220"/>
+      <c r="C229" s="219"/>
+      <c r="D229" s="218"/>
+      <c r="E229" s="219"/>
+      <c r="F229" s="233"/>
       <c r="G229" s="13" t="s">
         <v>481</v>
       </c>
@@ -59356,12 +59331,12 @@
       <c r="M229" s="12"/>
     </row>
     <row r="230" spans="1:13" ht="42" customHeight="1">
-      <c r="A230" s="221"/>
-      <c r="B230" s="222"/>
-      <c r="C230" s="221"/>
-      <c r="D230" s="220"/>
-      <c r="E230" s="221"/>
-      <c r="F230" s="235"/>
+      <c r="A230" s="219"/>
+      <c r="B230" s="220"/>
+      <c r="C230" s="219"/>
+      <c r="D230" s="218"/>
+      <c r="E230" s="219"/>
+      <c r="F230" s="233"/>
       <c r="G230" s="115" t="s">
         <v>483</v>
       </c>
@@ -59379,12 +59354,12 @@
       <c r="M230" s="12"/>
     </row>
     <row r="231" spans="1:13" ht="44.25" customHeight="1">
-      <c r="A231" s="221"/>
-      <c r="B231" s="222"/>
-      <c r="C231" s="221"/>
-      <c r="D231" s="220"/>
-      <c r="E231" s="221"/>
-      <c r="F231" s="235"/>
+      <c r="A231" s="219"/>
+      <c r="B231" s="220"/>
+      <c r="C231" s="219"/>
+      <c r="D231" s="218"/>
+      <c r="E231" s="219"/>
+      <c r="F231" s="233"/>
       <c r="G231" s="115" t="s">
         <v>484</v>
       </c>
@@ -59402,22 +59377,22 @@
       <c r="M231" s="12"/>
     </row>
     <row r="232" spans="1:13" ht="77.25" customHeight="1">
-      <c r="A232" s="221">
+      <c r="A232" s="219">
         <v>75</v>
       </c>
-      <c r="B232" s="222">
+      <c r="B232" s="220">
         <v>46135</v>
       </c>
-      <c r="C232" s="221" t="s">
+      <c r="C232" s="219" t="s">
         <v>125</v>
       </c>
-      <c r="D232" s="220" t="s">
+      <c r="D232" s="218" t="s">
         <v>485</v>
       </c>
-      <c r="E232" s="221" t="s">
+      <c r="E232" s="219" t="s">
         <v>47</v>
       </c>
-      <c r="F232" s="235" t="s">
+      <c r="F232" s="233" t="s">
         <v>486</v>
       </c>
       <c r="G232" s="115" t="s">
@@ -59439,12 +59414,12 @@
       <c r="M232" s="12"/>
     </row>
     <row r="233" spans="1:13" ht="42" customHeight="1">
-      <c r="A233" s="221"/>
-      <c r="B233" s="221"/>
-      <c r="C233" s="221"/>
-      <c r="D233" s="220"/>
-      <c r="E233" s="221"/>
-      <c r="F233" s="235"/>
+      <c r="A233" s="219"/>
+      <c r="B233" s="219"/>
+      <c r="C233" s="219"/>
+      <c r="D233" s="218"/>
+      <c r="E233" s="219"/>
+      <c r="F233" s="233"/>
       <c r="G233" s="13" t="s">
         <v>489</v>
       </c>
@@ -59462,12 +59437,12 @@
       <c r="M233" s="12"/>
     </row>
     <row r="234" spans="1:13" ht="52.5" customHeight="1">
-      <c r="A234" s="200"/>
-      <c r="B234" s="200"/>
-      <c r="C234" s="200"/>
-      <c r="D234" s="206"/>
-      <c r="E234" s="200"/>
-      <c r="F234" s="336"/>
+      <c r="A234" s="198"/>
+      <c r="B234" s="198"/>
+      <c r="C234" s="198"/>
+      <c r="D234" s="204"/>
+      <c r="E234" s="198"/>
+      <c r="F234" s="334"/>
       <c r="G234" s="118" t="s">
         <v>491</v>
       </c>
@@ -59485,22 +59460,22 @@
       <c r="M234" s="12"/>
     </row>
     <row r="235" spans="1:13" ht="52.5" customHeight="1">
-      <c r="A235" s="200">
+      <c r="A235" s="198">
         <v>77</v>
       </c>
-      <c r="B235" s="203">
+      <c r="B235" s="201">
         <v>46140</v>
       </c>
-      <c r="C235" s="200" t="s">
+      <c r="C235" s="198" t="s">
         <v>493</v>
       </c>
-      <c r="D235" s="206" t="s">
+      <c r="D235" s="204" t="s">
         <v>494</v>
       </c>
-      <c r="E235" s="200" t="s">
+      <c r="E235" s="198" t="s">
         <v>47</v>
       </c>
-      <c r="F235" s="206" t="s">
+      <c r="F235" s="204" t="s">
         <v>495</v>
       </c>
       <c r="G235" s="118" t="s">
@@ -59520,12 +59495,12 @@
       <c r="M235" s="60"/>
     </row>
     <row r="236" spans="1:13" ht="53.25" customHeight="1">
-      <c r="A236" s="201"/>
-      <c r="B236" s="204"/>
-      <c r="C236" s="201"/>
-      <c r="D236" s="207"/>
-      <c r="E236" s="201"/>
-      <c r="F236" s="207"/>
+      <c r="A236" s="199"/>
+      <c r="B236" s="202"/>
+      <c r="C236" s="199"/>
+      <c r="D236" s="205"/>
+      <c r="E236" s="199"/>
+      <c r="F236" s="205"/>
       <c r="G236" s="133" t="s">
         <v>499</v>
       </c>
@@ -59543,22 +59518,22 @@
       <c r="M236" s="60"/>
     </row>
     <row r="237" spans="1:13" ht="149.25" customHeight="1">
-      <c r="A237" s="221">
+      <c r="A237" s="219">
         <v>78</v>
       </c>
-      <c r="B237" s="222">
+      <c r="B237" s="220">
         <v>46145</v>
       </c>
-      <c r="C237" s="220" t="s">
+      <c r="C237" s="218" t="s">
         <v>501</v>
       </c>
-      <c r="D237" s="220" t="s">
+      <c r="D237" s="218" t="s">
         <v>502</v>
       </c>
-      <c r="E237" s="221" t="s">
+      <c r="E237" s="219" t="s">
         <v>182</v>
       </c>
-      <c r="F237" s="337" t="s">
+      <c r="F237" s="335" t="s">
         <v>503</v>
       </c>
       <c r="G237" s="145" t="s">
@@ -59573,21 +59548,21 @@
       <c r="J237" s="127" t="s">
         <v>20</v>
       </c>
-      <c r="K237" s="368" t="s">
+      <c r="K237" s="366" t="s">
         <v>506</v>
       </c>
       <c r="L237" s="98"/>
-      <c r="M237" s="369" t="s">
+      <c r="M237" s="367" t="s">
         <v>507</v>
       </c>
     </row>
     <row r="238" spans="1:13" ht="82.5" customHeight="1">
-      <c r="A238" s="201"/>
-      <c r="B238" s="204"/>
-      <c r="C238" s="207"/>
-      <c r="D238" s="207"/>
-      <c r="E238" s="201"/>
-      <c r="F238" s="217"/>
+      <c r="A238" s="199"/>
+      <c r="B238" s="202"/>
+      <c r="C238" s="205"/>
+      <c r="D238" s="205"/>
+      <c r="E238" s="199"/>
+      <c r="F238" s="215"/>
       <c r="G238" s="126" t="s">
         <v>508</v>
       </c>
@@ -59602,15 +59577,15 @@
       </c>
       <c r="K238" s="5"/>
       <c r="L238" s="98"/>
-      <c r="M238" s="227"/>
+      <c r="M238" s="225"/>
     </row>
     <row r="239" spans="1:13" ht="54" customHeight="1">
-      <c r="A239" s="202"/>
-      <c r="B239" s="205"/>
-      <c r="C239" s="208"/>
-      <c r="D239" s="208"/>
-      <c r="E239" s="202"/>
-      <c r="F239" s="218"/>
+      <c r="A239" s="200"/>
+      <c r="B239" s="203"/>
+      <c r="C239" s="206"/>
+      <c r="D239" s="206"/>
+      <c r="E239" s="200"/>
+      <c r="F239" s="216"/>
       <c r="G239" s="128" t="s">
         <v>509</v>
       </c>
@@ -59625,25 +59600,25 @@
       </c>
       <c r="K239" s="60"/>
       <c r="L239" s="95"/>
-      <c r="M239" s="228"/>
+      <c r="M239" s="226"/>
     </row>
     <row r="240" spans="1:13" ht="66" customHeight="1">
-      <c r="A240" s="200">
+      <c r="A240" s="198">
         <v>79</v>
       </c>
-      <c r="B240" s="203">
+      <c r="B240" s="201">
         <v>46145</v>
       </c>
-      <c r="C240" s="206" t="s">
+      <c r="C240" s="204" t="s">
         <v>501</v>
       </c>
-      <c r="D240" s="206" t="s">
+      <c r="D240" s="204" t="s">
         <v>510</v>
       </c>
-      <c r="E240" s="200" t="s">
+      <c r="E240" s="198" t="s">
         <v>27</v>
       </c>
-      <c r="F240" s="216" t="s">
+      <c r="F240" s="214" t="s">
         <v>511</v>
       </c>
       <c r="G240" s="14" t="s">
@@ -59663,12 +59638,12 @@
       <c r="M240" s="115"/>
     </row>
     <row r="241" spans="1:13" ht="81.75" customHeight="1">
-      <c r="A241" s="202"/>
-      <c r="B241" s="205"/>
-      <c r="C241" s="208"/>
-      <c r="D241" s="208"/>
-      <c r="E241" s="202"/>
-      <c r="F241" s="218"/>
+      <c r="A241" s="200"/>
+      <c r="B241" s="203"/>
+      <c r="C241" s="206"/>
+      <c r="D241" s="206"/>
+      <c r="E241" s="200"/>
+      <c r="F241" s="216"/>
       <c r="G241" s="139" t="s">
         <v>515</v>
       </c>
@@ -59717,22 +59692,22 @@
       <c r="M242" s="60"/>
     </row>
     <row r="243" spans="1:13" ht="76.5" customHeight="1">
-      <c r="A243" s="200">
+      <c r="A243" s="198">
         <v>81</v>
       </c>
-      <c r="B243" s="203">
+      <c r="B243" s="201">
         <v>46154</v>
       </c>
-      <c r="C243" s="200" t="s">
+      <c r="C243" s="198" t="s">
         <v>125</v>
       </c>
-      <c r="D243" s="206" t="s">
+      <c r="D243" s="204" t="s">
         <v>520</v>
       </c>
-      <c r="E243" s="200" t="s">
+      <c r="E243" s="198" t="s">
         <v>521</v>
       </c>
-      <c r="F243" s="214" t="s">
+      <c r="F243" s="212" t="s">
         <v>522</v>
       </c>
       <c r="G243" s="137" t="s">
@@ -59748,12 +59723,12 @@
       <c r="M243" s="60"/>
     </row>
     <row r="244" spans="1:13" ht="76.5" customHeight="1">
-      <c r="A244" s="201"/>
-      <c r="B244" s="204"/>
-      <c r="C244" s="201"/>
-      <c r="D244" s="207"/>
-      <c r="E244" s="201"/>
-      <c r="F244" s="338"/>
+      <c r="A244" s="199"/>
+      <c r="B244" s="202"/>
+      <c r="C244" s="199"/>
+      <c r="D244" s="205"/>
+      <c r="E244" s="199"/>
+      <c r="F244" s="336"/>
       <c r="G244" s="118" t="s">
         <v>524</v>
       </c>
@@ -59767,12 +59742,12 @@
       <c r="M244" s="60"/>
     </row>
     <row r="245" spans="1:13" ht="85.5" customHeight="1">
-      <c r="A245" s="202"/>
-      <c r="B245" s="205"/>
-      <c r="C245" s="202"/>
-      <c r="D245" s="208"/>
-      <c r="E245" s="202"/>
-      <c r="F245" s="215"/>
+      <c r="A245" s="200"/>
+      <c r="B245" s="203"/>
+      <c r="C245" s="200"/>
+      <c r="D245" s="206"/>
+      <c r="E245" s="200"/>
+      <c r="F245" s="213"/>
       <c r="G245" s="13" t="s">
         <v>525</v>
       </c>
@@ -59817,22 +59792,22 @@
       <c r="M246" s="5"/>
     </row>
     <row r="247" spans="1:13" ht="85.5" customHeight="1">
-      <c r="A247" s="200">
+      <c r="A247" s="198">
         <v>83</v>
       </c>
-      <c r="B247" s="203">
+      <c r="B247" s="201">
         <v>46158</v>
       </c>
-      <c r="C247" s="200" t="s">
+      <c r="C247" s="198" t="s">
         <v>125</v>
       </c>
-      <c r="D247" s="200" t="s">
+      <c r="D247" s="198" t="s">
         <v>529</v>
       </c>
-      <c r="E247" s="200" t="s">
+      <c r="E247" s="198" t="s">
         <v>521</v>
       </c>
-      <c r="F247" s="214" t="s">
+      <c r="F247" s="212" t="s">
         <v>530</v>
       </c>
       <c r="G247" s="58" t="s">
@@ -59852,12 +59827,12 @@
       <c r="M247" s="5"/>
     </row>
     <row r="248" spans="1:13" ht="125.25" customHeight="1">
-      <c r="A248" s="202"/>
-      <c r="B248" s="205"/>
-      <c r="C248" s="202"/>
-      <c r="D248" s="202"/>
-      <c r="E248" s="202"/>
-      <c r="F248" s="215"/>
+      <c r="A248" s="200"/>
+      <c r="B248" s="203"/>
+      <c r="C248" s="200"/>
+      <c r="D248" s="200"/>
+      <c r="E248" s="200"/>
+      <c r="F248" s="213"/>
       <c r="G248" s="58" t="s">
         <v>534</v>
       </c>
@@ -59875,22 +59850,22 @@
       <c r="M248" s="5"/>
     </row>
     <row r="249" spans="1:13" ht="62.25" customHeight="1">
-      <c r="A249" s="200">
+      <c r="A249" s="198">
         <v>84</v>
       </c>
-      <c r="B249" s="203">
+      <c r="B249" s="201">
         <v>46166</v>
       </c>
-      <c r="C249" s="206" t="s">
+      <c r="C249" s="204" t="s">
         <v>501</v>
       </c>
-      <c r="D249" s="206" t="s">
+      <c r="D249" s="204" t="s">
         <v>537</v>
       </c>
-      <c r="E249" s="200" t="s">
+      <c r="E249" s="198" t="s">
         <v>27</v>
       </c>
-      <c r="F249" s="214" t="s">
+      <c r="F249" s="212" t="s">
         <v>538</v>
       </c>
       <c r="G249" s="137" t="s">
@@ -59910,12 +59885,12 @@
       <c r="M249" s="5"/>
     </row>
     <row r="250" spans="1:13" ht="68.25" customHeight="1">
-      <c r="A250" s="202"/>
-      <c r="B250" s="205"/>
-      <c r="C250" s="208"/>
-      <c r="D250" s="208"/>
-      <c r="E250" s="202"/>
-      <c r="F250" s="215"/>
+      <c r="A250" s="200"/>
+      <c r="B250" s="203"/>
+      <c r="C250" s="206"/>
+      <c r="D250" s="206"/>
+      <c r="E250" s="200"/>
+      <c r="F250" s="213"/>
       <c r="G250" s="100" t="s">
         <v>541</v>
       </c>
@@ -59935,22 +59910,22 @@
       <c r="M250" s="5"/>
     </row>
     <row r="251" spans="1:13" ht="63.75" customHeight="1">
-      <c r="A251" s="200">
+      <c r="A251" s="198">
         <v>85</v>
       </c>
-      <c r="B251" s="340">
+      <c r="B251" s="338">
         <v>46166</v>
       </c>
-      <c r="C251" s="206" t="s">
+      <c r="C251" s="204" t="s">
         <v>501</v>
       </c>
-      <c r="D251" s="206" t="s">
+      <c r="D251" s="204" t="s">
         <v>544</v>
       </c>
-      <c r="E251" s="200" t="s">
+      <c r="E251" s="198" t="s">
         <v>521</v>
       </c>
-      <c r="F251" s="214" t="s">
+      <c r="F251" s="212" t="s">
         <v>545</v>
       </c>
       <c r="G251" s="14" t="s">
@@ -59970,12 +59945,12 @@
       <c r="M251" s="5"/>
     </row>
     <row r="252" spans="1:13" ht="63.75" customHeight="1">
-      <c r="A252" s="201"/>
-      <c r="B252" s="341"/>
-      <c r="C252" s="207"/>
-      <c r="D252" s="207"/>
-      <c r="E252" s="201"/>
-      <c r="F252" s="338"/>
+      <c r="A252" s="199"/>
+      <c r="B252" s="339"/>
+      <c r="C252" s="205"/>
+      <c r="D252" s="205"/>
+      <c r="E252" s="199"/>
+      <c r="F252" s="336"/>
       <c r="G252" s="100" t="s">
         <v>548</v>
       </c>
@@ -59993,12 +59968,12 @@
       <c r="M252" s="5"/>
     </row>
     <row r="253" spans="1:13" ht="63.75" customHeight="1">
-      <c r="A253" s="201"/>
-      <c r="B253" s="341"/>
-      <c r="C253" s="207"/>
-      <c r="D253" s="207"/>
-      <c r="E253" s="201"/>
-      <c r="F253" s="338"/>
+      <c r="A253" s="199"/>
+      <c r="B253" s="339"/>
+      <c r="C253" s="205"/>
+      <c r="D253" s="205"/>
+      <c r="E253" s="199"/>
+      <c r="F253" s="336"/>
       <c r="G253" s="100" t="s">
         <v>549</v>
       </c>
@@ -60016,12 +59991,12 @@
       <c r="M253" s="5"/>
     </row>
     <row r="254" spans="1:13" ht="63.75" customHeight="1">
-      <c r="A254" s="201"/>
-      <c r="B254" s="341"/>
-      <c r="C254" s="207"/>
-      <c r="D254" s="207"/>
-      <c r="E254" s="201"/>
-      <c r="F254" s="338"/>
+      <c r="A254" s="199"/>
+      <c r="B254" s="339"/>
+      <c r="C254" s="205"/>
+      <c r="D254" s="205"/>
+      <c r="E254" s="199"/>
+      <c r="F254" s="336"/>
       <c r="G254" s="100" t="s">
         <v>550</v>
       </c>
@@ -60039,12 +60014,12 @@
       <c r="M254" s="5"/>
     </row>
     <row r="255" spans="1:13" ht="63.75" customHeight="1">
-      <c r="A255" s="201"/>
-      <c r="B255" s="341"/>
-      <c r="C255" s="207"/>
-      <c r="D255" s="207"/>
-      <c r="E255" s="201"/>
-      <c r="F255" s="338"/>
+      <c r="A255" s="199"/>
+      <c r="B255" s="339"/>
+      <c r="C255" s="205"/>
+      <c r="D255" s="205"/>
+      <c r="E255" s="199"/>
+      <c r="F255" s="336"/>
       <c r="G255" s="100" t="s">
         <v>552</v>
       </c>
@@ -60062,22 +60037,22 @@
       <c r="M255" s="5"/>
     </row>
     <row r="256" spans="1:13" ht="59.25" customHeight="1">
-      <c r="A256" s="221">
+      <c r="A256" s="219">
         <v>86</v>
       </c>
-      <c r="B256" s="222">
+      <c r="B256" s="220">
         <v>46167</v>
       </c>
-      <c r="C256" s="220" t="s">
+      <c r="C256" s="218" t="s">
         <v>265</v>
       </c>
-      <c r="D256" s="220" t="s">
+      <c r="D256" s="218" t="s">
         <v>554</v>
       </c>
-      <c r="E256" s="221" t="s">
+      <c r="E256" s="219" t="s">
         <v>521</v>
       </c>
-      <c r="F256" s="339" t="s">
+      <c r="F256" s="337" t="s">
         <v>555</v>
       </c>
       <c r="G256" s="163" t="s">
@@ -60097,12 +60072,12 @@
       <c r="M256" s="5"/>
     </row>
     <row r="257" spans="1:13" ht="59.25" customHeight="1">
-      <c r="A257" s="221"/>
-      <c r="B257" s="222"/>
-      <c r="C257" s="220"/>
-      <c r="D257" s="220"/>
-      <c r="E257" s="221"/>
-      <c r="F257" s="227"/>
+      <c r="A257" s="219"/>
+      <c r="B257" s="220"/>
+      <c r="C257" s="218"/>
+      <c r="D257" s="218"/>
+      <c r="E257" s="219"/>
+      <c r="F257" s="225"/>
       <c r="G257" s="163" t="s">
         <v>558</v>
       </c>
@@ -60120,12 +60095,12 @@
       <c r="M257" s="5"/>
     </row>
     <row r="258" spans="1:13" ht="59.25" customHeight="1">
-      <c r="A258" s="221"/>
-      <c r="B258" s="222"/>
-      <c r="C258" s="220"/>
-      <c r="D258" s="220"/>
-      <c r="E258" s="221"/>
-      <c r="F258" s="227"/>
+      <c r="A258" s="219"/>
+      <c r="B258" s="220"/>
+      <c r="C258" s="218"/>
+      <c r="D258" s="218"/>
+      <c r="E258" s="219"/>
+      <c r="F258" s="225"/>
       <c r="G258" s="163" t="s">
         <v>559</v>
       </c>
@@ -60143,12 +60118,12 @@
       <c r="M258" s="5"/>
     </row>
     <row r="259" spans="1:13" ht="67.5" customHeight="1">
-      <c r="A259" s="200"/>
-      <c r="B259" s="203"/>
-      <c r="C259" s="206"/>
-      <c r="D259" s="206"/>
-      <c r="E259" s="200"/>
-      <c r="F259" s="228"/>
+      <c r="A259" s="198"/>
+      <c r="B259" s="201"/>
+      <c r="C259" s="204"/>
+      <c r="D259" s="204"/>
+      <c r="E259" s="198"/>
+      <c r="F259" s="226"/>
       <c r="G259" s="164" t="s">
         <v>560</v>
       </c>
@@ -60166,22 +60141,22 @@
       <c r="M259" s="56"/>
     </row>
     <row r="260" spans="1:13" ht="67.5" customHeight="1">
-      <c r="A260" s="221">
+      <c r="A260" s="219">
         <v>87</v>
       </c>
-      <c r="B260" s="222">
+      <c r="B260" s="220">
         <v>46172</v>
       </c>
-      <c r="C260" s="221" t="s">
+      <c r="C260" s="219" t="s">
         <v>32</v>
       </c>
-      <c r="D260" s="220" t="s">
+      <c r="D260" s="218" t="s">
         <v>561</v>
       </c>
-      <c r="E260" s="221" t="s">
+      <c r="E260" s="219" t="s">
         <v>27</v>
       </c>
-      <c r="F260" s="337" t="s">
+      <c r="F260" s="335" t="s">
         <v>562</v>
       </c>
       <c r="G260" s="13" t="s">
@@ -60197,12 +60172,12 @@
       <c r="M260" s="5"/>
     </row>
     <row r="261" spans="1:13" ht="64.5" customHeight="1">
-      <c r="A261" s="221"/>
-      <c r="B261" s="222"/>
-      <c r="C261" s="221"/>
-      <c r="D261" s="220"/>
-      <c r="E261" s="221"/>
-      <c r="F261" s="220"/>
+      <c r="A261" s="219"/>
+      <c r="B261" s="220"/>
+      <c r="C261" s="219"/>
+      <c r="D261" s="218"/>
+      <c r="E261" s="219"/>
+      <c r="F261" s="218"/>
       <c r="G261" s="13" t="s">
         <v>565</v>
       </c>
@@ -60236,7 +60211,7 @@
       <c r="F262" s="13" t="s">
         <v>567</v>
       </c>
-      <c r="G262" s="2" t="s">
+      <c r="G262" s="13" t="s">
         <v>568</v>
       </c>
       <c r="H262" s="2" t="s">
@@ -60252,7 +60227,7 @@
       <c r="L262" s="5"/>
       <c r="M262" s="5"/>
     </row>
-    <row r="263" spans="1:13" ht="81" customHeight="1">
+    <row r="263" spans="1:13" ht="62.25" customHeight="1">
       <c r="A263" s="56">
         <v>89</v>
       </c>
@@ -60271,7 +60246,7 @@
       <c r="F263" s="137" t="s">
         <v>570</v>
       </c>
-      <c r="G263" s="56" t="s">
+      <c r="G263" s="118" t="s">
         <v>571</v>
       </c>
       <c r="H263" s="56"/>
@@ -60285,26 +60260,26 @@
         <v>572</v>
       </c>
     </row>
-    <row r="264" spans="1:13" ht="81" customHeight="1">
-      <c r="A264" s="219">
+    <row r="264" spans="1:13" ht="62.25" customHeight="1">
+      <c r="A264" s="217">
         <v>90</v>
       </c>
-      <c r="B264" s="203">
+      <c r="B264" s="201">
         <v>46192</v>
       </c>
-      <c r="C264" s="206" t="s">
+      <c r="C264" s="204" t="s">
         <v>125</v>
       </c>
-      <c r="D264" s="206" t="s">
+      <c r="D264" s="204" t="s">
         <v>573</v>
       </c>
-      <c r="E264" s="200" t="s">
+      <c r="E264" s="198" t="s">
         <v>521</v>
       </c>
-      <c r="F264" s="214" t="s">
+      <c r="F264" s="212" t="s">
         <v>574</v>
       </c>
-      <c r="G264" s="56" t="s">
+      <c r="G264" s="118" t="s">
         <v>575</v>
       </c>
       <c r="H264" s="56" t="s">
@@ -60320,14 +60295,14 @@
       <c r="L264" s="85"/>
       <c r="M264" s="58"/>
     </row>
-    <row r="265" spans="1:13" ht="81" customHeight="1">
-      <c r="A265" s="219"/>
-      <c r="B265" s="204"/>
-      <c r="C265" s="207"/>
-      <c r="D265" s="207"/>
-      <c r="E265" s="201"/>
-      <c r="F265" s="338"/>
-      <c r="G265" s="56" t="s">
+    <row r="265" spans="1:13" ht="62.25" customHeight="1">
+      <c r="A265" s="217"/>
+      <c r="B265" s="202"/>
+      <c r="C265" s="205"/>
+      <c r="D265" s="205"/>
+      <c r="E265" s="199"/>
+      <c r="F265" s="336"/>
+      <c r="G265" s="118" t="s">
         <v>577</v>
       </c>
       <c r="H265" s="56" t="s">
@@ -60343,14 +60318,14 @@
       <c r="L265" s="85"/>
       <c r="M265" s="58"/>
     </row>
-    <row r="266" spans="1:13" ht="81" customHeight="1">
-      <c r="A266" s="213"/>
-      <c r="B266" s="205"/>
-      <c r="C266" s="208"/>
-      <c r="D266" s="208"/>
-      <c r="E266" s="202"/>
-      <c r="F266" s="215"/>
-      <c r="G266" s="56" t="s">
+    <row r="266" spans="1:13" ht="62.25" customHeight="1">
+      <c r="A266" s="211"/>
+      <c r="B266" s="203"/>
+      <c r="C266" s="206"/>
+      <c r="D266" s="206"/>
+      <c r="E266" s="200"/>
+      <c r="F266" s="213"/>
+      <c r="G266" s="118" t="s">
         <v>579</v>
       </c>
       <c r="H266" s="56" t="s">
@@ -60367,22 +60342,22 @@
       <c r="M266" s="58"/>
     </row>
     <row r="267" spans="1:13" ht="63.75" customHeight="1">
-      <c r="A267" s="200">
+      <c r="A267" s="198">
         <v>91</v>
       </c>
-      <c r="B267" s="222">
+      <c r="B267" s="220">
         <v>46201</v>
       </c>
-      <c r="C267" s="220" t="s">
+      <c r="C267" s="218" t="s">
         <v>581</v>
       </c>
-      <c r="D267" s="220" t="s">
+      <c r="D267" s="218" t="s">
         <v>582</v>
       </c>
-      <c r="E267" s="226" t="s">
+      <c r="E267" s="224" t="s">
         <v>199</v>
       </c>
-      <c r="F267" s="346" t="s">
+      <c r="F267" s="344" t="s">
         <v>583</v>
       </c>
       <c r="G267" s="150" t="s">
@@ -60399,17 +60374,17 @@
       </c>
       <c r="K267" s="111"/>
       <c r="L267" s="12"/>
-      <c r="M267" s="345" t="s">
+      <c r="M267" s="343" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="268" spans="1:13" ht="44.25" customHeight="1">
-      <c r="A268" s="201"/>
-      <c r="B268" s="222"/>
-      <c r="C268" s="220"/>
-      <c r="D268" s="220"/>
-      <c r="E268" s="226"/>
-      <c r="F268" s="346"/>
+    <row r="268" spans="1:13" ht="51" customHeight="1">
+      <c r="A268" s="199"/>
+      <c r="B268" s="220"/>
+      <c r="C268" s="218"/>
+      <c r="D268" s="218"/>
+      <c r="E268" s="224"/>
+      <c r="F268" s="344"/>
       <c r="G268" s="14" t="s">
         <v>587</v>
       </c>
@@ -60424,15 +60399,15 @@
       </c>
       <c r="K268" s="169"/>
       <c r="L268" s="170"/>
-      <c r="M268" s="338"/>
+      <c r="M268" s="336"/>
     </row>
     <row r="269" spans="1:13" ht="54.75" customHeight="1">
-      <c r="A269" s="202"/>
-      <c r="B269" s="203"/>
-      <c r="C269" s="206"/>
-      <c r="D269" s="206"/>
-      <c r="E269" s="347"/>
-      <c r="F269" s="216"/>
+      <c r="A269" s="200"/>
+      <c r="B269" s="201"/>
+      <c r="C269" s="204"/>
+      <c r="D269" s="204"/>
+      <c r="E269" s="345"/>
+      <c r="F269" s="214"/>
       <c r="G269" s="139" t="s">
         <v>588</v>
       </c>
@@ -60447,25 +60422,25 @@
       </c>
       <c r="K269" s="60"/>
       <c r="L269" s="95"/>
-      <c r="M269" s="338"/>
+      <c r="M269" s="336"/>
     </row>
     <row r="270" spans="1:13" ht="63.75" customHeight="1">
-      <c r="A270" s="200">
+      <c r="A270" s="198">
         <v>92</v>
       </c>
-      <c r="B270" s="358">
+      <c r="B270" s="356">
         <v>46227</v>
       </c>
-      <c r="C270" s="356" t="s">
+      <c r="C270" s="354" t="s">
         <v>501</v>
       </c>
-      <c r="D270" s="356" t="s">
+      <c r="D270" s="354" t="s">
         <v>589</v>
       </c>
-      <c r="E270" s="355" t="s">
+      <c r="E270" s="353" t="s">
         <v>27</v>
       </c>
-      <c r="F270" s="353" t="s">
+      <c r="F270" s="351" t="s">
         <v>590</v>
       </c>
       <c r="G270" s="166" t="s">
@@ -60485,12 +60460,12 @@
       <c r="M270" s="58"/>
     </row>
     <row r="271" spans="1:13" ht="63.75" customHeight="1">
-      <c r="A271" s="201"/>
-      <c r="B271" s="359"/>
-      <c r="C271" s="357"/>
-      <c r="D271" s="357"/>
-      <c r="E271" s="212"/>
-      <c r="F271" s="354"/>
+      <c r="A271" s="199"/>
+      <c r="B271" s="357"/>
+      <c r="C271" s="355"/>
+      <c r="D271" s="355"/>
+      <c r="E271" s="210"/>
+      <c r="F271" s="352"/>
       <c r="G271" s="14" t="s">
         <v>593</v>
       </c>
@@ -60526,7 +60501,7 @@
       <c r="F272" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="G272" s="190" t="s">
+      <c r="G272" s="189" t="s">
         <v>30</v>
       </c>
       <c r="H272" s="43" t="s">
@@ -60549,28 +60524,28 @@
       </c>
     </row>
     <row r="273" spans="1:13" ht="98.25" customHeight="1">
-      <c r="A273" s="224">
+      <c r="A273" s="222">
         <v>94</v>
       </c>
-      <c r="B273" s="222">
+      <c r="B273" s="220">
         <v>46242</v>
       </c>
-      <c r="C273" s="350" t="s">
+      <c r="C273" s="348" t="s">
         <v>265</v>
       </c>
-      <c r="D273" s="208" t="s">
+      <c r="D273" s="206" t="s">
         <v>597</v>
       </c>
-      <c r="E273" s="348" t="s">
+      <c r="E273" s="346" t="s">
         <v>320</v>
       </c>
-      <c r="F273" s="218" t="s">
+      <c r="F273" s="216" t="s">
         <v>598</v>
       </c>
       <c r="G273" s="13" t="s">
         <v>599</v>
       </c>
-      <c r="H273" s="189" t="s">
+      <c r="H273" s="188" t="s">
         <v>600</v>
       </c>
       <c r="I273" s="4">
@@ -60581,18 +60556,18 @@
       </c>
       <c r="K273" s="12"/>
       <c r="L273" s="12"/>
-      <c r="M273" s="337" t="s">
+      <c r="M273" s="335" t="s">
         <v>601</v>
       </c>
     </row>
     <row r="274" spans="1:13" ht="68.25" customHeight="1">
-      <c r="A274" s="224"/>
-      <c r="B274" s="222"/>
-      <c r="C274" s="351"/>
-      <c r="D274" s="220"/>
-      <c r="E274" s="266"/>
-      <c r="F274" s="346"/>
-      <c r="G274" s="187" t="s">
+      <c r="A274" s="222"/>
+      <c r="B274" s="220"/>
+      <c r="C274" s="349"/>
+      <c r="D274" s="218"/>
+      <c r="E274" s="264"/>
+      <c r="F274" s="344"/>
+      <c r="G274" s="186" t="s">
         <v>602</v>
       </c>
       <c r="H274" s="175" t="s">
@@ -60606,16 +60581,16 @@
       </c>
       <c r="K274" s="12"/>
       <c r="L274" s="12"/>
-      <c r="M274" s="337"/>
+      <c r="M274" s="335"/>
     </row>
     <row r="275" spans="1:13" ht="67.5" customHeight="1">
-      <c r="A275" s="224"/>
-      <c r="B275" s="222"/>
-      <c r="C275" s="351"/>
-      <c r="D275" s="220"/>
-      <c r="E275" s="266"/>
-      <c r="F275" s="337"/>
-      <c r="G275" s="191" t="s">
+      <c r="A275" s="222"/>
+      <c r="B275" s="220"/>
+      <c r="C275" s="349"/>
+      <c r="D275" s="218"/>
+      <c r="E275" s="264"/>
+      <c r="F275" s="335"/>
+      <c r="G275" s="190" t="s">
         <v>604</v>
       </c>
       <c r="H275" s="175" t="s">
@@ -60629,15 +60604,15 @@
       </c>
       <c r="K275" s="12"/>
       <c r="L275" s="12"/>
-      <c r="M275" s="337"/>
+      <c r="M275" s="335"/>
     </row>
     <row r="276" spans="1:13" ht="93.75" customHeight="1">
-      <c r="A276" s="224"/>
-      <c r="B276" s="222"/>
-      <c r="C276" s="351"/>
-      <c r="D276" s="220"/>
-      <c r="E276" s="266"/>
-      <c r="F276" s="346"/>
+      <c r="A276" s="222"/>
+      <c r="B276" s="220"/>
+      <c r="C276" s="349"/>
+      <c r="D276" s="218"/>
+      <c r="E276" s="264"/>
+      <c r="F276" s="344"/>
       <c r="G276" s="13" t="s">
         <v>606</v>
       </c>
@@ -60652,15 +60627,15 @@
       </c>
       <c r="K276" s="12"/>
       <c r="L276" s="12"/>
-      <c r="M276" s="337"/>
+      <c r="M276" s="335"/>
     </row>
     <row r="277" spans="1:13" ht="72" customHeight="1">
-      <c r="A277" s="224"/>
-      <c r="B277" s="222"/>
-      <c r="C277" s="351"/>
-      <c r="D277" s="220"/>
-      <c r="E277" s="266"/>
-      <c r="F277" s="346"/>
+      <c r="A277" s="222"/>
+      <c r="B277" s="220"/>
+      <c r="C277" s="349"/>
+      <c r="D277" s="218"/>
+      <c r="E277" s="264"/>
+      <c r="F277" s="344"/>
       <c r="G277" s="13" t="s">
         <v>607</v>
       </c>
@@ -60675,15 +60650,15 @@
       </c>
       <c r="K277" s="12"/>
       <c r="L277" s="12"/>
-      <c r="M277" s="337"/>
+      <c r="M277" s="335"/>
     </row>
     <row r="278" spans="1:13" ht="74.25" customHeight="1">
-      <c r="A278" s="224"/>
-      <c r="B278" s="222"/>
-      <c r="C278" s="351"/>
-      <c r="D278" s="220"/>
-      <c r="E278" s="266"/>
-      <c r="F278" s="346"/>
+      <c r="A278" s="222"/>
+      <c r="B278" s="220"/>
+      <c r="C278" s="349"/>
+      <c r="D278" s="218"/>
+      <c r="E278" s="264"/>
+      <c r="F278" s="344"/>
       <c r="G278" s="116" t="s">
         <v>609</v>
       </c>
@@ -60698,16 +60673,16 @@
       </c>
       <c r="K278" s="12"/>
       <c r="L278" s="12"/>
-      <c r="M278" s="337"/>
+      <c r="M278" s="335"/>
     </row>
     <row r="279" spans="1:13" ht="57" customHeight="1">
-      <c r="A279" s="224"/>
-      <c r="B279" s="222"/>
-      <c r="C279" s="351"/>
-      <c r="D279" s="220"/>
-      <c r="E279" s="266"/>
-      <c r="F279" s="346"/>
-      <c r="G279" s="187" t="s">
+      <c r="A279" s="222"/>
+      <c r="B279" s="220"/>
+      <c r="C279" s="349"/>
+      <c r="D279" s="218"/>
+      <c r="E279" s="264"/>
+      <c r="F279" s="344"/>
+      <c r="G279" s="186" t="s">
         <v>611</v>
       </c>
       <c r="H279" s="175" t="s">
@@ -60721,16 +60696,16 @@
       </c>
       <c r="K279" s="12"/>
       <c r="L279" s="12"/>
-      <c r="M279" s="337"/>
+      <c r="M279" s="335"/>
     </row>
     <row r="280" spans="1:13" ht="72" customHeight="1">
-      <c r="A280" s="224"/>
-      <c r="B280" s="203"/>
-      <c r="C280" s="352"/>
-      <c r="D280" s="206"/>
-      <c r="E280" s="349"/>
-      <c r="F280" s="216"/>
-      <c r="G280" s="181" t="s">
+      <c r="A280" s="222"/>
+      <c r="B280" s="201"/>
+      <c r="C280" s="350"/>
+      <c r="D280" s="204"/>
+      <c r="E280" s="347"/>
+      <c r="F280" s="214"/>
+      <c r="G280" s="187" t="s">
         <v>613</v>
       </c>
       <c r="H280" s="175" t="s">
@@ -60739,37 +60714,37 @@
       <c r="I280" s="4">
         <v>46295</v>
       </c>
-      <c r="J280" s="192" t="s">
-        <v>615</v>
+      <c r="J280" s="148" t="s">
+        <v>20</v>
       </c>
       <c r="K280" s="12"/>
       <c r="L280" s="12"/>
-      <c r="M280" s="337"/>
+      <c r="M280" s="335"/>
     </row>
     <row r="281" spans="1:13" ht="90" customHeight="1">
-      <c r="A281" s="200">
+      <c r="A281" s="198">
         <v>95</v>
       </c>
-      <c r="B281" s="203">
+      <c r="B281" s="201">
         <v>46247</v>
       </c>
-      <c r="C281" s="206" t="s">
+      <c r="C281" s="204" t="s">
         <v>265</v>
       </c>
-      <c r="D281" s="206" t="s">
+      <c r="D281" s="204" t="s">
+        <v>615</v>
+      </c>
+      <c r="E281" s="340" t="s">
+        <v>27</v>
+      </c>
+      <c r="F281" s="214" t="s">
         <v>616</v>
       </c>
-      <c r="E281" s="342" t="s">
-        <v>27</v>
-      </c>
-      <c r="F281" s="216" t="s">
+      <c r="G281" s="187" t="s">
         <v>617</v>
       </c>
-      <c r="G281" s="188" t="s">
+      <c r="H281" s="168" t="s">
         <v>618</v>
-      </c>
-      <c r="H281" s="168" t="s">
-        <v>619</v>
       </c>
       <c r="I281" s="179">
         <v>46315</v>
@@ -60781,17 +60756,17 @@
       <c r="M281" s="159"/>
     </row>
     <row r="282" spans="1:13" ht="90.75" customHeight="1">
-      <c r="A282" s="201"/>
-      <c r="B282" s="204"/>
-      <c r="C282" s="207"/>
-      <c r="D282" s="207"/>
-      <c r="E282" s="343"/>
-      <c r="F282" s="217"/>
-      <c r="G282" s="188" t="s">
-        <v>620</v>
+      <c r="A282" s="199"/>
+      <c r="B282" s="202"/>
+      <c r="C282" s="205"/>
+      <c r="D282" s="205"/>
+      <c r="E282" s="341"/>
+      <c r="F282" s="215"/>
+      <c r="G282" s="187" t="s">
+        <v>619</v>
       </c>
       <c r="H282" s="168" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="I282" s="171">
         <v>46315</v>
@@ -60804,14 +60779,14 @@
       <c r="M282" s="137"/>
     </row>
     <row r="283" spans="1:13" ht="61.5" customHeight="1">
-      <c r="A283" s="202"/>
-      <c r="B283" s="204"/>
-      <c r="C283" s="207"/>
-      <c r="D283" s="207"/>
-      <c r="E283" s="344"/>
-      <c r="F283" s="218"/>
-      <c r="G283" s="188" t="s">
-        <v>621</v>
+      <c r="A283" s="200"/>
+      <c r="B283" s="202"/>
+      <c r="C283" s="205"/>
+      <c r="D283" s="205"/>
+      <c r="E283" s="342"/>
+      <c r="F283" s="216"/>
+      <c r="G283" s="187" t="s">
+        <v>620</v>
       </c>
       <c r="H283" s="168" t="s">
         <v>88</v>
@@ -60827,29 +60802,29 @@
       <c r="M283" s="137"/>
     </row>
     <row r="284" spans="1:13" ht="96.75" customHeight="1">
-      <c r="A284" s="200">
+      <c r="A284" s="198">
         <v>96</v>
       </c>
-      <c r="B284" s="203">
+      <c r="B284" s="201">
         <v>46265</v>
       </c>
-      <c r="C284" s="206" t="s">
+      <c r="C284" s="204" t="s">
         <v>265</v>
       </c>
-      <c r="D284" s="206" t="s">
+      <c r="D284" s="204" t="s">
+        <v>621</v>
+      </c>
+      <c r="E284" s="198" t="s">
+        <v>182</v>
+      </c>
+      <c r="F284" s="214" t="s">
         <v>622</v>
       </c>
-      <c r="E284" s="200" t="s">
-        <v>182</v>
-      </c>
-      <c r="F284" s="216" t="s">
+      <c r="G284" s="13" t="s">
         <v>623</v>
       </c>
-      <c r="G284" s="13" t="s">
+      <c r="H284" s="134" t="s">
         <v>624</v>
-      </c>
-      <c r="H284" s="134" t="s">
-        <v>625</v>
       </c>
       <c r="I284" s="147">
         <v>46295</v>
@@ -60857,24 +60832,24 @@
       <c r="J284" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="K284" s="193"/>
+      <c r="K284" s="191"/>
       <c r="L284" s="60"/>
-      <c r="M284" s="214" t="s">
-        <v>626</v>
+      <c r="M284" s="212" t="s">
+        <v>625</v>
       </c>
     </row>
     <row r="285" spans="1:13" ht="96.75" customHeight="1">
-      <c r="A285" s="202"/>
-      <c r="B285" s="205"/>
-      <c r="C285" s="208"/>
-      <c r="D285" s="208"/>
-      <c r="E285" s="202"/>
-      <c r="F285" s="218"/>
+      <c r="A285" s="200"/>
+      <c r="B285" s="203"/>
+      <c r="C285" s="206"/>
+      <c r="D285" s="206"/>
+      <c r="E285" s="200"/>
+      <c r="F285" s="216"/>
       <c r="G285" s="14" t="s">
+        <v>626</v>
+      </c>
+      <c r="H285" s="134" t="s">
         <v>627</v>
-      </c>
-      <c r="H285" s="134" t="s">
-        <v>628</v>
       </c>
       <c r="I285" s="171">
         <v>46295</v>
@@ -60884,32 +60859,32 @@
       </c>
       <c r="K285" s="174"/>
       <c r="L285" s="60"/>
-      <c r="M285" s="215"/>
+      <c r="M285" s="213"/>
     </row>
     <row r="286" spans="1:13" ht="54.75" customHeight="1">
-      <c r="A286" s="223">
+      <c r="A286" s="221">
         <v>97</v>
       </c>
-      <c r="B286" s="222">
+      <c r="B286" s="220">
         <v>46275</v>
       </c>
-      <c r="C286" s="221" t="s">
+      <c r="C286" s="219" t="s">
         <v>125</v>
       </c>
-      <c r="D286" s="220" t="s">
+      <c r="D286" s="218" t="s">
+        <v>628</v>
+      </c>
+      <c r="E286" s="210" t="s">
+        <v>521</v>
+      </c>
+      <c r="F286" s="214" t="s">
         <v>629</v>
       </c>
-      <c r="E286" s="212" t="s">
-        <v>521</v>
-      </c>
-      <c r="F286" s="216" t="s">
+      <c r="G286" s="13" t="s">
         <v>630</v>
       </c>
-      <c r="G286" s="13" t="s">
+      <c r="H286" s="93" t="s">
         <v>631</v>
-      </c>
-      <c r="H286" s="93" t="s">
-        <v>632</v>
       </c>
       <c r="I286" s="171">
         <v>46285</v>
@@ -60922,17 +60897,17 @@
       <c r="M286" s="139"/>
     </row>
     <row r="287" spans="1:13" ht="54.75" customHeight="1">
-      <c r="A287" s="224"/>
-      <c r="B287" s="222"/>
-      <c r="C287" s="221"/>
-      <c r="D287" s="220"/>
-      <c r="E287" s="219"/>
-      <c r="F287" s="217"/>
+      <c r="A287" s="222"/>
+      <c r="B287" s="220"/>
+      <c r="C287" s="219"/>
+      <c r="D287" s="218"/>
+      <c r="E287" s="217"/>
+      <c r="F287" s="215"/>
       <c r="G287" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="H287" s="93" t="s">
         <v>633</v>
-      </c>
-      <c r="H287" s="93" t="s">
-        <v>634</v>
       </c>
       <c r="I287" s="171">
         <v>46285</v>
@@ -60945,17 +60920,17 @@
       <c r="M287" s="139"/>
     </row>
     <row r="288" spans="1:13" ht="54.75" customHeight="1">
-      <c r="A288" s="225"/>
-      <c r="B288" s="222"/>
-      <c r="C288" s="221"/>
-      <c r="D288" s="220"/>
-      <c r="E288" s="213"/>
-      <c r="F288" s="218"/>
+      <c r="A288" s="223"/>
+      <c r="B288" s="220"/>
+      <c r="C288" s="219"/>
+      <c r="D288" s="218"/>
+      <c r="E288" s="211"/>
+      <c r="F288" s="216"/>
       <c r="G288" s="13" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H288" s="93" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="I288" s="171">
         <v>46285</v>
@@ -60968,23 +60943,23 @@
       <c r="M288" s="139"/>
     </row>
     <row r="289" spans="1:13" ht="50.25" customHeight="1">
-      <c r="A289" s="200">
+      <c r="A289" s="198">
         <v>98</v>
       </c>
-      <c r="B289" s="203">
+      <c r="B289" s="201">
         <v>46278</v>
       </c>
-      <c r="C289" s="200" t="s">
+      <c r="C289" s="198" t="s">
         <v>125</v>
       </c>
-      <c r="D289" s="200" t="s">
+      <c r="D289" s="198" t="s">
+        <v>635</v>
+      </c>
+      <c r="E289" s="198" t="s">
+        <v>27</v>
+      </c>
+      <c r="F289" s="204" t="s">
         <v>636</v>
-      </c>
-      <c r="E289" s="200" t="s">
-        <v>27</v>
-      </c>
-      <c r="F289" s="206" t="s">
-        <v>637</v>
       </c>
       <c r="G289" s="12"/>
       <c r="H289" s="167"/>
@@ -60995,17 +60970,17 @@
       <c r="M289" s="60"/>
     </row>
     <row r="290" spans="1:13" ht="50.25" customHeight="1">
-      <c r="A290" s="201"/>
-      <c r="B290" s="204"/>
-      <c r="C290" s="201"/>
-      <c r="D290" s="201"/>
-      <c r="E290" s="201"/>
-      <c r="F290" s="207"/>
-      <c r="G290" s="194" t="s">
+      <c r="A290" s="199"/>
+      <c r="B290" s="202"/>
+      <c r="C290" s="199"/>
+      <c r="D290" s="199"/>
+      <c r="E290" s="199"/>
+      <c r="F290" s="205"/>
+      <c r="G290" s="192" t="s">
+        <v>637</v>
+      </c>
+      <c r="H290" s="193" t="s">
         <v>638</v>
-      </c>
-      <c r="H290" s="195" t="s">
-        <v>639</v>
       </c>
       <c r="I290" s="95"/>
       <c r="J290" s="12"/>
@@ -61014,12 +60989,12 @@
       <c r="M290" s="60"/>
     </row>
     <row r="291" spans="1:13" ht="50.25" customHeight="1">
-      <c r="A291" s="202"/>
-      <c r="B291" s="205"/>
-      <c r="C291" s="202"/>
-      <c r="D291" s="202"/>
-      <c r="E291" s="202"/>
-      <c r="F291" s="208"/>
+      <c r="A291" s="200"/>
+      <c r="B291" s="203"/>
+      <c r="C291" s="200"/>
+      <c r="D291" s="200"/>
+      <c r="E291" s="200"/>
+      <c r="F291" s="206"/>
       <c r="G291" s="60"/>
       <c r="H291" s="167"/>
       <c r="I291" s="95"/>
@@ -61029,93 +61004,93 @@
       <c r="M291" s="60"/>
     </row>
     <row r="292" spans="1:13" ht="75" customHeight="1">
-      <c r="A292" s="200">
+      <c r="A292" s="198">
         <v>99</v>
       </c>
-      <c r="B292" s="210">
+      <c r="B292" s="208">
         <v>46280</v>
       </c>
-      <c r="C292" s="212" t="s">
+      <c r="C292" s="210" t="s">
         <v>125</v>
       </c>
-      <c r="D292" s="200" t="s">
+      <c r="D292" s="198" t="s">
+        <v>639</v>
+      </c>
+      <c r="E292" s="198" t="s">
+        <v>182</v>
+      </c>
+      <c r="F292" s="204" t="s">
         <v>640</v>
       </c>
-      <c r="E292" s="200" t="s">
-        <v>182</v>
-      </c>
-      <c r="F292" s="206" t="s">
+      <c r="G292" s="192" t="s">
         <v>641</v>
       </c>
-      <c r="G292" s="194" t="s">
+      <c r="H292" s="194" t="s">
         <v>642</v>
       </c>
-      <c r="H292" s="196" t="s">
-        <v>643</v>
-      </c>
-      <c r="I292" s="197">
+      <c r="I292" s="195">
         <v>46310</v>
       </c>
       <c r="J292" s="177" t="s">
         <v>242</v>
       </c>
       <c r="K292" s="60" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="L292" s="60"/>
       <c r="M292" s="60"/>
     </row>
     <row r="293" spans="1:13" ht="75" customHeight="1">
-      <c r="A293" s="202"/>
-      <c r="B293" s="211"/>
-      <c r="C293" s="213"/>
-      <c r="D293" s="202"/>
-      <c r="E293" s="202"/>
-      <c r="F293" s="208"/>
-      <c r="G293" s="194" t="s">
-        <v>645</v>
+      <c r="A293" s="200"/>
+      <c r="B293" s="209"/>
+      <c r="C293" s="211"/>
+      <c r="D293" s="200"/>
+      <c r="E293" s="200"/>
+      <c r="F293" s="206"/>
+      <c r="G293" s="192" t="s">
+        <v>644</v>
       </c>
       <c r="H293" s="93" t="s">
         <v>257</v>
       </c>
-      <c r="I293" s="197">
+      <c r="I293" s="195">
         <v>46310</v>
       </c>
       <c r="J293" s="60" t="s">
         <v>242</v>
       </c>
       <c r="K293" s="60" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="L293" s="60"/>
       <c r="M293" s="60"/>
     </row>
     <row r="294" spans="1:13" ht="73.5" customHeight="1">
-      <c r="A294" s="200">
+      <c r="A294" s="198">
         <v>100</v>
       </c>
-      <c r="B294" s="203">
+      <c r="B294" s="201">
         <v>46289</v>
       </c>
-      <c r="C294" s="200" t="s">
+      <c r="C294" s="198" t="s">
         <v>265</v>
       </c>
-      <c r="D294" s="206" t="s">
+      <c r="D294" s="204" t="s">
+        <v>646</v>
+      </c>
+      <c r="E294" s="204" t="s">
+        <v>27</v>
+      </c>
+      <c r="F294" s="204" t="s">
         <v>647</v>
       </c>
-      <c r="E294" s="206" t="s">
-        <v>27</v>
-      </c>
-      <c r="F294" s="206" t="s">
+      <c r="G294" s="139" t="s">
         <v>648</v>
       </c>
-      <c r="G294" s="139" t="s">
+      <c r="H294" s="192" t="s">
         <v>649</v>
       </c>
-      <c r="H294" s="194" t="s">
-        <v>650</v>
-      </c>
-      <c r="I294" s="197">
+      <c r="I294" s="195">
         <v>46325</v>
       </c>
       <c r="J294" s="60" t="s">
@@ -61126,19 +61101,19 @@
       <c r="M294" s="60"/>
     </row>
     <row r="295" spans="1:13" ht="73.5" customHeight="1">
-      <c r="A295" s="201"/>
-      <c r="B295" s="204"/>
-      <c r="C295" s="201"/>
-      <c r="D295" s="207"/>
-      <c r="E295" s="207"/>
-      <c r="F295" s="207"/>
+      <c r="A295" s="199"/>
+      <c r="B295" s="202"/>
+      <c r="C295" s="199"/>
+      <c r="D295" s="205"/>
+      <c r="E295" s="205"/>
+      <c r="F295" s="205"/>
       <c r="G295" s="139" t="s">
-        <v>651</v>
-      </c>
-      <c r="H295" s="194" t="s">
         <v>650</v>
       </c>
-      <c r="I295" s="197">
+      <c r="H295" s="192" t="s">
+        <v>649</v>
+      </c>
+      <c r="I295" s="195">
         <v>46325</v>
       </c>
       <c r="J295" s="60" t="s">
@@ -61149,31 +61124,31 @@
       <c r="M295" s="60"/>
     </row>
     <row r="296" spans="1:13" ht="43.5" customHeight="1">
-      <c r="A296" s="200">
+      <c r="A296" s="198">
         <v>101</v>
       </c>
-      <c r="B296" s="203">
+      <c r="B296" s="201">
         <v>46299</v>
       </c>
-      <c r="C296" s="200" t="s">
+      <c r="C296" s="198" t="s">
         <v>125</v>
       </c>
-      <c r="D296" s="206" t="s">
+      <c r="D296" s="204" t="s">
+        <v>651</v>
+      </c>
+      <c r="E296" s="204" t="s">
+        <v>521</v>
+      </c>
+      <c r="F296" s="204" t="s">
         <v>652</v>
       </c>
-      <c r="E296" s="206" t="s">
-        <v>521</v>
-      </c>
-      <c r="F296" s="206" t="s">
+      <c r="G296" s="196" t="s">
         <v>653</v>
       </c>
-      <c r="G296" s="198" t="s">
-        <v>654</v>
-      </c>
-      <c r="H296" s="194" t="s">
-        <v>650</v>
-      </c>
-      <c r="I296" s="197">
+      <c r="H296" s="192" t="s">
+        <v>649</v>
+      </c>
+      <c r="I296" s="195">
         <v>46325</v>
       </c>
       <c r="J296" s="60" t="s">
@@ -61184,19 +61159,19 @@
       <c r="M296" s="12"/>
     </row>
     <row r="297" spans="1:13" ht="36.75" customHeight="1">
-      <c r="A297" s="201"/>
-      <c r="B297" s="204"/>
-      <c r="C297" s="201"/>
-      <c r="D297" s="207"/>
-      <c r="E297" s="207"/>
-      <c r="F297" s="207"/>
+      <c r="A297" s="199"/>
+      <c r="B297" s="202"/>
+      <c r="C297" s="199"/>
+      <c r="D297" s="205"/>
+      <c r="E297" s="205"/>
+      <c r="F297" s="205"/>
       <c r="G297" s="114" t="s">
-        <v>655</v>
-      </c>
-      <c r="H297" s="194" t="s">
-        <v>650</v>
-      </c>
-      <c r="I297" s="197">
+        <v>654</v>
+      </c>
+      <c r="H297" s="192" t="s">
+        <v>649</v>
+      </c>
+      <c r="I297" s="195">
         <v>46325</v>
       </c>
       <c r="J297" s="60" t="s">
@@ -61204,19 +61179,19 @@
       </c>
     </row>
     <row r="298" spans="1:13" ht="39.75" customHeight="1">
-      <c r="A298" s="202"/>
-      <c r="B298" s="205"/>
-      <c r="C298" s="202"/>
-      <c r="D298" s="208"/>
-      <c r="E298" s="208"/>
-      <c r="F298" s="209"/>
+      <c r="A298" s="200"/>
+      <c r="B298" s="203"/>
+      <c r="C298" s="200"/>
+      <c r="D298" s="206"/>
+      <c r="E298" s="206"/>
+      <c r="F298" s="207"/>
       <c r="G298" s="14" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H298" s="100" t="s">
-        <v>650</v>
-      </c>
-      <c r="I298" s="199">
+        <v>649</v>
+      </c>
+      <c r="I298" s="197">
         <v>46325</v>
       </c>
       <c r="J298" s="12" t="s">
@@ -61224,7 +61199,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:COT296" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:COT298" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="671">
     <mergeCell ref="M273:M280"/>
     <mergeCell ref="A273:A280"/>
@@ -61898,7 +61873,7 @@
     <mergeCell ref="E294:E295"/>
     <mergeCell ref="F294:F295"/>
   </mergeCells>
-  <conditionalFormatting sqref="J2:J66 J155:J170 I142:I145 J222 J227 J142:J150 J175:J214 J232:J271 J273:J1048576 J69:J138">
+  <conditionalFormatting sqref="J2:J66 J155:J170 I142:I145 J222 J227 J142:J150 J175:J214 J232:J271 J69:J138 J273:J1048576">
     <cfRule type="cellIs" dxfId="32" priority="36" operator="equal">
       <formula>"ABIERTO"</formula>
     </cfRule>
@@ -61906,7 +61881,7 @@
       <formula>NOT(ISERROR(SEARCH("ABIERTO",I2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J66 J222 J227 J142:J170 J175:J214 J232:J271 J273:J1048576 J69:J138">
+  <conditionalFormatting sqref="J2:J66 J222 J227 J142:J170 J175:J214 J232:J271 J69:J138 J273:J1048576">
     <cfRule type="containsText" dxfId="30" priority="35" operator="containsText" text="ABIERTO">
       <formula>NOT(ISERROR(SEARCH("ABIERTO",J2)))</formula>
     </cfRule>
@@ -62065,128 +62040,128 @@
   </cols>
   <sheetData>
     <row r="5" spans="2:7" hidden="1">
-      <c r="B5" s="200">
+      <c r="B5" s="198">
         <v>84</v>
       </c>
-      <c r="C5" s="203">
+      <c r="C5" s="201">
         <v>46166</v>
       </c>
-      <c r="D5" s="206" t="s">
+      <c r="D5" s="204" t="s">
         <v>501</v>
       </c>
-      <c r="E5" s="206" t="s">
+      <c r="E5" s="204" t="s">
         <v>537</v>
       </c>
-      <c r="F5" s="200" t="s">
+      <c r="F5" s="198" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="214" t="s">
+      <c r="G5" s="212" t="s">
         <v>538</v>
       </c>
     </row>
     <row r="6" spans="2:7" ht="79.5" hidden="1" customHeight="1">
-      <c r="B6" s="202"/>
-      <c r="C6" s="205"/>
-      <c r="D6" s="208"/>
-      <c r="E6" s="208"/>
-      <c r="F6" s="202"/>
-      <c r="G6" s="215"/>
+      <c r="B6" s="200"/>
+      <c r="C6" s="203"/>
+      <c r="D6" s="206"/>
+      <c r="E6" s="206"/>
+      <c r="F6" s="200"/>
+      <c r="G6" s="213"/>
     </row>
     <row r="7" spans="2:7" hidden="1">
-      <c r="B7" s="200">
+      <c r="B7" s="198">
         <v>85</v>
       </c>
-      <c r="C7" s="340">
+      <c r="C7" s="338">
         <v>46166</v>
       </c>
-      <c r="D7" s="206" t="s">
+      <c r="D7" s="204" t="s">
         <v>501</v>
       </c>
-      <c r="E7" s="206" t="s">
+      <c r="E7" s="204" t="s">
         <v>544</v>
       </c>
-      <c r="F7" s="200" t="s">
+      <c r="F7" s="198" t="s">
         <v>521</v>
       </c>
-      <c r="G7" s="214" t="s">
+      <c r="G7" s="212" t="s">
         <v>545</v>
       </c>
     </row>
     <row r="8" spans="2:7" hidden="1">
-      <c r="B8" s="201"/>
-      <c r="C8" s="341"/>
-      <c r="D8" s="207"/>
-      <c r="E8" s="207"/>
-      <c r="F8" s="201"/>
-      <c r="G8" s="338"/>
+      <c r="B8" s="199"/>
+      <c r="C8" s="339"/>
+      <c r="D8" s="205"/>
+      <c r="E8" s="205"/>
+      <c r="F8" s="199"/>
+      <c r="G8" s="336"/>
     </row>
     <row r="9" spans="2:7" hidden="1">
-      <c r="B9" s="201"/>
-      <c r="C9" s="341"/>
-      <c r="D9" s="207"/>
-      <c r="E9" s="207"/>
-      <c r="F9" s="201"/>
-      <c r="G9" s="338"/>
+      <c r="B9" s="199"/>
+      <c r="C9" s="339"/>
+      <c r="D9" s="205"/>
+      <c r="E9" s="205"/>
+      <c r="F9" s="199"/>
+      <c r="G9" s="336"/>
     </row>
     <row r="10" spans="2:7" hidden="1">
-      <c r="B10" s="201"/>
-      <c r="C10" s="341"/>
-      <c r="D10" s="207"/>
-      <c r="E10" s="207"/>
-      <c r="F10" s="201"/>
-      <c r="G10" s="338"/>
+      <c r="B10" s="199"/>
+      <c r="C10" s="339"/>
+      <c r="D10" s="205"/>
+      <c r="E10" s="205"/>
+      <c r="F10" s="199"/>
+      <c r="G10" s="336"/>
     </row>
     <row r="11" spans="2:7" hidden="1">
-      <c r="B11" s="202"/>
-      <c r="C11" s="366"/>
-      <c r="D11" s="208"/>
-      <c r="E11" s="208"/>
-      <c r="F11" s="202"/>
-      <c r="G11" s="215"/>
+      <c r="B11" s="200"/>
+      <c r="C11" s="364"/>
+      <c r="D11" s="206"/>
+      <c r="E11" s="206"/>
+      <c r="F11" s="200"/>
+      <c r="G11" s="213"/>
     </row>
     <row r="12" spans="2:7" hidden="1">
-      <c r="B12" s="200">
+      <c r="B12" s="198">
         <v>86</v>
       </c>
-      <c r="C12" s="203">
+      <c r="C12" s="201">
         <v>46167</v>
       </c>
-      <c r="D12" s="206" t="s">
+      <c r="D12" s="204" t="s">
         <v>501</v>
       </c>
-      <c r="E12" s="206" t="s">
+      <c r="E12" s="204" t="s">
         <v>554</v>
       </c>
-      <c r="F12" s="200" t="s">
+      <c r="F12" s="198" t="s">
         <v>521</v>
       </c>
-      <c r="G12" s="214" t="s">
+      <c r="G12" s="212" t="s">
         <v>555</v>
       </c>
     </row>
     <row r="13" spans="2:7" hidden="1">
-      <c r="B13" s="201"/>
-      <c r="C13" s="204"/>
-      <c r="D13" s="207"/>
-      <c r="E13" s="207"/>
-      <c r="F13" s="201"/>
-      <c r="G13" s="338"/>
+      <c r="B13" s="199"/>
+      <c r="C13" s="202"/>
+      <c r="D13" s="205"/>
+      <c r="E13" s="205"/>
+      <c r="F13" s="199"/>
+      <c r="G13" s="336"/>
     </row>
     <row r="14" spans="2:7" hidden="1">
-      <c r="B14" s="201"/>
-      <c r="C14" s="204"/>
-      <c r="D14" s="207"/>
-      <c r="E14" s="207"/>
-      <c r="F14" s="201"/>
-      <c r="G14" s="338"/>
+      <c r="B14" s="199"/>
+      <c r="C14" s="202"/>
+      <c r="D14" s="205"/>
+      <c r="E14" s="205"/>
+      <c r="F14" s="199"/>
+      <c r="G14" s="336"/>
     </row>
     <row r="15" spans="2:7" hidden="1">
-      <c r="B15" s="201"/>
-      <c r="C15" s="204"/>
-      <c r="D15" s="207"/>
-      <c r="E15" s="207"/>
-      <c r="F15" s="201"/>
-      <c r="G15" s="338"/>
+      <c r="B15" s="199"/>
+      <c r="C15" s="202"/>
+      <c r="D15" s="205"/>
+      <c r="E15" s="205"/>
+      <c r="F15" s="199"/>
+      <c r="G15" s="336"/>
     </row>
     <row r="16" spans="2:7" ht="110.25" hidden="1" customHeight="1">
       <c r="B16" s="56">
@@ -62209,13 +62184,13 @@
       </c>
     </row>
     <row r="17" spans="2:8" ht="76.5" customHeight="1">
-      <c r="B17" s="360" t="s">
-        <v>657</v>
-      </c>
-      <c r="C17" s="361"/>
-      <c r="D17" s="361"/>
-      <c r="E17" s="361"/>
-      <c r="F17" s="362"/>
+      <c r="B17" s="358" t="s">
+        <v>656</v>
+      </c>
+      <c r="C17" s="359"/>
+      <c r="D17" s="359"/>
+      <c r="E17" s="359"/>
+      <c r="F17" s="360"/>
     </row>
     <row r="19" spans="2:8" ht="30.75">
       <c r="B19" s="5" t="s">
@@ -62493,13 +62468,13 @@
       </c>
     </row>
     <row r="36" spans="2:8">
-      <c r="B36" s="363" t="s">
-        <v>658</v>
-      </c>
-      <c r="C36" s="364"/>
-      <c r="D36" s="364"/>
-      <c r="E36" s="364"/>
-      <c r="F36" s="365"/>
+      <c r="B36" s="361" t="s">
+        <v>657</v>
+      </c>
+      <c r="C36" s="362"/>
+      <c r="D36" s="362"/>
+      <c r="E36" s="362"/>
+      <c r="F36" s="363"/>
     </row>
     <row r="37" spans="2:8" ht="30.75">
       <c r="B37" s="5" t="s">
@@ -62679,7 +62654,7 @@
         <v>45856</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>172</v>
@@ -62696,7 +62671,7 @@
         <v>45895</v>
       </c>
       <c r="C48" s="21" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D48" s="21" t="s">
         <v>213</v>
@@ -62713,7 +62688,7 @@
         <v>45911</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>247</v>
@@ -62764,7 +62739,7 @@
         <v>45952</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>276</v>
